--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3961.5</v>
+        <v>3943.2</v>
       </c>
       <c r="C2" t="n">
-        <v>48.89</v>
+        <v>48.72</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>2811</v>
       </c>
       <c r="C3" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="C4" t="n">
-        <v>16.41</v>
+        <v>16.54</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="E2" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0189</v>
+        <v>1.0187</v>
       </c>
     </row>
     <row r="3">
@@ -1229,7 +1229,7 @@
         <v>2361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8047</v>
+        <v>0.8041</v>
       </c>
     </row>
     <row r="4">
@@ -1244,16 +1244,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="D4" t="n">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="E4" t="n">
-        <v>447.88</v>
+        <v>441.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4608</v>
+        <v>0.4619</v>
       </c>
     </row>
     <row r="5">
@@ -1271,13 +1271,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="E5" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9745</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1301,7 +1301,7 @@
         <v>2361</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9019</v>
+        <v>0.9021</v>
       </c>
     </row>
     <row r="7">
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="D7" t="n">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="E7" t="n">
-        <v>447.88</v>
+        <v>441.3</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4608</v>
+        <v>0.4619</v>
       </c>
     </row>
     <row r="8">
@@ -1343,13 +1343,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="E8" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6189</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="9">
@@ -1373,7 +1373,7 @@
         <v>2361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.727</v>
+        <v>0.7282</v>
       </c>
     </row>
     <row r="10">
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="D10" t="n">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="E10" t="n">
-        <v>447.88</v>
+        <v>441.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8608</v>
+        <v>0.8619</v>
       </c>
     </row>
   </sheetData>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13.3</v>
+        <v>13.39</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -2237,19 +2237,19 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>13.3</v>
+        <v>13.39</v>
       </c>
       <c r="L3" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="M3" t="n">
         <v>553</v>
       </c>
       <c r="N3" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="O3" t="n">
-        <v>140.51</v>
+        <v>142.13</v>
       </c>
     </row>
     <row r="4">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>610.84</v>
+        <v>610.37</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>213.31</v>
+        <v>213.73</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>430.94</v>
+        <v>432.91</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>264.09</v>
+        <v>262.85</v>
       </c>
       <c r="L7" t="n">
-        <v>3961.35</v>
+        <v>3942.75</v>
       </c>
       <c r="M7" t="n">
         <v>1896</v>
       </c>
       <c r="N7" t="n">
-        <v>2065.35</v>
+        <v>2046.75</v>
       </c>
       <c r="O7" t="n">
-        <v>108.93</v>
+        <v>107.95</v>
       </c>
     </row>
     <row r="8">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>383.23</v>
+        <v>382.75</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>137.21</v>
+        <v>137.26</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2685,16 +2685,16 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="D2" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="E2" t="n">
-        <v>7.77</v>
+        <v>7.86</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9745</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -2730,13 +2730,13 @@
         <v>39.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9019</v>
+        <v>0.9021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7569</v>
+        <v>0.7551</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5628</v>
+        <v>0.5653</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="C4" t="n">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="D4" t="n">
-        <v>447.86</v>
+        <v>441.25</v>
       </c>
       <c r="E4" t="n">
-        <v>137.69</v>
+        <v>136.45</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4608</v>
+        <v>0.4619</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107.04</v>
+        <v>107.47</v>
       </c>
       <c r="C2" t="n">
         <v>102.39</v>
@@ -2905,7 +2905,7 @@
         <v>100.14</v>
       </c>
       <c r="E2" t="n">
-        <v>35.85</v>
+        <v>36.23</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -2914,13 +2914,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8208</v>
+        <v>0.8189</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6415</v>
+        <v>0.6377</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>213.35</v>
+        <v>213.7</v>
       </c>
       <c r="C3" t="n">
-        <v>197.47</v>
+        <v>197.48</v>
       </c>
       <c r="D3" t="n">
         <v>187.18</v>
       </c>
       <c r="E3" t="n">
-        <v>62.51</v>
+        <v>62.84</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -2978,13 +2978,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6874</v>
+        <v>0.6858</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3749</v>
+        <v>0.3716</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8102</v>
+        <v>0.8097</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3601</v>
+        <v>0.3597</v>
       </c>
     </row>
     <row r="4">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.98</v>
+        <v>12.18</v>
       </c>
       <c r="C4" t="n">
         <v>11.44</v>
@@ -3033,7 +3033,7 @@
         <v>5.86</v>
       </c>
       <c r="E4" t="n">
-        <v>35.66</v>
+        <v>36.11</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3042,13 +3042,13 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8217</v>
+        <v>0.8194</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6434</v>
+        <v>0.6389</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7967</v>
+        <v>0.7957</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16.41</v>
+        <v>16.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8359</v>
+        <v>0.8345</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>0.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4321</v>
+        <v>0.4315</v>
       </c>
     </row>
     <row r="5">
@@ -3088,16 +3088,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>496.51</v>
+        <v>496.02</v>
       </c>
       <c r="C5" t="n">
-        <v>309.25</v>
+        <v>309.24</v>
       </c>
       <c r="D5" t="n">
-        <v>232.5</v>
+        <v>232.49</v>
       </c>
       <c r="E5" t="n">
-        <v>76.65000000000001</v>
+        <v>76.61</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3106,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6167</v>
+        <v>0.617</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2335</v>
+        <v>0.2339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7879</v>
+        <v>0.788</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3523</v>
+        <v>0.3525</v>
       </c>
     </row>
     <row r="6">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.3</v>
+        <v>13.39</v>
       </c>
       <c r="C6" t="n">
         <v>9.109999999999999</v>
@@ -3161,7 +3161,7 @@
         <v>6.92</v>
       </c>
       <c r="E6" t="n">
-        <v>58.98</v>
+        <v>59.22</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -3170,13 +3170,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.7039</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4102</v>
+        <v>0.4078</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7556</v>
+        <v>0.7549</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16.41</v>
+        <v>16.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8359</v>
+        <v>0.8345</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>0.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0.391</v>
+        <v>0.3906</v>
       </c>
     </row>
     <row r="7">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220.35</v>
+        <v>220.51</v>
       </c>
       <c r="C7" t="n">
         <v>208.21</v>
@@ -3225,7 +3225,7 @@
         <v>204.15</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>40.08</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -3234,13 +3234,13 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.7996</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>0.5992</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6993</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4086</v>
+        <v>0.4087</v>
       </c>
     </row>
     <row r="8">
@@ -3280,16 +3280,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>189.06</v>
+        <v>188.37</v>
       </c>
       <c r="C8" t="n">
-        <v>152.78</v>
+        <v>152.77</v>
       </c>
       <c r="D8" t="n">
-        <v>127</v>
+        <v>126.99</v>
       </c>
       <c r="E8" t="n">
-        <v>43.48</v>
+        <v>42.69</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -3298,13 +3298,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7826</v>
+        <v>0.7866</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5652</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6909</v>
+        <v>0.6921</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>0.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3878</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="9">
@@ -3344,16 +3344,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.47</v>
+        <v>80.38</v>
       </c>
       <c r="C9" t="n">
-        <v>77.51000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="D9" t="n">
         <v>72.2</v>
       </c>
       <c r="E9" t="n">
-        <v>63.96</v>
+        <v>63.16</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -3362,13 +3362,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6802</v>
+        <v>0.6842</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3604</v>
+        <v>0.3684</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6887</v>
+        <v>0.6898</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.578</v>
+        <v>0.5779</v>
       </c>
     </row>
     <row r="10">
@@ -3408,16 +3408,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159.49</v>
+        <v>158.95</v>
       </c>
       <c r="C10" t="n">
-        <v>147.58</v>
+        <v>147.57</v>
       </c>
       <c r="D10" t="n">
         <v>139.9</v>
       </c>
       <c r="E10" t="n">
-        <v>42.87</v>
+        <v>42.45</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -3426,13 +3426,13 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7856</v>
+        <v>0.7877</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5713</v>
+        <v>0.5755</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6885</v>
+        <v>0.6891</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3658</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="11">
@@ -3472,16 +3472,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>327.99</v>
+        <v>327.11</v>
       </c>
       <c r="C11" t="n">
-        <v>304.41</v>
+        <v>304.39</v>
       </c>
       <c r="D11" t="n">
         <v>208.61</v>
       </c>
       <c r="E11" t="n">
-        <v>45.59</v>
+        <v>45.28</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -3490,13 +3490,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.772</v>
+        <v>0.7736</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5441</v>
+        <v>0.5472</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6884</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3893</v>
+        <v>0.3894</v>
       </c>
     </row>
     <row r="12">
@@ -3536,16 +3536,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>181.87</v>
+        <v>181.1</v>
       </c>
       <c r="C12" t="n">
-        <v>143.37</v>
+        <v>143.36</v>
       </c>
       <c r="D12" t="n">
         <v>63.76</v>
       </c>
       <c r="E12" t="n">
-        <v>50.36</v>
+        <v>50.15</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7482</v>
+        <v>0.7492</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4964</v>
+        <v>0.4985</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6867</v>
+        <v>0.6869</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -3600,16 +3600,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>383.22</v>
+        <v>382.81</v>
       </c>
       <c r="C13" t="n">
-        <v>340.48</v>
+        <v>340.47</v>
       </c>
       <c r="D13" t="n">
-        <v>296.73</v>
+        <v>296.72</v>
       </c>
       <c r="E13" t="n">
-        <v>49.19</v>
+        <v>48.87</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -3618,13 +3618,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.754</v>
+        <v>0.7556</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5081</v>
+        <v>0.5113</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6833</v>
+        <v>0.6837</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3942</v>
+        <v>0.3944</v>
       </c>
     </row>
     <row r="14">
@@ -3664,16 +3664,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>408.13</v>
+        <v>405.67</v>
       </c>
       <c r="C14" t="n">
-        <v>390.35</v>
+        <v>390.3</v>
       </c>
       <c r="D14" t="n">
-        <v>362.36</v>
+        <v>362.34</v>
       </c>
       <c r="E14" t="n">
-        <v>49.47</v>
+        <v>48.63</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -3682,13 +3682,13 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7526</v>
+        <v>0.7568</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5053</v>
+        <v>0.5137</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6813</v>
+        <v>0.6825</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3834</v>
+        <v>0.3837</v>
       </c>
     </row>
     <row r="15">
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.09</v>
+        <v>262.89</v>
       </c>
       <c r="C15" t="n">
-        <v>243.05</v>
+        <v>243.03</v>
       </c>
       <c r="D15" t="n">
-        <v>230.76</v>
+        <v>230.75</v>
       </c>
       <c r="E15" t="n">
-        <v>39.17</v>
+        <v>38.12</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -3746,13 +3746,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8042</v>
+        <v>0.8094</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6083</v>
+        <v>0.6188</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6774</v>
+        <v>0.6793</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>48.89</v>
+        <v>48.72</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5111</v>
+        <v>0.5128</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>0.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3968</v>
+        <v>0.3973</v>
       </c>
     </row>
     <row r="16">
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>422.57</v>
+        <v>423.47</v>
       </c>
       <c r="C16" t="n">
-        <v>378.98</v>
+        <v>379</v>
       </c>
       <c r="D16" t="n">
         <v>349.5</v>
       </c>
       <c r="E16" t="n">
-        <v>47.93</v>
+        <v>48.33</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -3810,13 +3810,13 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7604</v>
+        <v>0.7584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5167</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6764</v>
+        <v>0.6757</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3353</v>
+        <v>0.3354</v>
       </c>
     </row>
     <row r="17">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.45</v>
+        <v>54.4</v>
       </c>
       <c r="C17" t="n">
         <v>46.05</v>
@@ -3865,7 +3865,7 @@
         <v>32.66</v>
       </c>
       <c r="E17" t="n">
-        <v>56.74</v>
+        <v>56.66</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -3874,13 +3874,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7163</v>
+        <v>0.7167</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4326</v>
+        <v>0.4334</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6712</v>
+        <v>0.6713</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3910,26 +3910,26 @@
         <v>0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0.389</v>
+        <v>0.3891</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>383.74</v>
+        <v>1596.43</v>
       </c>
       <c r="C18" t="n">
-        <v>343.73</v>
+        <v>1023.76</v>
       </c>
       <c r="D18" t="n">
-        <v>229.64</v>
+        <v>464.32</v>
       </c>
       <c r="E18" t="n">
-        <v>57.26</v>
+        <v>59.84</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -3938,13 +3938,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7137</v>
+        <v>0.7008</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4274</v>
+        <v>0.4016</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6681</v>
+        <v>0.6683</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3974,26 +3974,26 @@
         <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3738</v>
+        <v>0.4013</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1600.96</v>
+        <v>383.91</v>
       </c>
       <c r="C19" t="n">
-        <v>1023.85</v>
+        <v>343.73</v>
       </c>
       <c r="D19" t="n">
-        <v>464.34</v>
+        <v>229.64</v>
       </c>
       <c r="E19" t="n">
-        <v>60.03</v>
+        <v>57.3</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -4002,10 +4002,10 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6998</v>
+        <v>0.7135</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3997</v>
+        <v>0.427</v>
       </c>
       <c r="J19" t="n">
         <v>0.6681</v>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4011</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="20">
@@ -4048,16 +4048,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>216.7</v>
+        <v>216.42</v>
       </c>
       <c r="C20" t="n">
-        <v>151.82</v>
+        <v>151.81</v>
       </c>
       <c r="D20" t="n">
         <v>143.63</v>
       </c>
       <c r="E20" t="n">
-        <v>57.49</v>
+        <v>57.38</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -4066,13 +4066,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7126</v>
+        <v>0.7131</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4251</v>
+        <v>0.4262</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6677</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3731</v>
+        <v>0.3728</v>
       </c>
     </row>
     <row r="21">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>121.6</v>
+        <v>121.09</v>
       </c>
       <c r="C21" t="n">
-        <v>77.95999999999999</v>
+        <v>77.95</v>
       </c>
       <c r="D21" t="n">
         <v>47.68</v>
       </c>
       <c r="E21" t="n">
-        <v>60.56</v>
+        <v>60.24</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -4130,13 +4130,13 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6972</v>
+        <v>0.6988</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3944</v>
+        <v>0.3976</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6655</v>
+        <v>0.6659</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>0.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3889</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="22">
@@ -4176,16 +4176,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>454.36</v>
+        <v>454.13</v>
       </c>
       <c r="C22" t="n">
-        <v>401.7</v>
+        <v>401.69</v>
       </c>
       <c r="D22" t="n">
         <v>381.05</v>
       </c>
       <c r="E22" t="n">
-        <v>58.96</v>
+        <v>58.87</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -4194,10 +4194,10 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7052</v>
+        <v>0.7056</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4104</v>
+        <v>0.4113</v>
       </c>
       <c r="J22" t="n">
         <v>0.664</v>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>0.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3629</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="23">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>411.65</v>
+        <v>411.93</v>
       </c>
       <c r="C23" t="n">
         <v>374.56</v>
@@ -4249,7 +4249,7 @@
         <v>317.63</v>
       </c>
       <c r="E23" t="n">
-        <v>57.36</v>
+        <v>57.46</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -4258,13 +4258,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.7127</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4264</v>
+        <v>0.4254</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6633</v>
+        <v>0.6631</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>109.73</v>
+        <v>110.76</v>
       </c>
       <c r="C24" t="n">
-        <v>72.59999999999999</v>
+        <v>72.62</v>
       </c>
       <c r="D24" t="n">
-        <v>38.12</v>
+        <v>38.13</v>
       </c>
       <c r="E24" t="n">
-        <v>59.7</v>
+        <v>60.13</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -4322,13 +4322,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7015</v>
+        <v>0.6993</v>
       </c>
       <c r="I24" t="n">
-        <v>0.403</v>
+        <v>0.3987</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6601</v>
+        <v>0.6595</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4358,26 +4358,26 @@
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3449</v>
+        <v>0.3453</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1617.68</v>
+        <v>289.53</v>
       </c>
       <c r="C25" t="n">
-        <v>1439.7</v>
+        <v>267.45</v>
       </c>
       <c r="D25" t="n">
-        <v>1178.48</v>
+        <v>252.13</v>
       </c>
       <c r="E25" t="n">
-        <v>63.37</v>
+        <v>57.84</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -4386,13 +4386,13 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6832</v>
+        <v>0.7108</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3663</v>
+        <v>0.4216</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6559</v>
+        <v>0.6562</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4422,26 +4422,26 @@
         <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3529</v>
+        <v>0.3005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>289.97</v>
+        <v>1624.73</v>
       </c>
       <c r="C26" t="n">
-        <v>267.46</v>
+        <v>1439.84</v>
       </c>
       <c r="D26" t="n">
-        <v>252.13</v>
+        <v>1178.52</v>
       </c>
       <c r="E26" t="n">
-        <v>58.25</v>
+        <v>64.06</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -4450,13 +4450,13 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7088</v>
+        <v>0.6797</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4175</v>
+        <v>0.3594</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6556</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4486,26 +4486,26 @@
         <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3003</v>
+        <v>0.3526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>205.28</v>
+        <v>126.51</v>
       </c>
       <c r="C27" t="n">
-        <v>139.83</v>
+        <v>85.2</v>
       </c>
       <c r="D27" t="n">
-        <v>96.48</v>
+        <v>62.46</v>
       </c>
       <c r="E27" t="n">
-        <v>68.12</v>
+        <v>67.98</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -4514,13 +4514,13 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6594</v>
+        <v>0.6601</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3188</v>
+        <v>0.3202</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6538</v>
+        <v>0.654</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4550,26 +4550,26 @@
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3867</v>
+        <v>0.3868</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>126.74</v>
+        <v>205.86</v>
       </c>
       <c r="C28" t="n">
-        <v>85.20999999999999</v>
+        <v>139.84</v>
       </c>
       <c r="D28" t="n">
-        <v>62.46</v>
+        <v>96.48</v>
       </c>
       <c r="E28" t="n">
-        <v>68.08</v>
+        <v>68.3</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -4578,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6596</v>
+        <v>0.6585</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3192</v>
+        <v>0.317</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6538</v>
+        <v>0.6535</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>0.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3864</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="29">
@@ -4624,16 +4624,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1985.43</v>
+        <v>1995.4</v>
       </c>
       <c r="C29" t="n">
-        <v>1701.72</v>
+        <v>1701.92</v>
       </c>
       <c r="D29" t="n">
-        <v>1330.41</v>
+        <v>1330.46</v>
       </c>
       <c r="E29" t="n">
-        <v>66.41</v>
+        <v>66.84</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -4642,13 +4642,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.668</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3359</v>
+        <v>0.3316</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6518</v>
+        <v>0.6511</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3562</v>
+        <v>0.3565</v>
       </c>
     </row>
     <row r="30">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37.24</v>
+        <v>37.28</v>
       </c>
       <c r="C30" t="n">
         <v>31.47</v>
@@ -4697,7 +4697,7 @@
         <v>23.05</v>
       </c>
       <c r="E30" t="n">
-        <v>67.98999999999999</v>
+        <v>68.11</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -4706,13 +4706,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.66</v>
+        <v>0.6594</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3201</v>
+        <v>0.3189</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6504</v>
+        <v>0.6501</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4742,26 +4742,26 @@
         <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3626</v>
+        <v>0.3624</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LPTH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>886.41</v>
+        <v>16.83</v>
       </c>
       <c r="C31" t="n">
-        <v>528.1799999999999</v>
+        <v>12.65</v>
       </c>
       <c r="D31" t="n">
-        <v>326.28</v>
+        <v>9.59</v>
       </c>
       <c r="E31" t="n">
-        <v>70.18000000000001</v>
+        <v>71.88</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -4770,13 +4770,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6491</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2982</v>
+        <v>0.2812</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6493</v>
+        <v>0.6499</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4806,26 +4806,26 @@
         <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3771</v>
+        <v>0.3985</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.91</v>
+        <v>884.77</v>
       </c>
       <c r="C32" t="n">
-        <v>12.66</v>
+        <v>528.15</v>
       </c>
       <c r="D32" t="n">
-        <v>9.59</v>
+        <v>326.27</v>
       </c>
       <c r="E32" t="n">
-        <v>72.41</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -4834,13 +4834,13 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.638</v>
+        <v>0.6495</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2759</v>
+        <v>0.299</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6491</v>
+        <v>0.6494</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3984</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="33">
@@ -4880,16 +4880,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>303.09</v>
+        <v>303.62</v>
       </c>
       <c r="C33" t="n">
-        <v>203.86</v>
+        <v>203.87</v>
       </c>
       <c r="D33" t="n">
         <v>150.29</v>
       </c>
       <c r="E33" t="n">
-        <v>75.2</v>
+        <v>75.28</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -4898,13 +4898,13 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.624</v>
+        <v>0.6236</v>
       </c>
       <c r="I33" t="n">
-        <v>0.248</v>
+        <v>0.2472</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6466</v>
+        <v>0.6465</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>117.71</v>
+        <v>117.44</v>
       </c>
       <c r="C34" t="n">
         <v>90.56999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>77.53</v>
+        <v>77.52</v>
       </c>
       <c r="E34" t="n">
-        <v>77.09999999999999</v>
+        <v>76.62</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -4962,13 +4962,13 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6145</v>
+        <v>0.6169</v>
       </c>
       <c r="I34" t="n">
-        <v>0.229</v>
+        <v>0.2338</v>
       </c>
       <c r="J34" t="n">
-        <v>0.644</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>565.21</v>
+        <v>564.79</v>
       </c>
       <c r="C35" t="n">
         <v>423.8</v>
@@ -5017,7 +5017,7 @@
         <v>331.03</v>
       </c>
       <c r="E35" t="n">
-        <v>69.33</v>
+        <v>69.27</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -5026,10 +5026,10 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6534</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3067</v>
+        <v>0.3073</v>
       </c>
       <c r="J35" t="n">
         <v>0.6411</v>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3138</v>
+        <v>0.3142</v>
       </c>
     </row>
     <row r="36">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>597.08</v>
+        <v>597.01</v>
       </c>
       <c r="C36" t="n">
         <v>472.43</v>
@@ -5081,7 +5081,7 @@
         <v>383.71</v>
       </c>
       <c r="E36" t="n">
-        <v>69.31</v>
+        <v>69.3</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -5090,10 +5090,10 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6534</v>
+        <v>0.6535</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3069</v>
+        <v>0.307</v>
       </c>
       <c r="J36" t="n">
         <v>0.6401</v>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>0.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3075</v>
+        <v>0.3078</v>
       </c>
     </row>
     <row r="37">
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>318.4</v>
+        <v>317.33</v>
       </c>
       <c r="C37" t="n">
-        <v>186.1</v>
+        <v>186.08</v>
       </c>
       <c r="D37" t="n">
         <v>147.98</v>
       </c>
       <c r="E37" t="n">
-        <v>76.45999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -5154,13 +5154,13 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6177</v>
+        <v>0.6183</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2354</v>
+        <v>0.2366</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6377</v>
+        <v>0.6378</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5200,16 +5200,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>320.1</v>
+        <v>315.7</v>
       </c>
       <c r="C38" t="n">
-        <v>177.73</v>
+        <v>177.64</v>
       </c>
       <c r="D38" t="n">
-        <v>171.51</v>
+        <v>171.49</v>
       </c>
       <c r="E38" t="n">
-        <v>78.29000000000001</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -5218,13 +5218,13 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6085</v>
+        <v>0.6112</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2171</v>
+        <v>0.2224</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6357</v>
+        <v>0.6365</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N38" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>0.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="39">
@@ -5264,16 +5264,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>749.99</v>
+        <v>749.14</v>
       </c>
       <c r="C39" t="n">
-        <v>698.28</v>
+        <v>698.27</v>
       </c>
       <c r="D39" t="n">
         <v>676.86</v>
       </c>
       <c r="E39" t="n">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -5282,13 +5282,13 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.644</v>
+        <v>0.646</v>
       </c>
       <c r="I39" t="n">
-        <v>0.288</v>
+        <v>0.292</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6343</v>
+        <v>0.6348</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>0.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2873</v>
+        <v>0.2875</v>
       </c>
     </row>
     <row r="40">
@@ -5328,16 +5328,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>728.59</v>
+        <v>727.85</v>
       </c>
       <c r="C40" t="n">
-        <v>644.73</v>
+        <v>644.71</v>
       </c>
       <c r="D40" t="n">
         <v>614.4</v>
       </c>
       <c r="E40" t="n">
-        <v>74.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -5346,14 +5346,14 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
+        <v>0.6302</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.6292</v>
       </c>
-      <c r="I40" t="n">
-        <v>0.2585</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.6289</v>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>0.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2813</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="41">
@@ -5392,16 +5392,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>310.59</v>
+        <v>309.94</v>
       </c>
       <c r="C41" t="n">
-        <v>271.57</v>
+        <v>271.56</v>
       </c>
       <c r="D41" t="n">
-        <v>261.55</v>
+        <v>261.54</v>
       </c>
       <c r="E41" t="n">
-        <v>89.63</v>
+        <v>89.42</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -5410,13 +5410,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5518</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1037</v>
+        <v>0.1058</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6253</v>
+        <v>0.6256</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>0.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4118</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="42">
@@ -5456,16 +5456,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>225.18</v>
+        <v>224.52</v>
       </c>
       <c r="C42" t="n">
-        <v>146.97</v>
+        <v>146.96</v>
       </c>
       <c r="D42" t="n">
-        <v>142.36</v>
+        <v>142.35</v>
       </c>
       <c r="E42" t="n">
-        <v>90.12</v>
+        <v>90.06</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -5474,13 +5474,13 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5494</v>
+        <v>0.5497</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0988</v>
+        <v>0.0994</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6232</v>
+        <v>0.6233</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>0.5</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4031</v>
+        <v>0.4032</v>
       </c>
     </row>
     <row r="43">
@@ -5520,16 +5520,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>134.62</v>
+        <v>134.27</v>
       </c>
       <c r="C43" t="n">
-        <v>93.27</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="D43" t="n">
         <v>84.39</v>
       </c>
       <c r="E43" t="n">
-        <v>95.69</v>
+        <v>95.66</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -5538,10 +5538,10 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5216</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0431</v>
+        <v>0.0434</v>
       </c>
       <c r="J43" t="n">
         <v>0.6171</v>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>0.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0.4175</v>
+        <v>0.4177</v>
       </c>
     </row>
     <row r="44">
@@ -5584,16 +5584,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>674.59</v>
+        <v>673.1799999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>467.48</v>
+        <v>467.46</v>
       </c>
       <c r="D44" t="n">
         <v>466.45</v>
       </c>
       <c r="E44" t="n">
-        <v>94.48</v>
+        <v>94.44</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -5602,10 +5602,10 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5276</v>
+        <v>0.5278</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0552</v>
+        <v>0.0556</v>
       </c>
       <c r="J44" t="n">
         <v>0.6115</v>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N44" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>0.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3683</v>
+        <v>0.3684</v>
       </c>
     </row>
     <row r="45">
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>74.31</v>
+        <v>74.16</v>
       </c>
       <c r="C45" t="n">
         <v>76.23</v>
@@ -5657,7 +5657,7 @@
         <v>104.35</v>
       </c>
       <c r="E45" t="n">
-        <v>45.23</v>
+        <v>44.95</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -5666,13 +5666,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2739</v>
+        <v>0.2752</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5477</v>
+        <v>0.5505</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4715</v>
+        <v>0.4719</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>0.7</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3286</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="46">
@@ -5712,16 +5712,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>431.07</v>
+        <v>432.91</v>
       </c>
       <c r="C46" t="n">
-        <v>389.13</v>
+        <v>389.17</v>
       </c>
       <c r="D46" t="n">
-        <v>410.57</v>
+        <v>410.58</v>
       </c>
       <c r="E46" t="n">
-        <v>64.17</v>
+        <v>64.61</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -5730,13 +5730,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1791</v>
+        <v>0.177</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3583</v>
+        <v>0.3539</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4486</v>
+        <v>0.448</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5776,16 +5776,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>610.86</v>
+        <v>610.34</v>
       </c>
       <c r="C47" t="n">
-        <v>617.76</v>
+        <v>617.75</v>
       </c>
       <c r="D47" t="n">
         <v>667.9</v>
       </c>
       <c r="E47" t="n">
-        <v>54.02</v>
+        <v>53.69</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -5794,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2299</v>
+        <v>0.2316</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4598</v>
+        <v>0.4631</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4302</v>
+        <v>0.4307</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>0.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0.4082</v>
+        <v>0.4083</v>
       </c>
     </row>
     <row r="48">
@@ -5864,7 +5864,7 @@
         <v>0.5949</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4066</v>
+        <v>0.4065</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5904,16 +5904,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>242.55</v>
+        <v>242</v>
       </c>
       <c r="C49" t="n">
-        <v>244.76</v>
+        <v>244.75</v>
       </c>
       <c r="D49" t="n">
         <v>305.31</v>
       </c>
       <c r="E49" t="n">
-        <v>40.13</v>
+        <v>39.8</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2994</v>
+        <v>0.301</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5987</v>
+        <v>0.602</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4056</v>
+        <v>0.406</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>0.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4521</v>
+        <v>0.4523</v>
       </c>
     </row>
     <row r="50">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>47.74</v>
+        <v>47.71</v>
       </c>
       <c r="C50" t="n">
         <v>49.12</v>
@@ -5977,7 +5977,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>30.2</v>
+        <v>30.03</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -5986,13 +5986,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.349</v>
+        <v>0.3498</v>
       </c>
       <c r="I50" t="n">
-        <v>0.698</v>
+        <v>0.6997</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4049</v>
+        <v>0.4052</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>0.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0.3485</v>
+        <v>0.3487</v>
       </c>
     </row>
     <row r="51">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="C51" t="n">
         <v>3.28</v>
@@ -6041,7 +6041,7 @@
         <v>4.3</v>
       </c>
       <c r="E51" t="n">
-        <v>34.53</v>
+        <v>32.17</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -6050,17 +6050,17 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3274</v>
+        <v>0.3391</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6783</v>
       </c>
       <c r="J51" t="n">
-        <v>0.3999</v>
+        <v>0.4036</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>AVOID</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>0.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3583</v>
+        <v>0.3595</v>
       </c>
     </row>
     <row r="52">
@@ -6096,16 +6096,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>90.01000000000001</v>
+        <v>89.78</v>
       </c>
       <c r="C52" t="n">
-        <v>92.34</v>
+        <v>92.33</v>
       </c>
       <c r="D52" t="n">
         <v>94.75</v>
       </c>
       <c r="E52" t="n">
-        <v>43.24</v>
+        <v>42.6</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -6114,13 +6114,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2838</v>
+        <v>0.287</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5676</v>
+        <v>0.574</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3975</v>
+        <v>0.3985</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N52" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>0.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4295</v>
+        <v>0.4299</v>
       </c>
     </row>
     <row r="53">
@@ -6160,16 +6160,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>125.18</v>
+        <v>124.66</v>
       </c>
       <c r="C53" t="n">
-        <v>125.52</v>
+        <v>125.51</v>
       </c>
       <c r="D53" t="n">
         <v>187.15</v>
       </c>
       <c r="E53" t="n">
-        <v>46.84</v>
+        <v>46.42</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -6178,13 +6178,13 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2658</v>
+        <v>0.2679</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5316</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>0.395</v>
+        <v>0.3956</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N53" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6214,26 +6214,26 @@
         <v>0.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0.4486</v>
+        <v>0.4488</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>305.12</v>
+        <v>53.19</v>
       </c>
       <c r="C54" t="n">
-        <v>293.55</v>
+        <v>54.53</v>
       </c>
       <c r="D54" t="n">
-        <v>323</v>
+        <v>58.42</v>
       </c>
       <c r="E54" t="n">
-        <v>43.22</v>
+        <v>40.85</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -6242,13 +6242,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2839</v>
+        <v>0.2957</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5678</v>
+        <v>0.5915</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3945</v>
+        <v>0.3953</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6278,26 +6278,26 @@
         <v>0.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0.4094</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53.58</v>
+        <v>304.59</v>
       </c>
       <c r="C55" t="n">
-        <v>54.54</v>
+        <v>293.53</v>
       </c>
       <c r="D55" t="n">
-        <v>58.42</v>
+        <v>322.99</v>
       </c>
       <c r="E55" t="n">
-        <v>41.47</v>
+        <v>42.94</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -6306,13 +6306,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2926</v>
+        <v>0.2853</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5853</v>
+        <v>0.5706</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3944</v>
+        <v>0.395</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>0.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0.3909</v>
+        <v>0.4097</v>
       </c>
     </row>
     <row r="56">
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8.300000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="C56" t="n">
         <v>7.7</v>
@@ -6361,7 +6361,7 @@
         <v>11.46</v>
       </c>
       <c r="E56" t="n">
-        <v>36.78</v>
+        <v>37.17</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -6370,13 +6370,13 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3161</v>
+        <v>0.3142</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6322</v>
+        <v>0.6283</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3934</v>
+        <v>0.3928</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N56" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23.35</v>
+        <v>23.33</v>
       </c>
       <c r="C57" t="n">
         <v>17.73</v>
@@ -6425,7 +6425,7 @@
         <v>20.41</v>
       </c>
       <c r="E57" t="n">
-        <v>45.2</v>
+        <v>45.08</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.274</v>
+        <v>0.2746</v>
       </c>
       <c r="I57" t="n">
-        <v>0.548</v>
+        <v>0.5492</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3925</v>
+        <v>0.3927</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6470,26 +6470,26 @@
         <v>0.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0.4158</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>41</v>
+        <v>414.3</v>
       </c>
       <c r="C58" t="n">
-        <v>37.34</v>
+        <v>400</v>
       </c>
       <c r="D58" t="n">
-        <v>42.65</v>
+        <v>457.76</v>
       </c>
       <c r="E58" t="n">
-        <v>56.93</v>
+        <v>53.24</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -6498,13 +6498,13 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2154</v>
+        <v>0.2338</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4307</v>
+        <v>0.4676</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3752</v>
+        <v>0.3754</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6534,26 +6534,26 @@
         <v>0.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0.4174</v>
+        <v>0.3825</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11.36</v>
+        <v>41.02</v>
       </c>
       <c r="C59" t="n">
-        <v>10.75</v>
+        <v>37.34</v>
       </c>
       <c r="D59" t="n">
-        <v>12.99</v>
+        <v>42.65</v>
       </c>
       <c r="E59" t="n">
-        <v>57.24</v>
+        <v>56.99</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -6562,13 +6562,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2138</v>
+        <v>0.215</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4276</v>
+        <v>0.4301</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3738</v>
+        <v>0.375</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6598,26 +6598,26 @@
         <v>0.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0.4113</v>
+        <v>0.4174</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>416.06</v>
+        <v>11.28</v>
       </c>
       <c r="C60" t="n">
-        <v>400.04</v>
+        <v>10.75</v>
       </c>
       <c r="D60" t="n">
-        <v>457.77</v>
+        <v>12.98</v>
       </c>
       <c r="E60" t="n">
-        <v>54.88</v>
+        <v>56.52</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -6626,13 +6626,13 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2256</v>
+        <v>0.2174</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4512</v>
+        <v>0.4348</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3729</v>
+        <v>0.3749</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>0.5</v>
       </c>
       <c r="R60" t="n">
-        <v>0.382</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="61">
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="C61" t="n">
         <v>3.81</v>
       </c>
       <c r="D61" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
       <c r="E61" t="n">
-        <v>52.15</v>
+        <v>51.62</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -6690,13 +6690,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2392</v>
+        <v>0.2419</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4785</v>
+        <v>0.4838</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3703</v>
+        <v>0.3711</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N61" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>0.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0.3375</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="62">
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
       <c r="C62" t="n">
         <v>6.06</v>
@@ -6745,7 +6745,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>53.46</v>
+        <v>52.84</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2327</v>
+        <v>0.2358</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4654</v>
+        <v>0.4716</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3701</v>
+        <v>0.371</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N62" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6790,26 +6790,26 @@
         <v>0.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0.3487</v>
+        <v>0.3489</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9.68</v>
+        <v>81.33</v>
       </c>
       <c r="C63" t="n">
-        <v>8.869999999999999</v>
+        <v>61.87</v>
       </c>
       <c r="D63" t="n">
-        <v>13.28</v>
+        <v>65.42</v>
       </c>
       <c r="E63" t="n">
-        <v>53.76</v>
+        <v>61.68</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2312</v>
+        <v>0.1916</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4624</v>
+        <v>0.3832</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3699</v>
+        <v>0.3708</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>0.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0.3508</v>
+        <v>0.4363</v>
       </c>
     </row>
     <row r="64">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="C64" t="n">
         <v>11.46</v>
@@ -6873,7 +6873,7 @@
         <v>22.82</v>
       </c>
       <c r="E64" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -6882,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2365</v>
+        <v>0.237</v>
       </c>
       <c r="I64" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3698</v>
+        <v>0.3699</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6918,26 +6918,26 @@
         <v>0.5</v>
       </c>
       <c r="R64" t="n">
-        <v>0.3392</v>
+        <v>0.3393</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>81.79000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>61.88</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>65.42</v>
+        <v>13.28</v>
       </c>
       <c r="E65" t="n">
-        <v>62.45</v>
+        <v>54.19</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -6946,13 +6946,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1877</v>
+        <v>0.2291</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3755</v>
+        <v>0.4581</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3697</v>
+        <v>0.3693</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N65" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>0.5</v>
       </c>
       <c r="R65" t="n">
-        <v>0.436</v>
+        <v>0.3509</v>
       </c>
     </row>
     <row r="66">
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>101.77</v>
+        <v>101.54</v>
       </c>
       <c r="C66" t="n">
-        <v>97.88</v>
+        <v>97.87</v>
       </c>
       <c r="D66" t="n">
         <v>142.39</v>
       </c>
       <c r="E66" t="n">
-        <v>62.05</v>
+        <v>61.7</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -7010,13 +7010,13 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1898</v>
+        <v>0.1915</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3795</v>
+        <v>0.383</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3687</v>
+        <v>0.3692</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>0.5</v>
       </c>
       <c r="R66" t="n">
-        <v>0.4251</v>
+        <v>0.4253</v>
       </c>
     </row>
     <row r="67">
@@ -7056,16 +7056,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>512.53</v>
+        <v>510.96</v>
       </c>
       <c r="C67" t="n">
-        <v>449.37</v>
+        <v>449.34</v>
       </c>
       <c r="D67" t="n">
-        <v>534.4</v>
+        <v>534.39</v>
       </c>
       <c r="E67" t="n">
-        <v>57.04</v>
+        <v>56.76</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -7074,13 +7074,13 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2148</v>
+        <v>0.2162</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4296</v>
+        <v>0.4324</v>
       </c>
       <c r="J67" t="n">
-        <v>0.3685</v>
+        <v>0.3689</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N67" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>0.5</v>
       </c>
       <c r="R67" t="n">
-        <v>0.3739</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="68">
@@ -7120,16 +7120,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>102.48</v>
+        <v>102.24</v>
       </c>
       <c r="C68" t="n">
-        <v>89.95</v>
+        <v>89.94</v>
       </c>
       <c r="D68" t="n">
         <v>119.41</v>
       </c>
       <c r="E68" t="n">
-        <v>67.3</v>
+        <v>66.89</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -7138,13 +7138,13 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1635</v>
+        <v>0.1655</v>
       </c>
       <c r="I68" t="n">
-        <v>0.327</v>
+        <v>0.3311</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>0.5</v>
       </c>
       <c r="R68" t="n">
-        <v>0.4744</v>
+        <v>0.4745</v>
       </c>
     </row>
     <row r="69">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>191.97</v>
+        <v>191.53</v>
       </c>
       <c r="C69" t="n">
-        <v>167.77</v>
+        <v>167.76</v>
       </c>
       <c r="D69" t="n">
         <v>206.63</v>
       </c>
       <c r="E69" t="n">
-        <v>56.2</v>
+        <v>55.74</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -7202,13 +7202,13 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.219</v>
+        <v>0.2213</v>
       </c>
       <c r="I69" t="n">
-        <v>0.438</v>
+        <v>0.4426</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3642</v>
+        <v>0.3648</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N69" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>0.5</v>
       </c>
       <c r="R69" t="n">
-        <v>0.3369</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="70">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>77.48999999999999</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="C70" t="n">
         <v>73.92</v>
@@ -7257,7 +7257,7 @@
         <v>77.94</v>
       </c>
       <c r="E70" t="n">
-        <v>52.67</v>
+        <v>52.52</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -7266,13 +7266,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2366</v>
+        <v>0.2374</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4733</v>
+        <v>0.4748</v>
       </c>
       <c r="J70" t="n">
-        <v>0.3616</v>
+        <v>0.3618</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N70" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>0.5</v>
       </c>
       <c r="R70" t="n">
-        <v>0.2844</v>
+        <v>0.2845</v>
       </c>
     </row>
     <row r="71">
@@ -7312,16 +7312,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>307.82</v>
+        <v>310.3</v>
       </c>
       <c r="C71" t="n">
-        <v>269.47</v>
+        <v>269.52</v>
       </c>
       <c r="D71" t="n">
-        <v>322.79</v>
+        <v>322.8</v>
       </c>
       <c r="E71" t="n">
-        <v>65.12</v>
+        <v>66.33</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -7330,13 +7330,13 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1744</v>
+        <v>0.1684</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3488</v>
+        <v>0.3367</v>
       </c>
       <c r="J71" t="n">
-        <v>0.3604</v>
+        <v>0.3585</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N71" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>0.5</v>
       </c>
       <c r="R71" t="n">
-        <v>0.401</v>
+        <v>0.4005</v>
       </c>
     </row>
     <row r="72">
@@ -7376,16 +7376,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>250.92</v>
+        <v>250.65</v>
       </c>
       <c r="C72" t="n">
-        <v>236.69</v>
+        <v>236.68</v>
       </c>
       <c r="D72" t="n">
         <v>266.6</v>
       </c>
       <c r="E72" t="n">
-        <v>67.58</v>
+        <v>67.3</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -7394,13 +7394,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1621</v>
+        <v>0.1635</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3242</v>
+        <v>0.327</v>
       </c>
       <c r="J72" t="n">
-        <v>0.357</v>
+        <v>0.3573</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N72" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>63.57</v>
+        <v>63.88</v>
       </c>
       <c r="C73" t="n">
-        <v>41.57</v>
+        <v>41.58</v>
       </c>
       <c r="D73" t="n">
         <v>47.45</v>
       </c>
       <c r="E73" t="n">
-        <v>66.63</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -7458,13 +7458,13 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1668</v>
+        <v>0.1655</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3337</v>
+        <v>0.331</v>
       </c>
       <c r="J73" t="n">
-        <v>0.3502</v>
+        <v>0.3497</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N73" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -7494,26 +7494,26 @@
         <v>0.5</v>
       </c>
       <c r="R73" t="n">
-        <v>0.3479</v>
+        <v>0.3478</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>36.94</v>
+        <v>380</v>
       </c>
       <c r="C74" t="n">
-        <v>28.03</v>
+        <v>317.01</v>
       </c>
       <c r="D74" t="n">
-        <v>36.03</v>
+        <v>322.74</v>
       </c>
       <c r="E74" t="n">
-        <v>69.91</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -7522,13 +7522,13 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1505</v>
+        <v>0.166</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3009</v>
+        <v>0.3321</v>
       </c>
       <c r="J74" t="n">
-        <v>0.348</v>
+        <v>0.3469</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N74" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -7558,26 +7558,26 @@
         <v>0.5</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3662</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>379.79</v>
+        <v>37.65</v>
       </c>
       <c r="C75" t="n">
-        <v>317</v>
+        <v>28.04</v>
       </c>
       <c r="D75" t="n">
-        <v>322.74</v>
+        <v>36.04</v>
       </c>
       <c r="E75" t="n">
-        <v>66.7</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -7586,13 +7586,13 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1665</v>
+        <v>0.1459</v>
       </c>
       <c r="I75" t="n">
-        <v>0.333</v>
+        <v>0.2918</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3471</v>
+        <v>0.3466</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N75" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>0.5</v>
       </c>
       <c r="R75" t="n">
-        <v>0.3281</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="76">
@@ -7656,7 +7656,7 @@
         <v>0.265</v>
       </c>
       <c r="J76" t="n">
-        <v>0.3459</v>
+        <v>0.3458</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N76" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>0.5</v>
       </c>
       <c r="R76" t="n">
-        <v>0.3876</v>
+        <v>0.3877</v>
       </c>
     </row>
     <row r="77">
@@ -7696,16 +7696,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>97.84999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="C77" t="n">
-        <v>54.69</v>
+        <v>54.68</v>
       </c>
       <c r="D77" t="n">
         <v>56.84</v>
       </c>
       <c r="E77" t="n">
-        <v>75.19</v>
+        <v>75.09</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.124</v>
+        <v>0.1246</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2481</v>
+        <v>0.2491</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3454</v>
+        <v>0.3455</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N77" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>0.5</v>
       </c>
       <c r="R77" t="n">
-        <v>0.4016</v>
+        <v>0.4017</v>
       </c>
     </row>
     <row r="78">
@@ -7760,16 +7760,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>534.58</v>
+        <v>532.72</v>
       </c>
       <c r="C78" t="n">
-        <v>456.88</v>
+        <v>456.84</v>
       </c>
       <c r="D78" t="n">
-        <v>470.93</v>
+        <v>470.92</v>
       </c>
       <c r="E78" t="n">
-        <v>70.36</v>
+        <v>69.64</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -7778,13 +7778,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1482</v>
+        <v>0.1518</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2964</v>
+        <v>0.3036</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3405</v>
+        <v>0.3416</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N78" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>0.5</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3207</v>
+        <v>0.3209</v>
       </c>
     </row>
     <row r="79">
@@ -7824,16 +7824,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>189.14</v>
+        <v>189.57</v>
       </c>
       <c r="C79" t="n">
-        <v>145.06</v>
+        <v>145.07</v>
       </c>
       <c r="D79" t="n">
         <v>223.66</v>
       </c>
       <c r="E79" t="n">
-        <v>82.04000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -7842,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0898</v>
+        <v>0.0893</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1796</v>
+        <v>0.1786</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3353</v>
+        <v>0.3351</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N79" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>0.5</v>
       </c>
       <c r="R79" t="n">
-        <v>0.4026</v>
+        <v>0.4028</v>
       </c>
     </row>
     <row r="80">
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>94.38</v>
+        <v>94.25</v>
       </c>
       <c r="C80" t="n">
         <v>64.05</v>
@@ -7897,7 +7897,7 @@
         <v>71.94</v>
       </c>
       <c r="E80" t="n">
-        <v>77.38</v>
+        <v>77.3</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -7906,13 +7906,13 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1131</v>
+        <v>0.1135</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2262</v>
+        <v>0.227</v>
       </c>
       <c r="J80" t="n">
-        <v>0.3345</v>
+        <v>0.3346</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N80" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>0.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0.351</v>
+        <v>0.3512</v>
       </c>
     </row>
     <row r="81">
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>178.95</v>
+        <v>178.72</v>
       </c>
       <c r="C81" t="n">
         <v>153.05</v>
@@ -7961,7 +7961,7 @@
         <v>202.58</v>
       </c>
       <c r="E81" t="n">
-        <v>82.75</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0862</v>
+        <v>0.0866</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1725</v>
+        <v>0.1732</v>
       </c>
       <c r="J81" t="n">
-        <v>0.3312</v>
+        <v>0.3314</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N81" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>0.5</v>
       </c>
       <c r="R81" t="n">
-        <v>0.3828</v>
+        <v>0.3831</v>
       </c>
     </row>
     <row r="82">
@@ -8016,16 +8016,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>258.32</v>
+        <v>257.17</v>
       </c>
       <c r="C82" t="n">
-        <v>185.8</v>
+        <v>185.78</v>
       </c>
       <c r="D82" t="n">
-        <v>188.03</v>
+        <v>188.02</v>
       </c>
       <c r="E82" t="n">
-        <v>89.41</v>
+        <v>88.34</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -8034,13 +8034,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.053</v>
+        <v>0.0583</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1059</v>
+        <v>0.1166</v>
       </c>
       <c r="J82" t="n">
-        <v>0.3231</v>
+        <v>0.3246</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>34.69</v>
+        <v>34.73</v>
       </c>
       <c r="N82" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>0.5</v>
       </c>
       <c r="R82" t="n">
-        <v>0.3946</v>
+        <v>0.3949</v>
       </c>
     </row>
   </sheetData>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>107.04</v>
+        <v>107.44</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>35.85</v>
+        <v>36.2</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>213.35</v>
+        <v>213.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8102</v>
+        <v>0.8097</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>62.51</v>
+        <v>62.84</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.98</v>
+        <v>12.18</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7967</v>
+        <v>0.7957</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>35.66</v>
+        <v>36.11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8359</v>
+        <v>0.8345</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>496.51</v>
+        <v>495.95</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7879</v>
+        <v>0.788</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>76.65000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.3</v>
+        <v>13.39</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7556</v>
+        <v>0.755</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8308,10 +8308,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>58.98</v>
+        <v>59.21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8359</v>
+        <v>0.8345</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>220.35</v>
+        <v>220.51</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6993</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -8345,10 +8345,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>40.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>189.06</v>
+        <v>188.37</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6909</v>
+        <v>0.6921</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>43.48</v>
+        <v>42.69</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.47</v>
+        <v>80.38</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6887</v>
+        <v>0.6898</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -8419,10 +8419,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>63.96</v>
+        <v>63.16</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8442,10 +8442,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>159.49</v>
+        <v>158.85</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6885</v>
+        <v>0.6892</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -8456,10 +8456,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>42.87</v>
+        <v>42.38</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>327.99</v>
+        <v>327.11</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6884</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -8493,10 +8493,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>45.59</v>
+        <v>45.28</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181.87</v>
+        <v>180.82</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6867</v>
+        <v>0.6871</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -8530,10 +8530,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>50.36</v>
+        <v>50.07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>383.22</v>
+        <v>382.64</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6833</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>49.19</v>
+        <v>48.73</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>408.13</v>
+        <v>405.67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6813</v>
+        <v>0.6825</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>49.47</v>
+        <v>48.63</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>264.12</v>
+        <v>262.86</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6774</v>
+        <v>0.6794</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -8641,10 +8641,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>39.19</v>
+        <v>38.09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5111</v>
+        <v>0.5128</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>422.57</v>
+        <v>423.47</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6764</v>
+        <v>0.6757</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -8678,10 +8678,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>47.93</v>
+        <v>48.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54.45</v>
+        <v>54.4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6712</v>
+        <v>0.6713</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>56.74</v>
+        <v>56.66</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>383.74</v>
+        <v>1596.43</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6681</v>
+        <v>0.6683</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>57.26</v>
+        <v>59.84</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1600.96</v>
+        <v>383.91</v>
       </c>
       <c r="D19" t="n">
         <v>0.6681</v>
@@ -8789,10 +8789,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>60.03</v>
+        <v>57.3</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>216.7</v>
+        <v>216.42</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6677</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -8826,10 +8826,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>57.49</v>
+        <v>57.38</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>121.6</v>
+        <v>121.09</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6655</v>
+        <v>0.6659</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>60.56</v>
+        <v>60.24</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>454.36</v>
+        <v>454.13</v>
       </c>
       <c r="D22" t="n">
         <v>0.664</v>
@@ -8900,10 +8900,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>58.96</v>
+        <v>58.87</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>411.65</v>
+        <v>411.93</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6633</v>
+        <v>0.6631</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -8937,10 +8937,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>57.36</v>
+        <v>57.46</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8960,10 +8960,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>109.73</v>
+        <v>110.76</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6601</v>
+        <v>0.6595</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -8974,10 +8974,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>59.7</v>
+        <v>60.13</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1617.68</v>
+        <v>289.51</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6559</v>
+        <v>0.6562</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -9011,10 +9011,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>63.37</v>
+        <v>57.82</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>289.97</v>
+        <v>1624.73</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6556</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -9048,10 +9048,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>58.25</v>
+        <v>64.06</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9071,10 +9071,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>205.28</v>
+        <v>126.51</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6538</v>
+        <v>0.654</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>68.12</v>
+        <v>67.98</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9108,10 +9108,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>126.74</v>
+        <v>205.86</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6538</v>
+        <v>0.6535</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -9122,10 +9122,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>68.08</v>
+        <v>68.3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1985.43</v>
+        <v>1995.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6518</v>
+        <v>0.6511</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -9159,10 +9159,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>66.41</v>
+        <v>66.84</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37.24</v>
+        <v>37.28</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6504</v>
+        <v>0.6501</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -9196,10 +9196,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>67.98999999999999</v>
+        <v>68.11</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LPTH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>886.41</v>
+        <v>16.83</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6493</v>
+        <v>0.6499</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -9233,10 +9233,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>70.18000000000001</v>
+        <v>71.88</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.91</v>
+        <v>884.77</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6491</v>
+        <v>0.6494</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -9270,10 +9270,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>72.41</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>303.09</v>
+        <v>303.62</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6466</v>
+        <v>0.6465</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -9307,10 +9307,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>75.2</v>
+        <v>75.28</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9330,10 +9330,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>117.71</v>
+        <v>117.45</v>
       </c>
       <c r="D34" t="n">
-        <v>0.644</v>
+        <v>0.6446</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>77.09999999999999</v>
+        <v>76.64</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>565.21</v>
+        <v>564.79</v>
       </c>
       <c r="D35" t="n">
         <v>0.6411</v>
@@ -9381,10 +9381,10 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>69.33</v>
+        <v>69.27</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>597.08</v>
+        <v>597.01</v>
       </c>
       <c r="D36" t="n">
         <v>0.6401</v>
@@ -9418,10 +9418,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>69.31</v>
+        <v>69.3</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>318.4</v>
+        <v>317.14</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6377</v>
+        <v>0.6378</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -9455,10 +9455,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>76.45999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>320.1</v>
+        <v>315.35</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6357</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>78.29000000000001</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>749.99</v>
+        <v>749.14</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6343</v>
+        <v>0.6348</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -9529,10 +9529,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>728.59</v>
+        <v>727.85</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6289</v>
+        <v>0.6292</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -9566,10 +9566,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>74.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>310.59</v>
+        <v>309.94</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6253</v>
+        <v>0.6256</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>89.63</v>
+        <v>89.42</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>225.18</v>
+        <v>224.52</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6232</v>
+        <v>0.6233</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -9640,10 +9640,10 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>90.12</v>
+        <v>90.06</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>134.62</v>
+        <v>134.27</v>
       </c>
       <c r="D43" t="n">
         <v>0.6171</v>
@@ -9677,10 +9677,10 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>95.69</v>
+        <v>95.66</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>674.59</v>
+        <v>673.1799999999999</v>
       </c>
       <c r="D44" t="n">
         <v>0.6115</v>
@@ -9714,10 +9714,10 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>94.48</v>
+        <v>94.44</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>74.31</v>
+        <v>74.16</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4715</v>
+        <v>0.4719</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>45.23</v>
+        <v>44.95</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>431.07</v>
+        <v>432.91</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4486</v>
+        <v>0.448</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>64.17</v>
+        <v>64.61</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>610.86</v>
+        <v>610.34</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4302</v>
+        <v>0.4307</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>54.02</v>
+        <v>53.69</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -9851,7 +9851,7 @@
         <v>876</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4066</v>
+        <v>0.4065</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>40.51</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>242.55</v>
+        <v>241.96</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4056</v>
+        <v>0.4061</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -9899,14 +9899,14 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>40.13</v>
+        <v>39.78</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>47.74</v>
+        <v>47.71</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4049</v>
+        <v>0.4052</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>30.2</v>
+        <v>30.03</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -9959,24 +9959,24 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3999</v>
+        <v>0.4036</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AVOID</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>34.53</v>
+        <v>32.17</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>90.01000000000001</v>
+        <v>89.78</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3975</v>
+        <v>0.3985</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -10010,10 +10010,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>43.24</v>
+        <v>42.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>125.18</v>
+        <v>124.66</v>
       </c>
       <c r="D53" t="n">
-        <v>0.395</v>
+        <v>0.3956</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>46.84</v>
+        <v>46.42</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>305.12</v>
+        <v>53.19</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3945</v>
+        <v>0.3953</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>43.22</v>
+        <v>40.85</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>53.58</v>
+        <v>304.59</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3944</v>
+        <v>0.395</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -10121,10 +10121,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>41.47</v>
+        <v>42.94</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8.300000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3934</v>
+        <v>0.3928</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -10158,10 +10158,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>36.78</v>
+        <v>37.17</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>23.35</v>
+        <v>23.33</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3925</v>
+        <v>0.3927</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -10195,10 +10195,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>45.2</v>
+        <v>45.08</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>41</v>
+        <v>414.27</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3752</v>
+        <v>0.3755</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -10232,10 +10232,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>56.93</v>
+        <v>53.21</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11.36</v>
+        <v>41.02</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3738</v>
+        <v>0.375</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -10269,10 +10269,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>57.24</v>
+        <v>56.99</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>416.06</v>
+        <v>11.28</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3729</v>
+        <v>0.3749</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -10306,10 +10306,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>54.88</v>
+        <v>56.52</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3703</v>
+        <v>0.3711</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>52.15</v>
+        <v>51.62</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3701</v>
+        <v>0.371</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>53.46</v>
+        <v>52.84</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9.68</v>
+        <v>81.33</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3699</v>
+        <v>0.3708</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -10417,10 +10417,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>53.76</v>
+        <v>61.68</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3698</v>
+        <v>0.3699</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>81.79000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3697</v>
+        <v>0.3693</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -10491,10 +10491,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>62.45</v>
+        <v>54.19</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>101.77</v>
+        <v>101.54</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3687</v>
+        <v>0.3692</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>62.05</v>
+        <v>61.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -10551,10 +10551,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>512.53</v>
+        <v>511.09</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3685</v>
+        <v>0.3688</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -10565,10 +10565,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>57.04</v>
+        <v>56.78</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -10588,10 +10588,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>102.48</v>
+        <v>102.24</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>67.3</v>
+        <v>66.89</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -10625,10 +10625,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>191.97</v>
+        <v>191.53</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3642</v>
+        <v>0.3648</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -10639,10 +10639,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>56.2</v>
+        <v>55.74</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>77.48999999999999</v>
+        <v>77.44</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3616</v>
+        <v>0.3618</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -10676,10 +10676,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>52.67</v>
+        <v>52.53</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>307.82</v>
+        <v>310.3</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3604</v>
+        <v>0.3585</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -10713,10 +10713,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>65.12</v>
+        <v>66.33</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>250.92</v>
+        <v>250.65</v>
       </c>
       <c r="D72" t="n">
-        <v>0.357</v>
+        <v>0.3573</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>67.58</v>
+        <v>67.3</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>63.57</v>
+        <v>63.88</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3502</v>
+        <v>0.3497</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -10787,10 +10787,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>66.63</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>36.94</v>
+        <v>380</v>
       </c>
       <c r="D74" t="n">
-        <v>0.348</v>
+        <v>0.3469</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -10824,10 +10824,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>69.91</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>379.79</v>
+        <v>37.65</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3471</v>
+        <v>0.3466</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -10861,10 +10861,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>66.7</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>18.57</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3459</v>
+        <v>0.3458</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>73.5</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>97.84999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3454</v>
+        <v>0.3455</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -10935,10 +10935,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>75.19</v>
+        <v>75.09</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -10958,10 +10958,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>534.58</v>
+        <v>532.72</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3405</v>
+        <v>0.3416</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -10972,10 +10972,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>70.36</v>
+        <v>69.64</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -10995,10 +10995,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>189.14</v>
+        <v>189.57</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3353</v>
+        <v>0.3351</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -11009,10 +11009,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>82.04000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>94.38</v>
+        <v>94.23</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3345</v>
+        <v>0.3346</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>77.38</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>178.95</v>
+        <v>178.72</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3312</v>
+        <v>0.3314</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -11083,10 +11083,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>82.75</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>258.32</v>
+        <v>257.17</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3231</v>
+        <v>0.3246</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -11120,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>89.41</v>
+        <v>88.34</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8103</v>
+        <v>0.8098</v>
       </c>
       <c r="D2" t="n">
         <v>0.2532</v>
@@ -11234,10 +11234,10 @@
         <v>7260</v>
       </c>
       <c r="H2" t="n">
-        <v>213.32</v>
+        <v>213.65</v>
       </c>
       <c r="I2" t="n">
-        <v>34.03</v>
+        <v>33.98</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -11265,10 +11265,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4744</v>
+        <v>0.4741</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11280,10 +11280,10 @@
         <v>3480</v>
       </c>
       <c r="H3" t="n">
-        <v>496.95</v>
+        <v>495.95</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1218</v>
+        <v>0.1219</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11326,10 +11326,10 @@
         <v>3320</v>
       </c>
       <c r="H4" t="n">
-        <v>80.45</v>
+        <v>80.37</v>
       </c>
       <c r="I4" t="n">
-        <v>41.27</v>
+        <v>41.31</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.831</v>
+        <v>0.8305</v>
       </c>
       <c r="D5" t="n">
         <v>0.6681</v>
@@ -11372,10 +11372,10 @@
         <v>3310</v>
       </c>
       <c r="H5" t="n">
-        <v>107.12</v>
+        <v>107.44</v>
       </c>
       <c r="I5" t="n">
-        <v>30.9</v>
+        <v>30.81</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6342</v>
+        <v>0.6349</v>
       </c>
       <c r="D6" t="n">
         <v>0.1071</v>
@@ -11418,7 +11418,7 @@
         <v>3110</v>
       </c>
       <c r="H6" t="n">
-        <v>750.03</v>
+        <v>749.02</v>
       </c>
       <c r="I6" t="n">
         <v>4.15</v>
@@ -11449,10 +11449,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6555</v>
+        <v>0.6562</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1526</v>
+        <v>0.1525</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11464,10 +11464,10 @@
         <v>3050</v>
       </c>
       <c r="H7" t="n">
-        <v>290.03</v>
+        <v>289.51</v>
       </c>
       <c r="I7" t="n">
-        <v>10.52</v>
+        <v>10.54</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6289</v>
+        <v>0.6292</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1448</v>
+        <v>0.1446</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11510,7 +11510,7 @@
         <v>2950</v>
       </c>
       <c r="H8" t="n">
-        <v>728.66</v>
+        <v>727.7</v>
       </c>
       <c r="I8" t="n">
         <v>4.05</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6833</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0.2465</v>
@@ -11556,10 +11556,10 @@
         <v>2830</v>
       </c>
       <c r="H9" t="n">
-        <v>383.27</v>
+        <v>382.64</v>
       </c>
       <c r="I9" t="n">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6253</v>
+        <v>0.6257</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1765</v>
+        <v>0.1764</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11602,10 +11602,10 @@
         <v>2820</v>
       </c>
       <c r="H10" t="n">
-        <v>310.6</v>
+        <v>309.77</v>
       </c>
       <c r="I10" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -11633,25 +11633,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6813</v>
+        <v>0.6825</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2504</v>
+        <v>0.2496</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="G11" t="n">
-        <v>2800</v>
+        <v>2810</v>
       </c>
       <c r="H11" t="n">
-        <v>408.2</v>
+        <v>405.68</v>
       </c>
       <c r="I11" t="n">
-        <v>6.86</v>
+        <v>6.93</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6641</v>
+        <v>0.664</v>
       </c>
       <c r="D12" t="n">
         <v>0.2603</v>
@@ -11694,7 +11694,7 @@
         <v>2690</v>
       </c>
       <c r="H12" t="n">
-        <v>454.09</v>
+        <v>454.13</v>
       </c>
       <c r="I12" t="n">
         <v>5.92</v>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6439</v>
+        <v>0.6446</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2513</v>
+        <v>0.2515</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11740,10 +11740,10 @@
         <v>2640</v>
       </c>
       <c r="H13" t="n">
-        <v>117.75</v>
+        <v>117.45</v>
       </c>
       <c r="I13" t="n">
-        <v>22.42</v>
+        <v>22.48</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6401</v>
+        <v>0.6402</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2473</v>
+        <v>0.2472</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11786,7 +11786,7 @@
         <v>2640</v>
       </c>
       <c r="H14" t="n">
-        <v>597.16</v>
+        <v>596.9</v>
       </c>
       <c r="I14" t="n">
         <v>4.42</v>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6633</v>
+        <v>0.6632</v>
       </c>
       <c r="D15" t="n">
         <v>0.2818</v>
@@ -11832,7 +11832,7 @@
         <v>2610</v>
       </c>
       <c r="H15" t="n">
-        <v>411.68</v>
+        <v>411.84</v>
       </c>
       <c r="I15" t="n">
         <v>6.34</v>
@@ -11863,10 +11863,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.641</v>
+        <v>0.6412</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2726</v>
+        <v>0.2725</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -11878,7 +11878,7 @@
         <v>2560</v>
       </c>
       <c r="H16" t="n">
-        <v>565.3200000000001</v>
+        <v>564.6900000000001</v>
       </c>
       <c r="I16" t="n">
         <v>4.53</v>
@@ -11909,25 +11909,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6559</v>
+        <v>0.6549</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3225</v>
+        <v>0.3224</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="G17" t="n">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="H17" t="n">
-        <v>1617.7</v>
+        <v>1623.87</v>
       </c>
       <c r="I17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11955,25 +11955,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6171</v>
+        <v>0.6758</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2944</v>
+        <v>0.3577</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="G18" t="n">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="H18" t="n">
-        <v>134.71</v>
+        <v>423.37</v>
       </c>
       <c r="I18" t="n">
-        <v>17.74</v>
+        <v>5.62</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6762</v>
+        <v>0.6171</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3577</v>
+        <v>0.2944</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12016,10 +12016,10 @@
         <v>2380</v>
       </c>
       <c r="H19" t="n">
-        <v>422.77</v>
+        <v>134.24</v>
       </c>
       <c r="I19" t="n">
-        <v>5.63</v>
+        <v>17.73</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6885</v>
+        <v>0.6892</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3954</v>
+        <v>0.3951</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12062,10 +12062,10 @@
         <v>2290</v>
       </c>
       <c r="H20" t="n">
-        <v>159.49</v>
+        <v>158.85</v>
       </c>
       <c r="I20" t="n">
-        <v>14.36</v>
+        <v>14.42</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6909</v>
+        <v>0.6921</v>
       </c>
       <c r="D21" t="n">
         <v>0.4091</v>
@@ -12108,10 +12108,10 @@
         <v>2240</v>
       </c>
       <c r="H21" t="n">
-        <v>189.06</v>
+        <v>188.37</v>
       </c>
       <c r="I21" t="n">
-        <v>11.85</v>
+        <v>11.89</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -12139,10 +12139,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6512</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3759</v>
+        <v>0.3763</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
         <v>2230</v>
       </c>
       <c r="H22" t="n">
-        <v>1986.06</v>
+        <v>1994.52</v>
       </c>
       <c r="I22" t="n">
         <v>1.12</v>
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6538</v>
+        <v>0.6539</v>
       </c>
       <c r="D23" t="n">
-        <v>0.395</v>
+        <v>0.3947</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12200,10 +12200,10 @@
         <v>2170</v>
       </c>
       <c r="H23" t="n">
-        <v>126.74</v>
+        <v>126.54</v>
       </c>
       <c r="I23" t="n">
-        <v>17.12</v>
+        <v>17.15</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6881</v>
+        <v>0.6885</v>
       </c>
       <c r="D24" t="n">
         <v>0.4362</v>
@@ -12246,10 +12246,10 @@
         <v>2130</v>
       </c>
       <c r="H24" t="n">
-        <v>327.78</v>
+        <v>326.95</v>
       </c>
       <c r="I24" t="n">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6466</v>
+        <v>0.6465</v>
       </c>
       <c r="D25" t="n">
         <v>0.431</v>
@@ -12286,16 +12286,16 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="G25" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="H25" t="n">
-        <v>303.27</v>
+        <v>303.62</v>
       </c>
       <c r="I25" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -12323,10 +12323,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6538</v>
+        <v>0.6535</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4392</v>
+        <v>0.4394</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>2010</v>
       </c>
       <c r="H26" t="n">
-        <v>205.34</v>
+        <v>205.82</v>
       </c>
       <c r="I26" t="n">
-        <v>9.789999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>0.6115</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4086</v>
+        <v>0.4085</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -12384,10 +12384,10 @@
         <v>1980</v>
       </c>
       <c r="H27" t="n">
-        <v>675.01</v>
+        <v>673.1799999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -12415,25 +12415,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6994</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4869</v>
+        <v>0.487</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G28" t="n">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="H28" t="n">
-        <v>220.14</v>
+        <v>220.54</v>
       </c>
       <c r="I28" t="n">
-        <v>8.949999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>bullish trend, potentially oversold</t>
+          <t>bullish trend</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.668</v>
+        <v>0.6681</v>
       </c>
       <c r="D29" t="n">
         <v>0.4871</v>
@@ -12476,10 +12476,10 @@
         <v>1880</v>
       </c>
       <c r="H29" t="n">
-        <v>384.07</v>
+        <v>383.92</v>
       </c>
       <c r="I29" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6504</v>
+        <v>0.6501</v>
       </c>
       <c r="D30" t="n">
         <v>0.4868</v>
@@ -12522,10 +12522,10 @@
         <v>1830</v>
       </c>
       <c r="H30" t="n">
-        <v>37.24</v>
+        <v>37.28</v>
       </c>
       <c r="I30" t="n">
-        <v>49.14</v>
+        <v>49.09</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6378</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5053</v>
+        <v>0.5051</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -12568,10 +12568,10 @@
         <v>1730</v>
       </c>
       <c r="H31" t="n">
-        <v>318.43</v>
+        <v>317.14</v>
       </c>
       <c r="I31" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.6655</v>
+        <v>0.666</v>
       </c>
       <c r="D32" t="n">
         <v>0.5348000000000001</v>
@@ -12614,10 +12614,10 @@
         <v>1700</v>
       </c>
       <c r="H32" t="n">
-        <v>121.6</v>
+        <v>120.99</v>
       </c>
       <c r="I32" t="n">
-        <v>13.98</v>
+        <v>14.05</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -12645,25 +12645,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.6493</v>
+        <v>0.6495</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5414</v>
+        <v>0.5406</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G33" t="n">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="H33" t="n">
-        <v>886.34</v>
+        <v>884.04</v>
       </c>
       <c r="I33" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -12691,10 +12691,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.6232</v>
+        <v>0.6233</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5407</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -12706,10 +12706,10 @@
         <v>1570</v>
       </c>
       <c r="H34" t="n">
-        <v>225.25</v>
+        <v>224.52</v>
       </c>
       <c r="I34" t="n">
-        <v>6.97</v>
+        <v>6.99</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -12737,10 +12737,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.6712</v>
+        <v>0.6713</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5934</v>
+        <v>0.5933</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -12752,10 +12752,10 @@
         <v>1500</v>
       </c>
       <c r="H35" t="n">
-        <v>54.45</v>
+        <v>54.4</v>
       </c>
       <c r="I35" t="n">
-        <v>27.55</v>
+        <v>27.57</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -12783,25 +12783,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.6774</v>
+        <v>0.6794</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2382</v>
+        <v>0.2384</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3476</v>
+        <v>0.3462</v>
       </c>
       <c r="F36" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G36" t="n">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="H36" t="n">
-        <v>264.12</v>
+        <v>262.86</v>
       </c>
       <c r="I36" t="n">
-        <v>5.49</v>
+        <v>5.55</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -12829,10 +12829,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.4486</v>
+        <v>0.4481</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3413</v>
+        <v>0.3414</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -12844,10 +12844,10 @@
         <v>1420</v>
       </c>
       <c r="H37" t="n">
-        <v>431.21</v>
+        <v>432.65</v>
       </c>
       <c r="I37" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4301</v>
+        <v>0.4308</v>
       </c>
       <c r="D38" t="n">
         <v>0.3286</v>
@@ -12884,16 +12884,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G38" t="n">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="H38" t="n">
-        <v>610.92</v>
+        <v>610.21</v>
       </c>
       <c r="I38" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.6682</v>
+        <v>0.6685</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6506</v>
+        <v>0.6503</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -12936,7 +12936,7 @@
         <v>1280</v>
       </c>
       <c r="H39" t="n">
-        <v>1599.55</v>
+        <v>1594.06</v>
       </c>
       <c r="I39" t="n">
         <v>0.8</v>
@@ -12982,7 +12982,7 @@
         <v>960</v>
       </c>
       <c r="H40" t="n">
-        <v>216.7</v>
+        <v>216.59</v>
       </c>
       <c r="I40" t="n">
         <v>4.43</v>
@@ -13013,10 +13013,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.6357</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7356</v>
+        <v>0.7352</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -13028,10 +13028,10 @@
         <v>920</v>
       </c>
       <c r="H41" t="n">
-        <v>320</v>
+        <v>315.35</v>
       </c>
       <c r="I41" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.4714</v>
+        <v>0.4719</v>
       </c>
       <c r="D42" t="n">
         <v>0.6026</v>
@@ -13074,10 +13074,10 @@
         <v>900</v>
       </c>
       <c r="H42" t="n">
-        <v>74.31999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>12.11</v>
+        <v>12.14</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.4066</v>
+        <v>0.4065</v>
       </c>
       <c r="D43" t="n">
         <v>0.3063</v>
@@ -13151,10 +13151,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.6491</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7678</v>
+        <v>0.7679</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>830</v>
       </c>
       <c r="H44" t="n">
-        <v>16.91</v>
+        <v>16.85</v>
       </c>
       <c r="I44" t="n">
-        <v>49.08</v>
+        <v>49.26</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4055</v>
+        <v>0.4061</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3714</v>
+        <v>0.3715</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -13212,10 +13212,10 @@
         <v>800</v>
       </c>
       <c r="H45" t="n">
-        <v>242.6</v>
+        <v>241.96</v>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
@@ -13243,10 +13243,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.6597</v>
+        <v>0.6594</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7839</v>
+        <v>0.7837</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -13258,10 +13258,10 @@
         <v>780</v>
       </c>
       <c r="H46" t="n">
-        <v>110.5</v>
+        <v>110.87</v>
       </c>
       <c r="I46" t="n">
-        <v>7.06</v>
+        <v>7.04</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -13289,25 +13289,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.7966</v>
+        <v>0.7958</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8847</v>
+        <v>0.884</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G47" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>12.17</v>
       </c>
       <c r="I47" t="n">
-        <v>53.33</v>
+        <v>53.41</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -13335,25 +13335,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.4049</v>
+        <v>0.4038</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5306</v>
+        <v>0.5236</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="G48" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="H48" t="n">
-        <v>47.74</v>
+        <v>2.95</v>
       </c>
       <c r="I48" t="n">
-        <v>12.57</v>
+        <v>206.78</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.4004</v>
+        <v>0.4052</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5234</v>
+        <v>0.5305</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -13396,10 +13396,10 @@
         <v>600</v>
       </c>
       <c r="H49" t="n">
-        <v>3.02</v>
+        <v>47.71</v>
       </c>
       <c r="I49" t="n">
-        <v>198.68</v>
+        <v>12.58</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.3976</v>
+        <v>0.3985</v>
       </c>
       <c r="D50" t="n">
         <v>0.2222</v>
@@ -13442,7 +13442,7 @@
         <v>240</v>
       </c>
       <c r="H50" t="n">
-        <v>90</v>
+        <v>89.78</v>
       </c>
       <c r="I50" t="n">
         <v>2.67</v>
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.3727</v>
+        <v>0.3755</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2841</v>
+        <v>0.2842</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -13488,10 +13488,10 @@
         <v>210</v>
       </c>
       <c r="H51" t="n">
-        <v>416.21</v>
+        <v>414.27</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.3616</v>
+        <v>0.3618</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2973</v>
+        <v>0.2972</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>200</v>
       </c>
       <c r="H52" t="n">
-        <v>77.48999999999999</v>
+        <v>77.44</v>
       </c>
       <c r="I52" t="n">
         <v>2.58</v>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.347</v>
+        <v>0.3469</v>
       </c>
       <c r="D53" t="n">
         <v>0.3113</v>
@@ -13580,7 +13580,7 @@
         <v>190</v>
       </c>
       <c r="H53" t="n">
-        <v>379.93</v>
+        <v>380</v>
       </c>
       <c r="I53" t="n">
         <v>0.5</v>
@@ -13611,10 +13611,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.3697</v>
+        <v>0.3707</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3503</v>
+        <v>0.3505</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -13626,10 +13626,10 @@
         <v>190</v>
       </c>
       <c r="H54" t="n">
-        <v>81.79000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="I54" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.3945</v>
+        <v>0.3949</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4313</v>
+        <v>0.4311</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -13672,7 +13672,7 @@
         <v>180</v>
       </c>
       <c r="H55" t="n">
-        <v>305.24</v>
+        <v>304.61</v>
       </c>
       <c r="I55" t="n">
         <v>0.59</v>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.3752</v>
+        <v>0.375</v>
       </c>
       <c r="D56" t="n">
         <v>0.3769</v>
@@ -13718,7 +13718,7 @@
         <v>180</v>
       </c>
       <c r="H56" t="n">
-        <v>41</v>
+        <v>41.02</v>
       </c>
       <c r="I56" t="n">
         <v>4.39</v>
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.357</v>
+        <v>0.3572</v>
       </c>
       <c r="D57" t="n">
         <v>0.3654</v>
@@ -13764,7 +13764,7 @@
         <v>180</v>
       </c>
       <c r="H57" t="n">
-        <v>250.88</v>
+        <v>250.75</v>
       </c>
       <c r="I57" t="n">
         <v>0.72</v>
@@ -13795,10 +13795,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.3405</v>
+        <v>0.3416</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3524</v>
+        <v>0.3523</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -13810,7 +13810,7 @@
         <v>170</v>
       </c>
       <c r="H58" t="n">
-        <v>534.66</v>
+        <v>532.6900000000001</v>
       </c>
       <c r="I58" t="n">
         <v>0.32</v>
@@ -13841,7 +13841,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.3455</v>
+        <v>0.3458</v>
       </c>
       <c r="D59" t="n">
         <v>0.4031</v>
@@ -13856,10 +13856,10 @@
         <v>160</v>
       </c>
       <c r="H59" t="n">
-        <v>18.58</v>
+        <v>18.57</v>
       </c>
       <c r="I59" t="n">
-        <v>8.609999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.323</v>
+        <v>0.3246</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3511</v>
+        <v>0.3513</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -13902,7 +13902,7 @@
         <v>160</v>
       </c>
       <c r="H60" t="n">
-        <v>258.35</v>
+        <v>257.17</v>
       </c>
       <c r="I60" t="n">
         <v>0.62</v>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.395</v>
+        <v>0.3956</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4918</v>
+        <v>0.492</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -13948,7 +13948,7 @@
         <v>160</v>
       </c>
       <c r="H61" t="n">
-        <v>125.18</v>
+        <v>124.7</v>
       </c>
       <c r="I61" t="n">
         <v>1.28</v>
@@ -13979,7 +13979,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.3641</v>
+        <v>0.3648</v>
       </c>
       <c r="D62" t="n">
         <v>0.4651</v>
@@ -13994,10 +13994,10 @@
         <v>160</v>
       </c>
       <c r="H62" t="n">
-        <v>192.01</v>
+        <v>191.53</v>
       </c>
       <c r="I62" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.3348</v>
+        <v>0.3346</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4744</v>
+        <v>0.475</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -14040,7 +14040,7 @@
         <v>140</v>
       </c>
       <c r="H63" t="n">
-        <v>94.13</v>
+        <v>94.23</v>
       </c>
       <c r="I63" t="n">
         <v>1.49</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.3925</v>
+        <v>0.3929</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5417</v>
+        <v>0.5416</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -14086,10 +14086,10 @@
         <v>140</v>
       </c>
       <c r="H64" t="n">
-        <v>23.35</v>
+        <v>23.31</v>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="D65" t="n">
         <v>0.5</v>
@@ -14132,7 +14132,7 @@
         <v>140</v>
       </c>
       <c r="H65" t="n">
-        <v>102.48</v>
+        <v>102.24</v>
       </c>
       <c r="I65" t="n">
         <v>1.37</v>
@@ -14163,10 +14163,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.3685</v>
+        <v>0.3693</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5538</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
         <v>130</v>
       </c>
       <c r="H66" t="n">
-        <v>101.81</v>
+        <v>101.49</v>
       </c>
       <c r="I66" t="n">
         <v>1.28</v>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.3737</v>
+        <v>0.3751</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6017</v>
+        <v>0.6012</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14224,10 +14224,10 @@
         <v>120</v>
       </c>
       <c r="H67" t="n">
-        <v>11.37</v>
+        <v>11.27</v>
       </c>
       <c r="I67" t="n">
-        <v>10.55</v>
+        <v>10.65</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.3352</v>
+        <v>0.3351</v>
       </c>
       <c r="D68" t="n">
         <v>0.5502</v>
@@ -14270,7 +14270,7 @@
         <v>120</v>
       </c>
       <c r="H68" t="n">
-        <v>189.34</v>
+        <v>189.49</v>
       </c>
       <c r="I68" t="n">
         <v>0.63</v>
@@ -14301,10 +14301,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.3945</v>
+        <v>0.3953</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6035</v>
+        <v>0.6036</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -14316,10 +14316,10 @@
         <v>120</v>
       </c>
       <c r="H69" t="n">
-        <v>53.55</v>
+        <v>53.19</v>
       </c>
       <c r="I69" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -14347,10 +14347,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.37</v>
+        <v>0.3693</v>
       </c>
       <c r="D70" t="n">
-        <v>0.587</v>
+        <v>0.5873</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14362,10 +14362,10 @@
         <v>120</v>
       </c>
       <c r="H70" t="n">
-        <v>9.68</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.3312</v>
+        <v>0.3314</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5682</v>
+        <v>0.5681</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -14408,10 +14408,10 @@
         <v>110</v>
       </c>
       <c r="H71" t="n">
-        <v>178.99</v>
+        <v>178.66</v>
       </c>
       <c r="I71" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.3933</v>
+        <v>0.3928</v>
       </c>
       <c r="D72" t="n">
         <v>0.644</v>
@@ -14454,10 +14454,10 @@
         <v>110</v>
       </c>
       <c r="H72" t="n">
-        <v>8.300000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="I72" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -14485,10 +14485,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.3604</v>
+        <v>0.3585</v>
       </c>
       <c r="D73" t="n">
-        <v>0.602</v>
+        <v>0.6014</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14500,10 +14500,10 @@
         <v>110</v>
       </c>
       <c r="H73" t="n">
-        <v>307.89</v>
+        <v>310.3</v>
       </c>
       <c r="I73" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3701</v>
+        <v>0.371</v>
       </c>
       <c r="D74" t="n">
-        <v>0.6427</v>
+        <v>0.6417</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -14546,10 +14546,10 @@
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
       <c r="I74" t="n">
-        <v>13.79</v>
+        <v>13.93</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14577,10 +14577,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.3684</v>
+        <v>0.3688</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6531</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -14592,10 +14592,10 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>512.84</v>
+        <v>511.09</v>
       </c>
       <c r="I75" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.348</v>
+        <v>0.3465</v>
       </c>
       <c r="D76" t="n">
-        <v>0.6567</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14638,10 +14638,10 @@
         <v>90</v>
       </c>
       <c r="H76" t="n">
-        <v>36.96</v>
+        <v>37.66</v>
       </c>
       <c r="I76" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -14669,10 +14669,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.3702</v>
+        <v>0.3714</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6869</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>90</v>
       </c>
       <c r="H77" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="I77" t="n">
-        <v>21.33</v>
+        <v>21.48</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.6866</v>
+        <v>0.6871</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9813</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -14730,10 +14730,10 @@
         <v>70</v>
       </c>
       <c r="H78" t="n">
-        <v>182.04</v>
+        <v>180.82</v>
       </c>
       <c r="I78" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.35</v>
+        <v>0.3497</v>
       </c>
       <c r="D79" t="n">
         <v>0.754</v>
@@ -14776,7 +14776,7 @@
         <v>70</v>
       </c>
       <c r="H79" t="n">
-        <v>63.66</v>
+        <v>63.91</v>
       </c>
       <c r="I79" t="n">
         <v>1.1</v>
@@ -14807,10 +14807,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.3696</v>
+        <v>0.3699</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8041</v>
+        <v>0.8037</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -14822,10 +14822,10 @@
         <v>60</v>
       </c>
       <c r="H80" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="I80" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48090</v>
+        <v>47800</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34660</v>
+        <v>34520</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15850</v>
+        <v>16270</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4072.35</v>
+        <v>4067.1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.5</v>
+        <v>49.22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>2851.8</v>
       </c>
       <c r="C3" t="n">
-        <v>34.67</v>
+        <v>34.51</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1302</v>
+        <v>1344</v>
       </c>
       <c r="C4" t="n">
-        <v>15.83</v>
+        <v>16.27</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>1302</v>
+        <v>1344</v>
       </c>
       <c r="E2" t="n">
-        <v>749</v>
+        <v>791</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0205</v>
+        <v>1.0195</v>
       </c>
     </row>
     <row r="3">
@@ -1347,7 +1347,7 @@
         <v>2401.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8078</v>
+        <v>0.8077</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="D4" t="n">
-        <v>846.2</v>
+        <v>804.2</v>
       </c>
       <c r="E4" t="n">
-        <v>452.23</v>
+        <v>429.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4537</v>
+        <v>0.4541</v>
       </c>
     </row>
     <row r="5">
@@ -1389,13 +1389,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>1302</v>
+        <v>1344</v>
       </c>
       <c r="E5" t="n">
-        <v>749</v>
+        <v>791</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9762</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="6">
@@ -1419,7 +1419,7 @@
         <v>2401.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9023</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="7">
@@ -1434,16 +1434,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="D7" t="n">
-        <v>846.2</v>
+        <v>804.2</v>
       </c>
       <c r="E7" t="n">
-        <v>452.23</v>
+        <v>429.3</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4537</v>
+        <v>0.4541</v>
       </c>
     </row>
     <row r="8">
@@ -1461,13 +1461,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>1302</v>
+        <v>1344</v>
       </c>
       <c r="E8" t="n">
-        <v>749</v>
+        <v>791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6195000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1491,7 +1491,7 @@
         <v>2401.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7261</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="10">
@@ -1506,16 +1506,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="D10" t="n">
-        <v>846.2</v>
+        <v>804.2</v>
       </c>
       <c r="E10" t="n">
-        <v>452.23</v>
+        <v>429.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8537</v>
+        <v>0.8541</v>
       </c>
     </row>
   </sheetData>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48090</v>
+        <v>47800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34660</v>
+        <v>34520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15850</v>
+        <v>16270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3290</v>
+        <v>3310</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3140</v>
+        <v>3150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3080</v>
+        <v>3090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2860</v>
+        <v>2880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2840</v>
+        <v>2860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2840</v>
+        <v>2850</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13.02</v>
+        <v>13.44</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -2721,19 +2721,19 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>13.02</v>
+        <v>13.44</v>
       </c>
       <c r="L3" t="n">
-        <v>1302</v>
+        <v>1344</v>
       </c>
       <c r="M3" t="n">
         <v>553</v>
       </c>
       <c r="N3" t="n">
-        <v>749</v>
+        <v>791</v>
       </c>
       <c r="O3" t="n">
-        <v>135.44</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="4">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>633.37</v>
+        <v>634.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>212.83</v>
+        <v>212.73</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>440.23</v>
+        <v>440.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2925,19 +2925,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>271.49</v>
+        <v>271.14</v>
       </c>
       <c r="L7" t="n">
-        <v>4072.35</v>
+        <v>4067.1</v>
       </c>
       <c r="M7" t="n">
         <v>1896</v>
       </c>
       <c r="N7" t="n">
-        <v>2176.35</v>
+        <v>2171.1</v>
       </c>
       <c r="O7" t="n">
-        <v>114.79</v>
+        <v>114.51</v>
       </c>
     </row>
     <row r="8">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>386.83</v>
+        <v>386.29</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>133.07</v>
+        <v>133.29</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -3206,16 +3206,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103.18</v>
+        <v>103.99</v>
       </c>
       <c r="C2" t="n">
-        <v>102.71</v>
+        <v>102.73</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>100.01</v>
       </c>
       <c r="E2" t="n">
-        <v>23.3</v>
+        <v>23.59</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -3224,13 +3224,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8835</v>
+        <v>0.882</v>
       </c>
       <c r="I2" t="n">
-        <v>0.767</v>
+        <v>0.7641</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8499</v>
+        <v>0.8495</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>212.8</v>
+        <v>212.61</v>
       </c>
       <c r="C3" t="n">
         <v>198.09</v>
@@ -3279,7 +3279,7 @@
         <v>187.34</v>
       </c>
       <c r="E3" t="n">
-        <v>54.39</v>
+        <v>54.21</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -3288,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4561</v>
+        <v>0.4579</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8223</v>
+        <v>0.8226</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>496.72</v>
+        <v>496.75</v>
       </c>
       <c r="C4" t="n">
         <v>315.4</v>
@@ -3343,7 +3343,7 @@
         <v>234.15</v>
       </c>
       <c r="E4" t="n">
-        <v>67.65000000000001</v>
+        <v>67.66</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3355,7 +3355,7 @@
         <v>0.6617</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3235</v>
+        <v>0.3234</v>
       </c>
       <c r="J4" t="n">
         <v>0.8014</v>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.43</v>
+        <v>11.58</v>
       </c>
       <c r="C5" t="n">
         <v>11.52</v>
@@ -3407,7 +3407,7 @@
         <v>5.91</v>
       </c>
       <c r="E5" t="n">
-        <v>37.39</v>
+        <v>37.75</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3416,13 +3416,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8131</v>
+        <v>0.8112</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6261</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7936</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>15.85</v>
+        <v>16.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8415</v>
+        <v>0.837</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.05</v>
+        <v>13.47</v>
       </c>
       <c r="C6" t="n">
-        <v>9.23</v>
+        <v>9.24</v>
       </c>
       <c r="D6" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="E6" t="n">
-        <v>57.39</v>
+        <v>58.4</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -3480,13 +3480,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.713</v>
+        <v>0.708</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4261</v>
+        <v>0.416</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7587</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>15.85</v>
+        <v>16.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8415</v>
+        <v>0.837</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3526,16 +3526,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>212.09</v>
+        <v>211.44</v>
       </c>
       <c r="C7" t="n">
-        <v>208.24</v>
+        <v>208.23</v>
       </c>
       <c r="D7" t="n">
         <v>204.17</v>
       </c>
       <c r="E7" t="n">
-        <v>34.65</v>
+        <v>34.46</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -3544,13 +3544,13 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8268</v>
+        <v>0.8277</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6535</v>
+        <v>0.6554</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7074</v>
+        <v>0.708</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>321.3</v>
+        <v>320.92</v>
       </c>
       <c r="C8" t="n">
-        <v>305.46</v>
+        <v>305.45</v>
       </c>
       <c r="D8" t="n">
         <v>209.5</v>
       </c>
       <c r="E8" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -3608,13 +3608,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8195</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7022</v>
+        <v>0.7027</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -3654,16 +3654,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>386.97</v>
+        <v>386.14</v>
       </c>
       <c r="C9" t="n">
-        <v>342.16</v>
+        <v>342.14</v>
       </c>
       <c r="D9" t="n">
         <v>297.66</v>
       </c>
       <c r="E9" t="n">
-        <v>42.91</v>
+        <v>42.07</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -3672,13 +3672,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7854</v>
+        <v>0.7896</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5709</v>
+        <v>0.5793</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6928</v>
+        <v>0.6943</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183.24</v>
+        <v>182.79</v>
       </c>
       <c r="C10" t="n">
-        <v>153.93</v>
+        <v>153.92</v>
       </c>
       <c r="D10" t="n">
         <v>127.42</v>
       </c>
       <c r="E10" t="n">
-        <v>42.28</v>
+        <v>41.92</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -3736,13 +3736,13 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7886</v>
+        <v>0.7904</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5772</v>
+        <v>0.5808</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6927</v>
+        <v>0.6935</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -3782,16 +3782,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>405.14</v>
+        <v>405.41</v>
       </c>
       <c r="C11" t="n">
-        <v>391.15</v>
+        <v>391.16</v>
       </c>
       <c r="D11" t="n">
         <v>362.56</v>
       </c>
       <c r="E11" t="n">
-        <v>44.48</v>
+        <v>44.59</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -3800,13 +3800,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7776</v>
+        <v>0.777</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5552</v>
+        <v>0.5541</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6889</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -3842,20 +3842,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>185.14</v>
+        <v>81.83</v>
       </c>
       <c r="C12" t="n">
-        <v>145.11</v>
+        <v>77.59</v>
       </c>
       <c r="D12" t="n">
-        <v>64.56</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>51.74</v>
+        <v>66.75</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -3864,13 +3864,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7413</v>
+        <v>0.6662</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4826</v>
+        <v>0.3325</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6847</v>
+        <v>0.6849</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -3900,26 +3900,26 @@
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0.429</v>
+        <v>0.5787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>81.93000000000001</v>
+        <v>186.77</v>
       </c>
       <c r="C13" t="n">
-        <v>77.59</v>
+        <v>145.14</v>
       </c>
       <c r="D13" t="n">
-        <v>72.27</v>
+        <v>64.56</v>
       </c>
       <c r="E13" t="n">
-        <v>67.2</v>
+        <v>52.16</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -3928,13 +3928,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.664</v>
+        <v>0.7392</v>
       </c>
       <c r="I13" t="n">
-        <v>0.328</v>
+        <v>0.4784</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6844</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5787</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="14">
@@ -3974,16 +3974,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373.43</v>
+        <v>376.49</v>
       </c>
       <c r="C14" t="n">
-        <v>345.34</v>
+        <v>345.4</v>
       </c>
       <c r="D14" t="n">
-        <v>231</v>
+        <v>231.02</v>
       </c>
       <c r="E14" t="n">
-        <v>47.53</v>
+        <v>48.35</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -3992,13 +3992,13 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7624</v>
+        <v>0.7582</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5165</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6827</v>
+        <v>0.6817</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>456.19</v>
+        <v>455.8</v>
       </c>
       <c r="C15" t="n">
-        <v>403.6</v>
+        <v>403.59</v>
       </c>
       <c r="D15" t="n">
         <v>381.7</v>
       </c>
       <c r="E15" t="n">
-        <v>49.02</v>
+        <v>48.8</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -4056,13 +4056,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7549</v>
+        <v>0.756</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5098</v>
+        <v>0.512</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6795</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -4102,16 +4102,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53.88</v>
+        <v>53.66</v>
       </c>
       <c r="C16" t="n">
-        <v>46.44</v>
+        <v>46.43</v>
       </c>
       <c r="D16" t="n">
         <v>32.83</v>
       </c>
       <c r="E16" t="n">
-        <v>53.57</v>
+        <v>53.11</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -4120,13 +4120,13 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7322</v>
+        <v>0.7345</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4643</v>
+        <v>0.4689</v>
       </c>
       <c r="J16" t="n">
-        <v>0.676</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -4166,16 +4166,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>422.82</v>
+        <v>423.63</v>
       </c>
       <c r="C17" t="n">
-        <v>380.94</v>
+        <v>380.96</v>
       </c>
       <c r="D17" t="n">
-        <v>350.09</v>
+        <v>350.1</v>
       </c>
       <c r="E17" t="n">
-        <v>48.85</v>
+        <v>49.21</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -4184,13 +4184,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7558</v>
+        <v>0.754</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5115</v>
+        <v>0.5079</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6751</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -4230,16 +4230,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119.99</v>
+        <v>120.8</v>
       </c>
       <c r="C18" t="n">
-        <v>79.48</v>
+        <v>79.5</v>
       </c>
       <c r="D18" t="n">
-        <v>48.19</v>
+        <v>48.2</v>
       </c>
       <c r="E18" t="n">
-        <v>55.43</v>
+        <v>56.14</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -4248,13 +4248,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7228</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4457</v>
+        <v>0.4386</v>
       </c>
       <c r="J18" t="n">
-        <v>0.673</v>
+        <v>0.6722</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -4294,16 +4294,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>423.5</v>
+        <v>424.79</v>
       </c>
       <c r="C19" t="n">
-        <v>376.26</v>
+        <v>376.28</v>
       </c>
       <c r="D19" t="n">
-        <v>318.55</v>
+        <v>318.56</v>
       </c>
       <c r="E19" t="n">
-        <v>51.92</v>
+        <v>52.51</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -4312,13 +4312,13 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4808</v>
+        <v>0.4749</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6713</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -4354,20 +4354,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1580.37</v>
+        <v>104.06</v>
       </c>
       <c r="C20" t="n">
-        <v>1041.16</v>
+        <v>73.94</v>
       </c>
       <c r="D20" t="n">
-        <v>471.96</v>
+        <v>38.55</v>
       </c>
       <c r="E20" t="n">
-        <v>58.83</v>
+        <v>53.81</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -4376,13 +4376,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7059</v>
+        <v>0.731</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4117</v>
+        <v>0.4619</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6693</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4412,26 +4412,26 @@
         <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4011</v>
+        <v>0.3449</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>103.42</v>
+        <v>1593.2</v>
       </c>
       <c r="C21" t="n">
-        <v>73.92</v>
+        <v>1041.42</v>
       </c>
       <c r="D21" t="n">
-        <v>38.55</v>
+        <v>472.03</v>
       </c>
       <c r="E21" t="n">
-        <v>53.46</v>
+        <v>59.55</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -4440,13 +4440,13 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7327</v>
+        <v>0.7022</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4654</v>
+        <v>0.4045</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6695</v>
+        <v>0.6691</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -4476,26 +4476,26 @@
         <v>0.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3449</v>
+        <v>0.4011</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>219.19</v>
+        <v>1604.22</v>
       </c>
       <c r="C22" t="n">
-        <v>153.96</v>
+        <v>1444.62</v>
       </c>
       <c r="D22" t="n">
-        <v>144.15</v>
+        <v>1182.98</v>
       </c>
       <c r="E22" t="n">
-        <v>56.8</v>
+        <v>55.26</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -4504,13 +4504,13 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.716</v>
+        <v>0.7237</v>
       </c>
       <c r="I22" t="n">
-        <v>0.432</v>
+        <v>0.4474</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6686</v>
+        <v>0.6681</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4540,26 +4540,26 @@
         <v>0.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3725</v>
+        <v>0.3518</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1601.69</v>
+        <v>221.38</v>
       </c>
       <c r="C23" t="n">
-        <v>1444.57</v>
+        <v>154.01</v>
       </c>
       <c r="D23" t="n">
-        <v>1182.97</v>
+        <v>144.16</v>
       </c>
       <c r="E23" t="n">
-        <v>55.01</v>
+        <v>57.62</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -4568,13 +4568,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.725</v>
+        <v>0.7119</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4499</v>
+        <v>0.4238</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6682</v>
+        <v>0.6677</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3518</v>
+        <v>0.3725</v>
       </c>
     </row>
     <row r="24">
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>271.07</v>
+        <v>271.09</v>
       </c>
       <c r="C24" t="n">
         <v>244.26</v>
@@ -4623,7 +4623,7 @@
         <v>231.01</v>
       </c>
       <c r="E24" t="n">
-        <v>45.81</v>
+        <v>45.84</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -4632,13 +4632,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.771</v>
+        <v>0.7708</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5419</v>
+        <v>0.5416</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6669</v>
+        <v>0.6673</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>49.46</v>
+        <v>49.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5054</v>
+        <v>0.508</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>155.11</v>
+        <v>154.95</v>
       </c>
       <c r="C25" t="n">
         <v>147.95</v>
@@ -4687,7 +4687,7 @@
         <v>139.97</v>
       </c>
       <c r="E25" t="n">
-        <v>57.52</v>
+        <v>57.35</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -4696,13 +4696,13 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7124</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4248</v>
+        <v>0.4265</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6666</v>
+        <v>0.6671</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4738,20 +4738,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1956.84</v>
+        <v>290.29</v>
       </c>
       <c r="C26" t="n">
-        <v>1712.65</v>
+        <v>268.31</v>
       </c>
       <c r="D26" t="n">
-        <v>1335.78</v>
+        <v>252.49</v>
       </c>
       <c r="E26" t="n">
-        <v>59.24</v>
+        <v>54.21</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -4760,13 +4760,13 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7038</v>
+        <v>0.729</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4076</v>
+        <v>0.4579</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6625</v>
+        <v>0.6621</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4796,26 +4796,26 @@
         <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3562</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>290.05</v>
+        <v>1963.46</v>
       </c>
       <c r="C27" t="n">
-        <v>268.3</v>
+        <v>1712.78</v>
       </c>
       <c r="D27" t="n">
-        <v>252.49</v>
+        <v>1335.81</v>
       </c>
       <c r="E27" t="n">
-        <v>53.9</v>
+        <v>59.75</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -4824,13 +4824,13 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7305</v>
+        <v>0.7012</v>
       </c>
       <c r="I27" t="n">
-        <v>0.461</v>
+        <v>0.4025</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6623</v>
+        <v>0.662</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3011</v>
+        <v>0.3562</v>
       </c>
     </row>
     <row r="28">
@@ -4870,16 +4870,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>201.6</v>
+        <v>200.83</v>
       </c>
       <c r="C28" t="n">
-        <v>142.09</v>
+        <v>142.08</v>
       </c>
       <c r="D28" t="n">
         <v>97.11</v>
       </c>
       <c r="E28" t="n">
-        <v>63.76</v>
+        <v>63.3</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -4888,13 +4888,13 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6812</v>
+        <v>0.6835</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3624</v>
+        <v>0.367</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6602</v>
+        <v>0.6612</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4934,16 +4934,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>125.14</v>
+        <v>124.41</v>
       </c>
       <c r="C29" t="n">
-        <v>86.52</v>
+        <v>86.5</v>
       </c>
       <c r="D29" t="n">
         <v>62.85</v>
       </c>
       <c r="E29" t="n">
-        <v>64.77</v>
+        <v>64.06</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -4952,13 +4952,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6762</v>
+        <v>0.6797</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3523</v>
+        <v>0.3594</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6601</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.67</v>
+        <v>17.85</v>
       </c>
       <c r="C30" t="n">
         <v>12.78</v>
@@ -5007,7 +5007,7 @@
         <v>9.66</v>
       </c>
       <c r="E30" t="n">
-        <v>69.91</v>
+        <v>70.36</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -5016,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6504</v>
+        <v>0.6482</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3009</v>
+        <v>0.2964</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6534</v>
+        <v>0.653</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>304.3</v>
+        <v>304.36</v>
       </c>
       <c r="C31" t="n">
         <v>189.81</v>
@@ -5071,7 +5071,7 @@
         <v>148.82</v>
       </c>
       <c r="E31" t="n">
-        <v>66.90000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -5080,13 +5080,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6655</v>
+        <v>0.6654</v>
       </c>
       <c r="I31" t="n">
-        <v>0.331</v>
+        <v>0.3308</v>
       </c>
       <c r="J31" t="n">
-        <v>0.652</v>
+        <v>0.6522</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -5122,20 +5122,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SKYT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>37.79</v>
+        <v>309.37</v>
       </c>
       <c r="C32" t="n">
-        <v>31.67</v>
+        <v>206.96</v>
       </c>
       <c r="D32" t="n">
-        <v>23.17</v>
+        <v>151.16</v>
       </c>
       <c r="E32" t="n">
-        <v>67.36</v>
+        <v>72.63</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -5144,13 +5144,13 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6632</v>
+        <v>0.6368</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3264</v>
+        <v>0.2737</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6514</v>
+        <v>0.6508</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -5180,26 +5180,26 @@
         <v>0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3631</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SKYT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>308.48</v>
+        <v>38.1</v>
       </c>
       <c r="C33" t="n">
-        <v>206.95</v>
+        <v>31.68</v>
       </c>
       <c r="D33" t="n">
-        <v>151.16</v>
+        <v>23.17</v>
       </c>
       <c r="E33" t="n">
-        <v>72.47</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -5208,13 +5208,13 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6377</v>
+        <v>0.6586</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2753</v>
+        <v>0.3171</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6508</v>
+        <v>0.6503</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>0.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0.41</v>
+        <v>0.3631</v>
       </c>
     </row>
     <row r="34">
@@ -5254,16 +5254,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>594.4</v>
+        <v>595.78</v>
       </c>
       <c r="C34" t="n">
-        <v>476.54</v>
+        <v>476.57</v>
       </c>
       <c r="D34" t="n">
-        <v>385.24</v>
+        <v>385.25</v>
       </c>
       <c r="E34" t="n">
-        <v>62.52</v>
+        <v>63.01</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -5272,13 +5272,13 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6874</v>
+        <v>0.6849</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3748</v>
+        <v>0.3699</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6504</v>
+        <v>0.6499</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -5318,16 +5318,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>562.28</v>
+        <v>563.5700000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>428.4</v>
+        <v>428.42</v>
       </c>
       <c r="D35" t="n">
         <v>332.66</v>
       </c>
       <c r="E35" t="n">
-        <v>63.72</v>
+        <v>64.13</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -5336,13 +5336,13 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6814</v>
+        <v>0.6794</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3628</v>
+        <v>0.3587</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6496</v>
+        <v>0.6493</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -5382,16 +5382,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>926.9400000000001</v>
+        <v>925</v>
       </c>
       <c r="C36" t="n">
-        <v>538.08</v>
+        <v>538.04</v>
       </c>
       <c r="D36" t="n">
-        <v>330.37</v>
+        <v>330.36</v>
       </c>
       <c r="E36" t="n">
-        <v>70.86</v>
+        <v>70.77</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -5400,13 +5400,13 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.6462</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2914</v>
+        <v>0.2923</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6486</v>
+        <v>0.649</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>750.83</v>
+        <v>750.65</v>
       </c>
       <c r="C37" t="n">
         <v>699.97</v>
@@ -5455,7 +5455,7 @@
         <v>677.46</v>
       </c>
       <c r="E37" t="n">
-        <v>66.15000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -5464,13 +5464,13 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6692</v>
+        <v>0.6698</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3385</v>
+        <v>0.3396</v>
       </c>
       <c r="J37" t="n">
-        <v>0.642</v>
+        <v>0.6424</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>729.5700000000001</v>
+        <v>729.8</v>
       </c>
       <c r="C38" t="n">
         <v>647.36</v>
@@ -5519,7 +5519,7 @@
         <v>615.2</v>
       </c>
       <c r="E38" t="n">
-        <v>69.77</v>
+        <v>69.95</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -5528,10 +5528,10 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6512</v>
+        <v>0.6502</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3023</v>
+        <v>0.3005</v>
       </c>
       <c r="J38" t="n">
         <v>0.6357</v>
@@ -5547,10 +5547,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>320.91</v>
+        <v>321.43</v>
       </c>
       <c r="C39" t="n">
-        <v>181.57</v>
+        <v>181.58</v>
       </c>
       <c r="D39" t="n">
         <v>172.21</v>
       </c>
       <c r="E39" t="n">
-        <v>79.14</v>
+        <v>79.2</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -5592,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.604</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2086</v>
+        <v>0.208</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6345</v>
+        <v>0.6347</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>119.68</v>
+        <v>119.98</v>
       </c>
       <c r="C40" t="n">
         <v>91.41</v>
       </c>
       <c r="D40" t="n">
-        <v>77.77</v>
+        <v>77.78</v>
       </c>
       <c r="E40" t="n">
-        <v>83.98</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -5656,13 +5656,13 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5795</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1602</v>
+        <v>0.159</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6337</v>
+        <v>0.6338</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5702,16 +5702,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>127.97</v>
+        <v>128.33</v>
       </c>
       <c r="C41" t="n">
         <v>94.13</v>
       </c>
       <c r="D41" t="n">
-        <v>84.65000000000001</v>
+        <v>84.66</v>
       </c>
       <c r="E41" t="n">
-        <v>85.06</v>
+        <v>85.63</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -5720,13 +5720,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5747</v>
+        <v>0.5718</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1494</v>
+        <v>0.1437</v>
       </c>
       <c r="J41" t="n">
-        <v>0.633</v>
+        <v>0.6324</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>310.41</v>
+        <v>309.85</v>
       </c>
       <c r="C42" t="n">
-        <v>272.68</v>
+        <v>272.67</v>
       </c>
       <c r="D42" t="n">
         <v>261.94</v>
       </c>
       <c r="E42" t="n">
-        <v>87.20999999999999</v>
+        <v>86.98</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -5784,13 +5784,13 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5639</v>
+        <v>0.5651</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1279</v>
+        <v>0.1302</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6292</v>
+        <v>0.6299</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5826,20 +5826,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>220.75</v>
+        <v>645.47</v>
       </c>
       <c r="C43" t="n">
-        <v>148.83</v>
+        <v>471.86</v>
       </c>
       <c r="D43" t="n">
-        <v>142.8</v>
+        <v>467.54</v>
       </c>
       <c r="E43" t="n">
-        <v>89.16</v>
+        <v>87.39</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -5848,13 +5848,13 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5542</v>
+        <v>0.5631</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1084</v>
+        <v>0.1261</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6249</v>
+        <v>0.6226</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5884,26 +5884,26 @@
         <v>0.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0.4042</v>
+        <v>0.3692</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>648</v>
+        <v>223.27</v>
       </c>
       <c r="C44" t="n">
-        <v>471.91</v>
+        <v>148.88</v>
       </c>
       <c r="D44" t="n">
-        <v>467.56</v>
+        <v>142.81</v>
       </c>
       <c r="E44" t="n">
-        <v>88.33</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -5912,13 +5912,13 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5584</v>
+        <v>0.5424</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1167</v>
+        <v>0.0849</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6209</v>
+        <v>0.6216</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>0.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3692</v>
+        <v>0.4042</v>
       </c>
     </row>
     <row r="45">
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>76.39</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="C45" t="n">
         <v>76.25</v>
@@ -5967,7 +5967,7 @@
         <v>104.15</v>
       </c>
       <c r="E45" t="n">
-        <v>45.34</v>
+        <v>45.63</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -5976,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2733</v>
+        <v>0.2718</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5466</v>
+        <v>0.5437</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4717</v>
+        <v>0.4712</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6022,16 +6022,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>440.24</v>
+        <v>440.11</v>
       </c>
       <c r="C46" t="n">
-        <v>390.08</v>
+        <v>390.07</v>
       </c>
       <c r="D46" t="n">
         <v>411.14</v>
       </c>
       <c r="E46" t="n">
-        <v>64.13</v>
+        <v>64.09</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1794</v>
+        <v>0.1795</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3587</v>
+        <v>0.3591</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4489</v>
+        <v>0.449</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6086,16 +6086,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>633.25</v>
+        <v>634.09</v>
       </c>
       <c r="C47" t="n">
-        <v>617.9</v>
+        <v>617.92</v>
       </c>
       <c r="D47" t="n">
         <v>667.24</v>
       </c>
       <c r="E47" t="n">
-        <v>61.59</v>
+        <v>61.95</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -6104,13 +6104,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.192</v>
+        <v>0.1902</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3841</v>
+        <v>0.3805</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4193</v>
+        <v>0.4188</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6150,16 +6150,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>85.72</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>92.17</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="D48" t="n">
         <v>94.69</v>
       </c>
       <c r="E48" t="n">
-        <v>34.18</v>
+        <v>34.37</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -6168,10 +6168,10 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3291</v>
+        <v>0.3282</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6582</v>
+        <v>0.6563</v>
       </c>
       <c r="J48" t="n">
         <v>0.4111</v>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>46.73</v>
+        <v>46.84</v>
       </c>
       <c r="C49" t="n">
         <v>49.02</v>
@@ -6223,7 +6223,7 @@
         <v>66.16</v>
       </c>
       <c r="E49" t="n">
-        <v>26.48</v>
+        <v>27.03</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -6232,13 +6232,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3676</v>
+        <v>0.3648</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7352</v>
+        <v>0.7297</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4108</v>
+        <v>0.4102</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52.66</v>
+        <v>52.72</v>
       </c>
       <c r="C50" t="n">
         <v>54.56</v>
@@ -6287,7 +6287,7 @@
         <v>58.4</v>
       </c>
       <c r="E50" t="n">
-        <v>32.42</v>
+        <v>32.5</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -6296,13 +6296,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3379</v>
+        <v>0.3375</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6758</v>
+        <v>0.675</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4081</v>
+        <v>0.4082</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -6338,20 +6338,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>SGE.L</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>287.58</v>
+        <v>856</v>
       </c>
       <c r="C51" t="n">
-        <v>293.12</v>
+        <v>865.89</v>
       </c>
       <c r="D51" t="n">
-        <v>322.75</v>
+        <v>996.87</v>
       </c>
       <c r="E51" t="n">
-        <v>35.2</v>
+        <v>40.99</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -6360,13 +6360,13 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.324</v>
+        <v>0.295</v>
       </c>
       <c r="I51" t="n">
-        <v>0.648</v>
+        <v>0.5901</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4065</v>
+        <v>0.4061</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -6396,26 +6396,26 @@
         <v>0.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0.4091</v>
+        <v>0.4621</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SGE.L</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>856</v>
+        <v>289.77</v>
       </c>
       <c r="C52" t="n">
-        <v>865.89</v>
+        <v>293.17</v>
       </c>
       <c r="D52" t="n">
-        <v>996.87</v>
+        <v>322.76</v>
       </c>
       <c r="E52" t="n">
-        <v>40.99</v>
+        <v>35.87</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -6424,10 +6424,10 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.295</v>
+        <v>0.3206</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5901</v>
+        <v>0.6413</v>
       </c>
       <c r="J52" t="n">
         <v>0.4058</v>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>0.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4621</v>
+        <v>0.4091</v>
       </c>
     </row>
     <row r="53">
@@ -6479,7 +6479,7 @@
         <v>11.43</v>
       </c>
       <c r="E53" t="n">
-        <v>28.84</v>
+        <v>29.09</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3558</v>
+        <v>0.3546</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7116</v>
+        <v>0.7091</v>
       </c>
       <c r="J53" t="n">
         <v>0.4056</v>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N53" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6534,16 +6534,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>239.3</v>
+        <v>238.49</v>
       </c>
       <c r="C54" t="n">
-        <v>244.46</v>
+        <v>244.45</v>
       </c>
       <c r="D54" t="n">
         <v>304.79</v>
       </c>
       <c r="E54" t="n">
-        <v>41.51</v>
+        <v>40.99</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -6552,13 +6552,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2924</v>
+        <v>0.295</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5849</v>
+        <v>0.5901</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4037</v>
+        <v>0.4048</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6594,20 +6594,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.16</v>
+        <v>127.3</v>
       </c>
       <c r="C55" t="n">
-        <v>3.28</v>
+        <v>144.44</v>
       </c>
       <c r="D55" t="n">
-        <v>4.29</v>
+        <v>222.93</v>
       </c>
       <c r="E55" t="n">
-        <v>39.37</v>
+        <v>45.38</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -6616,13 +6616,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3032</v>
+        <v>0.2731</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6063</v>
+        <v>0.5462</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3935</v>
+        <v>0.3929</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6652,26 +6652,26 @@
         <v>0.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0.3641</v>
+        <v>0.4178</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>126.58</v>
+        <v>3.18</v>
       </c>
       <c r="C56" t="n">
-        <v>144.43</v>
+        <v>3.28</v>
       </c>
       <c r="D56" t="n">
-        <v>222.92</v>
+        <v>4.29</v>
       </c>
       <c r="E56" t="n">
-        <v>45.12</v>
+        <v>40.19</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -6680,13 +6680,13 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2744</v>
+        <v>0.2991</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5488</v>
+        <v>0.5981</v>
       </c>
       <c r="J56" t="n">
-        <v>0.393</v>
+        <v>0.3926</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N56" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>0.5</v>
       </c>
       <c r="R56" t="n">
-        <v>0.4178</v>
+        <v>0.3641</v>
       </c>
     </row>
     <row r="57">
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="C57" t="n">
         <v>11.46</v>
@@ -6735,7 +6735,7 @@
         <v>22.68</v>
       </c>
       <c r="E57" t="n">
-        <v>39.97</v>
+        <v>39.95</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -6747,10 +6747,10 @@
         <v>0.3002</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6005</v>
       </c>
       <c r="J57" t="n">
-        <v>0.389</v>
+        <v>0.3893</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>124.25</v>
+        <v>124.58</v>
       </c>
       <c r="C58" t="n">
         <v>125.31</v>
@@ -6799,7 +6799,7 @@
         <v>186.65</v>
       </c>
       <c r="E58" t="n">
-        <v>51.51</v>
+        <v>51.81</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -6808,13 +6808,13 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2424</v>
+        <v>0.241</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4849</v>
+        <v>0.4819</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3883</v>
+        <v>0.3881</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>0.4808</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3828</v>
+        <v>0.3831</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6914,20 +6914,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.37</v>
+        <v>412.87</v>
       </c>
       <c r="C60" t="n">
-        <v>17.85</v>
+        <v>400.31</v>
       </c>
       <c r="D60" t="n">
-        <v>20.4</v>
+        <v>457.25</v>
       </c>
       <c r="E60" t="n">
-        <v>53.37</v>
+        <v>49.83</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -6936,13 +6936,13 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2332</v>
+        <v>0.2508</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4663</v>
+        <v>0.5017</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3805</v>
+        <v>0.3809</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6972,26 +6972,26 @@
         <v>0.5</v>
       </c>
       <c r="R60" t="n">
-        <v>0.4171</v>
+        <v>0.3828</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>413.17</v>
+        <v>22.5</v>
       </c>
       <c r="C61" t="n">
-        <v>400.32</v>
+        <v>17.85</v>
       </c>
       <c r="D61" t="n">
-        <v>457.25</v>
+        <v>20.4</v>
       </c>
       <c r="E61" t="n">
-        <v>50.09</v>
+        <v>54.35</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2496</v>
+        <v>0.2282</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4991</v>
+        <v>0.4565</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3803</v>
+        <v>0.3793</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>0.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0.3828</v>
+        <v>0.4171</v>
       </c>
     </row>
     <row r="62">
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>190.59</v>
+        <v>190.76</v>
       </c>
       <c r="C62" t="n">
         <v>168.5</v>
@@ -7055,7 +7055,7 @@
         <v>206.35</v>
       </c>
       <c r="E62" t="n">
-        <v>46.41</v>
+        <v>46.58</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -7064,13 +7064,13 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.268</v>
+        <v>0.2671</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5359</v>
+        <v>0.5342</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3789</v>
+        <v>0.379</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="C63" t="n">
         <v>8.880000000000001</v>
@@ -7119,7 +7119,7 @@
         <v>13.22</v>
       </c>
       <c r="E63" t="n">
-        <v>48.74</v>
+        <v>49.62</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -7128,13 +7128,13 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2563</v>
+        <v>0.2519</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5038</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3776</v>
+        <v>0.3766</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>98.84</v>
+        <v>98.78</v>
       </c>
       <c r="C64" t="n">
         <v>90.02</v>
@@ -7183,7 +7183,7 @@
         <v>119.26</v>
       </c>
       <c r="E64" t="n">
-        <v>62.5</v>
+        <v>62.38</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -7192,13 +7192,13 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1875</v>
+        <v>0.1881</v>
       </c>
       <c r="I64" t="n">
-        <v>0.375</v>
+        <v>0.3762</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3753</v>
+        <v>0.3758</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>77.95999999999999</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="C65" t="n">
         <v>74.04000000000001</v>
@@ -7247,7 +7247,7 @@
         <v>77.95999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>44.41</v>
+        <v>44.53</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -7256,13 +7256,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.278</v>
+        <v>0.2774</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5547</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3743</v>
+        <v>0.3744</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N65" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>11.09</v>
+        <v>11.14</v>
       </c>
       <c r="C66" t="n">
         <v>10.74</v>
@@ -7311,7 +7311,7 @@
         <v>12.99</v>
       </c>
       <c r="E66" t="n">
-        <v>57.14</v>
+        <v>57.68</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2143</v>
+        <v>0.2116</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4286</v>
+        <v>0.4232</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3742</v>
+        <v>0.3737</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
       <c r="C67" t="n">
         <v>3.82</v>
@@ -7375,7 +7375,7 @@
         <v>5.31</v>
       </c>
       <c r="E67" t="n">
-        <v>50.35</v>
+        <v>50.69</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -7384,13 +7384,13 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2482</v>
+        <v>0.2466</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4965</v>
+        <v>0.4931</v>
       </c>
       <c r="J67" t="n">
-        <v>0.3735</v>
+        <v>0.3733</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N67" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>295.09</v>
+        <v>296.6</v>
       </c>
       <c r="C68" t="n">
-        <v>270.02</v>
+        <v>270.05</v>
       </c>
       <c r="D68" t="n">
         <v>323.22</v>
       </c>
       <c r="E68" t="n">
-        <v>60.12</v>
+        <v>60.74</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -7448,13 +7448,13 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1994</v>
+        <v>0.1963</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3988</v>
+        <v>0.3926</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3679</v>
+        <v>0.3673</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7494,16 +7494,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7.41</v>
+        <v>7.3</v>
       </c>
       <c r="C69" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="D69" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>56.77</v>
+        <v>55.9</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -7512,13 +7512,13 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2162</v>
+        <v>0.2205</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4323</v>
+        <v>0.441</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3654</v>
+        <v>0.367</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N69" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7558,16 +7558,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>37.94</v>
+        <v>38.1</v>
       </c>
       <c r="C70" t="n">
-        <v>28.15</v>
+        <v>28.16</v>
       </c>
       <c r="D70" t="n">
         <v>36</v>
       </c>
       <c r="E70" t="n">
-        <v>59.61</v>
+        <v>60.01</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -7576,13 +7576,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4039</v>
+        <v>0.3999</v>
       </c>
       <c r="J70" t="n">
-        <v>0.3637</v>
+        <v>0.3633</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N70" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>102.94</v>
+        <v>103.08</v>
       </c>
       <c r="C71" t="n">
         <v>97.59999999999999</v>
@@ -7631,7 +7631,7 @@
         <v>142.02</v>
       </c>
       <c r="E71" t="n">
-        <v>66.38</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1681</v>
+        <v>0.1676</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3362</v>
+        <v>0.3351</v>
       </c>
       <c r="J71" t="n">
-        <v>0.3627</v>
+        <v>0.3629</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N71" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -7686,16 +7686,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>78.33</v>
+        <v>78.75</v>
       </c>
       <c r="C72" t="n">
-        <v>61.88</v>
+        <v>61.89</v>
       </c>
       <c r="D72" t="n">
         <v>64.92</v>
       </c>
       <c r="E72" t="n">
-        <v>69.66</v>
+        <v>70.47</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -7704,13 +7704,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1517</v>
+        <v>0.1476</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3034</v>
+        <v>0.2953</v>
       </c>
       <c r="J72" t="n">
-        <v>0.3585</v>
+        <v>0.3575</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N72" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -7750,16 +7750,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>372.79</v>
+        <v>373.88</v>
       </c>
       <c r="C73" t="n">
-        <v>318.65</v>
+        <v>318.67</v>
       </c>
       <c r="D73" t="n">
-        <v>322.85</v>
+        <v>322.86</v>
       </c>
       <c r="E73" t="n">
-        <v>60.17</v>
+        <v>60.92</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -7768,13 +7768,13 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1992</v>
+        <v>0.1954</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3983</v>
+        <v>0.3908</v>
       </c>
       <c r="J73" t="n">
-        <v>0.357</v>
+        <v>0.3562</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N73" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -7810,20 +7810,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>88.54000000000001</v>
+        <v>567.7</v>
       </c>
       <c r="C74" t="n">
-        <v>55.54</v>
+        <v>451.69</v>
       </c>
       <c r="D74" t="n">
-        <v>57.06</v>
+        <v>534.97</v>
       </c>
       <c r="E74" t="n">
-        <v>69.42</v>
+        <v>67.02</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -7832,13 +7832,13 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1529</v>
+        <v>0.1649</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3058</v>
+        <v>0.3298</v>
       </c>
       <c r="J74" t="n">
-        <v>0.3541</v>
+        <v>0.3548</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -7868,26 +7868,26 @@
         <v>0.5</v>
       </c>
       <c r="R74" t="n">
-        <v>0.4016</v>
+        <v>0.3806</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>570.53</v>
+        <v>88.89</v>
       </c>
       <c r="C75" t="n">
-        <v>451.75</v>
+        <v>55.54</v>
       </c>
       <c r="D75" t="n">
-        <v>534.98</v>
+        <v>57.06</v>
       </c>
       <c r="E75" t="n">
-        <v>67.34</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -7896,10 +7896,10 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1633</v>
+        <v>0.1518</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3266</v>
+        <v>0.3035</v>
       </c>
       <c r="J75" t="n">
         <v>0.354</v>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N75" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>0.5</v>
       </c>
       <c r="R75" t="n">
-        <v>0.3806</v>
+        <v>0.4016</v>
       </c>
     </row>
     <row r="76">
@@ -7942,16 +7942,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>65.05</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>42.21</v>
+        <v>42.22</v>
       </c>
       <c r="D76" t="n">
         <v>47.57</v>
       </c>
       <c r="E76" t="n">
-        <v>64.31</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -7960,13 +7960,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1784</v>
+        <v>0.1751</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3569</v>
+        <v>0.3501</v>
       </c>
       <c r="J76" t="n">
-        <v>0.3538</v>
+        <v>0.3531</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -8006,16 +8006,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>524.65</v>
+        <v>526.98</v>
       </c>
       <c r="C77" t="n">
-        <v>458.85</v>
+        <v>458.9</v>
       </c>
       <c r="D77" t="n">
-        <v>470.46</v>
+        <v>470.47</v>
       </c>
       <c r="E77" t="n">
-        <v>61.66</v>
+        <v>63.36</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -8024,13 +8024,13 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1917</v>
+        <v>0.1832</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3834</v>
+        <v>0.3664</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3537</v>
+        <v>0.3514</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -8066,20 +8066,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>89.12</v>
+        <v>256.83</v>
       </c>
       <c r="C78" t="n">
-        <v>64.77</v>
+        <v>236.87</v>
       </c>
       <c r="D78" t="n">
-        <v>72.06</v>
+        <v>266.7</v>
       </c>
       <c r="E78" t="n">
-        <v>67.45</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -8088,13 +8088,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1628</v>
+        <v>0.1333</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3255</v>
+        <v>0.2665</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3495</v>
+        <v>0.349</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -8107,10 +8107,10 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -8124,26 +8124,26 @@
         <v>0.5</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3513</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMBA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>256.11</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>236.86</v>
+        <v>64.78</v>
       </c>
       <c r="D79" t="n">
-        <v>266.69</v>
+        <v>72.06</v>
       </c>
       <c r="E79" t="n">
-        <v>73.06999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -8152,13 +8152,13 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1347</v>
+        <v>0.1576</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2693</v>
+        <v>0.3152</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3491</v>
+        <v>0.3482</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N79" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>0.5</v>
       </c>
       <c r="R79" t="n">
-        <v>0.405</v>
+        <v>0.3513</v>
       </c>
     </row>
     <row r="80">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
       <c r="C80" t="n">
         <v>14.81</v>
@@ -8207,7 +8207,7 @@
         <v>15.61</v>
       </c>
       <c r="E80" t="n">
-        <v>72.43000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -8216,13 +8216,13 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1378</v>
+        <v>0.1366</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2757</v>
+        <v>0.2732</v>
       </c>
       <c r="J80" t="n">
-        <v>0.3475</v>
+        <v>0.3474</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N80" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>248.31</v>
+        <v>248.71</v>
       </c>
       <c r="C81" t="n">
-        <v>187.39</v>
+        <v>187.4</v>
       </c>
       <c r="D81" t="n">
         <v>188.43</v>
       </c>
       <c r="E81" t="n">
-        <v>81.06999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -8280,13 +8280,13 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0931</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1893</v>
+        <v>0.1862</v>
       </c>
       <c r="J81" t="n">
-        <v>0.3357</v>
+        <v>0.3355</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N81" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -8326,16 +8326,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>175.29</v>
+        <v>175.75</v>
       </c>
       <c r="C82" t="n">
-        <v>153.04</v>
+        <v>153.05</v>
       </c>
       <c r="D82" t="n">
         <v>202.49</v>
       </c>
       <c r="E82" t="n">
-        <v>81.81999999999999</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -8344,13 +8344,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1818</v>
+        <v>0.1749</v>
       </c>
       <c r="J82" t="n">
-        <v>0.3329</v>
+        <v>0.3321</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>34.69</v>
+        <v>34.5</v>
       </c>
       <c r="N82" t="n">
-        <v>0.6531</v>
+        <v>0.655</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>103.18</v>
+        <v>103.99</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8499</v>
+        <v>0.8495</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>23.3</v>
+        <v>23.59</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>212.8</v>
+        <v>212.61</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8223</v>
+        <v>0.8226</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>54.39</v>
+        <v>54.21</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>496.72</v>
+        <v>496.75</v>
       </c>
       <c r="D4" t="n">
         <v>0.8014</v>
@@ -8544,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>67.65000000000001</v>
+        <v>67.66</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.43</v>
+        <v>11.58</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7948</v>
+        <v>0.7936</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8581,10 +8581,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>37.39</v>
+        <v>37.75</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8413</v>
+        <v>0.837</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.05</v>
+        <v>13.47</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7587</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8618,10 +8618,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>57.39</v>
+        <v>58.4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8413</v>
+        <v>0.837</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>212.09</v>
+        <v>211.44</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7074</v>
+        <v>0.708</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>34.65</v>
+        <v>34.46</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>321.3</v>
+        <v>320.92</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7023</v>
+        <v>0.7027</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>386.97</v>
+        <v>386.14</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6928</v>
+        <v>0.6943</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -8729,10 +8729,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>42.91</v>
+        <v>42.07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>183.24</v>
+        <v>182.79</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6927</v>
+        <v>0.6935</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -8766,10 +8766,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>42.28</v>
+        <v>41.92</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>405.14</v>
+        <v>405.36</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6889</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -8803,10 +8803,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>44.48</v>
+        <v>44.57</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8826,10 +8826,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>185.14</v>
+        <v>81.83</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6847</v>
+        <v>0.6849</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>51.74</v>
+        <v>66.75</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>81.93000000000001</v>
+        <v>186.77</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6844</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -8877,10 +8877,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>67.2</v>
+        <v>52.16</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>373.43</v>
+        <v>376.49</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6827</v>
+        <v>0.6817</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -8914,10 +8914,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>47.53</v>
+        <v>48.35</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8937,10 +8937,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>456.19</v>
+        <v>455.8</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6795</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -8951,10 +8951,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>49.02</v>
+        <v>48.8</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8974,10 +8974,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53.88</v>
+        <v>53.66</v>
       </c>
       <c r="D16" t="n">
-        <v>0.676</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -8988,10 +8988,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>53.57</v>
+        <v>53.11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>422.82</v>
+        <v>423.63</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6751</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -9025,10 +9025,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>48.85</v>
+        <v>49.21</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>119.99</v>
+        <v>120.8</v>
       </c>
       <c r="D18" t="n">
-        <v>0.673</v>
+        <v>0.6722</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -9062,10 +9062,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>55.43</v>
+        <v>56.14</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>423.5</v>
+        <v>424.79</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6713</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -9099,10 +9099,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>51.92</v>
+        <v>52.51</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9122,10 +9122,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1580.37</v>
+        <v>104.06</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6693</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -9136,10 +9136,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>58.83</v>
+        <v>53.81</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>103.42</v>
+        <v>1593.2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6695</v>
+        <v>0.6691</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -9173,10 +9173,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>53.46</v>
+        <v>59.55</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>219.19</v>
+        <v>1604.22</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6687</v>
+        <v>0.6681</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -9210,10 +9210,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>56.8</v>
+        <v>55.26</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1601.69</v>
+        <v>221.38</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6682</v>
+        <v>0.6677</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -9247,10 +9247,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>55.01</v>
+        <v>57.62</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9270,10 +9270,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>271.07</v>
+        <v>271.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.667</v>
+        <v>0.6673</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -9284,10 +9284,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>45.81</v>
+        <v>45.84</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.508</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>155.11</v>
+        <v>154.95</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6666</v>
+        <v>0.6671</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -9321,10 +9321,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>57.52</v>
+        <v>57.35</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1956.84</v>
+        <v>290.29</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6626</v>
+        <v>0.6621</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -9358,10 +9358,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>59.24</v>
+        <v>54.21</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>290.05</v>
+        <v>1963.46</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6623</v>
+        <v>0.662</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -9395,10 +9395,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>53.9</v>
+        <v>59.75</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>201.6</v>
+        <v>200.83</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6602</v>
+        <v>0.6612</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -9432,10 +9432,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>63.76</v>
+        <v>63.3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9455,10 +9455,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>125.14</v>
+        <v>124.41</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6601</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>64.77</v>
+        <v>64.06</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.67</v>
+        <v>17.85</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6534</v>
+        <v>0.653</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -9506,10 +9506,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>69.91</v>
+        <v>70.36</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>304.3</v>
+        <v>304.36</v>
       </c>
       <c r="D31" t="n">
-        <v>0.652</v>
+        <v>0.6522</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -9543,10 +9543,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>66.90000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SKYT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37.79</v>
+        <v>309.37</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6514</v>
+        <v>0.6508</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -9580,10 +9580,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>67.36</v>
+        <v>72.63</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SKYT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>308.48</v>
+        <v>38.1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6508</v>
+        <v>0.6503</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -9617,10 +9617,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>72.47</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>594.4</v>
+        <v>595.78</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6504</v>
+        <v>0.6499</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>62.52</v>
+        <v>63.01</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>562.28</v>
+        <v>563.5700000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6496</v>
+        <v>0.6493</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>63.72</v>
+        <v>64.13</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>926.9400000000001</v>
+        <v>925</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6486</v>
+        <v>0.649</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -9728,10 +9728,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>70.86</v>
+        <v>70.77</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>750.83</v>
+        <v>750.65</v>
       </c>
       <c r="D37" t="n">
-        <v>0.642</v>
+        <v>0.6424</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -9765,10 +9765,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>66.15000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>729.5700000000001</v>
+        <v>729.8</v>
       </c>
       <c r="D38" t="n">
         <v>0.6357</v>
@@ -9802,10 +9802,10 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>69.77</v>
+        <v>69.95</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>320.91</v>
+        <v>321.43</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6345</v>
+        <v>0.6347</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -9839,10 +9839,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>79.14</v>
+        <v>79.2</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>119.68</v>
+        <v>119.98</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6337</v>
+        <v>0.6338</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -9876,10 +9876,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>83.98</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9899,10 +9899,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>127.97</v>
+        <v>128.33</v>
       </c>
       <c r="D41" t="n">
-        <v>0.633</v>
+        <v>0.6324</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -9913,10 +9913,10 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>85.06</v>
+        <v>85.63</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>310.41</v>
+        <v>309.85</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6292</v>
+        <v>0.6299</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -9950,10 +9950,10 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>87.20999999999999</v>
+        <v>86.98</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>220.75</v>
+        <v>645.47</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6249</v>
+        <v>0.6226</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -9987,10 +9987,10 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>89.16</v>
+        <v>87.39</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10010,10 +10010,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>648</v>
+        <v>223.27</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6209</v>
+        <v>0.6216</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>88.33</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>76.39</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4717</v>
+        <v>0.4712</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>45.34</v>
+        <v>45.63</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>440.24</v>
+        <v>440.11</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4489</v>
+        <v>0.449</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>64.13</v>
+        <v>64.09</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>633.25</v>
+        <v>634.09</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4193</v>
+        <v>0.4188</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>61.59</v>
+        <v>61.95</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>85.72</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0.4111</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>34.18</v>
+        <v>34.37</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>46.73</v>
+        <v>46.84</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4108</v>
+        <v>0.4102</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -10209,10 +10209,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>26.48</v>
+        <v>27.03</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>52.66</v>
+        <v>52.72</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4081</v>
+        <v>0.4082</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -10246,10 +10246,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>32.42</v>
+        <v>32.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>SGE.L</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10269,10 +10269,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>287.58</v>
+        <v>856</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4065</v>
+        <v>0.4061</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -10283,21 +10283,21 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>35.2</v>
+        <v>40.99</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>potentially oversold</t>
+          <t>balanced opportunity profile</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SGE.L</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10306,7 +10306,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>856</v>
+        <v>289.77</v>
       </c>
       <c r="D52" t="n">
         <v>0.4058</v>
@@ -10320,14 +10320,14 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>40.99</v>
+        <v>35.87</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
         <v>8.15</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4057</v>
+        <v>0.4056</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>28.84</v>
+        <v>29.09</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>239.3</v>
+        <v>238.49</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4037</v>
+        <v>0.4048</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -10394,10 +10394,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>41.51</v>
+        <v>40.99</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10417,10 +10417,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3.16</v>
+        <v>127.3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3936</v>
+        <v>0.3929</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>39.37</v>
+        <v>45.38</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>potentially oversold</t>
+          <t>balanced opportunity profile</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>126.58</v>
+        <v>3.18</v>
       </c>
       <c r="D56" t="n">
-        <v>0.393</v>
+        <v>0.3926</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -10468,10 +10468,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>45.12</v>
+        <v>40.19</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="D57" t="n">
-        <v>0.389</v>
+        <v>0.3893</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -10505,10 +10505,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>39.97</v>
+        <v>39.95</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>124.25</v>
+        <v>124.58</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3883</v>
+        <v>0.3881</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>51.51</v>
+        <v>51.81</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>38.94</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3828</v>
+        <v>0.3831</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>51.92</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>22.37</v>
+        <v>412.87</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3805</v>
+        <v>0.3809</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>53.37</v>
+        <v>49.83</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>413.17</v>
+        <v>22.5</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3803</v>
+        <v>0.3793</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>50.09</v>
+        <v>54.35</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>190.59</v>
+        <v>190.76</v>
       </c>
       <c r="D62" t="n">
         <v>0.379</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>46.41</v>
+        <v>46.58</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3776</v>
+        <v>0.3767</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -10727,10 +10727,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>48.74</v>
+        <v>49.55</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>98.84</v>
+        <v>98.78</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3754</v>
+        <v>0.3758</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -10764,10 +10764,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>62.5</v>
+        <v>62.38</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>77.95999999999999</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="D65" t="n">
         <v>0.3744</v>
@@ -10801,10 +10801,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>44.41</v>
+        <v>44.53</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11.09</v>
+        <v>11.14</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3742</v>
+        <v>0.3737</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -10838,10 +10838,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>57.14</v>
+        <v>57.68</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3735</v>
+        <v>0.3731</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -10875,10 +10875,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>50.35</v>
+        <v>50.83</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>295.09</v>
+        <v>296.6</v>
       </c>
       <c r="D68" t="n">
-        <v>0.368</v>
+        <v>0.3673</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -10912,10 +10912,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>60.12</v>
+        <v>60.74</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7.41</v>
+        <v>7.3</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3654</v>
+        <v>0.367</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>56.77</v>
+        <v>55.9</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>37.94</v>
+        <v>38.1</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3637</v>
+        <v>0.3633</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -10986,10 +10986,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>59.61</v>
+        <v>60.01</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>102.94</v>
+        <v>103.08</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3627</v>
+        <v>0.3629</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -11023,10 +11023,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>66.38</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>78.33</v>
+        <v>78.75</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3585</v>
+        <v>0.3575</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -11060,10 +11060,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>69.66</v>
+        <v>70.47</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>372.79</v>
+        <v>373.88</v>
       </c>
       <c r="D73" t="n">
-        <v>0.357</v>
+        <v>0.3562</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -11097,10 +11097,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>60.17</v>
+        <v>60.92</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>570.53</v>
+        <v>567.7</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3541</v>
+        <v>0.3548</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>67.34</v>
+        <v>67.02</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -11157,10 +11157,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>88.54000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3541</v>
+        <v>0.354</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -11171,10 +11171,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>69.42</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>65.05</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3538</v>
+        <v>0.3531</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -11208,10 +11208,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>64.31</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>524.65</v>
+        <v>526.98</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3537</v>
+        <v>0.3514</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -11245,10 +11245,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>61.66</v>
+        <v>63.36</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>89.12</v>
+        <v>256.83</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3495</v>
+        <v>0.349</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>67.45</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMBA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11305,10 +11305,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>256.11</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3491</v>
+        <v>0.3482</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -11319,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>73.06999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3475</v>
+        <v>0.3474</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -11356,10 +11356,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>72.43000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>248.31</v>
+        <v>248.71</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3357</v>
+        <v>0.3355</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -11393,10 +11393,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>81.06999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="H81" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -11416,10 +11416,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>175.29</v>
+        <v>175.75</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3329</v>
+        <v>0.3321</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -11430,10 +11430,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>81.81999999999999</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6532</v>
+        <v>0.655</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8223</v>
+        <v>0.8225</v>
       </c>
       <c r="D2" t="n">
         <v>0.2525</v>
@@ -11544,10 +11544,10 @@
         <v>7380</v>
       </c>
       <c r="H2" t="n">
-        <v>212.76</v>
+        <v>212.63</v>
       </c>
       <c r="I2" t="n">
-        <v>34.69</v>
+        <v>34.71</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -11575,10 +11575,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8015</v>
+        <v>0.8013</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4748</v>
+        <v>0.4747</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11590,10 +11590,10 @@
         <v>5050</v>
       </c>
       <c r="H3" t="n">
-        <v>496.67</v>
+        <v>496.92</v>
       </c>
       <c r="I3" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -11621,10 +11621,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8499</v>
+        <v>0.8495</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6666</v>
+        <v>0.6663</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11636,10 +11636,10 @@
         <v>3400</v>
       </c>
       <c r="H4" t="n">
-        <v>103.18</v>
+        <v>104.01</v>
       </c>
       <c r="I4" t="n">
-        <v>32.95</v>
+        <v>32.69</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -11667,25 +11667,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6839</v>
+        <v>0.6849</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1225</v>
+        <v>0.1223</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="G5" t="n">
-        <v>3290</v>
+        <v>3310</v>
       </c>
       <c r="H5" t="n">
-        <v>81.95</v>
+        <v>81.83</v>
       </c>
       <c r="I5" t="n">
-        <v>40.15</v>
+        <v>40.45</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.642</v>
+        <v>0.6424</v>
       </c>
       <c r="D6" t="n">
         <v>0.1069</v>
@@ -11722,16 +11722,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>3140</v>
+        <v>3150</v>
       </c>
       <c r="H6" t="n">
-        <v>750.84</v>
+        <v>750.6900000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6623</v>
+        <v>0.6621</v>
       </c>
       <c r="D7" t="n">
         <v>0.1524</v>
@@ -11768,16 +11768,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="G7" t="n">
-        <v>3080</v>
+        <v>3090</v>
       </c>
       <c r="H7" t="n">
-        <v>290.05</v>
+        <v>290.29</v>
       </c>
       <c r="I7" t="n">
-        <v>10.62</v>
+        <v>10.64</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6357</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>0.1446</v>
@@ -11820,7 +11820,7 @@
         <v>2990</v>
       </c>
       <c r="H8" t="n">
-        <v>729.55</v>
+        <v>729.87</v>
       </c>
       <c r="I8" t="n">
         <v>4.1</v>
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6929</v>
+        <v>0.6943</v>
       </c>
       <c r="D9" t="n">
         <v>0.2461</v>
@@ -11860,16 +11860,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>2860</v>
+        <v>2880</v>
       </c>
       <c r="H9" t="n">
-        <v>386.9</v>
+        <v>386.15</v>
       </c>
       <c r="I9" t="n">
-        <v>7.39</v>
+        <v>7.46</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6293</v>
+        <v>0.6298</v>
       </c>
       <c r="D10" t="n">
         <v>0.176</v>
@@ -11906,16 +11906,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G10" t="n">
-        <v>2840</v>
+        <v>2860</v>
       </c>
       <c r="H10" t="n">
-        <v>310.37</v>
+        <v>309.91</v>
       </c>
       <c r="I10" t="n">
-        <v>9.15</v>
+        <v>9.23</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6889</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D11" t="n">
         <v>0.2483</v>
@@ -11952,16 +11952,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="G11" t="n">
-        <v>2840</v>
+        <v>2850</v>
       </c>
       <c r="H11" t="n">
-        <v>405.14</v>
+        <v>405.36</v>
       </c>
       <c r="I11" t="n">
-        <v>7.01</v>
+        <v>7.03</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6794</v>
       </c>
       <c r="D12" t="n">
         <v>0.2597</v>
@@ -11998,16 +11998,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="G12" t="n">
-        <v>2760</v>
+        <v>2770</v>
       </c>
       <c r="H12" t="n">
-        <v>456.19</v>
+        <v>455.84</v>
       </c>
       <c r="I12" t="n">
-        <v>6.05</v>
+        <v>6.08</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -12035,22 +12035,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6504</v>
+        <v>0.6499</v>
       </c>
       <c r="D13" t="n">
-        <v>0.248</v>
+        <v>0.2479</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="G13" t="n">
-        <v>2680</v>
+        <v>2690</v>
       </c>
       <c r="H13" t="n">
-        <v>594.37</v>
+        <v>595.84</v>
       </c>
       <c r="I13" t="n">
         <v>4.51</v>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2818</v>
+        <v>0.282</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12096,10 +12096,10 @@
         <v>2650</v>
       </c>
       <c r="H14" t="n">
-        <v>423.39</v>
+        <v>424.8</v>
       </c>
       <c r="I14" t="n">
-        <v>6.26</v>
+        <v>6.24</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6337</v>
+        <v>0.6338</v>
       </c>
       <c r="D15" t="n">
         <v>0.2503</v>
@@ -12136,16 +12136,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2610</v>
+        <v>2620</v>
       </c>
       <c r="H15" t="n">
-        <v>119.77</v>
+        <v>119.97</v>
       </c>
       <c r="I15" t="n">
-        <v>21.79</v>
+        <v>21.84</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6496</v>
+        <v>0.6492</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2736</v>
+        <v>0.2735</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12188,10 +12188,10 @@
         <v>2590</v>
       </c>
       <c r="H16" t="n">
-        <v>562.27</v>
+        <v>563.63</v>
       </c>
       <c r="I16" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -12219,25 +12219,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6682</v>
+        <v>0.6681</v>
       </c>
       <c r="D17" t="n">
-        <v>0.322</v>
+        <v>0.3219</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2490</v>
+        <v>2500</v>
       </c>
       <c r="H17" t="n">
-        <v>1601.77</v>
+        <v>1604.51</v>
       </c>
       <c r="I17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -12265,25 +12265,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6331</v>
+        <v>0.6324</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2965</v>
+        <v>0.2961</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="G18" t="n">
-        <v>2440</v>
+        <v>2450</v>
       </c>
       <c r="H18" t="n">
-        <v>127.94</v>
+        <v>128.33</v>
       </c>
       <c r="I18" t="n">
-        <v>19.07</v>
+        <v>19.09</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.675</v>
+        <v>0.6747</v>
       </c>
       <c r="D19" t="n">
         <v>0.3567</v>
@@ -12320,16 +12320,16 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="G19" t="n">
-        <v>2380</v>
+        <v>2390</v>
       </c>
       <c r="H19" t="n">
-        <v>423.08</v>
+        <v>423.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -12357,10 +12357,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6627</v>
+        <v>0.6619</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3773</v>
+        <v>0.3771</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
         <v>2270</v>
       </c>
       <c r="H20" t="n">
-        <v>1956.02</v>
+        <v>1964.77</v>
       </c>
       <c r="I20" t="n">
         <v>1.16</v>
@@ -12403,25 +12403,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6927</v>
+        <v>0.6935</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4093</v>
+        <v>0.4094</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2240</v>
+        <v>2260</v>
       </c>
       <c r="H21" t="n">
-        <v>183.24</v>
+        <v>182.79</v>
       </c>
       <c r="I21" t="n">
-        <v>12.22</v>
+        <v>12.36</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6666</v>
+        <v>0.6672</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3941</v>
+        <v>0.3942</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12464,10 +12464,10 @@
         <v>2220</v>
       </c>
       <c r="H22" t="n">
-        <v>155.1</v>
+        <v>154.92</v>
       </c>
       <c r="I22" t="n">
-        <v>14.31</v>
+        <v>14.33</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -12495,25 +12495,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6587</v>
+        <v>0.6601</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3947</v>
+        <v>0.3951</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="G23" t="n">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="H23" t="n">
-        <v>125.23</v>
+        <v>124.44</v>
       </c>
       <c r="I23" t="n">
-        <v>17.49</v>
+        <v>17.68</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7023</v>
+        <v>0.7027</v>
       </c>
       <c r="D24" t="n">
         <v>0.4352</v>
@@ -12550,16 +12550,16 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="G24" t="n">
-        <v>2170</v>
+        <v>2190</v>
       </c>
       <c r="H24" t="n">
-        <v>321.13</v>
+        <v>320.85</v>
       </c>
       <c r="I24" t="n">
-        <v>6.76</v>
+        <v>6.83</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -12602,10 +12602,10 @@
         <v>2040</v>
       </c>
       <c r="H25" t="n">
-        <v>308.38</v>
+        <v>309.13</v>
       </c>
       <c r="I25" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -12633,25 +12633,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6602</v>
+        <v>0.6613</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4404</v>
+        <v>0.4407</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="G26" t="n">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="H26" t="n">
-        <v>201.65</v>
+        <v>200.74</v>
       </c>
       <c r="I26" t="n">
-        <v>10.07</v>
+        <v>10.16</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -12679,10 +12679,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.6208</v>
+        <v>0.6223</v>
       </c>
       <c r="D27" t="n">
-        <v>0.409</v>
+        <v>0.4093</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -12694,10 +12694,10 @@
         <v>2020</v>
       </c>
       <c r="H27" t="n">
-        <v>648.05</v>
+        <v>645.92</v>
       </c>
       <c r="I27" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -12725,25 +12725,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7074</v>
+        <v>0.708</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4859</v>
+        <v>0.486</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="H28" t="n">
-        <v>212.09</v>
+        <v>211.44</v>
       </c>
       <c r="I28" t="n">
-        <v>9.380000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -12771,10 +12771,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.6827</v>
+        <v>0.6817</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4888</v>
+        <v>0.4883</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -12786,10 +12786,10 @@
         <v>1920</v>
       </c>
       <c r="H29" t="n">
-        <v>373.59</v>
+        <v>376.58</v>
       </c>
       <c r="I29" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6514</v>
+        <v>0.6501</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4853</v>
+        <v>0.4854</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -12832,10 +12832,10 @@
         <v>1840</v>
       </c>
       <c r="H30" t="n">
-        <v>37.8</v>
+        <v>38.15</v>
       </c>
       <c r="I30" t="n">
-        <v>48.68</v>
+        <v>48.23</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.652</v>
+        <v>0.6522</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5068</v>
+        <v>0.5067</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -12878,10 +12878,10 @@
         <v>1770</v>
       </c>
       <c r="H31" t="n">
-        <v>304.35</v>
+        <v>304.39</v>
       </c>
       <c r="I31" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -12909,10 +12909,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.673</v>
+        <v>0.6722</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5343</v>
+        <v>0.534</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -12924,10 +12924,10 @@
         <v>1720</v>
       </c>
       <c r="H32" t="n">
-        <v>119.99</v>
+        <v>120.83</v>
       </c>
       <c r="I32" t="n">
-        <v>14.33</v>
+        <v>14.23</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="D33" t="n">
         <v>0.543</v>
@@ -12970,7 +12970,7 @@
         <v>1630</v>
       </c>
       <c r="H33" t="n">
-        <v>926.85</v>
+        <v>924.96</v>
       </c>
       <c r="I33" t="n">
         <v>1.76</v>
@@ -13001,10 +13001,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.6244</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5394</v>
+        <v>0.5392</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -13016,10 +13016,10 @@
         <v>1580</v>
       </c>
       <c r="H34" t="n">
-        <v>221.04</v>
+        <v>223.34</v>
       </c>
       <c r="I34" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -13047,10 +13047,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.676</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5916</v>
+        <v>0.5917</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>1520</v>
       </c>
       <c r="H35" t="n">
-        <v>53.88</v>
+        <v>53.66</v>
       </c>
       <c r="I35" t="n">
-        <v>28.21</v>
+        <v>28.33</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -13084,22 +13084,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.4489</v>
+        <v>0.6672</v>
       </c>
       <c r="D36" t="n">
-        <v>0.341</v>
+        <v>0.2383</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.3472</v>
       </c>
       <c r="F36" t="n">
         <v>1.42</v>
@@ -13108,10 +13108,10 @@
         <v>1420</v>
       </c>
       <c r="H36" t="n">
-        <v>440.24</v>
+        <v>271.11</v>
       </c>
       <c r="I36" t="n">
-        <v>3.23</v>
+        <v>5.24</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -13123,41 +13123,41 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>improves diversification</t>
+          <t>bullish trend</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.6671</v>
+        <v>0.449</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2384</v>
+        <v>0.341</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3486</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G37" t="n">
-        <v>1400</v>
+        <v>1420</v>
       </c>
       <c r="H37" t="n">
-        <v>270.96</v>
+        <v>440.09</v>
       </c>
       <c r="I37" t="n">
-        <v>5.17</v>
+        <v>3.23</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bullish trend</t>
+          <t>improves diversification</t>
         </is>
       </c>
     </row>
@@ -13185,10 +13185,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4193</v>
+        <v>0.4187</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3295</v>
+        <v>0.3297</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -13200,7 +13200,7 @@
         <v>1350</v>
       </c>
       <c r="H38" t="n">
-        <v>633.26</v>
+        <v>634.27</v>
       </c>
       <c r="I38" t="n">
         <v>2.13</v>
@@ -13231,10 +13231,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6691</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6483</v>
+        <v>0.6481</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -13246,10 +13246,10 @@
         <v>1290</v>
       </c>
       <c r="H39" t="n">
-        <v>1580.48</v>
+        <v>1592.51</v>
       </c>
       <c r="I39" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -13277,10 +13277,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.4112</v>
+        <v>0.4111</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2351</v>
+        <v>0.2342</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -13292,10 +13292,10 @@
         <v>990</v>
       </c>
       <c r="H40" t="n">
-        <v>85.68000000000001</v>
+        <v>85.83</v>
       </c>
       <c r="I40" t="n">
-        <v>11.55</v>
+        <v>11.53</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -13323,22 +13323,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.6687</v>
+        <v>0.6677</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7371</v>
+        <v>0.737</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="G41" t="n">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="H41" t="n">
-        <v>219.19</v>
+        <v>221.38</v>
       </c>
       <c r="I41" t="n">
         <v>4.38</v>
@@ -13369,7 +13369,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.6345</v>
+        <v>0.6347</v>
       </c>
       <c r="D42" t="n">
         <v>0.7333</v>
@@ -13384,10 +13384,10 @@
         <v>930</v>
       </c>
       <c r="H42" t="n">
-        <v>320.92</v>
+        <v>321.52</v>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.4715</v>
+        <v>0.4713</v>
       </c>
       <c r="D43" t="n">
         <v>0.6021</v>
@@ -13430,10 +13430,10 @@
         <v>900</v>
       </c>
       <c r="H43" t="n">
-        <v>76.47</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>11.77</v>
+        <v>11.76</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4058</v>
+        <v>0.4061</v>
       </c>
       <c r="D44" t="n">
         <v>0.3069</v>
@@ -13470,16 +13470,16 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G44" t="n">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="H44" t="n">
         <v>856</v>
       </c>
       <c r="I44" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -13507,25 +13507,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.6534</v>
+        <v>0.653</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7693</v>
+        <v>0.7702</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G45" t="n">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="H45" t="n">
-        <v>17.67</v>
+        <v>17.85</v>
       </c>
       <c r="I45" t="n">
-        <v>46.97</v>
+        <v>45.94</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.6695</v>
+        <v>0.669</v>
       </c>
       <c r="D46" t="n">
-        <v>0.783</v>
+        <v>0.7825</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -13568,10 +13568,10 @@
         <v>800</v>
       </c>
       <c r="H46" t="n">
-        <v>103.42</v>
+        <v>104.32</v>
       </c>
       <c r="I46" t="n">
-        <v>7.74</v>
+        <v>7.67</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.4038</v>
+        <v>0.4048</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3709</v>
+        <v>0.371</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -13614,10 +13614,10 @@
         <v>800</v>
       </c>
       <c r="H47" t="n">
-        <v>239.17</v>
+        <v>238.52</v>
       </c>
       <c r="I47" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -13645,25 +13645,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.4065</v>
+        <v>0.4058</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4314</v>
+        <v>0.4308</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="G48" t="n">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="H48" t="n">
-        <v>287.58</v>
+        <v>289.78</v>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -13691,25 +13691,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.7948</v>
+        <v>0.7936</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8877</v>
+        <v>0.8829</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="G49" t="n">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="H49" t="n">
-        <v>11.43</v>
+        <v>11.58</v>
       </c>
       <c r="I49" t="n">
-        <v>55.12</v>
+        <v>56.13</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.4108</v>
+        <v>0.4104</v>
       </c>
       <c r="D50" t="n">
         <v>0.5283</v>
@@ -13752,10 +13752,10 @@
         <v>610</v>
       </c>
       <c r="H50" t="n">
-        <v>46.73</v>
+        <v>46.82</v>
       </c>
       <c r="I50" t="n">
-        <v>13.05</v>
+        <v>13.03</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.4081</v>
+        <v>0.4083</v>
       </c>
       <c r="D51" t="n">
         <v>0.5959</v>
@@ -13798,7 +13798,7 @@
         <v>520</v>
       </c>
       <c r="H51" t="n">
-        <v>52.66</v>
+        <v>52.71</v>
       </c>
       <c r="I51" t="n">
         <v>9.869999999999999</v>
@@ -13838,16 +13838,16 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G52" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="H52" t="n">
         <v>8.15</v>
       </c>
       <c r="I52" t="n">
-        <v>55.21</v>
+        <v>56.44</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.3803</v>
+        <v>0.3808</v>
       </c>
       <c r="D53" t="n">
         <v>0.2836</v>
@@ -13890,7 +13890,7 @@
         <v>210</v>
       </c>
       <c r="H53" t="n">
-        <v>413.13</v>
+        <v>412.97</v>
       </c>
       <c r="I53" t="n">
         <v>0.51</v>
@@ -13936,10 +13936,10 @@
         <v>200</v>
       </c>
       <c r="H54" t="n">
-        <v>77.95999999999999</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -13967,10 +13967,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3115</v>
+        <v>0.3113</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -13982,7 +13982,7 @@
         <v>190</v>
       </c>
       <c r="H55" t="n">
-        <v>372.79</v>
+        <v>373.98</v>
       </c>
       <c r="I55" t="n">
         <v>0.51</v>
@@ -14013,10 +14013,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.3828</v>
+        <v>0.383</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3782</v>
+        <v>0.3781</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>190</v>
       </c>
       <c r="H56" t="n">
-        <v>38.93</v>
+        <v>38.94</v>
       </c>
       <c r="I56" t="n">
         <v>4.88</v>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.3534</v>
+        <v>0.3512</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3521</v>
+        <v>0.3519</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
         <v>180</v>
       </c>
       <c r="H57" t="n">
-        <v>524.97</v>
+        <v>527.15</v>
       </c>
       <c r="I57" t="n">
         <v>0.34</v>
@@ -14105,10 +14105,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.3583</v>
+        <v>0.3575</v>
       </c>
       <c r="D58" t="n">
-        <v>0.354</v>
+        <v>0.3535</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>180</v>
       </c>
       <c r="H58" t="n">
-        <v>78.39</v>
+        <v>78.75</v>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -14151,10 +14151,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.3358</v>
+        <v>0.3354</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3521</v>
+        <v>0.352</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -14166,7 +14166,7 @@
         <v>170</v>
       </c>
       <c r="H59" t="n">
-        <v>248.22</v>
+        <v>248.79</v>
       </c>
       <c r="I59" t="n">
         <v>0.68</v>
@@ -14197,10 +14197,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.3492</v>
+        <v>0.349</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3651</v>
+        <v>0.3653</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -14212,7 +14212,7 @@
         <v>170</v>
       </c>
       <c r="H60" t="n">
-        <v>256.07</v>
+        <v>256.89</v>
       </c>
       <c r="I60" t="n">
         <v>0.66</v>
@@ -14243,10 +14243,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.3475</v>
+        <v>0.3474</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4033</v>
+        <v>0.4032</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -14258,10 +14258,10 @@
         <v>160</v>
       </c>
       <c r="H61" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
       <c r="I61" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>160</v>
       </c>
       <c r="H62" t="n">
-        <v>190.59</v>
+        <v>190.83</v>
       </c>
       <c r="I62" t="n">
         <v>0.84</v>
@@ -14326,7 +14326,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -14335,10 +14335,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.3936</v>
+        <v>0.388</v>
       </c>
       <c r="D63" t="n">
-        <v>0.5259</v>
+        <v>0.4914</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -14350,10 +14350,10 @@
         <v>150</v>
       </c>
       <c r="H63" t="n">
-        <v>3.16</v>
+        <v>124.69</v>
       </c>
       <c r="I63" t="n">
-        <v>47.47</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -14365,14 +14365,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>potentially oversold</t>
+          <t>balanced opportunity profile</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -14381,10 +14381,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.3884</v>
+        <v>0.3758</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4913</v>
+        <v>0.5</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -14396,10 +14396,10 @@
         <v>150</v>
       </c>
       <c r="H64" t="n">
-        <v>124.17</v>
+        <v>98.78</v>
       </c>
       <c r="I64" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -14427,25 +14427,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.3497</v>
+        <v>0.3927</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4751</v>
+        <v>0.5265</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="G65" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H65" t="n">
-        <v>89.04000000000001</v>
+        <v>3.17</v>
       </c>
       <c r="I65" t="n">
-        <v>1.57</v>
+        <v>47.32</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>AMBA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.3805</v>
+        <v>0.348</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5401</v>
+        <v>0.4744</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -14488,10 +14488,10 @@
         <v>140</v>
       </c>
       <c r="H66" t="n">
-        <v>22.37</v>
+        <v>89.81</v>
       </c>
       <c r="I66" t="n">
-        <v>6.26</v>
+        <v>1.56</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.3754</v>
+        <v>0.3791</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5</v>
+        <v>0.5399</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14534,10 +14534,10 @@
         <v>140</v>
       </c>
       <c r="H67" t="n">
-        <v>98.84</v>
+        <v>22.51</v>
       </c>
       <c r="I67" t="n">
-        <v>1.42</v>
+        <v>6.22</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -14565,25 +14565,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.3628</v>
+        <v>0.3627</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G68" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H68" t="n">
-        <v>102.9</v>
+        <v>103.18</v>
       </c>
       <c r="I68" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.3678</v>
+        <v>0.3671</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6018</v>
+        <v>0.6015</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -14626,10 +14626,10 @@
         <v>120</v>
       </c>
       <c r="H69" t="n">
-        <v>295.39</v>
+        <v>296.92</v>
       </c>
       <c r="I69" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -14657,10 +14657,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.3776</v>
+        <v>0.3736</v>
       </c>
       <c r="D70" t="n">
-        <v>0.5851</v>
+        <v>0.5992</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14672,10 +14672,10 @@
         <v>120</v>
       </c>
       <c r="H70" t="n">
-        <v>9.52</v>
+        <v>11.14</v>
       </c>
       <c r="I70" t="n">
-        <v>12.61</v>
+        <v>10.77</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.393</v>
+        <v>0.3929</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6271</v>
+        <v>0.6257</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -14718,10 +14718,10 @@
         <v>120</v>
       </c>
       <c r="H71" t="n">
-        <v>126.6</v>
+        <v>127.16</v>
       </c>
       <c r="I71" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14749,10 +14749,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.3741</v>
+        <v>0.3767</v>
       </c>
       <c r="D72" t="n">
-        <v>0.5992</v>
+        <v>0.5851</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -14764,10 +14764,10 @@
         <v>120</v>
       </c>
       <c r="H72" t="n">
-        <v>11.09</v>
+        <v>9.57</v>
       </c>
       <c r="I72" t="n">
-        <v>10.82</v>
+        <v>12.54</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -14795,10 +14795,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.3331</v>
+        <v>0.332</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5666</v>
+        <v>0.5665</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14810,7 +14810,7 @@
         <v>110</v>
       </c>
       <c r="H73" t="n">
-        <v>175.18</v>
+        <v>175.82</v>
       </c>
       <c r="I73" t="n">
         <v>0.63</v>
@@ -14841,10 +14841,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3637</v>
+        <v>0.3633</v>
       </c>
       <c r="D74" t="n">
-        <v>0.6552</v>
+        <v>0.6553</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -14856,10 +14856,10 @@
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>37.94</v>
+        <v>38.1</v>
       </c>
       <c r="I74" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14887,10 +14887,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.3541</v>
+        <v>0.3546</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6591</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -14902,7 +14902,7 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>570.05</v>
+        <v>568.75</v>
       </c>
       <c r="I75" t="n">
         <v>0.18</v>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.3654</v>
+        <v>0.3669</v>
       </c>
       <c r="D76" t="n">
-        <v>0.6413</v>
+        <v>0.6411</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14948,10 +14948,10 @@
         <v>100</v>
       </c>
       <c r="H76" t="n">
-        <v>7.41</v>
+        <v>7.31</v>
       </c>
       <c r="I76" t="n">
-        <v>13.5</v>
+        <v>13.68</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.3733</v>
+        <v>0.3731</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6868</v>
+        <v>0.6872</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -14994,10 +14994,10 @@
         <v>90</v>
       </c>
       <c r="H77" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="I77" t="n">
-        <v>20.5</v>
+        <v>20.45</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.6847</v>
+        <v>0.6843</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9785</v>
+        <v>0.9787</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -15040,7 +15040,7 @@
         <v>80</v>
       </c>
       <c r="H78" t="n">
-        <v>185.12</v>
+        <v>186.86</v>
       </c>
       <c r="I78" t="n">
         <v>0.43</v>
@@ -15071,10 +15071,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.3539</v>
+        <v>0.3532</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7521</v>
+        <v>0.7524</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -15086,10 +15086,10 @@
         <v>70</v>
       </c>
       <c r="H79" t="n">
-        <v>65.04000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="I79" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.3889</v>
+        <v>0.3893</v>
       </c>
       <c r="D80" t="n">
         <v>0.8008999999999999</v>
@@ -15132,10 +15132,10 @@
         <v>60</v>
       </c>
       <c r="H80" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="I80" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
@@ -15227,16 +15227,16 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1304</v>
+        <v>1344</v>
       </c>
       <c r="D2" t="n">
-        <v>751</v>
+        <v>791</v>
       </c>
       <c r="E2" t="n">
-        <v>7.51</v>
+        <v>7.91</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9761</v>
+        <v>0.9752</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -15272,13 +15272,13 @@
         <v>40.03</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9023</v>
+        <v>0.9016</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7635</v>
+        <v>0.7652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5593</v>
+        <v>0.5538</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -15296,19 +15296,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="C4" t="n">
-        <v>844.2</v>
+        <v>804.2</v>
       </c>
       <c r="D4" t="n">
-        <v>451.07</v>
+        <v>429.24</v>
       </c>
       <c r="E4" t="n">
-        <v>145.03</v>
+        <v>144.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4538</v>
+        <v>0.4542</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1960</v>
+        <v>1940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>bullish trend, potentially oversold</t>
+          <t>bullish trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>BZ=F</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1950</v>
+        <v>1930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1705,14 +1705,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>bullish trend</t>
+          <t>bullish trend, potentially oversold</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SI=F</t>
+          <t>CL=F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1940</v>
+        <v>1910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SI=F</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1930</v>
+        <v>1910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1890</v>
+        <v>1880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1840</v>
+        <v>1860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>0.7716</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7389</v>
+        <v>0.7305</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3185,26 +3185,26 @@
         <v>0.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5</v>
+        <v>0.4436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93.55999755859375</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="C3" t="n">
-        <v>104.7419999694824</v>
+        <v>20.32680011749268</v>
       </c>
       <c r="D3" t="n">
-        <v>76.57019987106324</v>
+        <v>18.37480008125305</v>
       </c>
       <c r="E3" t="n">
-        <v>39.85259342193125</v>
+        <v>48.98279176848897</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -3213,13 +3213,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8007</v>
+        <v>0.7551</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6015</v>
+        <v>0.5102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7134</v>
+        <v>0.7045</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3249,26 +3249,26 @@
         <v>0.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>0.5318000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>BZ=F</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90.16000366210938</v>
+        <v>93.55999755859375</v>
       </c>
       <c r="C4" t="n">
-        <v>98.21839981079101</v>
+        <v>104.7419999694824</v>
       </c>
       <c r="D4" t="n">
-        <v>71.80154985427856</v>
+        <v>76.57019987106324</v>
       </c>
       <c r="E4" t="n">
-        <v>43.05869679501007</v>
+        <v>39.85259342193125</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3277,13 +3277,13 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7847</v>
+        <v>0.8007</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5694</v>
+        <v>0.6015</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7086</v>
+        <v>0.7004</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3313,26 +3313,26 @@
         <v>0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5</v>
+        <v>0.4135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SI=F</t>
+          <t>CL=F</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.77999877929688</v>
+        <v>90.16000366210938</v>
       </c>
       <c r="C5" t="n">
-        <v>75.93557952880859</v>
+        <v>98.21839981079101</v>
       </c>
       <c r="D5" t="n">
-        <v>65.23656997680663</v>
+        <v>71.80154985427856</v>
       </c>
       <c r="E5" t="n">
-        <v>46.71263911332996</v>
+        <v>43.05869679501007</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3341,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7664</v>
+        <v>0.7847</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5329</v>
+        <v>0.5694</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6949</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3377,26 +3377,26 @@
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5</v>
+        <v>0.4084</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SI=F</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.95000076293945</v>
+        <v>74.77999877929688</v>
       </c>
       <c r="C6" t="n">
-        <v>20.32680011749268</v>
+        <v>75.93557952880859</v>
       </c>
       <c r="D6" t="n">
-        <v>18.37480008125305</v>
+        <v>65.23656997680663</v>
       </c>
       <c r="E6" t="n">
-        <v>48.98279176848897</v>
+        <v>46.71263911332996</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -3405,13 +3405,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7551</v>
+        <v>0.7664</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5102</v>
+        <v>0.5329</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6997</v>
+        <v>0.694</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5</v>
+        <v>0.4394</v>
       </c>
     </row>
     <row r="7">
@@ -3475,7 +3475,7 @@
         <v>0.4247</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6869</v>
+        <v>0.6825</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5</v>
+        <v>0.4709</v>
       </c>
     </row>
     <row r="8">
@@ -3539,7 +3539,7 @@
         <v>0.3202</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6712</v>
+        <v>0.6758</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>0.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>0.5305</v>
       </c>
     </row>
     <row r="9">
@@ -3603,7 +3603,7 @@
         <v>0.309</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3695</v>
+        <v>0.3676</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5</v>
+        <v>0.4872</v>
       </c>
     </row>
   </sheetData>
@@ -3712,7 +3712,7 @@
         <v>4462.89990234375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7389</v>
+        <v>0.7305</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93.55999755859375</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7134</v>
+        <v>0.7045</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>39.85259342193125</v>
+        <v>48.98279176848897</v>
       </c>
       <c r="H3" t="n">
         <v>0.6546</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>bullish trend, potentially oversold</t>
+          <t>bullish trend</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>BZ=F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90.16000366210938</v>
+        <v>93.55999755859375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7086</v>
+        <v>0.7004</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3797,21 +3797,21 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>43.05869679501007</v>
+        <v>39.85259342193125</v>
       </c>
       <c r="H4" t="n">
         <v>0.6546</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>bullish trend</t>
+          <t>bullish trend, potentially oversold</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SI=F</t>
+          <t>CL=F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.77999877929688</v>
+        <v>90.16000366210938</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6949</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>46.71263911332996</v>
+        <v>43.05869679501007</v>
       </c>
       <c r="H5" t="n">
         <v>0.6546</v>
@@ -3848,7 +3848,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SI=F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.95000076293945</v>
+        <v>74.77999877929688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6997</v>
+        <v>0.694</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>48.98279176848897</v>
+        <v>46.71263911332996</v>
       </c>
       <c r="H6" t="n">
         <v>0.6546</v>
@@ -3897,7 +3897,7 @@
         <v>6.335000038146973</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6869</v>
+        <v>0.6825</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>99.22200012207031</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6712</v>
+        <v>0.6758</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>3.117000102996826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3695</v>
+        <v>0.3676</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7389</v>
+        <v>0.7305</v>
       </c>
       <c r="D2" t="n">
         <v>0.5</v>
@@ -4090,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="H2" t="n">
         <v>4462.89990234375</v>
@@ -4118,7 +4118,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7134</v>
+        <v>0.7045</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
@@ -4136,16 +4136,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
-        <v>1960</v>
+        <v>1940</v>
       </c>
       <c r="H3" t="n">
-        <v>93.55999755859375</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>20.95</v>
+        <v>114.45</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4157,14 +4157,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>bullish trend, potentially oversold</t>
+          <t>bullish trend</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>BZ=F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7086</v>
+        <v>0.7004</v>
       </c>
       <c r="D4" t="n">
         <v>0.5</v>
@@ -4182,16 +4182,16 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>1950</v>
+        <v>1930</v>
       </c>
       <c r="H4" t="n">
-        <v>90.16000366210938</v>
+        <v>93.55999755859375</v>
       </c>
       <c r="I4" t="n">
-        <v>21.63</v>
+        <v>20.63</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>bullish trend</t>
+          <t>bullish trend, potentially oversold</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SI=F</t>
+          <t>CL=F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6949</v>
       </c>
       <c r="D5" t="n">
         <v>0.5</v>
@@ -4228,16 +4228,16 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G5" t="n">
-        <v>1940</v>
+        <v>1910</v>
       </c>
       <c r="H5" t="n">
-        <v>74.77999877929688</v>
+        <v>90.16000366210938</v>
       </c>
       <c r="I5" t="n">
-        <v>25.94</v>
+        <v>21.18</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SI=F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6997</v>
+        <v>0.694</v>
       </c>
       <c r="D6" t="n">
         <v>0.5</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>1930</v>
+        <v>1910</v>
       </c>
       <c r="H6" t="n">
-        <v>16.95000076293945</v>
+        <v>74.77999877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>113.86</v>
+        <v>25.54</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6869</v>
+        <v>0.6825</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G7" t="n">
-        <v>1890</v>
+        <v>1880</v>
       </c>
       <c r="H7" t="n">
         <v>6.335000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>298.34</v>
+        <v>296.76</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6712</v>
+        <v>0.6758</v>
       </c>
       <c r="D8" t="n">
         <v>0.5</v>
@@ -4366,16 +4366,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G8" t="n">
-        <v>1840</v>
+        <v>1860</v>
       </c>
       <c r="H8" t="n">
         <v>99.22200012207031</v>
       </c>
       <c r="I8" t="n">
-        <v>18.54</v>
+        <v>18.75</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3695</v>
+        <v>0.3676</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49380</v>
+        <v>49510</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34540</v>
+        <v>34810</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16080</v>
+        <v>15690</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4077.75</v>
+        <v>4054.95</v>
       </c>
       <c r="C2" t="n">
-        <v>49.38</v>
+        <v>49.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2851.8</v>
+        <v>2851.2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1328</v>
+        <v>1285</v>
       </c>
       <c r="C4" t="n">
-        <v>16.08</v>
+        <v>15.69</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>1328</v>
+        <v>1285</v>
       </c>
       <c r="E2" t="n">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0198</v>
+        <v>1.0206</v>
       </c>
     </row>
     <row r="3">
@@ -1341,13 +1341,13 @@
         <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>2851.8</v>
+        <v>2851.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2401.8</v>
+        <v>2401.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8079</v>
+        <v>0.8093</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>820.2</v>
+        <v>863.8</v>
       </c>
       <c r="E4" t="n">
-        <v>438.84</v>
+        <v>459.91</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4533</v>
+        <v>0.4509</v>
       </c>
     </row>
     <row r="5">
@@ -1389,13 +1389,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>1328</v>
+        <v>1285</v>
       </c>
       <c r="E5" t="n">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9755</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="6">
@@ -1413,13 +1413,13 @@
         <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>2851.8</v>
+        <v>2851.2</v>
       </c>
       <c r="E6" t="n">
-        <v>2401.8</v>
+        <v>2401.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="7">
@@ -1434,16 +1434,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="n">
-        <v>820.2</v>
+        <v>863.8</v>
       </c>
       <c r="E7" t="n">
-        <v>438.84</v>
+        <v>459.91</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4533</v>
+        <v>0.4509</v>
       </c>
     </row>
     <row r="8">
@@ -1461,13 +1461,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>1328</v>
+        <v>1285</v>
       </c>
       <c r="E8" t="n">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6198</v>
+        <v>0.6206</v>
       </c>
     </row>
     <row r="9">
@@ -1485,13 +1485,13 @@
         <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>2851.8</v>
+        <v>2851.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2401.8</v>
+        <v>2401.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7234</v>
+        <v>0.7312</v>
       </c>
     </row>
     <row r="10">
@@ -1506,16 +1506,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="n">
-        <v>820.2</v>
+        <v>863.8</v>
       </c>
       <c r="E10" t="n">
-        <v>438.84</v>
+        <v>459.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8509</v>
       </c>
     </row>
   </sheetData>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49380</v>
+        <v>49510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34540</v>
+        <v>34810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16080</v>
+        <v>15690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1940</v>
+        <v>1930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1930</v>
+        <v>1920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1910</v>
+        <v>1900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1910</v>
+        <v>1900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1880</v>
+        <v>1870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13.28</v>
+        <v>12.85</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -2646,19 +2646,19 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>13.28</v>
+        <v>12.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1328</v>
+        <v>1285</v>
       </c>
       <c r="M3" t="n">
         <v>553</v>
       </c>
       <c r="N3" t="n">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="O3" t="n">
-        <v>140.14</v>
+        <v>132.37</v>
       </c>
     </row>
     <row r="4">
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>635.26</v>
+        <v>635.83</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>212.6</v>
+        <v>212.09</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>440.36</v>
+        <v>441.79</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2850,19 +2850,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>271.85</v>
+        <v>270.33</v>
       </c>
       <c r="L7" t="n">
-        <v>4077.75</v>
+        <v>4054.95</v>
       </c>
       <c r="M7" t="n">
         <v>1896</v>
       </c>
       <c r="N7" t="n">
-        <v>2181.75</v>
+        <v>2158.95</v>
       </c>
       <c r="O7" t="n">
-        <v>115.07</v>
+        <v>113.87</v>
       </c>
     </row>
     <row r="8">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>384.83</v>
+        <v>384.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>132.51</v>
+        <v>137.87</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -3003,19 +3003,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>47.53</v>
+        <v>47.52</v>
       </c>
       <c r="L10" t="n">
-        <v>2851.8</v>
+        <v>2851.2</v>
       </c>
       <c r="M10" t="n">
         <v>450</v>
       </c>
       <c r="N10" t="n">
-        <v>2401.8</v>
+        <v>2401.2</v>
       </c>
       <c r="O10" t="n">
-        <v>533.73</v>
+        <v>533.6</v>
       </c>
     </row>
   </sheetData>
@@ -3155,7 +3155,7 @@
         <v>0.7716</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7305</v>
+        <v>0.7301</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>0.5102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7045</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>0.6015</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7004</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>0.5694</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6949</v>
+        <v>0.6945</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>0.5329</v>
       </c>
       <c r="J6" t="n">
-        <v>0.694</v>
+        <v>0.6936</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>0.4247</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6825</v>
+        <v>0.6821</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>0.3202</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6758</v>
+        <v>0.6754</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>0.309</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3676</v>
+        <v>0.3672</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>34.54</v>
+        <v>34.81</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>4462.89990234375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7305</v>
+        <v>0.7301</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>22.84227506012687</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>16.95000076293945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7045</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>48.98279176848897</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>93.55999755859375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7004</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>39.85259342193125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>90.16000366210938</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6949</v>
+        <v>0.6945</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>43.05869679501007</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>74.77999877929688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.694</v>
+        <v>0.6936</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>46.71263911332996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>6.335000038146973</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6825</v>
+        <v>0.6821</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>57.53321483881452</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>99.22200012207031</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6758</v>
+        <v>0.6754</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>67.98328018025629</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>3.117000102996826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3676</v>
+        <v>0.3672</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>69.1016731186359</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6546</v>
+        <v>0.6519</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7305</v>
+        <v>0.7301</v>
       </c>
       <c r="D2" t="n">
         <v>0.5</v>
@@ -4090,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="H2" t="n">
         <v>4462.89990234375</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7045</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
@@ -4136,16 +4136,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>1940</v>
+        <v>1930</v>
       </c>
       <c r="H3" t="n">
         <v>16.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>114.45</v>
+        <v>113.86</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7004</v>
+        <v>0.7</v>
       </c>
       <c r="D4" t="n">
         <v>0.5</v>
@@ -4182,16 +4182,16 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>1930</v>
+        <v>1920</v>
       </c>
       <c r="H4" t="n">
         <v>93.55999755859375</v>
       </c>
       <c r="I4" t="n">
-        <v>20.63</v>
+        <v>20.52</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6949</v>
+        <v>0.6945</v>
       </c>
       <c r="D5" t="n">
         <v>0.5</v>
@@ -4228,16 +4228,16 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>1910</v>
+        <v>1900</v>
       </c>
       <c r="H5" t="n">
         <v>90.16000366210938</v>
       </c>
       <c r="I5" t="n">
-        <v>21.18</v>
+        <v>21.07</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.694</v>
+        <v>0.6936</v>
       </c>
       <c r="D6" t="n">
         <v>0.5</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1910</v>
+        <v>1900</v>
       </c>
       <c r="H6" t="n">
         <v>74.77999877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>25.54</v>
+        <v>25.41</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6825</v>
+        <v>0.6821</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G7" t="n">
-        <v>1880</v>
+        <v>1870</v>
       </c>
       <c r="H7" t="n">
         <v>6.335000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>296.76</v>
+        <v>295.19</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6758</v>
+        <v>0.6754</v>
       </c>
       <c r="D8" t="n">
         <v>0.5</v>
@@ -4366,16 +4366,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="H8" t="n">
         <v>99.22200012207031</v>
       </c>
       <c r="I8" t="n">
-        <v>18.75</v>
+        <v>18.65</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3676</v>
+        <v>0.3672</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
@@ -4513,16 +4513,16 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1328</v>
+        <v>1285</v>
       </c>
       <c r="D2" t="n">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="E2" t="n">
-        <v>7.75</v>
+        <v>7.32</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9755</v>
+        <v>0.9762</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -4549,22 +4549,22 @@
         <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>2851.8</v>
+        <v>2851.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2401.8</v>
+        <v>2401.2</v>
       </c>
       <c r="E3" t="n">
-        <v>40.03</v>
+        <v>40.02</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.905</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7607</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5542</v>
+        <v>0.5653</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -4582,19 +4582,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="C4" t="n">
-        <v>820.2</v>
+        <v>863.8</v>
       </c>
       <c r="D4" t="n">
-        <v>438.84</v>
+        <v>459.98</v>
       </c>
       <c r="E4" t="n">
-        <v>145.45</v>
+        <v>143.98</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4533</v>
+        <v>0.4509</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="204">
   <si>
     <t>trade_date</t>
   </si>
@@ -518,7 +518,7 @@
     <t>potentially oversold</t>
   </si>
   <si>
-    <t>risk_score</t>
+    <t>asset_risk_score</t>
   </si>
   <si>
     <t>portfolio_risk</t>
@@ -549,6 +549,9 @@
   </si>
   <si>
     <t>tax_score</t>
+  </si>
+  <si>
+    <t>position_risk_score</t>
   </si>
   <si>
     <t>holding_score</t>
@@ -1486,13 +1489,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1500,16 +1503,16 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D2">
         <v>3963.91</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1517,16 +1520,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D3">
         <v>2834.03</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1534,16 +1537,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D4">
         <v>1228.97</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1564,10 +1567,10 @@
         <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1581,7 +1584,7 @@
         <v>49.98</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1595,7 +1598,7 @@
         <v>34.89</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1609,7 +1612,7 @@
         <v>15.13</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1624,7 +1627,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1644,7 +1647,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1664,7 +1667,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1684,7 +1687,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1704,7 +1707,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1724,7 +1727,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -1744,7 +1747,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1764,7 +1767,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1784,7 +1787,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -1804,7 +1807,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1840,13 +1843,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" t="s">
         <v>179</v>
       </c>
-      <c r="D1" t="s">
-        <v>178</v>
-      </c>
       <c r="E1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1860,10 +1863,10 @@
         <v>3963.91</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1877,10 +1880,10 @@
         <v>2834.03</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1894,10 +1897,10 @@
         <v>1228.97</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1917,15 +1920,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B2">
         <v>40000</v>
@@ -1933,7 +1936,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B3">
         <v>15000</v>
@@ -1941,7 +1944,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B4">
         <v>20000</v>
@@ -1949,7 +1952,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -1957,7 +1960,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B6">
         <v>33738.31</v>
@@ -1965,7 +1968,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B7">
         <v>70</v>
@@ -1973,7 +1976,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B8">
         <v>28000</v>
@@ -1981,7 +1984,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B9">
         <v>13000</v>
@@ -13344,10 +13347,10 @@
         <v>173</v>
       </c>
       <c r="H1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="I1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J1" t="s">
         <v>154</v>
@@ -13382,7 +13385,7 @@
         <v>0.8892</v>
       </c>
       <c r="J2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -13414,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -13446,7 +13449,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -629,7 +629,7 @@
     <t>TargetCashReserve</t>
   </si>
   <si>
-    <t>MonthlyContributions</t>
+    <t>Contributions</t>
   </si>
   <si>
     <t>MaxDeploymentPercent</t>
@@ -11843,7 +11843,7 @@
         <v>0.4085</v>
       </c>
       <c r="D41">
-        <v>0.3076</v>
+        <v>0.3085</v>
       </c>
       <c r="E41">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -11843,22 +11843,22 @@
         <v>0.4085</v>
       </c>
       <c r="D41">
-        <v>0.3085</v>
+        <v>0.3103</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="G41">
-        <v>72.29000000000001</v>
+        <v>71.48</v>
       </c>
       <c r="H41">
         <v>842.4000244140625</v>
       </c>
       <c r="I41">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J41" t="s">
         <v>153</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -11843,7 +11843,7 @@
         <v>0.4085</v>
       </c>
       <c r="D41">
-        <v>0.3103</v>
+        <v>0.3109</v>
       </c>
       <c r="E41">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -11843,7 +11843,7 @@
         <v>0.4085</v>
       </c>
       <c r="D41">
-        <v>0.3109</v>
+        <v>0.3117</v>
       </c>
       <c r="E41">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -239,10 +239,10 @@
     <t>CRWV</t>
   </si>
   <si>
+    <t>AMD</t>
+  </si>
+  <si>
     <t>LWLG</t>
-  </si>
-  <si>
-    <t>AMD</t>
   </si>
   <si>
     <t>PLAB</t>
@@ -1509,7 +1509,7 @@
         <v>183</v>
       </c>
       <c r="D2">
-        <v>3963.91</v>
+        <v>3820.98</v>
       </c>
       <c r="E2" t="s">
         <v>185</v>
@@ -1526,7 +1526,7 @@
         <v>183</v>
       </c>
       <c r="D3">
-        <v>2834.03</v>
+        <v>2730.88</v>
       </c>
       <c r="E3" t="s">
         <v>185</v>
@@ -1543,7 +1543,7 @@
         <v>184</v>
       </c>
       <c r="D4">
-        <v>1228.97</v>
+        <v>1389.16</v>
       </c>
       <c r="E4" t="s">
         <v>186</v>
@@ -1578,10 +1578,10 @@
         <v>149</v>
       </c>
       <c r="B2">
-        <v>4059.6</v>
+        <v>3918.9</v>
       </c>
       <c r="C2">
-        <v>49.98</v>
+        <v>48.75</v>
       </c>
       <c r="D2" t="s">
         <v>183</v>
@@ -1592,10 +1592,10 @@
         <v>148</v>
       </c>
       <c r="B3">
-        <v>2834.4</v>
+        <v>2731.2</v>
       </c>
       <c r="C3">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1606,10 +1606,10 @@
         <v>147</v>
       </c>
       <c r="B4">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="C4">
-        <v>15.13</v>
+        <v>17.28</v>
       </c>
       <c r="D4" t="s">
         <v>189</v>
@@ -1656,13 +1656,13 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="E2">
-        <v>676</v>
+        <v>836</v>
       </c>
       <c r="F2">
-        <v>1.0248</v>
+        <v>1.0279</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1676,13 +1676,13 @@
         <v>60</v>
       </c>
       <c r="D3">
-        <v>2834.4</v>
+        <v>2731.2</v>
       </c>
       <c r="E3">
-        <v>2384.4</v>
+        <v>2281.2</v>
       </c>
       <c r="F3">
-        <v>0.8161</v>
+        <v>0.8260999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1693,16 +1693,16 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="D4">
-        <v>936.6</v>
+        <v>879.8</v>
       </c>
       <c r="E4">
-        <v>499.17</v>
+        <v>454.14</v>
       </c>
       <c r="F4">
-        <v>0.4521</v>
+        <v>0.4572</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1716,13 +1716,13 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="E5">
-        <v>676</v>
+        <v>836</v>
       </c>
       <c r="F5">
-        <v>0.9804</v>
+        <v>0.9835</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1736,13 +1736,13 @@
         <v>60</v>
       </c>
       <c r="D6">
-        <v>2834.4</v>
+        <v>2731.2</v>
       </c>
       <c r="E6">
-        <v>2384.4</v>
+        <v>2281.2</v>
       </c>
       <c r="F6">
-        <v>0.912</v>
+        <v>0.9199000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1753,16 +1753,16 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="D7">
-        <v>936.6</v>
+        <v>879.8</v>
       </c>
       <c r="E7">
-        <v>499.17</v>
+        <v>454.14</v>
       </c>
       <c r="F7">
-        <v>0.4521</v>
+        <v>0.4572</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="E8">
-        <v>676</v>
+        <v>836</v>
       </c>
       <c r="F8">
-        <v>0.6248</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1796,13 +1796,13 @@
         <v>60</v>
       </c>
       <c r="D9">
-        <v>2834.4</v>
+        <v>2731.2</v>
       </c>
       <c r="E9">
-        <v>2384.4</v>
+        <v>2281.2</v>
       </c>
       <c r="F9">
-        <v>0.7389</v>
+        <v>0.7321</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1813,16 +1813,16 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="D10">
-        <v>936.6</v>
+        <v>879.8</v>
       </c>
       <c r="E10">
-        <v>499.17</v>
+        <v>454.14</v>
       </c>
       <c r="F10">
-        <v>0.8521</v>
+        <v>0.8572</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +1860,7 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>3963.91</v>
+        <v>3820.98</v>
       </c>
       <c r="D2" t="s">
         <v>183</v>
@@ -1877,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>2834.03</v>
+        <v>2730.88</v>
       </c>
       <c r="D3" t="s">
         <v>183</v>
@@ -1894,7 +1894,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>1228.97</v>
+        <v>1389.16</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -1955,7 +1955,7 @@
         <v>199</v>
       </c>
       <c r="B5">
-        <v>12000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1963,7 +1963,7 @@
         <v>200</v>
       </c>
       <c r="B6">
-        <v>33738.31</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1971,7 +1971,7 @@
         <v>201</v>
       </c>
       <c r="B7">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1979,7 +1979,7 @@
         <v>202</v>
       </c>
       <c r="B8">
-        <v>28000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1987,7 +1987,7 @@
         <v>203</v>
       </c>
       <c r="B9">
-        <v>13000</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2614,7 @@
         <v>34</v>
       </c>
       <c r="K2">
-        <v>12.29</v>
+        <v>13.89</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2658,19 +2658,19 @@
         <v>553</v>
       </c>
       <c r="K3">
-        <v>12.29</v>
+        <v>13.89</v>
       </c>
       <c r="L3">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="M3">
         <v>553</v>
       </c>
       <c r="N3">
-        <v>676</v>
+        <v>836</v>
       </c>
       <c r="O3">
-        <v>122.24</v>
+        <v>151.18</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2705,7 +2705,7 @@
         <v>32</v>
       </c>
       <c r="K4">
-        <v>632.51</v>
+        <v>600.47</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>33</v>
       </c>
       <c r="K5">
-        <v>211.14</v>
+        <v>224.36</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>34</v>
       </c>
       <c r="K6">
-        <v>435.79</v>
+        <v>415.88</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2846,19 +2846,19 @@
         <v>34</v>
       </c>
       <c r="K7">
-        <v>270.64</v>
+        <v>261.26</v>
       </c>
       <c r="L7">
-        <v>4059.6</v>
+        <v>3918.9</v>
       </c>
       <c r="M7">
         <v>1896</v>
       </c>
       <c r="N7">
-        <v>2163.6</v>
+        <v>2022.9</v>
       </c>
       <c r="O7">
-        <v>114.11</v>
+        <v>106.69</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2893,7 +2893,7 @@
         <v>34</v>
       </c>
       <c r="K8">
-        <v>376.43</v>
+        <v>372.58</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2940,7 +2940,7 @@
         <v>34</v>
       </c>
       <c r="K9">
-        <v>156.54</v>
+        <v>160.65</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2987,19 +2987,19 @@
         <v>34</v>
       </c>
       <c r="K10">
-        <v>47.24</v>
+        <v>45.52</v>
       </c>
       <c r="L10">
-        <v>2834.4</v>
+        <v>2731.2</v>
       </c>
       <c r="M10">
         <v>450</v>
       </c>
       <c r="N10">
-        <v>2384.4</v>
+        <v>2281.2</v>
       </c>
       <c r="O10">
-        <v>529.87</v>
+        <v>506.93</v>
       </c>
     </row>
   </sheetData>
@@ -3185,16 +3185,16 @@
         <v>70</v>
       </c>
       <c r="B4">
-        <v>10.6201000213623</v>
+        <v>504.6749877929688</v>
       </c>
       <c r="C4">
-        <v>11.68120206832886</v>
+        <v>327.9179010009765</v>
       </c>
       <c r="D4">
-        <v>5.99625052690506</v>
+        <v>237.5253751373291</v>
       </c>
       <c r="E4">
-        <v>29.84059297913404</v>
+        <v>62.96130036008142</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3203,25 +3203,25 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0.8508</v>
+        <v>0.6852</v>
       </c>
       <c r="I4">
-        <v>0.7016</v>
+        <v>0.3704</v>
       </c>
       <c r="J4">
-        <v>0.8044</v>
+        <v>0.8028</v>
       </c>
       <c r="K4" t="s">
         <v>142</v>
       </c>
       <c r="L4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M4">
-        <v>15.13</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8487</v>
+        <v>1</v>
       </c>
       <c r="O4" t="s">
         <v>153</v>
@@ -3230,10 +3230,10 @@
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0.4121</v>
+        <v>0.3148</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -3241,16 +3241,16 @@
         <v>71</v>
       </c>
       <c r="B5">
-        <v>504.6749877929688</v>
+        <v>10.6201000213623</v>
       </c>
       <c r="C5">
-        <v>327.9179010009765</v>
+        <v>11.68120206832886</v>
       </c>
       <c r="D5">
-        <v>237.5253751373291</v>
+        <v>5.99625052690506</v>
       </c>
       <c r="E5">
-        <v>62.96130036008142</v>
+        <v>29.84059297913404</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3259,25 +3259,25 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0.6852</v>
+        <v>0.8508</v>
       </c>
       <c r="I5">
-        <v>0.3704</v>
+        <v>0.7016</v>
       </c>
       <c r="J5">
-        <v>0.8028</v>
+        <v>0.8011</v>
       </c>
       <c r="K5" t="s">
         <v>142</v>
       </c>
       <c r="L5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>17.28</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0.8272</v>
       </c>
       <c r="O5" t="s">
         <v>153</v>
@@ -3286,10 +3286,10 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R5">
-        <v>0.3148</v>
+        <v>0.4121</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -3321,7 +3321,7 @@
         <v>0.4721</v>
       </c>
       <c r="J6">
-        <v>0.767</v>
+        <v>0.7638</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -3330,10 +3330,10 @@
         <v>147</v>
       </c>
       <c r="M6">
-        <v>15.13</v>
+        <v>17.28</v>
       </c>
       <c r="N6">
-        <v>0.8487</v>
+        <v>0.8272</v>
       </c>
       <c r="O6" t="s">
         <v>153</v>
@@ -3377,7 +3377,7 @@
         <v>0.7568</v>
       </c>
       <c r="J7">
-        <v>0.7169</v>
+        <v>0.7183</v>
       </c>
       <c r="K7" t="s">
         <v>18</v>
@@ -3386,10 +3386,10 @@
         <v>148</v>
       </c>
       <c r="M7">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N7">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O7" t="s">
         <v>153</v>
@@ -3433,7 +3433,7 @@
         <v>0.6506</v>
       </c>
       <c r="J8">
-        <v>0.6975</v>
+        <v>0.6989</v>
       </c>
       <c r="K8" t="s">
         <v>18</v>
@@ -3442,10 +3442,10 @@
         <v>148</v>
       </c>
       <c r="M8">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N8">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O8" t="s">
         <v>153</v>
@@ -3489,7 +3489,7 @@
         <v>0.4425</v>
       </c>
       <c r="J9">
-        <v>0.6973</v>
+        <v>0.6987</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -3498,10 +3498,10 @@
         <v>148</v>
       </c>
       <c r="M9">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N9">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O9" t="s">
         <v>153</v>
@@ -3545,7 +3545,7 @@
         <v>0.5721000000000001</v>
       </c>
       <c r="J10">
-        <v>0.6881</v>
+        <v>0.6895</v>
       </c>
       <c r="K10" t="s">
         <v>18</v>
@@ -3554,10 +3554,10 @@
         <v>148</v>
       </c>
       <c r="M10">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N10">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O10" t="s">
         <v>153</v>
@@ -3601,7 +3601,7 @@
         <v>0.6075</v>
       </c>
       <c r="J11">
-        <v>0.6870000000000001</v>
+        <v>0.6884</v>
       </c>
       <c r="K11" t="s">
         <v>18</v>
@@ -3610,10 +3610,10 @@
         <v>148</v>
       </c>
       <c r="M11">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N11">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O11" t="s">
         <v>153</v>
@@ -3657,7 +3657,7 @@
         <v>0.5871</v>
       </c>
       <c r="J12">
-        <v>0.6857</v>
+        <v>0.6871</v>
       </c>
       <c r="K12" t="s">
         <v>18</v>
@@ -3666,10 +3666,10 @@
         <v>148</v>
       </c>
       <c r="M12">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N12">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O12" t="s">
         <v>153</v>
@@ -3713,7 +3713,7 @@
         <v>0.527</v>
       </c>
       <c r="J13">
-        <v>0.6775</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="K13" t="s">
         <v>18</v>
@@ -3722,10 +3722,10 @@
         <v>148</v>
       </c>
       <c r="M13">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N13">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O13" t="s">
         <v>153</v>
@@ -3769,7 +3769,7 @@
         <v>0.4798</v>
       </c>
       <c r="J14">
-        <v>0.6736</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="K14" t="s">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>148</v>
       </c>
       <c r="M14">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N14">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O14" t="s">
         <v>153</v>
@@ -3825,7 +3825,7 @@
         <v>0.499</v>
       </c>
       <c r="J15">
-        <v>0.67</v>
+        <v>0.6714</v>
       </c>
       <c r="K15" t="s">
         <v>18</v>
@@ -3834,10 +3834,10 @@
         <v>148</v>
       </c>
       <c r="M15">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N15">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O15" t="s">
         <v>153</v>
@@ -3881,7 +3881,7 @@
         <v>0.5041</v>
       </c>
       <c r="J16">
-        <v>0.6694</v>
+        <v>0.6708</v>
       </c>
       <c r="K16" t="s">
         <v>18</v>
@@ -3890,10 +3890,10 @@
         <v>148</v>
       </c>
       <c r="M16">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N16">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O16" t="s">
         <v>153</v>
@@ -3937,7 +3937,7 @@
         <v>0.4418</v>
       </c>
       <c r="J17">
-        <v>0.6667</v>
+        <v>0.6681</v>
       </c>
       <c r="K17" t="s">
         <v>18</v>
@@ -3946,10 +3946,10 @@
         <v>148</v>
       </c>
       <c r="M17">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N17">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O17" t="s">
         <v>153</v>
@@ -3993,7 +3993,7 @@
         <v>0.4748</v>
       </c>
       <c r="J18">
-        <v>0.6652</v>
+        <v>0.6666</v>
       </c>
       <c r="K18" t="s">
         <v>18</v>
@@ -4002,10 +4002,10 @@
         <v>148</v>
       </c>
       <c r="M18">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N18">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O18" t="s">
         <v>153</v>
@@ -4049,7 +4049,7 @@
         <v>0.4626</v>
       </c>
       <c r="J19">
-        <v>0.6613</v>
+        <v>0.6627</v>
       </c>
       <c r="K19" t="s">
         <v>18</v>
@@ -4058,10 +4058,10 @@
         <v>148</v>
       </c>
       <c r="M19">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N19">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O19" t="s">
         <v>153</v>
@@ -4105,7 +4105,7 @@
         <v>0.4666</v>
       </c>
       <c r="J20">
-        <v>0.6611</v>
+        <v>0.6625</v>
       </c>
       <c r="K20" t="s">
         <v>18</v>
@@ -4114,10 +4114,10 @@
         <v>148</v>
       </c>
       <c r="M20">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N20">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O20" t="s">
         <v>153</v>
@@ -4161,7 +4161,7 @@
         <v>0.4511</v>
       </c>
       <c r="J21">
-        <v>0.6608000000000001</v>
+        <v>0.6621</v>
       </c>
       <c r="K21" t="s">
         <v>18</v>
@@ -4170,10 +4170,10 @@
         <v>148</v>
       </c>
       <c r="M21">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N21">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O21" t="s">
         <v>153</v>
@@ -4217,7 +4217,7 @@
         <v>0.3831</v>
       </c>
       <c r="J22">
-        <v>0.6603</v>
+        <v>0.6616</v>
       </c>
       <c r="K22" t="s">
         <v>18</v>
@@ -4226,10 +4226,10 @@
         <v>148</v>
       </c>
       <c r="M22">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N22">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O22" t="s">
         <v>153</v>
@@ -4246,19 +4246,19 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B23">
-        <v>289.6799926757812</v>
+        <v>270.2804870605469</v>
       </c>
       <c r="C23">
-        <v>270.0206011962891</v>
+        <v>246.6624099731445</v>
       </c>
       <c r="D23">
-        <v>253.1802939605713</v>
+        <v>231.5187524414063</v>
       </c>
       <c r="E23">
-        <v>57.0804147127497</v>
+        <v>47.50671781742124</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -4267,25 +4267,25 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>0.7146</v>
+        <v>0.7625</v>
       </c>
       <c r="I23">
-        <v>0.4292</v>
+        <v>0.5249</v>
       </c>
       <c r="J23">
-        <v>0.6511</v>
+        <v>0.6529</v>
       </c>
       <c r="K23" t="s">
         <v>18</v>
       </c>
       <c r="L23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M23">
-        <v>34.89</v>
+        <v>48.75</v>
       </c>
       <c r="N23">
-        <v>0.6511</v>
+        <v>0.5125</v>
       </c>
       <c r="O23" t="s">
         <v>153</v>
@@ -4297,24 +4297,24 @@
         <v>0.5</v>
       </c>
       <c r="R23">
-        <v>0.2601</v>
+        <v>0.3152</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="B24">
-        <v>270.2804870605469</v>
+        <v>289.6799926757812</v>
       </c>
       <c r="C24">
-        <v>246.6624099731445</v>
+        <v>270.0206011962891</v>
       </c>
       <c r="D24">
-        <v>231.5187524414063</v>
+        <v>253.1802939605713</v>
       </c>
       <c r="E24">
-        <v>47.50671781742124</v>
+        <v>57.0804147127497</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -4323,25 +4323,25 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>0.7625</v>
+        <v>0.7146</v>
       </c>
       <c r="I24">
-        <v>0.5249</v>
+        <v>0.4292</v>
       </c>
       <c r="J24">
-        <v>0.6511</v>
+        <v>0.6524</v>
       </c>
       <c r="K24" t="s">
         <v>18</v>
       </c>
       <c r="L24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M24">
-        <v>49.98</v>
+        <v>33.97</v>
       </c>
       <c r="N24">
-        <v>0.5002</v>
+        <v>0.6603</v>
       </c>
       <c r="O24" t="s">
         <v>153</v>
@@ -4353,7 +4353,7 @@
         <v>0.5</v>
       </c>
       <c r="R24">
-        <v>0.3152</v>
+        <v>0.2601</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -4385,7 +4385,7 @@
         <v>0.3639</v>
       </c>
       <c r="J25">
-        <v>0.6496</v>
+        <v>0.6509</v>
       </c>
       <c r="K25" t="s">
         <v>18</v>
@@ -4394,10 +4394,10 @@
         <v>148</v>
       </c>
       <c r="M25">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N25">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O25" t="s">
         <v>153</v>
@@ -4441,7 +4441,7 @@
         <v>0.2744</v>
       </c>
       <c r="J26">
-        <v>0.6479</v>
+        <v>0.6493</v>
       </c>
       <c r="K26" t="s">
         <v>18</v>
@@ -4450,10 +4450,10 @@
         <v>148</v>
       </c>
       <c r="M26">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N26">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O26" t="s">
         <v>153</v>
@@ -4497,7 +4497,7 @@
         <v>0.3322</v>
       </c>
       <c r="J27">
-        <v>0.6477000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="K27" t="s">
         <v>18</v>
@@ -4506,10 +4506,10 @@
         <v>148</v>
       </c>
       <c r="M27">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N27">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O27" t="s">
         <v>153</v>
@@ -4553,7 +4553,7 @@
         <v>0.3869</v>
       </c>
       <c r="J28">
-        <v>0.6435</v>
+        <v>0.6448</v>
       </c>
       <c r="K28" t="s">
         <v>18</v>
@@ -4562,10 +4562,10 @@
         <v>148</v>
       </c>
       <c r="M28">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N28">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O28" t="s">
         <v>153</v>
@@ -4609,7 +4609,7 @@
         <v>0.32</v>
       </c>
       <c r="J29">
-        <v>0.6431</v>
+        <v>0.6445</v>
       </c>
       <c r="K29" t="s">
         <v>18</v>
@@ -4618,10 +4618,10 @@
         <v>148</v>
       </c>
       <c r="M29">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N29">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O29" t="s">
         <v>153</v>
@@ -4665,7 +4665,7 @@
         <v>0.3127</v>
       </c>
       <c r="J30">
-        <v>0.6427</v>
+        <v>0.6441</v>
       </c>
       <c r="K30" t="s">
         <v>18</v>
@@ -4674,10 +4674,10 @@
         <v>148</v>
       </c>
       <c r="M30">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N30">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O30" t="s">
         <v>153</v>
@@ -4721,7 +4721,7 @@
         <v>0.2662</v>
       </c>
       <c r="J31">
-        <v>0.6422</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="K31" t="s">
         <v>18</v>
@@ -4730,10 +4730,10 @@
         <v>148</v>
       </c>
       <c r="M31">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N31">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O31" t="s">
         <v>153</v>
@@ -4777,7 +4777,7 @@
         <v>0.3628</v>
       </c>
       <c r="J32">
-        <v>0.6407</v>
+        <v>0.6421</v>
       </c>
       <c r="K32" t="s">
         <v>18</v>
@@ -4786,10 +4786,10 @@
         <v>148</v>
       </c>
       <c r="M32">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N32">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O32" t="s">
         <v>153</v>
@@ -4833,7 +4833,7 @@
         <v>0.2428</v>
       </c>
       <c r="J33">
-        <v>0.6342</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="K33" t="s">
         <v>18</v>
@@ -4842,10 +4842,10 @@
         <v>148</v>
       </c>
       <c r="M33">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N33">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O33" t="s">
         <v>153</v>
@@ -4889,7 +4889,7 @@
         <v>0.2081</v>
       </c>
       <c r="J34">
-        <v>0.6321</v>
+        <v>0.6335</v>
       </c>
       <c r="K34" t="s">
         <v>18</v>
@@ -4898,10 +4898,10 @@
         <v>148</v>
       </c>
       <c r="M34">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N34">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O34" t="s">
         <v>153</v>
@@ -4945,7 +4945,7 @@
         <v>0.3289</v>
       </c>
       <c r="J35">
-        <v>0.6319</v>
+        <v>0.6333</v>
       </c>
       <c r="K35" t="s">
         <v>18</v>
@@ -4954,10 +4954,10 @@
         <v>148</v>
       </c>
       <c r="M35">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N35">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O35" t="s">
         <v>153</v>
@@ -5001,7 +5001,7 @@
         <v>0.3131</v>
       </c>
       <c r="J36">
-        <v>0.6308</v>
+        <v>0.6322</v>
       </c>
       <c r="K36" t="s">
         <v>18</v>
@@ -5010,10 +5010,10 @@
         <v>148</v>
       </c>
       <c r="M36">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N36">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O36" t="s">
         <v>153</v>
@@ -5057,7 +5057,7 @@
         <v>0.1925</v>
       </c>
       <c r="J37">
-        <v>0.6299</v>
+        <v>0.6313</v>
       </c>
       <c r="K37" t="s">
         <v>18</v>
@@ -5066,10 +5066,10 @@
         <v>148</v>
       </c>
       <c r="M37">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N37">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O37" t="s">
         <v>153</v>
@@ -5113,7 +5113,7 @@
         <v>0.154</v>
       </c>
       <c r="J38">
-        <v>0.6256</v>
+        <v>0.627</v>
       </c>
       <c r="K38" t="s">
         <v>18</v>
@@ -5122,10 +5122,10 @@
         <v>148</v>
       </c>
       <c r="M38">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N38">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O38" t="s">
         <v>153</v>
@@ -5169,7 +5169,7 @@
         <v>0.177</v>
       </c>
       <c r="J39">
-        <v>0.6239</v>
+        <v>0.6253</v>
       </c>
       <c r="K39" t="s">
         <v>18</v>
@@ -5178,10 +5178,10 @@
         <v>148</v>
       </c>
       <c r="M39">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N39">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O39" t="s">
         <v>153</v>
@@ -5225,7 +5225,7 @@
         <v>0.1659</v>
       </c>
       <c r="J40">
-        <v>0.6237</v>
+        <v>0.6251</v>
       </c>
       <c r="K40" t="s">
         <v>18</v>
@@ -5234,10 +5234,10 @@
         <v>148</v>
       </c>
       <c r="M40">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N40">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O40" t="s">
         <v>153</v>
@@ -5281,7 +5281,7 @@
         <v>0.1927</v>
       </c>
       <c r="J41">
-        <v>0.6235000000000001</v>
+        <v>0.6249</v>
       </c>
       <c r="K41" t="s">
         <v>18</v>
@@ -5290,10 +5290,10 @@
         <v>148</v>
       </c>
       <c r="M41">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N41">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O41" t="s">
         <v>153</v>
@@ -5337,7 +5337,7 @@
         <v>0.1777</v>
       </c>
       <c r="J42">
-        <v>0.6231</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="K42" t="s">
         <v>18</v>
@@ -5346,10 +5346,10 @@
         <v>148</v>
       </c>
       <c r="M42">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N42">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O42" t="s">
         <v>153</v>
@@ -5393,7 +5393,7 @@
         <v>0.1524</v>
       </c>
       <c r="J43">
-        <v>0.6222</v>
+        <v>0.6236</v>
       </c>
       <c r="K43" t="s">
         <v>18</v>
@@ -5402,10 +5402,10 @@
         <v>148</v>
       </c>
       <c r="M43">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N43">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O43" t="s">
         <v>153</v>
@@ -5449,7 +5449,7 @@
         <v>0.1162</v>
       </c>
       <c r="J44">
-        <v>0.6114000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="K44" t="s">
         <v>18</v>
@@ -5458,10 +5458,10 @@
         <v>148</v>
       </c>
       <c r="M44">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N44">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O44" t="s">
         <v>153</v>
@@ -5590,19 +5590,19 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B47">
-        <v>627.8200073242188</v>
+        <v>842.4000244140625</v>
       </c>
       <c r="C47">
-        <v>618.4381994628907</v>
+        <v>865.7679956054687</v>
       </c>
       <c r="D47">
-        <v>665.8026406860351</v>
+        <v>994.0373638916016</v>
       </c>
       <c r="E47">
-        <v>60.53759874634309</v>
+        <v>40.11494958459248</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -5611,25 +5611,25 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0.1973</v>
+        <v>0.2994</v>
       </c>
       <c r="I47">
-        <v>0.3946</v>
+        <v>0.5989</v>
       </c>
       <c r="J47">
-        <v>0.4093</v>
+        <v>0.4099</v>
       </c>
       <c r="K47" t="s">
         <v>143</v>
       </c>
       <c r="L47" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>33.97</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0.6603</v>
       </c>
       <c r="O47" t="s">
         <v>153</v>
@@ -5641,24 +5641,24 @@
         <v>0.5</v>
       </c>
       <c r="R47">
-        <v>0.3338</v>
+        <v>0.4733</v>
       </c>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="B48">
-        <v>842.4000244140625</v>
+        <v>627.8200073242188</v>
       </c>
       <c r="C48">
-        <v>865.7679956054687</v>
+        <v>618.4381994628907</v>
       </c>
       <c r="D48">
-        <v>994.0373638916016</v>
+        <v>665.8026406860351</v>
       </c>
       <c r="E48">
-        <v>40.11494958459248</v>
+        <v>60.53759874634309</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -5667,25 +5667,25 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0.2994</v>
+        <v>0.1973</v>
       </c>
       <c r="I48">
-        <v>0.5989</v>
+        <v>0.3946</v>
       </c>
       <c r="J48">
-        <v>0.4085</v>
+        <v>0.4093</v>
       </c>
       <c r="K48" t="s">
         <v>143</v>
       </c>
       <c r="L48" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="M48">
-        <v>34.89</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>0.6511</v>
+        <v>1</v>
       </c>
       <c r="O48" t="s">
         <v>153</v>
@@ -5697,7 +5697,7 @@
         <v>0.5</v>
       </c>
       <c r="R48">
-        <v>0.4733</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -5729,19 +5729,19 @@
         <v>0.6603</v>
       </c>
       <c r="J49">
-        <v>0.3998</v>
+        <v>0.4012</v>
       </c>
       <c r="K49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L49" t="s">
         <v>148</v>
       </c>
       <c r="M49">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N49">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O49" t="s">
         <v>153</v>
@@ -5785,7 +5785,7 @@
         <v>0.6298</v>
       </c>
       <c r="J50">
-        <v>0.3957</v>
+        <v>0.3971</v>
       </c>
       <c r="K50" t="s">
         <v>144</v>
@@ -5794,10 +5794,10 @@
         <v>148</v>
       </c>
       <c r="M50">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N50">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O50" t="s">
         <v>153</v>
@@ -5841,7 +5841,7 @@
         <v>0.5545</v>
       </c>
       <c r="J51">
-        <v>0.3852</v>
+        <v>0.3866</v>
       </c>
       <c r="K51" t="s">
         <v>144</v>
@@ -5850,10 +5850,10 @@
         <v>148</v>
       </c>
       <c r="M51">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N51">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O51" t="s">
         <v>153</v>
@@ -5897,7 +5897,7 @@
         <v>0.5809</v>
       </c>
       <c r="J52">
-        <v>0.3849</v>
+        <v>0.3863</v>
       </c>
       <c r="K52" t="s">
         <v>144</v>
@@ -5906,10 +5906,10 @@
         <v>148</v>
       </c>
       <c r="M52">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N52">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O52" t="s">
         <v>153</v>
@@ -5953,7 +5953,7 @@
         <v>0.5475</v>
       </c>
       <c r="J53">
-        <v>0.3836</v>
+        <v>0.385</v>
       </c>
       <c r="K53" t="s">
         <v>144</v>
@@ -5962,10 +5962,10 @@
         <v>148</v>
       </c>
       <c r="M53">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N53">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O53" t="s">
         <v>153</v>
@@ -6009,7 +6009,7 @@
         <v>0.5421</v>
       </c>
       <c r="J54">
-        <v>0.3784</v>
+        <v>0.3798</v>
       </c>
       <c r="K54" t="s">
         <v>144</v>
@@ -6018,10 +6018,10 @@
         <v>148</v>
       </c>
       <c r="M54">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N54">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O54" t="s">
         <v>153</v>
@@ -6065,7 +6065,7 @@
         <v>0.4753</v>
       </c>
       <c r="J55">
-        <v>0.3764</v>
+        <v>0.3778</v>
       </c>
       <c r="K55" t="s">
         <v>144</v>
@@ -6074,10 +6074,10 @@
         <v>148</v>
       </c>
       <c r="M55">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N55">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O55" t="s">
         <v>153</v>
@@ -6121,7 +6121,7 @@
         <v>0.5065</v>
       </c>
       <c r="J56">
-        <v>0.3754</v>
+        <v>0.3768</v>
       </c>
       <c r="K56" t="s">
         <v>144</v>
@@ -6130,10 +6130,10 @@
         <v>148</v>
       </c>
       <c r="M56">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N56">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O56" t="s">
         <v>153</v>
@@ -6177,7 +6177,7 @@
         <v>0.5144</v>
       </c>
       <c r="J57">
-        <v>0.3751</v>
+        <v>0.3765</v>
       </c>
       <c r="K57" t="s">
         <v>144</v>
@@ -6186,10 +6186,10 @@
         <v>148</v>
       </c>
       <c r="M57">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N57">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O57" t="s">
         <v>153</v>
@@ -6233,7 +6233,7 @@
         <v>0.4911</v>
       </c>
       <c r="J58">
-        <v>0.3707</v>
+        <v>0.372</v>
       </c>
       <c r="K58" t="s">
         <v>144</v>
@@ -6242,10 +6242,10 @@
         <v>148</v>
       </c>
       <c r="M58">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N58">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O58" t="s">
         <v>153</v>
@@ -6289,7 +6289,7 @@
         <v>0.4823</v>
       </c>
       <c r="J59">
-        <v>0.3677</v>
+        <v>0.3691</v>
       </c>
       <c r="K59" t="s">
         <v>144</v>
@@ -6298,10 +6298,10 @@
         <v>148</v>
       </c>
       <c r="M59">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N59">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O59" t="s">
         <v>153</v>
@@ -6345,7 +6345,7 @@
         <v>0.448</v>
       </c>
       <c r="J60">
-        <v>0.3676</v>
+        <v>0.369</v>
       </c>
       <c r="K60" t="s">
         <v>144</v>
@@ -6354,10 +6354,10 @@
         <v>148</v>
       </c>
       <c r="M60">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N60">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O60" t="s">
         <v>153</v>
@@ -6401,7 +6401,7 @@
         <v>0.4072</v>
       </c>
       <c r="J61">
-        <v>0.3633</v>
+        <v>0.3647</v>
       </c>
       <c r="K61" t="s">
         <v>144</v>
@@ -6410,10 +6410,10 @@
         <v>148</v>
       </c>
       <c r="M61">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N61">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O61" t="s">
         <v>153</v>
@@ -6457,7 +6457,7 @@
         <v>0.4251</v>
       </c>
       <c r="J62">
-        <v>0.3615</v>
+        <v>0.3629</v>
       </c>
       <c r="K62" t="s">
         <v>144</v>
@@ -6466,10 +6466,10 @@
         <v>148</v>
       </c>
       <c r="M62">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N62">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O62" t="s">
         <v>153</v>
@@ -6513,7 +6513,7 @@
         <v>0.3951</v>
       </c>
       <c r="J63">
-        <v>0.3613</v>
+        <v>0.3627</v>
       </c>
       <c r="K63" t="s">
         <v>144</v>
@@ -6522,10 +6522,10 @@
         <v>148</v>
       </c>
       <c r="M63">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N63">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O63" t="s">
         <v>153</v>
@@ -6569,7 +6569,7 @@
         <v>0.3647</v>
       </c>
       <c r="J64">
-        <v>0.3601</v>
+        <v>0.3615</v>
       </c>
       <c r="K64" t="s">
         <v>144</v>
@@ -6578,10 +6578,10 @@
         <v>148</v>
       </c>
       <c r="M64">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N64">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O64" t="s">
         <v>153</v>
@@ -6625,7 +6625,7 @@
         <v>0.3813</v>
       </c>
       <c r="J65">
-        <v>0.3557</v>
+        <v>0.3571</v>
       </c>
       <c r="K65" t="s">
         <v>144</v>
@@ -6634,10 +6634,10 @@
         <v>148</v>
       </c>
       <c r="M65">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N65">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O65" t="s">
         <v>153</v>
@@ -6681,7 +6681,7 @@
         <v>0.4173</v>
       </c>
       <c r="J66">
-        <v>0.3553</v>
+        <v>0.3567</v>
       </c>
       <c r="K66" t="s">
         <v>144</v>
@@ -6690,10 +6690,10 @@
         <v>148</v>
       </c>
       <c r="M66">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N66">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O66" t="s">
         <v>153</v>
@@ -6737,7 +6737,7 @@
         <v>0.3845</v>
       </c>
       <c r="J67">
-        <v>0.3543</v>
+        <v>0.3557</v>
       </c>
       <c r="K67" t="s">
         <v>144</v>
@@ -6746,10 +6746,10 @@
         <v>148</v>
       </c>
       <c r="M67">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N67">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O67" t="s">
         <v>153</v>
@@ -6793,7 +6793,7 @@
         <v>0.3053</v>
       </c>
       <c r="J68">
-        <v>0.354</v>
+        <v>0.3554</v>
       </c>
       <c r="K68" t="s">
         <v>144</v>
@@ -6802,10 +6802,10 @@
         <v>148</v>
       </c>
       <c r="M68">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N68">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O68" t="s">
         <v>153</v>
@@ -6849,7 +6849,7 @@
         <v>0.3708</v>
       </c>
       <c r="J69">
-        <v>0.3513</v>
+        <v>0.3527</v>
       </c>
       <c r="K69" t="s">
         <v>144</v>
@@ -6858,10 +6858,10 @@
         <v>148</v>
       </c>
       <c r="M69">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N69">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O69" t="s">
         <v>153</v>
@@ -6905,7 +6905,7 @@
         <v>0.3241</v>
       </c>
       <c r="J70">
-        <v>0.3493</v>
+        <v>0.3507</v>
       </c>
       <c r="K70" t="s">
         <v>144</v>
@@ -6914,10 +6914,10 @@
         <v>148</v>
       </c>
       <c r="M70">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N70">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O70" t="s">
         <v>153</v>
@@ -6961,7 +6961,7 @@
         <v>0.3412</v>
       </c>
       <c r="J71">
-        <v>0.3481</v>
+        <v>0.3495</v>
       </c>
       <c r="K71" t="s">
         <v>144</v>
@@ -6970,10 +6970,10 @@
         <v>148</v>
       </c>
       <c r="M71">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N71">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O71" t="s">
         <v>153</v>
@@ -7017,7 +7017,7 @@
         <v>0.4192</v>
       </c>
       <c r="J72">
-        <v>0.3477</v>
+        <v>0.3491</v>
       </c>
       <c r="K72" t="s">
         <v>144</v>
@@ -7026,10 +7026,10 @@
         <v>148</v>
       </c>
       <c r="M72">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N72">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O72" t="s">
         <v>153</v>
@@ -7073,7 +7073,7 @@
         <v>0.3099</v>
       </c>
       <c r="J73">
-        <v>0.3466</v>
+        <v>0.348</v>
       </c>
       <c r="K73" t="s">
         <v>144</v>
@@ -7082,10 +7082,10 @@
         <v>148</v>
       </c>
       <c r="M73">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N73">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O73" t="s">
         <v>153</v>
@@ -7129,7 +7129,7 @@
         <v>0.3114</v>
       </c>
       <c r="J74">
-        <v>0.3435</v>
+        <v>0.3449</v>
       </c>
       <c r="K74" t="s">
         <v>144</v>
@@ -7138,10 +7138,10 @@
         <v>148</v>
       </c>
       <c r="M74">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N74">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O74" t="s">
         <v>153</v>
@@ -7185,7 +7185,7 @@
         <v>0.2727</v>
       </c>
       <c r="J75">
-        <v>0.3393</v>
+        <v>0.3407</v>
       </c>
       <c r="K75" t="s">
         <v>144</v>
@@ -7194,10 +7194,10 @@
         <v>148</v>
       </c>
       <c r="M75">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N75">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O75" t="s">
         <v>153</v>
@@ -7241,7 +7241,7 @@
         <v>0.2664</v>
       </c>
       <c r="J76">
-        <v>0.3386</v>
+        <v>0.34</v>
       </c>
       <c r="K76" t="s">
         <v>144</v>
@@ -7250,10 +7250,10 @@
         <v>148</v>
       </c>
       <c r="M76">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N76">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O76" t="s">
         <v>153</v>
@@ -7297,7 +7297,7 @@
         <v>0.2376</v>
       </c>
       <c r="J77">
-        <v>0.335</v>
+        <v>0.3364</v>
       </c>
       <c r="K77" t="s">
         <v>144</v>
@@ -7306,10 +7306,10 @@
         <v>148</v>
       </c>
       <c r="M77">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N77">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O77" t="s">
         <v>153</v>
@@ -7353,7 +7353,7 @@
         <v>0.214</v>
       </c>
       <c r="J78">
-        <v>0.3329</v>
+        <v>0.3343</v>
       </c>
       <c r="K78" t="s">
         <v>144</v>
@@ -7362,10 +7362,10 @@
         <v>148</v>
       </c>
       <c r="M78">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N78">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O78" t="s">
         <v>153</v>
@@ -7409,7 +7409,7 @@
         <v>0.1772</v>
       </c>
       <c r="J79">
-        <v>0.3311</v>
+        <v>0.3325</v>
       </c>
       <c r="K79" t="s">
         <v>144</v>
@@ -7418,10 +7418,10 @@
         <v>148</v>
       </c>
       <c r="M79">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N79">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O79" t="s">
         <v>153</v>
@@ -7465,7 +7465,7 @@
         <v>0.075</v>
       </c>
       <c r="J80">
-        <v>0.3118</v>
+        <v>0.3132</v>
       </c>
       <c r="K80" t="s">
         <v>144</v>
@@ -7474,10 +7474,10 @@
         <v>148</v>
       </c>
       <c r="M80">
-        <v>34.89</v>
+        <v>33.97</v>
       </c>
       <c r="N80">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="O80" t="s">
         <v>153</v>
@@ -7612,19 +7612,19 @@
         <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4">
-        <v>10.6201000213623</v>
+        <v>504.6749877929688</v>
       </c>
       <c r="D4">
-        <v>0.8044</v>
+        <v>0.8028</v>
       </c>
       <c r="E4">
-        <v>11.68120206832886</v>
+        <v>327.9179010009765</v>
       </c>
       <c r="F4">
-        <v>5.99625052690506</v>
+        <v>237.5253751373291</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -7633,13 +7633,13 @@
         <v>155</v>
       </c>
       <c r="I4">
-        <v>29.84059297913404</v>
+        <v>62.96130036008142</v>
       </c>
       <c r="J4">
-        <v>0.8487</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -7647,19 +7647,19 @@
         <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5">
-        <v>504.6749877929688</v>
+        <v>10.6201000213623</v>
       </c>
       <c r="D5">
-        <v>0.8028</v>
+        <v>0.8011</v>
       </c>
       <c r="E5">
-        <v>327.9179010009765</v>
+        <v>11.68120206832886</v>
       </c>
       <c r="F5">
-        <v>237.5253751373291</v>
+        <v>5.99625052690506</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -7668,13 +7668,13 @@
         <v>155</v>
       </c>
       <c r="I5">
-        <v>62.96130036008142</v>
+        <v>29.84059297913404</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.8272</v>
       </c>
       <c r="K5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7688,7 +7688,7 @@
         <v>12.17000007629395</v>
       </c>
       <c r="D6">
-        <v>0.767</v>
+        <v>0.7638</v>
       </c>
       <c r="E6">
         <v>9.490199975967407</v>
@@ -7706,7 +7706,7 @@
         <v>52.79048555853054</v>
       </c>
       <c r="J6">
-        <v>0.8487</v>
+        <v>0.8272</v>
       </c>
       <c r="K6" t="s">
         <v>156</v>
@@ -7723,7 +7723,7 @@
         <v>32.22999954223633</v>
       </c>
       <c r="D7">
-        <v>0.7169</v>
+        <v>0.7183</v>
       </c>
       <c r="E7">
         <v>46.35139991760254</v>
@@ -7741,7 +7741,7 @@
         <v>24.32237410558415</v>
       </c>
       <c r="J7">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K7" t="s">
         <v>158</v>
@@ -7758,7 +7758,7 @@
         <v>378.1099853515625</v>
       </c>
       <c r="D8">
-        <v>0.6975</v>
+        <v>0.6989</v>
       </c>
       <c r="E8">
         <v>345.0875982666016</v>
@@ -7776,7 +7776,7 @@
         <v>34.93956665818956</v>
       </c>
       <c r="J8">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K8" t="s">
         <v>158</v>
@@ -7793,7 +7793,7 @@
         <v>79.44499969482422</v>
       </c>
       <c r="D9">
-        <v>0.6973</v>
+        <v>0.6987</v>
       </c>
       <c r="E9">
         <v>77.7081005859375</v>
@@ -7811,7 +7811,7 @@
         <v>55.74873620999067</v>
       </c>
       <c r="J9">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K9" t="s">
         <v>159</v>
@@ -7828,7 +7828,7 @@
         <v>118.0699996948242</v>
       </c>
       <c r="D10">
-        <v>0.6881</v>
+        <v>0.6895</v>
       </c>
       <c r="E10">
         <v>82.51759986877441</v>
@@ -7846,7 +7846,7 @@
         <v>42.79099330023248</v>
       </c>
       <c r="J10">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K10" t="s">
         <v>159</v>
@@ -7863,7 +7863,7 @@
         <v>313.2200012207031</v>
       </c>
       <c r="D11">
-        <v>0.6870000000000001</v>
+        <v>0.6884</v>
       </c>
       <c r="E11">
         <v>307.3132015991211</v>
@@ -7881,7 +7881,7 @@
         <v>39.25098385656076</v>
       </c>
       <c r="J11">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K11" t="s">
         <v>158</v>
@@ -7898,7 +7898,7 @@
         <v>192.1600036621094</v>
       </c>
       <c r="D12">
-        <v>0.6857</v>
+        <v>0.6871</v>
       </c>
       <c r="E12">
         <v>156.3657997131348</v>
@@ -7916,7 +7916,7 @@
         <v>41.29244115486681</v>
       </c>
       <c r="J12">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K12" t="s">
         <v>159</v>
@@ -7933,7 +7933,7 @@
         <v>92</v>
       </c>
       <c r="D13">
-        <v>0.6775</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="E13">
         <v>76.30360012054443</v>
@@ -7951,7 +7951,7 @@
         <v>47.29547809343844</v>
       </c>
       <c r="J13">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K13" t="s">
         <v>159</v>
@@ -7968,7 +7968,7 @@
         <v>156.1300048828125</v>
       </c>
       <c r="D14">
-        <v>0.6736</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E14">
         <v>147.9280003356934</v>
@@ -7986,7 +7986,7 @@
         <v>52.01954969224415</v>
       </c>
       <c r="J14">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K14" t="s">
         <v>159</v>
@@ -8003,7 +8003,7 @@
         <v>452.6400146484375</v>
       </c>
       <c r="D15">
-        <v>0.67</v>
+        <v>0.6714</v>
       </c>
       <c r="E15">
         <v>407.5396551513672</v>
@@ -8021,7 +8021,7 @@
         <v>50.0953380320746</v>
       </c>
       <c r="J15">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K15" t="s">
         <v>159</v>
@@ -8038,7 +8038,7 @@
         <v>400.5350036621094</v>
       </c>
       <c r="D16">
-        <v>0.6694</v>
+        <v>0.6708</v>
       </c>
       <c r="E16">
         <v>392.7751910400391</v>
@@ -8056,7 +8056,7 @@
         <v>49.58712417755017</v>
       </c>
       <c r="J16">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K16" t="s">
         <v>159</v>
@@ -8073,7 +8073,7 @@
         <v>1646.010009765625</v>
       </c>
       <c r="D17">
-        <v>0.6667</v>
+        <v>0.6681</v>
       </c>
       <c r="E17">
         <v>1077.626197509766</v>
@@ -8091,7 +8091,7 @@
         <v>55.81680137154054</v>
       </c>
       <c r="J17">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K17" t="s">
         <v>159</v>
@@ -8108,7 +8108,7 @@
         <v>1616.579956054688</v>
       </c>
       <c r="D18">
-        <v>0.6652</v>
+        <v>0.6666</v>
       </c>
       <c r="E18">
         <v>1454.169504394531</v>
@@ -8126,7 +8126,7 @@
         <v>52.52196685210854</v>
       </c>
       <c r="J18">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K18" t="s">
         <v>159</v>
@@ -8143,7 +8143,7 @@
         <v>437.3999938964844</v>
       </c>
       <c r="D19">
-        <v>0.6613</v>
+        <v>0.6627</v>
       </c>
       <c r="E19">
         <v>385.4850103759766</v>
@@ -8161,7 +8161,7 @@
         <v>53.74493548838463</v>
       </c>
       <c r="J19">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K19" t="s">
         <v>159</v>
@@ -8178,7 +8178,7 @@
         <v>418.6000061035156</v>
       </c>
       <c r="D20">
-        <v>0.6611</v>
+        <v>0.6625</v>
       </c>
       <c r="E20">
         <v>379.3989996337891</v>
@@ -8196,7 +8196,7 @@
         <v>53.33591079169458</v>
       </c>
       <c r="J20">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K20" t="s">
         <v>159</v>
@@ -8213,7 +8213,7 @@
         <v>1930.010009765625</v>
       </c>
       <c r="D21">
-        <v>0.6608000000000001</v>
+        <v>0.6621</v>
       </c>
       <c r="E21">
         <v>1730.606733398437</v>
@@ -8231,7 +8231,7 @@
         <v>54.89072413854991</v>
       </c>
       <c r="J21">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K21" t="s">
         <v>159</v>
@@ -8248,7 +8248,7 @@
         <v>104.2600021362305</v>
       </c>
       <c r="D22">
-        <v>0.6603</v>
+        <v>0.6616</v>
       </c>
       <c r="E22">
         <v>57.82180000305176</v>
@@ -8266,7 +8266,7 @@
         <v>61.68698087643116</v>
       </c>
       <c r="J22">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K22" t="s">
         <v>159</v>
@@ -8274,22 +8274,22 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C23">
-        <v>289.6799926757812</v>
+        <v>270.2804870605469</v>
       </c>
       <c r="D23">
-        <v>0.6511</v>
+        <v>0.6529</v>
       </c>
       <c r="E23">
-        <v>270.0206011962891</v>
+        <v>246.6624099731445</v>
       </c>
       <c r="F23">
-        <v>253.1802939605713</v>
+        <v>231.5187524414063</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -8298,10 +8298,10 @@
         <v>18</v>
       </c>
       <c r="I23">
-        <v>57.0804147127497</v>
+        <v>47.50671781742124</v>
       </c>
       <c r="J23">
-        <v>0.6511</v>
+        <v>0.5125</v>
       </c>
       <c r="K23" t="s">
         <v>159</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C24">
-        <v>270.2804870605469</v>
+        <v>289.6799926757812</v>
       </c>
       <c r="D24">
-        <v>0.6511</v>
+        <v>0.6524</v>
       </c>
       <c r="E24">
-        <v>246.6624099731445</v>
+        <v>270.0206011962891</v>
       </c>
       <c r="F24">
-        <v>231.5187524414063</v>
+        <v>253.1802939605713</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -8333,10 +8333,10 @@
         <v>18</v>
       </c>
       <c r="I24">
-        <v>47.50671781742124</v>
+        <v>57.0804147127497</v>
       </c>
       <c r="J24">
-        <v>0.5002</v>
+        <v>0.6603</v>
       </c>
       <c r="K24" t="s">
         <v>159</v>
@@ -8353,7 +8353,7 @@
         <v>229.1600036621094</v>
       </c>
       <c r="D25">
-        <v>0.6496</v>
+        <v>0.6509</v>
       </c>
       <c r="E25">
         <v>158.9171002197266</v>
@@ -8371,7 +8371,7 @@
         <v>63.60836779223327</v>
       </c>
       <c r="J25">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K25" t="s">
         <v>159</v>
@@ -8388,7 +8388,7 @@
         <v>17.04999923706055</v>
       </c>
       <c r="D26">
-        <v>0.6479</v>
+        <v>0.6493</v>
       </c>
       <c r="E26">
         <v>13.00539991378784</v>
@@ -8406,7 +8406,7 @@
         <v>72.55699795767705</v>
       </c>
       <c r="J26">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K26" t="s">
         <v>159</v>
@@ -8423,7 +8423,7 @@
         <v>160.1600036621094</v>
       </c>
       <c r="D27">
-        <v>0.6477000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="E27">
         <v>148.8601998901367</v>
@@ -8441,7 +8441,7 @@
         <v>66.77614060250662</v>
       </c>
       <c r="J27">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K27" t="s">
         <v>159</v>
@@ -8458,7 +8458,7 @@
         <v>599.510009765625</v>
       </c>
       <c r="D28">
-        <v>0.6435</v>
+        <v>0.6448</v>
       </c>
       <c r="E28">
         <v>484.7420007324219</v>
@@ -8476,7 +8476,7 @@
         <v>61.30891593465972</v>
       </c>
       <c r="J28">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K28" t="s">
         <v>159</v>
@@ -8493,7 +8493,7 @@
         <v>204.1499938964844</v>
       </c>
       <c r="D29">
-        <v>0.6431</v>
+        <v>0.6445</v>
       </c>
       <c r="E29">
         <v>146.6463409423828</v>
@@ -8511,7 +8511,7 @@
         <v>68.00380242260704</v>
       </c>
       <c r="J29">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K29" t="s">
         <v>159</v>
@@ -8528,7 +8528,7 @@
         <v>946.5999755859375</v>
       </c>
       <c r="D30">
-        <v>0.6427</v>
+        <v>0.6441</v>
       </c>
       <c r="E30">
         <v>557.0476068115235</v>
@@ -8546,7 +8546,7 @@
         <v>68.7262179373717</v>
       </c>
       <c r="J30">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K30" t="s">
         <v>159</v>
@@ -8563,7 +8563,7 @@
         <v>38.50500106811523</v>
       </c>
       <c r="D31">
-        <v>0.6422</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="E31">
         <v>32.1243002319336</v>
@@ -8581,7 +8581,7 @@
         <v>73.3756782876756</v>
       </c>
       <c r="J31">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K31" t="s">
         <v>159</v>
@@ -8598,7 +8598,7 @@
         <v>566.0499877929688</v>
       </c>
       <c r="D32">
-        <v>0.6407</v>
+        <v>0.6421</v>
       </c>
       <c r="E32">
         <v>437.5693994140625</v>
@@ -8616,7 +8616,7 @@
         <v>63.72471183466363</v>
       </c>
       <c r="J32">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K32" t="s">
         <v>159</v>
@@ -8633,7 +8633,7 @@
         <v>238.2949981689453</v>
       </c>
       <c r="D33">
-        <v>0.6342</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="E33">
         <v>208.7752996826172</v>
@@ -8651,7 +8651,7 @@
         <v>75.71506554383619</v>
       </c>
       <c r="J33">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K33" t="s">
         <v>159</v>
@@ -8668,7 +8668,7 @@
         <v>136.8999938964844</v>
       </c>
       <c r="D34">
-        <v>0.6321</v>
+        <v>0.6335</v>
       </c>
       <c r="E34">
         <v>96.12719970703125</v>
@@ -8686,7 +8686,7 @@
         <v>79.18690654428941</v>
       </c>
       <c r="J34">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K34" t="s">
         <v>159</v>
@@ -8703,7 +8703,7 @@
         <v>737.3900146484375</v>
       </c>
       <c r="D35">
-        <v>0.6319</v>
+        <v>0.6333</v>
       </c>
       <c r="E35">
         <v>652.883203125</v>
@@ -8721,7 +8721,7 @@
         <v>67.11149544232157</v>
       </c>
       <c r="J35">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K35" t="s">
         <v>159</v>
@@ -8738,7 +8738,7 @@
         <v>756.3519897460938</v>
       </c>
       <c r="D36">
-        <v>0.6308</v>
+        <v>0.6322</v>
       </c>
       <c r="E36">
         <v>703.6085009765625</v>
@@ -8756,7 +8756,7 @@
         <v>68.69012892264033</v>
       </c>
       <c r="J36">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K36" t="s">
         <v>159</v>
@@ -8773,7 +8773,7 @@
         <v>120.9800033569336</v>
       </c>
       <c r="D37">
-        <v>0.6299</v>
+        <v>0.6313</v>
       </c>
       <c r="E37">
         <v>93.07899780273438</v>
@@ -8791,7 +8791,7 @@
         <v>80.7508215679068</v>
       </c>
       <c r="J37">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K37" t="s">
         <v>159</v>
@@ -8808,7 +8808,7 @@
         <v>243.2799987792969</v>
       </c>
       <c r="D38">
-        <v>0.6256</v>
+        <v>0.627</v>
       </c>
       <c r="E38">
         <v>153.0168003845215</v>
@@ -8826,7 +8826,7 @@
         <v>84.59564438781432</v>
       </c>
       <c r="J38">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K38" t="s">
         <v>159</v>
@@ -8843,7 +8843,7 @@
         <v>279.1600036621094</v>
       </c>
       <c r="D39">
-        <v>0.6239</v>
+        <v>0.6253</v>
       </c>
       <c r="E39">
         <v>191.3692004394531</v>
@@ -8861,7 +8861,7 @@
         <v>82.30017258450833</v>
       </c>
       <c r="J39">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K39" t="s">
         <v>159</v>
@@ -8878,7 +8878,7 @@
         <v>335.5</v>
       </c>
       <c r="D40">
-        <v>0.6237</v>
+        <v>0.6251</v>
       </c>
       <c r="E40">
         <v>190.2706001281738</v>
@@ -8896,7 +8896,7 @@
         <v>83.40800204702586</v>
       </c>
       <c r="J40">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K40" t="s">
         <v>159</v>
@@ -8913,7 +8913,7 @@
         <v>351.0299987792969</v>
       </c>
       <c r="D41">
-        <v>0.6235000000000001</v>
+        <v>0.6249</v>
       </c>
       <c r="E41">
         <v>198.3919012451172</v>
@@ -8931,7 +8931,7 @@
         <v>80.72804757289227</v>
       </c>
       <c r="J41">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K41" t="s">
         <v>159</v>
@@ -8948,7 +8948,7 @@
         <v>311.3699951171875</v>
       </c>
       <c r="D42">
-        <v>0.6231</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="E42">
         <v>275.0954885864258</v>
@@ -8966,7 +8966,7 @@
         <v>82.2306288932008</v>
       </c>
       <c r="J42">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K42" t="s">
         <v>159</v>
@@ -8983,7 +8983,7 @@
         <v>416.2999877929688</v>
       </c>
       <c r="D43">
-        <v>0.6222</v>
+        <v>0.6236</v>
       </c>
       <c r="E43">
         <v>215.5247280883789</v>
@@ -9001,7 +9001,7 @@
         <v>84.76398843833833</v>
       </c>
       <c r="J43">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K43" t="s">
         <v>159</v>
@@ -9018,7 +9018,7 @@
         <v>726.155029296875</v>
       </c>
       <c r="D44">
-        <v>0.6114000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="E44">
         <v>482.4160998535156</v>
@@ -9036,7 +9036,7 @@
         <v>88.38347146788549</v>
       </c>
       <c r="J44">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K44" t="s">
         <v>159</v>
@@ -9114,22 +9114,22 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C47">
-        <v>627.8200073242188</v>
+        <v>842.4000244140625</v>
       </c>
       <c r="D47">
-        <v>0.4093</v>
+        <v>0.4099</v>
       </c>
       <c r="E47">
-        <v>618.4381994628907</v>
+        <v>865.7679956054687</v>
       </c>
       <c r="F47">
-        <v>665.8026406860351</v>
+        <v>994.0373638916016</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
@@ -9138,33 +9138,33 @@
         <v>143</v>
       </c>
       <c r="I47">
-        <v>60.53759874634309</v>
+        <v>40.11494958459248</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0.6603</v>
       </c>
       <c r="K47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C48">
-        <v>842.4000244140625</v>
+        <v>627.8200073242188</v>
       </c>
       <c r="D48">
-        <v>0.4085</v>
+        <v>0.4093</v>
       </c>
       <c r="E48">
-        <v>865.7679956054687</v>
+        <v>618.4381994628907</v>
       </c>
       <c r="F48">
-        <v>994.0373638916016</v>
+        <v>665.8026406860351</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -9173,13 +9173,13 @@
         <v>143</v>
       </c>
       <c r="I48">
-        <v>40.11494958459248</v>
+        <v>60.53759874634309</v>
       </c>
       <c r="J48">
-        <v>0.6511</v>
+        <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -9193,7 +9193,7 @@
         <v>477.3900146484375</v>
       </c>
       <c r="D49">
-        <v>0.3998</v>
+        <v>0.4012</v>
       </c>
       <c r="E49">
         <v>460.8796020507813</v>
@@ -9205,13 +9205,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I49">
         <v>33.9729473260635</v>
       </c>
       <c r="J49">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K49" t="s">
         <v>162</v>
@@ -9228,7 +9228,7 @@
         <v>46.2599983215332</v>
       </c>
       <c r="D50">
-        <v>0.3957</v>
+        <v>0.3971</v>
       </c>
       <c r="E50">
         <v>54.42779983520508</v>
@@ -9246,7 +9246,7 @@
         <v>37.02109183728933</v>
       </c>
       <c r="J50">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K50" t="s">
         <v>162</v>
@@ -9263,7 +9263,7 @@
         <v>138.6849975585938</v>
       </c>
       <c r="D51">
-        <v>0.3852</v>
+        <v>0.3866</v>
       </c>
       <c r="E51">
         <v>143.5598994445801</v>
@@ -9281,7 +9281,7 @@
         <v>44.54939598291897</v>
       </c>
       <c r="J51">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K51" t="s">
         <v>161</v>
@@ -9298,7 +9298,7 @@
         <v>286.9700012207031</v>
       </c>
       <c r="D52">
-        <v>0.3849</v>
+        <v>0.3863</v>
       </c>
       <c r="E52">
         <v>292.132578125</v>
@@ -9316,7 +9316,7 @@
         <v>41.9093713425007</v>
       </c>
       <c r="J52">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K52" t="s">
         <v>161</v>
@@ -9333,7 +9333,7 @@
         <v>86.90000152587891</v>
       </c>
       <c r="D53">
-        <v>0.3836</v>
+        <v>0.385</v>
       </c>
       <c r="E53">
         <v>91.8866683959961</v>
@@ -9351,7 +9351,7 @@
         <v>45.24736162443781</v>
       </c>
       <c r="J53">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K53" t="s">
         <v>161</v>
@@ -9368,7 +9368,7 @@
         <v>71.58999633789062</v>
       </c>
       <c r="D54">
-        <v>0.3784</v>
+        <v>0.3798</v>
       </c>
       <c r="E54">
         <v>65.93580032348633</v>
@@ -9386,7 +9386,7 @@
         <v>45.78635887349753</v>
       </c>
       <c r="J54">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K54" t="s">
         <v>161</v>
@@ -9403,7 +9403,7 @@
         <v>256.6799926757812</v>
       </c>
       <c r="D55">
-        <v>0.3764</v>
+        <v>0.3778</v>
       </c>
       <c r="E55">
         <v>244.4010006713867</v>
@@ -9421,7 +9421,7 @@
         <v>52.4694725609674</v>
       </c>
       <c r="J55">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K55" t="s">
         <v>161</v>
@@ -9438,7 +9438,7 @@
         <v>12.4601001739502</v>
       </c>
       <c r="D56">
-        <v>0.3754</v>
+        <v>0.3768</v>
       </c>
       <c r="E56">
         <v>11.46560195922851</v>
@@ -9456,7 +9456,7 @@
         <v>49.34571546247042</v>
       </c>
       <c r="J56">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K56" t="s">
         <v>161</v>
@@ -9473,7 +9473,7 @@
         <v>16.40999984741211</v>
       </c>
       <c r="D57">
-        <v>0.3751</v>
+        <v>0.3765</v>
       </c>
       <c r="E57">
         <v>14.91660001754761</v>
@@ -9491,7 +9491,7 @@
         <v>48.56229749649761</v>
       </c>
       <c r="J57">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K57" t="s">
         <v>161</v>
@@ -9508,7 +9508,7 @@
         <v>50.13999938964844</v>
       </c>
       <c r="D58">
-        <v>0.3707</v>
+        <v>0.372</v>
       </c>
       <c r="E58">
         <v>49.06369972229004</v>
@@ -9526,7 +9526,7 @@
         <v>50.89285279849747</v>
       </c>
       <c r="J58">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K58" t="s">
         <v>161</v>
@@ -9543,7 +9543,7 @@
         <v>8.979999542236328</v>
       </c>
       <c r="D59">
-        <v>0.3677</v>
+        <v>0.3691</v>
       </c>
       <c r="E59">
         <v>7.755500020980835</v>
@@ -9561,7 +9561,7 @@
         <v>51.77304029140512</v>
       </c>
       <c r="J59">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K59" t="s">
         <v>161</v>
@@ -9578,7 +9578,7 @@
         <v>42.81000137329102</v>
       </c>
       <c r="D60">
-        <v>0.3676</v>
+        <v>0.369</v>
       </c>
       <c r="E60">
         <v>37.38979988098144</v>
@@ -9596,7 +9596,7 @@
         <v>55.20473843066302</v>
       </c>
       <c r="J60">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K60" t="s">
         <v>161</v>
@@ -9613,7 +9613,7 @@
         <v>326.5499877929688</v>
       </c>
       <c r="D61">
-        <v>0.3633</v>
+        <v>0.3647</v>
       </c>
       <c r="E61">
         <v>272.237200012207</v>
@@ -9631,7 +9631,7 @@
         <v>59.28286837585451</v>
       </c>
       <c r="J61">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K61" t="s">
         <v>161</v>
@@ -9648,7 +9648,7 @@
         <v>3.535000085830688</v>
       </c>
       <c r="D62">
-        <v>0.3615</v>
+        <v>0.3629</v>
       </c>
       <c r="E62">
         <v>3.281500005722046</v>
@@ -9666,7 +9666,7 @@
         <v>57.49129481397203</v>
       </c>
       <c r="J62">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K62" t="s">
         <v>161</v>
@@ -9683,7 +9683,7 @@
         <v>11.64500045776367</v>
       </c>
       <c r="D63">
-        <v>0.3613</v>
+        <v>0.3627</v>
       </c>
       <c r="E63">
         <v>10.71590005874634</v>
@@ -9701,7 +9701,7 @@
         <v>60.49079921150475</v>
       </c>
       <c r="J63">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K63" t="s">
         <v>161</v>
@@ -9718,7 +9718,7 @@
         <v>144.8500061035156</v>
       </c>
       <c r="D64">
-        <v>0.3601</v>
+        <v>0.3615</v>
       </c>
       <c r="E64">
         <v>125.4602005004883</v>
@@ -9736,7 +9736,7 @@
         <v>63.52941319169427</v>
       </c>
       <c r="J64">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K64" t="s">
         <v>161</v>
@@ -9753,7 +9753,7 @@
         <v>24.07999992370605</v>
       </c>
       <c r="D65">
-        <v>0.3557</v>
+        <v>0.3571</v>
       </c>
       <c r="E65">
         <v>18.156100025177</v>
@@ -9771,7 +9771,7 @@
         <v>61.87049520601642</v>
       </c>
       <c r="J65">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K65" t="s">
         <v>161</v>
@@ -9788,7 +9788,7 @@
         <v>376.1700134277344</v>
       </c>
       <c r="D66">
-        <v>0.3553</v>
+        <v>0.3567</v>
       </c>
       <c r="E66">
         <v>322.0032006835938</v>
@@ -9806,7 +9806,7 @@
         <v>58.27090592171268</v>
       </c>
       <c r="J66">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K66" t="s">
         <v>161</v>
@@ -9823,7 +9823,7 @@
         <v>10.85499954223633</v>
       </c>
       <c r="D67">
-        <v>0.3543</v>
+        <v>0.3557</v>
       </c>
       <c r="E67">
         <v>8.953699989318848</v>
@@ -9841,7 +9841,7 @@
         <v>61.54747452974244</v>
       </c>
       <c r="J67">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K67" t="s">
         <v>161</v>
@@ -9858,7 +9858,7 @@
         <v>109.3625030517578</v>
       </c>
       <c r="D68">
-        <v>0.354</v>
+        <v>0.3554</v>
       </c>
       <c r="E68">
         <v>90.37204956054687</v>
@@ -9876,7 +9876,7 @@
         <v>69.46505928053598</v>
       </c>
       <c r="J68">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K68" t="s">
         <v>161</v>
@@ -9893,7 +9893,7 @@
         <v>8.024999618530273</v>
       </c>
       <c r="D69">
-        <v>0.3513</v>
+        <v>0.3527</v>
       </c>
       <c r="E69">
         <v>6.22210000038147</v>
@@ -9911,7 +9911,7 @@
         <v>62.92237220217377</v>
       </c>
       <c r="J69">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K69" t="s">
         <v>161</v>
@@ -9928,7 +9928,7 @@
         <v>223.4850006103516</v>
       </c>
       <c r="D70">
-        <v>0.3493</v>
+        <v>0.3507</v>
       </c>
       <c r="E70">
         <v>170.9187496948242</v>
@@ -9946,7 +9946,7 @@
         <v>67.58864039885938</v>
       </c>
       <c r="J70">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K70" t="s">
         <v>161</v>
@@ -9963,7 +9963,7 @@
         <v>78.55000305175781</v>
       </c>
       <c r="D71">
-        <v>0.3481</v>
+        <v>0.3495</v>
       </c>
       <c r="E71">
         <v>62.95691932678223</v>
@@ -9981,7 +9981,7 @@
         <v>65.88147838728383</v>
       </c>
       <c r="J71">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K71" t="s">
         <v>161</v>
@@ -9998,7 +9998,7 @@
         <v>81.58999633789062</v>
       </c>
       <c r="D72">
-        <v>0.3477</v>
+        <v>0.3491</v>
       </c>
       <c r="E72">
         <v>74.40000007629395</v>
@@ -10016,7 +10016,7 @@
         <v>58.07715318316384</v>
       </c>
       <c r="J72">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K72" t="s">
         <v>161</v>
@@ -10033,7 +10033,7 @@
         <v>5.026599884033203</v>
       </c>
       <c r="D73">
-        <v>0.3466</v>
+        <v>0.348</v>
       </c>
       <c r="E73">
         <v>3.864331970214844</v>
@@ -10051,7 +10051,7 @@
         <v>69.011043961692</v>
       </c>
       <c r="J73">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K73" t="s">
         <v>161</v>
@@ -10068,7 +10068,7 @@
         <v>442.6698913574219</v>
       </c>
       <c r="D74">
-        <v>0.3435</v>
+        <v>0.3449</v>
       </c>
       <c r="E74">
         <v>401.9135546875</v>
@@ -10086,7 +10086,7 @@
         <v>68.86465938081456</v>
       </c>
       <c r="J74">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K74" t="s">
         <v>161</v>
@@ -10103,7 +10103,7 @@
         <v>68.98000335693359</v>
       </c>
       <c r="D75">
-        <v>0.3393</v>
+        <v>0.3407</v>
       </c>
       <c r="E75">
         <v>43.68120010375976</v>
@@ -10121,7 +10121,7 @@
         <v>72.73146105094992</v>
       </c>
       <c r="J75">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K75" t="s">
         <v>161</v>
@@ -10138,7 +10138,7 @@
         <v>45.6150016784668</v>
       </c>
       <c r="D76">
-        <v>0.3386</v>
+        <v>0.34</v>
       </c>
       <c r="E76">
         <v>28.65929988861084</v>
@@ -10156,7 +10156,7 @@
         <v>73.36374709939457</v>
       </c>
       <c r="J76">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K76" t="s">
         <v>161</v>
@@ -10173,7 +10173,7 @@
         <v>613.1300048828125</v>
       </c>
       <c r="D77">
-        <v>0.335</v>
+        <v>0.3364</v>
       </c>
       <c r="E77">
         <v>457.9214019775391</v>
@@ -10191,7 +10191,7 @@
         <v>76.23765512710006</v>
       </c>
       <c r="J77">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K77" t="s">
         <v>161</v>
@@ -10208,7 +10208,7 @@
         <v>122.8566970825195</v>
       </c>
       <c r="D78">
-        <v>0.3329</v>
+        <v>0.3343</v>
       </c>
       <c r="E78">
         <v>97.60793411254883</v>
@@ -10226,7 +10226,7 @@
         <v>78.60111662018215</v>
       </c>
       <c r="J78">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K78" t="s">
         <v>161</v>
@@ -10243,7 +10243,7 @@
         <v>297.8349914550781</v>
       </c>
       <c r="D79">
-        <v>0.3311</v>
+        <v>0.3325</v>
       </c>
       <c r="E79">
         <v>237.9992828369141</v>
@@ -10261,7 +10261,7 @@
         <v>82.27680786422185</v>
       </c>
       <c r="J79">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K79" t="s">
         <v>161</v>
@@ -10278,7 +10278,7 @@
         <v>253.3600006103516</v>
       </c>
       <c r="D80">
-        <v>0.3118</v>
+        <v>0.3132</v>
       </c>
       <c r="E80">
         <v>155.9348007202148</v>
@@ -10296,7 +10296,7 @@
         <v>92.49556488986379</v>
       </c>
       <c r="J80">
-        <v>0.6511</v>
+        <v>0.6603</v>
       </c>
       <c r="K80" t="s">
         <v>161</v>
@@ -10361,22 +10361,22 @@
         <v>0.8158</v>
       </c>
       <c r="D2">
-        <v>0.2519</v>
+        <v>0.2573</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>7.32</v>
+        <v>7.27</v>
       </c>
       <c r="G2">
-        <v>594.59</v>
+        <v>584.4400000000001</v>
       </c>
       <c r="H2">
         <v>217.2599945068359</v>
       </c>
       <c r="I2">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="s">
         <v>153</v>
@@ -10390,7 +10390,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
         <v>155</v>
@@ -10399,7 +10399,7 @@
         <v>0.8028</v>
       </c>
       <c r="D3">
-        <v>0.4746</v>
+        <v>0.4743</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -10408,7 +10408,7 @@
         <v>5.06</v>
       </c>
       <c r="G3">
-        <v>411.01</v>
+        <v>406.78</v>
       </c>
       <c r="H3">
         <v>504.6749877929688</v>
@@ -10434,25 +10434,25 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>0.6973</v>
+        <v>0.6987</v>
       </c>
       <c r="D4">
-        <v>0.1232</v>
+        <v>0.1222</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="G4">
-        <v>271.3</v>
+        <v>274.13</v>
       </c>
       <c r="H4">
         <v>79.44499969482422</v>
       </c>
       <c r="I4">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="s">
         <v>153</v>
@@ -10475,22 +10475,22 @@
         <v>0.8250999999999999</v>
       </c>
       <c r="D5">
-        <v>0.6634</v>
+        <v>0.6728</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>3.33</v>
+        <v>3.24</v>
       </c>
       <c r="G5">
-        <v>270.49</v>
+        <v>260.47</v>
       </c>
       <c r="H5">
         <v>105.504997253418</v>
       </c>
       <c r="I5">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="J5" t="s">
         <v>153</v>
@@ -10510,7 +10510,7 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>0.6308</v>
+        <v>0.6322</v>
       </c>
       <c r="D6">
         <v>0.1066</v>
@@ -10519,10 +10519,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="G6">
-        <v>250.18</v>
+        <v>252.43</v>
       </c>
       <c r="H6">
         <v>756.3519897460938</v>
@@ -10548,19 +10548,19 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>0.6511</v>
+        <v>0.6524</v>
       </c>
       <c r="D7">
-        <v>0.1516</v>
+        <v>0.1517</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="G7">
-        <v>245.31</v>
+        <v>246.8</v>
       </c>
       <c r="H7">
         <v>289.6799926757812</v>
@@ -10586,7 +10586,7 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>0.6319</v>
+        <v>0.6333</v>
       </c>
       <c r="D8">
         <v>0.1443</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>240.43</v>
+        <v>241.17</v>
       </c>
       <c r="H8">
         <v>737.3900146484375</v>
@@ -10624,19 +10624,19 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>0.6975</v>
+        <v>0.6989</v>
       </c>
       <c r="D9">
-        <v>0.2463</v>
+        <v>0.2465</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="G9">
-        <v>233.12</v>
+        <v>234.74</v>
       </c>
       <c r="H9">
         <v>378.1099853515625</v>
@@ -10662,25 +10662,25 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0.6231</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="D10">
-        <v>0.1752</v>
+        <v>0.1759</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="G10">
-        <v>228.25</v>
+        <v>229.11</v>
       </c>
       <c r="H10">
         <v>311.3699951171875</v>
       </c>
       <c r="I10">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="J10" t="s">
         <v>153</v>
@@ -10700,19 +10700,19 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>0.6694</v>
+        <v>0.6708</v>
       </c>
       <c r="D11">
-        <v>0.2473</v>
+        <v>0.2467</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="G11">
-        <v>223.38</v>
+        <v>225.09</v>
       </c>
       <c r="H11">
         <v>400.5350036621094</v>
@@ -10738,19 +10738,19 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <v>0.67</v>
+        <v>0.6714</v>
       </c>
       <c r="D12">
-        <v>0.2587</v>
+        <v>0.2589</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>220.13</v>
+        <v>221.88</v>
       </c>
       <c r="H12">
         <v>452.6400146484375</v>
@@ -10776,19 +10776,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.6435</v>
+        <v>0.6448</v>
       </c>
       <c r="D13">
-        <v>0.2472</v>
+        <v>0.2471</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="G13">
-        <v>215.25</v>
+        <v>217.06</v>
       </c>
       <c r="H13">
         <v>599.510009765625</v>
@@ -10808,31 +10808,31 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14">
-        <v>0.6611</v>
+        <v>0.6313</v>
       </c>
       <c r="D14">
-        <v>0.281</v>
+        <v>0.2495</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="G14">
-        <v>211.19</v>
+        <v>211.43</v>
       </c>
       <c r="H14">
-        <v>418.6000061035156</v>
+        <v>120.9800033569336</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="J14" t="s">
         <v>153</v>
@@ -10846,31 +10846,31 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0.6299</v>
+        <v>0.6625</v>
       </c>
       <c r="D15">
-        <v>0.2495</v>
+        <v>0.2827</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="G15">
-        <v>210.38</v>
+        <v>211.43</v>
       </c>
       <c r="H15">
-        <v>120.9800033569336</v>
+        <v>418.6000061035156</v>
       </c>
       <c r="I15">
-        <v>1.74</v>
+        <v>0.51</v>
       </c>
       <c r="J15" t="s">
         <v>153</v>
@@ -10890,19 +10890,19 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>0.6407</v>
+        <v>0.6421</v>
       </c>
       <c r="D16">
-        <v>0.2726</v>
+        <v>0.2724</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="G16">
-        <v>207.13</v>
+        <v>208.21</v>
       </c>
       <c r="H16">
         <v>566.0499877929688</v>
@@ -10928,19 +10928,19 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>0.6652</v>
+        <v>0.6666</v>
       </c>
       <c r="D17">
-        <v>0.3205</v>
+        <v>0.3203</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="G17">
-        <v>200.63</v>
+        <v>201.78</v>
       </c>
       <c r="H17">
         <v>1616.579956054688</v>
@@ -10966,25 +10966,25 @@
         <v>18</v>
       </c>
       <c r="C18">
-        <v>0.6321</v>
+        <v>0.6335</v>
       </c>
       <c r="D18">
-        <v>0.2996</v>
+        <v>0.3038</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G18">
-        <v>196.57</v>
+        <v>196.15</v>
       </c>
       <c r="H18">
         <v>136.8999938964844</v>
       </c>
       <c r="I18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J18" t="s">
         <v>153</v>
@@ -11004,25 +11004,25 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>0.6613</v>
+        <v>0.6627</v>
       </c>
       <c r="D19">
-        <v>0.3562</v>
+        <v>0.3569</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="G19">
-        <v>189.26</v>
+        <v>190.53</v>
       </c>
       <c r="H19">
         <v>437.3999938964844</v>
       </c>
       <c r="I19">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J19" t="s">
         <v>153</v>
@@ -11042,25 +11042,25 @@
         <v>18</v>
       </c>
       <c r="C20">
-        <v>0.6608000000000001</v>
+        <v>0.6621</v>
       </c>
       <c r="D20">
-        <v>0.3762</v>
+        <v>0.3757</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="G20">
-        <v>182.76</v>
+        <v>184.1</v>
       </c>
       <c r="H20">
         <v>1930.010009765625</v>
       </c>
       <c r="I20">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J20" t="s">
         <v>153</v>
@@ -11074,31 +11074,31 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21">
-        <v>0.6857</v>
+        <v>0.6253</v>
       </c>
       <c r="D21">
-        <v>0.4093</v>
+        <v>0.3667</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G21">
-        <v>180.33</v>
+        <v>176.86</v>
       </c>
       <c r="H21">
-        <v>192.1600036621094</v>
+        <v>279.1600036621094</v>
       </c>
       <c r="I21">
-        <v>0.9399999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="J21" t="s">
         <v>153</v>
@@ -11112,31 +11112,31 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
         <v>18</v>
       </c>
       <c r="C22">
-        <v>0.6239</v>
+        <v>0.649</v>
       </c>
       <c r="D22">
-        <v>0.3621</v>
+        <v>0.3975</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="G22">
-        <v>177.08</v>
+        <v>174.45</v>
       </c>
       <c r="H22">
-        <v>279.1600036621094</v>
+        <v>160.1600036621094</v>
       </c>
       <c r="I22">
-        <v>0.63</v>
+        <v>1.09</v>
       </c>
       <c r="J22" t="s">
         <v>153</v>
@@ -11150,31 +11150,31 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23">
-        <v>0.6477000000000001</v>
+        <v>0.6884</v>
       </c>
       <c r="D23">
-        <v>0.3933</v>
+        <v>0.4345</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="G23">
-        <v>174.64</v>
+        <v>173.64</v>
       </c>
       <c r="H23">
-        <v>160.1600036621094</v>
+        <v>313.2200012207031</v>
       </c>
       <c r="I23">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="J23" t="s">
         <v>153</v>
@@ -11183,21 +11183,21 @@
         <v>1.2</v>
       </c>
       <c r="L23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
       </c>
       <c r="C24">
-        <v>0.6870000000000001</v>
+        <v>0.6871</v>
       </c>
       <c r="D24">
-        <v>0.4343</v>
+        <v>0.4402</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -11206,13 +11206,13 @@
         <v>2.13</v>
       </c>
       <c r="G24">
-        <v>173.01</v>
+        <v>171.23</v>
       </c>
       <c r="H24">
-        <v>313.2200012207031</v>
+        <v>192.1600036621094</v>
       </c>
       <c r="I24">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="J24" t="s">
         <v>153</v>
@@ -11221,7 +11221,7 @@
         <v>1.2</v>
       </c>
       <c r="L24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -11232,19 +11232,19 @@
         <v>18</v>
       </c>
       <c r="C25">
-        <v>0.6431</v>
+        <v>0.6445</v>
       </c>
       <c r="D25">
-        <v>0.4407</v>
+        <v>0.4439</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G25">
-        <v>160.02</v>
+        <v>159.98</v>
       </c>
       <c r="H25">
         <v>204.1499938964844</v>
@@ -11270,19 +11270,19 @@
         <v>18</v>
       </c>
       <c r="C26">
-        <v>0.6114000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="D26">
-        <v>0.4174</v>
+        <v>0.4215</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G26">
-        <v>158.39</v>
+        <v>158.37</v>
       </c>
       <c r="H26">
         <v>726.155029296875</v>
@@ -11308,25 +11308,25 @@
         <v>18</v>
       </c>
       <c r="C27">
-        <v>0.6422</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="D27">
-        <v>0.484</v>
+        <v>0.4773</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G27">
-        <v>147.02</v>
+        <v>150.33</v>
       </c>
       <c r="H27">
         <v>38.50500106811523</v>
       </c>
       <c r="I27">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="s">
         <v>153</v>
@@ -11340,31 +11340,31 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
       </c>
       <c r="C28">
-        <v>0.6342</v>
+        <v>0.6895</v>
       </c>
       <c r="D28">
-        <v>0.493</v>
+        <v>0.5324</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G28">
-        <v>142.96</v>
+        <v>143.9</v>
       </c>
       <c r="H28">
-        <v>238.2949981689453</v>
+        <v>118.0699996948242</v>
       </c>
       <c r="I28">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="J28" t="s">
         <v>153</v>
@@ -11378,31 +11378,31 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
         <v>18</v>
       </c>
       <c r="C29">
-        <v>0.6881</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="D29">
-        <v>0.5342</v>
+        <v>0.5026</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G29">
-        <v>142.15</v>
+        <v>141.49</v>
       </c>
       <c r="H29">
-        <v>118.0699996948242</v>
+        <v>238.2949981689453</v>
       </c>
       <c r="I29">
-        <v>1.2</v>
+        <v>0.59</v>
       </c>
       <c r="J29" t="s">
         <v>153</v>
@@ -11422,19 +11422,19 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>0.6222</v>
+        <v>0.6236</v>
       </c>
       <c r="D30">
-        <v>0.5019</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G30">
-        <v>137.27</v>
+        <v>136.66</v>
       </c>
       <c r="H30">
         <v>416.2999877929688</v>
@@ -11460,19 +11460,19 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>0.6235000000000001</v>
+        <v>0.6249</v>
       </c>
       <c r="D31">
-        <v>0.5138</v>
+        <v>0.5285</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G31">
-        <v>134.84</v>
+        <v>131.84</v>
       </c>
       <c r="H31">
         <v>351.0299987792969</v>
@@ -11498,19 +11498,19 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>0.6427</v>
+        <v>0.6441</v>
       </c>
       <c r="D32">
-        <v>0.5426</v>
+        <v>0.5443</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G32">
-        <v>130.78</v>
+        <v>131.04</v>
       </c>
       <c r="H32">
         <v>946.5999755859375</v>
@@ -11536,19 +11536,19 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>0.6256</v>
+        <v>0.627</v>
       </c>
       <c r="D33">
-        <v>0.5397</v>
+        <v>0.5462</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G33">
-        <v>127.53</v>
+        <v>127.02</v>
       </c>
       <c r="H33">
         <v>243.2799987792969</v>
@@ -11577,16 +11577,16 @@
         <v>0.4589</v>
       </c>
       <c r="D34">
-        <v>0.3406</v>
+        <v>0.3435</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G34">
-        <v>117.78</v>
+        <v>115.76</v>
       </c>
       <c r="H34">
         <v>434.2398986816406</v>
@@ -11606,31 +11606,31 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>0.4093</v>
+        <v>0.6681</v>
       </c>
       <c r="D35">
-        <v>0.3289</v>
+        <v>0.6424</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G35">
-        <v>107.22</v>
+        <v>106.92</v>
       </c>
       <c r="H35">
-        <v>627.8200073242188</v>
+        <v>1646.010009765625</v>
       </c>
       <c r="I35">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="J35" t="s">
         <v>153</v>
@@ -11639,36 +11639,36 @@
         <v>1.2</v>
       </c>
       <c r="L35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="C36">
-        <v>0.6667</v>
+        <v>0.4093</v>
       </c>
       <c r="D36">
-        <v>0.6431</v>
+        <v>0.3324</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G36">
-        <v>105.6</v>
+        <v>105.31</v>
       </c>
       <c r="H36">
-        <v>1646.010009765625</v>
+        <v>627.8200073242188</v>
       </c>
       <c r="I36">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="J36" t="s">
         <v>153</v>
@@ -11677,7 +11677,7 @@
         <v>1.2</v>
       </c>
       <c r="L36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -11688,25 +11688,25 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>0.6511</v>
+        <v>0.6529</v>
       </c>
       <c r="D37">
-        <v>0.2384</v>
+        <v>0.2408</v>
       </c>
       <c r="E37">
-        <v>0.4346</v>
+        <v>0.4285</v>
       </c>
       <c r="F37">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="G37">
-        <v>95.84999999999999</v>
+        <v>98.08</v>
       </c>
       <c r="H37">
         <v>270.2804870605469</v>
       </c>
       <c r="I37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="J37" t="s">
         <v>153</v>
@@ -11726,10 +11726,10 @@
         <v>18</v>
       </c>
       <c r="C38">
-        <v>0.7169</v>
+        <v>0.7183</v>
       </c>
       <c r="D38">
-        <v>0.7451</v>
+        <v>0.7488</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -11738,13 +11738,13 @@
         <v>1</v>
       </c>
       <c r="G38">
-        <v>81.23</v>
+        <v>80.39</v>
       </c>
       <c r="H38">
         <v>32.22999954223633</v>
       </c>
       <c r="I38">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="J38" t="s">
         <v>153</v>
@@ -11764,25 +11764,25 @@
         <v>18</v>
       </c>
       <c r="C39">
-        <v>0.6496</v>
+        <v>0.6509</v>
       </c>
       <c r="D39">
-        <v>0.736</v>
+        <v>0.7318</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="G39">
-        <v>76.34999999999999</v>
+        <v>77.98</v>
       </c>
       <c r="H39">
         <v>229.1600036621094</v>
       </c>
       <c r="I39">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J39" t="s">
         <v>153</v>
@@ -11802,25 +11802,25 @@
         <v>18</v>
       </c>
       <c r="C40">
-        <v>0.6237</v>
+        <v>0.6251</v>
       </c>
       <c r="D40">
-        <v>0.7331</v>
+        <v>0.7252</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G40">
-        <v>73.92</v>
+        <v>76.37</v>
       </c>
       <c r="H40">
         <v>335.5</v>
       </c>
       <c r="I40">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J40" t="s">
         <v>153</v>
@@ -11840,19 +11840,19 @@
         <v>143</v>
       </c>
       <c r="C41">
-        <v>0.4085</v>
+        <v>0.4099</v>
       </c>
       <c r="D41">
-        <v>0.3117</v>
+        <v>0.317</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G41">
-        <v>71.48</v>
+        <v>71.55</v>
       </c>
       <c r="H41">
         <v>842.4000244140625</v>
@@ -11872,31 +11872,31 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="C42">
-        <v>0.8044</v>
+        <v>0.6493</v>
       </c>
       <c r="D42">
-        <v>0.8986</v>
+        <v>0.7651</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="G42">
-        <v>67.42</v>
+        <v>68.33</v>
       </c>
       <c r="H42">
-        <v>10.6201000213623</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="I42">
-        <v>6.35</v>
+        <v>4.01</v>
       </c>
       <c r="J42" t="s">
         <v>153</v>
@@ -11905,36 +11905,36 @@
         <v>1.2</v>
       </c>
       <c r="L42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="C43">
-        <v>0.6479</v>
+        <v>0.8011</v>
       </c>
       <c r="D43">
-        <v>0.7687</v>
+        <v>0.8985</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G43">
-        <v>66.61</v>
+        <v>65.12</v>
       </c>
       <c r="H43">
-        <v>17.04999923706055</v>
+        <v>10.6201000213623</v>
       </c>
       <c r="I43">
-        <v>3.91</v>
+        <v>6.13</v>
       </c>
       <c r="J43" t="s">
         <v>153</v>
@@ -11943,36 +11943,36 @@
         <v>1.2</v>
       </c>
       <c r="L43" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="C44">
-        <v>0.6775</v>
+        <v>0.4012</v>
       </c>
       <c r="D44">
-        <v>0.7843</v>
+        <v>0.3589</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G44">
-        <v>64.98</v>
+        <v>65.12</v>
       </c>
       <c r="H44">
-        <v>92</v>
+        <v>477.3900146484375</v>
       </c>
       <c r="I44">
-        <v>0.71</v>
+        <v>0.14</v>
       </c>
       <c r="J44" t="s">
         <v>153</v>
@@ -11981,36 +11981,36 @@
         <v>1.2</v>
       </c>
       <c r="L44" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="C45">
-        <v>0.4315</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="D45">
-        <v>0.6191</v>
+        <v>0.7842</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G45">
-        <v>64.17</v>
+        <v>65.12</v>
       </c>
       <c r="H45">
-        <v>92.66010284423828</v>
+        <v>92</v>
       </c>
       <c r="I45">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="J45" t="s">
         <v>153</v>
@@ -12019,36 +12019,36 @@
         <v>1.2</v>
       </c>
       <c r="L45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C46">
-        <v>0.3836</v>
+        <v>0.4315</v>
       </c>
       <c r="D46">
-        <v>0.2374</v>
+        <v>0.6197</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0.23</v>
+        <v>0.79</v>
       </c>
       <c r="G46">
-        <v>18.68</v>
+        <v>63.51</v>
       </c>
       <c r="H46">
-        <v>86.90000152587891</v>
+        <v>92.66010284423828</v>
       </c>
       <c r="I46">
-        <v>0.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J46" t="s">
         <v>153</v>
@@ -12057,36 +12057,36 @@
         <v>1.2</v>
       </c>
       <c r="L46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B47" t="s">
         <v>144</v>
       </c>
       <c r="C47">
-        <v>0.3998</v>
+        <v>0.385</v>
       </c>
       <c r="D47">
-        <v>0.3583</v>
+        <v>0.2378</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G47">
-        <v>16.25</v>
+        <v>19.29</v>
       </c>
       <c r="H47">
-        <v>477.3900146484375</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="I47">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="J47" t="s">
         <v>153</v>
@@ -12095,7 +12095,7 @@
         <v>1.2</v>
       </c>
       <c r="L47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -12106,25 +12106,25 @@
         <v>144</v>
       </c>
       <c r="C48">
-        <v>0.3477</v>
+        <v>0.3491</v>
       </c>
       <c r="D48">
-        <v>0.297</v>
+        <v>0.2971</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G48">
-        <v>15.43</v>
+        <v>16.08</v>
       </c>
       <c r="H48">
         <v>81.58999633789062</v>
       </c>
       <c r="I48">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="s">
         <v>153</v>
@@ -12144,10 +12144,10 @@
         <v>144</v>
       </c>
       <c r="C49">
-        <v>0.3435</v>
+        <v>0.3449</v>
       </c>
       <c r="D49">
-        <v>0.2903</v>
+        <v>0.2911</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -12156,7 +12156,7 @@
         <v>0.19</v>
       </c>
       <c r="G49">
-        <v>15.43</v>
+        <v>15.27</v>
       </c>
       <c r="H49">
         <v>442.6698913574219</v>
@@ -12182,10 +12182,10 @@
         <v>144</v>
       </c>
       <c r="C50">
-        <v>0.3553</v>
+        <v>0.3567</v>
       </c>
       <c r="D50">
-        <v>0.3103</v>
+        <v>0.3226</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -12194,7 +12194,7 @@
         <v>0.19</v>
       </c>
       <c r="G50">
-        <v>15.43</v>
+        <v>15.27</v>
       </c>
       <c r="H50">
         <v>376.1700134277344</v>
@@ -12214,31 +12214,31 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
         <v>144</v>
       </c>
       <c r="C51">
-        <v>0.3676</v>
+        <v>0.3778</v>
       </c>
       <c r="D51">
-        <v>0.3821</v>
+        <v>0.3827</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G51">
-        <v>14.62</v>
+        <v>15.27</v>
       </c>
       <c r="H51">
-        <v>42.81000137329102</v>
+        <v>256.6799926757812</v>
       </c>
       <c r="I51">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="J51" t="s">
         <v>153</v>
@@ -12252,16 +12252,16 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B52" t="s">
         <v>144</v>
       </c>
       <c r="C52">
-        <v>0.3764</v>
+        <v>0.3765</v>
       </c>
       <c r="D52">
-        <v>0.3782</v>
+        <v>0.4138</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -12270,13 +12270,13 @@
         <v>0.18</v>
       </c>
       <c r="G52">
-        <v>14.62</v>
+        <v>14.47</v>
       </c>
       <c r="H52">
-        <v>256.6799926757812</v>
+        <v>16.40999984741211</v>
       </c>
       <c r="I52">
-        <v>0.06</v>
+        <v>0.88</v>
       </c>
       <c r="J52" t="s">
         <v>153</v>
@@ -12290,31 +12290,31 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="B53" t="s">
         <v>144</v>
       </c>
       <c r="C53">
-        <v>0.3849</v>
+        <v>0.3495</v>
       </c>
       <c r="D53">
-        <v>0.4299</v>
+        <v>0.3559</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G53">
-        <v>13.81</v>
+        <v>14.47</v>
       </c>
       <c r="H53">
-        <v>286.9700012207031</v>
+        <v>78.55000305175781</v>
       </c>
       <c r="I53">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="J53" t="s">
         <v>153</v>
@@ -12328,31 +12328,31 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B54" t="s">
         <v>144</v>
       </c>
       <c r="C54">
-        <v>0.3481</v>
+        <v>0.369</v>
       </c>
       <c r="D54">
-        <v>0.3561</v>
+        <v>0.3842</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G54">
-        <v>13.81</v>
+        <v>14.47</v>
       </c>
       <c r="H54">
-        <v>78.55000305175781</v>
+        <v>42.81000137329102</v>
       </c>
       <c r="I54">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="J54" t="s">
         <v>153</v>
@@ -12366,31 +12366,31 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
         <v>144</v>
       </c>
       <c r="C55">
-        <v>0.3751</v>
+        <v>0.3863</v>
       </c>
       <c r="D55">
-        <v>0.4092</v>
+        <v>0.4354</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G55">
-        <v>13.81</v>
+        <v>14.47</v>
       </c>
       <c r="H55">
-        <v>16.40999984741211</v>
+        <v>286.9700012207031</v>
       </c>
       <c r="I55">
-        <v>0.84</v>
+        <v>0.05</v>
       </c>
       <c r="J55" t="s">
         <v>153</v>
@@ -12410,10 +12410,10 @@
         <v>144</v>
       </c>
       <c r="C56">
-        <v>0.3311</v>
+        <v>0.3325</v>
       </c>
       <c r="D56">
-        <v>0.3847</v>
+        <v>0.3907</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -12422,7 +12422,7 @@
         <v>0.16</v>
       </c>
       <c r="G56">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="H56">
         <v>297.8349914550781</v>
@@ -12442,16 +12442,16 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
         <v>144</v>
       </c>
       <c r="C57">
-        <v>0.3784</v>
+        <v>0.3971</v>
       </c>
       <c r="D57">
-        <v>0.5125</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -12460,13 +12460,13 @@
         <v>0.15</v>
       </c>
       <c r="G57">
-        <v>12.18</v>
+        <v>12.06</v>
       </c>
       <c r="H57">
-        <v>71.58999633789062</v>
+        <v>46.2599983215332</v>
       </c>
       <c r="I57">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="J57" t="s">
         <v>153</v>
@@ -12475,36 +12475,36 @@
         <v>1.2</v>
       </c>
       <c r="L57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
         <v>144</v>
       </c>
       <c r="C58">
-        <v>0.354</v>
+        <v>0.3798</v>
       </c>
       <c r="D58">
-        <v>0.508</v>
+        <v>0.5144</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="G58">
-        <v>11.37</v>
+        <v>12.06</v>
       </c>
       <c r="H58">
-        <v>109.3625030517578</v>
+        <v>71.58999633789062</v>
       </c>
       <c r="I58">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="J58" t="s">
         <v>153</v>
@@ -12518,16 +12518,16 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
         <v>144</v>
       </c>
       <c r="C59">
-        <v>0.3601</v>
+        <v>0.3554</v>
       </c>
       <c r="D59">
-        <v>0.5097</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -12536,13 +12536,13 @@
         <v>0.14</v>
       </c>
       <c r="G59">
-        <v>11.37</v>
+        <v>11.25</v>
       </c>
       <c r="H59">
-        <v>144.8500061035156</v>
+        <v>109.3625030517578</v>
       </c>
       <c r="I59">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J59" t="s">
         <v>153</v>
@@ -12556,16 +12556,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
         <v>144</v>
       </c>
       <c r="C60">
-        <v>0.3707</v>
+        <v>0.3507</v>
       </c>
       <c r="D60">
-        <v>0.5293</v>
+        <v>0.4861</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12574,13 +12574,13 @@
         <v>0.14</v>
       </c>
       <c r="G60">
-        <v>11.37</v>
+        <v>11.25</v>
       </c>
       <c r="H60">
-        <v>50.13999938964844</v>
+        <v>223.4850006103516</v>
       </c>
       <c r="I60">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="J60" t="s">
         <v>153</v>
@@ -12594,16 +12594,16 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
         <v>144</v>
       </c>
       <c r="C61">
-        <v>0.3493</v>
+        <v>0.3615</v>
       </c>
       <c r="D61">
-        <v>0.4777</v>
+        <v>0.5157</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -12612,13 +12612,13 @@
         <v>0.14</v>
       </c>
       <c r="G61">
-        <v>11.37</v>
+        <v>11.25</v>
       </c>
       <c r="H61">
-        <v>223.4850006103516</v>
+        <v>144.8500061035156</v>
       </c>
       <c r="I61">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J61" t="s">
         <v>153</v>
@@ -12632,31 +12632,31 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B62" t="s">
         <v>144</v>
       </c>
       <c r="C62">
-        <v>0.3557</v>
+        <v>0.372</v>
       </c>
       <c r="D62">
-        <v>0.5419</v>
+        <v>0.5313</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="G62">
-        <v>10.56</v>
+        <v>11.25</v>
       </c>
       <c r="H62">
-        <v>24.07999992370605</v>
+        <v>50.13999938964844</v>
       </c>
       <c r="I62">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="J62" t="s">
         <v>153</v>
@@ -12676,25 +12676,25 @@
         <v>144</v>
       </c>
       <c r="C63">
-        <v>0.3615</v>
+        <v>0.3629</v>
       </c>
       <c r="D63">
-        <v>0.5301</v>
+        <v>0.5326</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="G63">
-        <v>10.56</v>
+        <v>11.25</v>
       </c>
       <c r="H63">
         <v>3.535000085830688</v>
       </c>
       <c r="I63">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="J63" t="s">
         <v>153</v>
@@ -12708,31 +12708,31 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
         <v>144</v>
       </c>
       <c r="C64">
-        <v>0.3957</v>
+        <v>0.3571</v>
       </c>
       <c r="D64">
-        <v>0.6022</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G64">
-        <v>9.75</v>
+        <v>10.45</v>
       </c>
       <c r="H64">
-        <v>46.2599983215332</v>
+        <v>24.07999992370605</v>
       </c>
       <c r="I64">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="J64" t="s">
         <v>153</v>
@@ -12741,7 +12741,7 @@
         <v>1.2</v>
       </c>
       <c r="L64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -12752,19 +12752,19 @@
         <v>144</v>
       </c>
       <c r="C65">
-        <v>0.3633</v>
+        <v>0.3647</v>
       </c>
       <c r="D65">
-        <v>0.609</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="G65">
-        <v>8.94</v>
+        <v>9.65</v>
       </c>
       <c r="H65">
         <v>326.5499877929688</v>
@@ -12790,10 +12790,10 @@
         <v>144</v>
       </c>
       <c r="C66">
-        <v>0.3852</v>
+        <v>0.3866</v>
       </c>
       <c r="D66">
-        <v>0.6242</v>
+        <v>0.6338</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>0.11</v>
       </c>
       <c r="G66">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="H66">
         <v>138.6849975585938</v>
@@ -12828,10 +12828,10 @@
         <v>144</v>
       </c>
       <c r="C67">
-        <v>0.3329</v>
+        <v>0.3343</v>
       </c>
       <c r="D67">
-        <v>0.5745</v>
+        <v>0.5817</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12840,7 +12840,7 @@
         <v>0.11</v>
       </c>
       <c r="G67">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="H67">
         <v>122.8566970825195</v>
@@ -12866,10 +12866,10 @@
         <v>144</v>
       </c>
       <c r="C68">
-        <v>0.3613</v>
+        <v>0.3627</v>
       </c>
       <c r="D68">
-        <v>0.5988</v>
+        <v>0.6091</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         <v>0.11</v>
       </c>
       <c r="G68">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="H68">
         <v>11.64500045776367</v>
       </c>
       <c r="I68">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="J68" t="s">
         <v>153</v>
@@ -12904,10 +12904,10 @@
         <v>144</v>
       </c>
       <c r="C69">
-        <v>0.3543</v>
+        <v>0.3557</v>
       </c>
       <c r="D69">
-        <v>0.5893</v>
+        <v>0.5955</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -12916,13 +12916,13 @@
         <v>0.11</v>
       </c>
       <c r="G69">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="H69">
         <v>10.85499954223633</v>
       </c>
       <c r="I69">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J69" t="s">
         <v>153</v>
@@ -12942,10 +12942,10 @@
         <v>144</v>
       </c>
       <c r="C70">
-        <v>0.3677</v>
+        <v>0.3691</v>
       </c>
       <c r="D70">
-        <v>0.6438</v>
+        <v>0.6439</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -12954,7 +12954,7 @@
         <v>0.1</v>
       </c>
       <c r="G70">
-        <v>8.119999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H70">
         <v>8.979999542236328</v>
@@ -12980,10 +12980,10 @@
         <v>144</v>
       </c>
       <c r="C71">
-        <v>0.3513</v>
+        <v>0.3527</v>
       </c>
       <c r="D71">
-        <v>0.6384</v>
+        <v>0.6412</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -12992,13 +12992,13 @@
         <v>0.1</v>
       </c>
       <c r="G71">
-        <v>8.119999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H71">
         <v>8.024999618530273</v>
       </c>
       <c r="I71">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J71" t="s">
         <v>153</v>
@@ -13012,16 +13012,16 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B72" t="s">
         <v>144</v>
       </c>
       <c r="C72">
-        <v>0.3386</v>
+        <v>0.3364</v>
       </c>
       <c r="D72">
-        <v>0.6642</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -13030,13 +13030,13 @@
         <v>0.09</v>
       </c>
       <c r="G72">
-        <v>7.31</v>
+        <v>7.24</v>
       </c>
       <c r="H72">
-        <v>45.6150016784668</v>
+        <v>613.1300048828125</v>
       </c>
       <c r="I72">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="J72" t="s">
         <v>153</v>
@@ -13050,16 +13050,16 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
         <v>144</v>
       </c>
       <c r="C73">
-        <v>0.335</v>
+        <v>0.34</v>
       </c>
       <c r="D73">
-        <v>0.6581</v>
+        <v>0.6641</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -13068,13 +13068,13 @@
         <v>0.09</v>
       </c>
       <c r="G73">
-        <v>7.31</v>
+        <v>7.24</v>
       </c>
       <c r="H73">
-        <v>613.1300048828125</v>
+        <v>45.6150016784668</v>
       </c>
       <c r="I73">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="J73" t="s">
         <v>153</v>
@@ -13088,31 +13088,31 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="C74">
-        <v>0.6736</v>
+        <v>0.348</v>
       </c>
       <c r="D74">
-        <v>0.979</v>
+        <v>0.6959</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="G74">
-        <v>6.5</v>
+        <v>7.24</v>
       </c>
       <c r="H74">
-        <v>156.1300048828125</v>
+        <v>5.026599884033203</v>
       </c>
       <c r="I74">
-        <v>0.04</v>
+        <v>1.44</v>
       </c>
       <c r="J74" t="s">
         <v>153</v>
@@ -13121,7 +13121,7 @@
         <v>1.2</v>
       </c>
       <c r="L74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -13132,10 +13132,10 @@
         <v>144</v>
       </c>
       <c r="C75">
-        <v>0.3118</v>
+        <v>0.3132</v>
       </c>
       <c r="D75">
-        <v>0.6699000000000001</v>
+        <v>0.6752</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -13144,7 +13144,7 @@
         <v>0.08</v>
       </c>
       <c r="G75">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="H75">
         <v>253.3600006103516</v>
@@ -13164,31 +13164,31 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
         <v>144</v>
       </c>
       <c r="C76">
-        <v>0.3466</v>
+        <v>0.3407</v>
       </c>
       <c r="D76">
-        <v>0.695</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G76">
+        <v>5.63</v>
+      </c>
+      <c r="H76">
+        <v>68.98000335693359</v>
+      </c>
+      <c r="I76">
         <v>0.08</v>
-      </c>
-      <c r="G76">
-        <v>6.5</v>
-      </c>
-      <c r="H76">
-        <v>5.026599884033203</v>
-      </c>
-      <c r="I76">
-        <v>1.29</v>
       </c>
       <c r="J76" t="s">
         <v>153</v>
@@ -13202,31 +13202,31 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B77" t="s">
         <v>144</v>
       </c>
       <c r="C77">
-        <v>0.3393</v>
+        <v>0.3768</v>
       </c>
       <c r="D77">
-        <v>0.7514999999999999</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G77">
-        <v>5.69</v>
+        <v>4.82</v>
       </c>
       <c r="H77">
-        <v>68.98000335693359</v>
+        <v>12.4601001739502</v>
       </c>
       <c r="I77">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="J77" t="s">
         <v>153</v>
@@ -13240,31 +13240,31 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="C78">
-        <v>0.3754</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="D78">
-        <v>0.7949000000000001</v>
+        <v>0.9859</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G78">
-        <v>4.87</v>
+        <v>4.02</v>
       </c>
       <c r="H78">
-        <v>12.4601001739502</v>
+        <v>156.1300048828125</v>
       </c>
       <c r="I78">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="J78" t="s">
         <v>153</v>
@@ -13273,7 +13273,7 @@
         <v>1.2</v>
       </c>
       <c r="L78" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -13284,10 +13284,10 @@
         <v>18</v>
       </c>
       <c r="C79">
-        <v>0.6603</v>
+        <v>0.6616</v>
       </c>
       <c r="D79">
-        <v>0.9933999999999999</v>
+        <v>0.9947</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -13296,7 +13296,7 @@
         <v>0.02</v>
       </c>
       <c r="G79">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H79">
         <v>104.2600021362305</v>
@@ -13364,16 +13364,16 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="D2">
-        <v>676</v>
+        <v>836</v>
       </c>
       <c r="E2">
-        <v>6.76</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F2">
-        <v>0.9804</v>
+        <v>0.9835</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -13396,22 +13396,22 @@
         <v>60</v>
       </c>
       <c r="C3">
-        <v>2834.4</v>
+        <v>2731.2</v>
       </c>
       <c r="D3">
-        <v>2384.4</v>
+        <v>2281.2</v>
       </c>
       <c r="E3">
-        <v>39.74</v>
+        <v>38.02</v>
       </c>
       <c r="F3">
-        <v>0.912</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="G3">
-        <v>0.7601</v>
+        <v>0.7655</v>
       </c>
       <c r="H3">
-        <v>0.5672</v>
+        <v>0.5305</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -13425,19 +13425,19 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="C4">
-        <v>936.6</v>
+        <v>879.8</v>
       </c>
       <c r="D4">
-        <v>499.17</v>
+        <v>454.14</v>
       </c>
       <c r="E4">
-        <v>144.24</v>
+        <v>134.86</v>
       </c>
       <c r="F4">
-        <v>0.4521</v>
+        <v>0.4572</v>
       </c>
       <c r="G4">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="216">
   <si>
     <t>trade_date</t>
   </si>
@@ -617,28 +617,64 @@
     <t>Value</t>
   </si>
   <si>
-    <t>PortfolioValue</t>
-  </si>
-  <si>
-    <t>CurrentCash</t>
-  </si>
-  <si>
-    <t>EmergencyReserve</t>
-  </si>
-  <si>
-    <t>TargetCashReserve</t>
-  </si>
-  <si>
-    <t>Contributions</t>
-  </si>
-  <si>
-    <t>MaxDeploymentPercent</t>
-  </si>
-  <si>
-    <t>DeployableCapital</t>
-  </si>
-  <si>
-    <t>AvailableToInvest</t>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>target_cash_reserve</t>
+  </si>
+  <si>
+    <t>cash_shortfall</t>
+  </si>
+  <si>
+    <t>cash_surplus</t>
+  </si>
+  <si>
+    <t>portfolio_value</t>
+  </si>
+  <si>
+    <t>invested_value</t>
+  </si>
+  <si>
+    <t>max_deployment_percent</t>
+  </si>
+  <si>
+    <t>target_invested_value</t>
+  </si>
+  <si>
+    <t>deployment_difference</t>
+  </si>
+  <si>
+    <t>required_sale_value</t>
+  </si>
+  <si>
+    <t>available_cash</t>
+  </si>
+  <si>
+    <t>deployable_capital</t>
+  </si>
+  <si>
+    <t>required_sale_for_cash</t>
+  </si>
+  <si>
+    <t>required_sale_for_deployment</t>
+  </si>
+  <si>
+    <t>cash_target_achievable</t>
+  </si>
+  <si>
+    <t>capital_status</t>
+  </si>
+  <si>
+    <t>cash_funding_ratio</t>
+  </si>
+  <si>
+    <t>cash_percentage</t>
+  </si>
+  <si>
+    <t>invested_percentage</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
   </si>
 </sst>
 </file>
@@ -1509,7 +1545,7 @@
         <v>183</v>
       </c>
       <c r="D2">
-        <v>3820.98</v>
+        <v>3815.2</v>
       </c>
       <c r="E2" t="s">
         <v>185</v>
@@ -1526,7 +1562,7 @@
         <v>183</v>
       </c>
       <c r="D3">
-        <v>2730.88</v>
+        <v>2741.29</v>
       </c>
       <c r="E3" t="s">
         <v>185</v>
@@ -1543,7 +1579,7 @@
         <v>184</v>
       </c>
       <c r="D4">
-        <v>1389.16</v>
+        <v>1418.69</v>
       </c>
       <c r="E4" t="s">
         <v>186</v>
@@ -1578,10 +1614,10 @@
         <v>149</v>
       </c>
       <c r="B2">
-        <v>3918.9</v>
+        <v>3915.9</v>
       </c>
       <c r="C2">
-        <v>48.75</v>
+        <v>48.49</v>
       </c>
       <c r="D2" t="s">
         <v>183</v>
@@ -1592,10 +1628,10 @@
         <v>148</v>
       </c>
       <c r="B3">
-        <v>2731.2</v>
+        <v>2741.4</v>
       </c>
       <c r="C3">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="D3" t="s">
         <v>184</v>
@@ -1606,10 +1642,10 @@
         <v>147</v>
       </c>
       <c r="B4">
-        <v>1389</v>
+        <v>1418</v>
       </c>
       <c r="C4">
-        <v>17.28</v>
+        <v>17.56</v>
       </c>
       <c r="D4" t="s">
         <v>189</v>
@@ -1656,13 +1692,13 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>1389</v>
+        <v>1418</v>
       </c>
       <c r="E2">
-        <v>836</v>
+        <v>865</v>
       </c>
       <c r="F2">
-        <v>1.0279</v>
+        <v>1.0267</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1676,13 +1712,13 @@
         <v>60</v>
       </c>
       <c r="D3">
-        <v>2731.2</v>
+        <v>2741.4</v>
       </c>
       <c r="E3">
-        <v>2281.2</v>
+        <v>2291.4</v>
       </c>
       <c r="F3">
-        <v>0.8260999999999999</v>
+        <v>0.8206</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1693,16 +1729,16 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="D4">
-        <v>879.8</v>
+        <v>840.6</v>
       </c>
       <c r="E4">
-        <v>454.14</v>
+        <v>433.6</v>
       </c>
       <c r="F4">
-        <v>0.4572</v>
+        <v>0.4547</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1716,13 +1752,13 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>1389</v>
+        <v>1418</v>
       </c>
       <c r="E5">
-        <v>836</v>
+        <v>865</v>
       </c>
       <c r="F5">
-        <v>0.9835</v>
+        <v>0.9824000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1736,13 +1772,13 @@
         <v>60</v>
       </c>
       <c r="D6">
-        <v>2731.2</v>
+        <v>2741.4</v>
       </c>
       <c r="E6">
-        <v>2281.2</v>
+        <v>2291.4</v>
       </c>
       <c r="F6">
-        <v>0.9199000000000001</v>
+        <v>0.9144</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1753,16 +1789,16 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="D7">
-        <v>879.8</v>
+        <v>840.6</v>
       </c>
       <c r="E7">
-        <v>454.14</v>
+        <v>433.6</v>
       </c>
       <c r="F7">
-        <v>0.4572</v>
+        <v>0.4547</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1776,13 +1812,13 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>1389</v>
+        <v>1418</v>
       </c>
       <c r="E8">
-        <v>836</v>
+        <v>865</v>
       </c>
       <c r="F8">
-        <v>0.6279</v>
+        <v>0.6267</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1796,13 +1832,13 @@
         <v>60</v>
       </c>
       <c r="D9">
-        <v>2731.2</v>
+        <v>2741.4</v>
       </c>
       <c r="E9">
-        <v>2281.2</v>
+        <v>2291.4</v>
       </c>
       <c r="F9">
-        <v>0.7321</v>
+        <v>0.7262999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1813,16 +1849,16 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="D10">
-        <v>879.8</v>
+        <v>840.6</v>
       </c>
       <c r="E10">
-        <v>454.14</v>
+        <v>433.6</v>
       </c>
       <c r="F10">
-        <v>0.8572</v>
+        <v>0.8547</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +1896,7 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>3820.98</v>
+        <v>3815.2</v>
       </c>
       <c r="D2" t="s">
         <v>183</v>
@@ -1877,7 +1913,7 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>2730.88</v>
+        <v>2741.29</v>
       </c>
       <c r="D3" t="s">
         <v>183</v>
@@ -1894,7 +1930,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>1389.16</v>
+        <v>1418.69</v>
       </c>
       <c r="D4" t="s">
         <v>184</v>
@@ -1910,7 +1946,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1931,7 +1967,7 @@
         <v>196</v>
       </c>
       <c r="B2">
-        <v>40000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1939,7 +1975,7 @@
         <v>197</v>
       </c>
       <c r="B3">
-        <v>15000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1947,7 +1983,7 @@
         <v>198</v>
       </c>
       <c r="B4">
-        <v>20000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1955,7 +1991,7 @@
         <v>199</v>
       </c>
       <c r="B5">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1963,7 +1999,7 @@
         <v>200</v>
       </c>
       <c r="B6">
-        <v>1000</v>
+        <v>8076.62</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1971,7 +2007,7 @@
         <v>201</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>8076.62</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1979,7 +2015,7 @@
         <v>202</v>
       </c>
       <c r="B8">
-        <v>20000</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1987,7 +2023,95 @@
         <v>203</v>
       </c>
       <c r="B9">
-        <v>5000</v>
+        <v>5653.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10">
+        <v>2422.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11">
+        <v>2422.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15">
+        <v>2422.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2738,7 @@
         <v>34</v>
       </c>
       <c r="K2">
-        <v>13.89</v>
+        <v>14.18</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2658,19 +2782,19 @@
         <v>553</v>
       </c>
       <c r="K3">
-        <v>13.89</v>
+        <v>14.18</v>
       </c>
       <c r="L3">
-        <v>1389</v>
+        <v>1418</v>
       </c>
       <c r="M3">
         <v>553</v>
       </c>
       <c r="N3">
-        <v>836</v>
+        <v>865</v>
       </c>
       <c r="O3">
-        <v>151.18</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2705,7 +2829,7 @@
         <v>32</v>
       </c>
       <c r="K4">
-        <v>600.47</v>
+        <v>607.37</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2752,7 +2876,7 @@
         <v>33</v>
       </c>
       <c r="K5">
-        <v>224.36</v>
+        <v>225.99</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2799,7 +2923,7 @@
         <v>34</v>
       </c>
       <c r="K6">
-        <v>415.88</v>
+        <v>422.15</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2846,19 +2970,19 @@
         <v>34</v>
       </c>
       <c r="K7">
-        <v>261.26</v>
+        <v>261.06</v>
       </c>
       <c r="L7">
-        <v>3918.9</v>
+        <v>3915.9</v>
       </c>
       <c r="M7">
         <v>1896</v>
       </c>
       <c r="N7">
-        <v>2022.9</v>
+        <v>2019.9</v>
       </c>
       <c r="O7">
-        <v>106.69</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2893,7 +3017,7 @@
         <v>34</v>
       </c>
       <c r="K8">
-        <v>372.58</v>
+        <v>366.7</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2940,7 +3064,7 @@
         <v>34</v>
       </c>
       <c r="K9">
-        <v>160.65</v>
+        <v>150.9</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2987,19 +3111,19 @@
         <v>34</v>
       </c>
       <c r="K10">
-        <v>45.52</v>
+        <v>45.69</v>
       </c>
       <c r="L10">
-        <v>2731.2</v>
+        <v>2741.4</v>
       </c>
       <c r="M10">
         <v>450</v>
       </c>
       <c r="N10">
-        <v>2281.2</v>
+        <v>2291.4</v>
       </c>
       <c r="O10">
-        <v>506.93</v>
+        <v>509.2</v>
       </c>
     </row>
   </sheetData>
@@ -3265,7 +3389,7 @@
         <v>0.7016</v>
       </c>
       <c r="J5">
-        <v>0.8011</v>
+        <v>0.8007</v>
       </c>
       <c r="K5" t="s">
         <v>142</v>
@@ -3274,10 +3398,10 @@
         <v>147</v>
       </c>
       <c r="M5">
-        <v>17.28</v>
+        <v>17.57</v>
       </c>
       <c r="N5">
-        <v>0.8272</v>
+        <v>0.8243</v>
       </c>
       <c r="O5" t="s">
         <v>153</v>
@@ -3321,7 +3445,7 @@
         <v>0.4721</v>
       </c>
       <c r="J6">
-        <v>0.7638</v>
+        <v>0.7634</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -3330,10 +3454,10 @@
         <v>147</v>
       </c>
       <c r="M6">
-        <v>17.28</v>
+        <v>17.57</v>
       </c>
       <c r="N6">
-        <v>0.8272</v>
+        <v>0.8243</v>
       </c>
       <c r="O6" t="s">
         <v>153</v>
@@ -3386,10 +3510,10 @@
         <v>148</v>
       </c>
       <c r="M7">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N7">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O7" t="s">
         <v>153</v>
@@ -3442,10 +3566,10 @@
         <v>148</v>
       </c>
       <c r="M8">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N8">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O8" t="s">
         <v>153</v>
@@ -3498,10 +3622,10 @@
         <v>148</v>
       </c>
       <c r="M9">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N9">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O9" t="s">
         <v>153</v>
@@ -3554,10 +3678,10 @@
         <v>148</v>
       </c>
       <c r="M10">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N10">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O10" t="s">
         <v>153</v>
@@ -3610,10 +3734,10 @@
         <v>148</v>
       </c>
       <c r="M11">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N11">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O11" t="s">
         <v>153</v>
@@ -3666,10 +3790,10 @@
         <v>148</v>
       </c>
       <c r="M12">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N12">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O12" t="s">
         <v>153</v>
@@ -3722,10 +3846,10 @@
         <v>148</v>
       </c>
       <c r="M13">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N13">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O13" t="s">
         <v>153</v>
@@ -3769,7 +3893,7 @@
         <v>0.4798</v>
       </c>
       <c r="J14">
-        <v>0.6749000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="K14" t="s">
         <v>18</v>
@@ -3778,10 +3902,10 @@
         <v>148</v>
       </c>
       <c r="M14">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N14">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O14" t="s">
         <v>153</v>
@@ -3834,10 +3958,10 @@
         <v>148</v>
       </c>
       <c r="M15">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N15">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O15" t="s">
         <v>153</v>
@@ -3890,10 +4014,10 @@
         <v>148</v>
       </c>
       <c r="M16">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N16">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O16" t="s">
         <v>153</v>
@@ -3946,10 +4070,10 @@
         <v>148</v>
       </c>
       <c r="M17">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N17">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O17" t="s">
         <v>153</v>
@@ -4002,10 +4126,10 @@
         <v>148</v>
       </c>
       <c r="M18">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N18">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O18" t="s">
         <v>153</v>
@@ -4049,7 +4173,7 @@
         <v>0.4626</v>
       </c>
       <c r="J19">
-        <v>0.6627</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="K19" t="s">
         <v>18</v>
@@ -4058,10 +4182,10 @@
         <v>148</v>
       </c>
       <c r="M19">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N19">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O19" t="s">
         <v>153</v>
@@ -4114,10 +4238,10 @@
         <v>148</v>
       </c>
       <c r="M20">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N20">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O20" t="s">
         <v>153</v>
@@ -4161,7 +4285,7 @@
         <v>0.4511</v>
       </c>
       <c r="J21">
-        <v>0.6621</v>
+        <v>0.6622</v>
       </c>
       <c r="K21" t="s">
         <v>18</v>
@@ -4170,10 +4294,10 @@
         <v>148</v>
       </c>
       <c r="M21">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N21">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O21" t="s">
         <v>153</v>
@@ -4217,7 +4341,7 @@
         <v>0.3831</v>
       </c>
       <c r="J22">
-        <v>0.6616</v>
+        <v>0.6617</v>
       </c>
       <c r="K22" t="s">
         <v>18</v>
@@ -4226,10 +4350,10 @@
         <v>148</v>
       </c>
       <c r="M22">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N22">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O22" t="s">
         <v>153</v>
@@ -4273,7 +4397,7 @@
         <v>0.5249</v>
       </c>
       <c r="J23">
-        <v>0.6529</v>
+        <v>0.6533</v>
       </c>
       <c r="K23" t="s">
         <v>18</v>
@@ -4282,10 +4406,10 @@
         <v>149</v>
       </c>
       <c r="M23">
-        <v>48.75</v>
+        <v>48.48</v>
       </c>
       <c r="N23">
-        <v>0.5125</v>
+        <v>0.5152</v>
       </c>
       <c r="O23" t="s">
         <v>153</v>
@@ -4329,7 +4453,7 @@
         <v>0.4292</v>
       </c>
       <c r="J24">
-        <v>0.6524</v>
+        <v>0.6525</v>
       </c>
       <c r="K24" t="s">
         <v>18</v>
@@ -4338,10 +4462,10 @@
         <v>148</v>
       </c>
       <c r="M24">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N24">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O24" t="s">
         <v>153</v>
@@ -4385,7 +4509,7 @@
         <v>0.3639</v>
       </c>
       <c r="J25">
-        <v>0.6509</v>
+        <v>0.651</v>
       </c>
       <c r="K25" t="s">
         <v>18</v>
@@ -4394,10 +4518,10 @@
         <v>148</v>
       </c>
       <c r="M25">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N25">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O25" t="s">
         <v>153</v>
@@ -4450,10 +4574,10 @@
         <v>148</v>
       </c>
       <c r="M26">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N26">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O26" t="s">
         <v>153</v>
@@ -4497,7 +4621,7 @@
         <v>0.3322</v>
       </c>
       <c r="J27">
-        <v>0.649</v>
+        <v>0.6491</v>
       </c>
       <c r="K27" t="s">
         <v>18</v>
@@ -4506,10 +4630,10 @@
         <v>148</v>
       </c>
       <c r="M27">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N27">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O27" t="s">
         <v>153</v>
@@ -4553,7 +4677,7 @@
         <v>0.3869</v>
       </c>
       <c r="J28">
-        <v>0.6448</v>
+        <v>0.6449</v>
       </c>
       <c r="K28" t="s">
         <v>18</v>
@@ -4562,10 +4686,10 @@
         <v>148</v>
       </c>
       <c r="M28">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N28">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O28" t="s">
         <v>153</v>
@@ -4618,10 +4742,10 @@
         <v>148</v>
       </c>
       <c r="M29">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N29">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O29" t="s">
         <v>153</v>
@@ -4674,10 +4798,10 @@
         <v>148</v>
       </c>
       <c r="M30">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N30">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O30" t="s">
         <v>153</v>
@@ -4730,10 +4854,10 @@
         <v>148</v>
       </c>
       <c r="M31">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N31">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O31" t="s">
         <v>153</v>
@@ -4786,10 +4910,10 @@
         <v>148</v>
       </c>
       <c r="M32">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N32">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O32" t="s">
         <v>153</v>
@@ -4842,10 +4966,10 @@
         <v>148</v>
       </c>
       <c r="M33">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N33">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O33" t="s">
         <v>153</v>
@@ -4898,10 +5022,10 @@
         <v>148</v>
       </c>
       <c r="M34">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N34">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O34" t="s">
         <v>153</v>
@@ -4954,10 +5078,10 @@
         <v>148</v>
       </c>
       <c r="M35">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N35">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O35" t="s">
         <v>153</v>
@@ -5010,10 +5134,10 @@
         <v>148</v>
       </c>
       <c r="M36">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N36">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O36" t="s">
         <v>153</v>
@@ -5066,10 +5190,10 @@
         <v>148</v>
       </c>
       <c r="M37">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N37">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O37" t="s">
         <v>153</v>
@@ -5122,10 +5246,10 @@
         <v>148</v>
       </c>
       <c r="M38">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N38">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O38" t="s">
         <v>153</v>
@@ -5169,7 +5293,7 @@
         <v>0.177</v>
       </c>
       <c r="J39">
-        <v>0.6253</v>
+        <v>0.6254</v>
       </c>
       <c r="K39" t="s">
         <v>18</v>
@@ -5178,10 +5302,10 @@
         <v>148</v>
       </c>
       <c r="M39">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N39">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O39" t="s">
         <v>153</v>
@@ -5234,10 +5358,10 @@
         <v>148</v>
       </c>
       <c r="M40">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N40">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O40" t="s">
         <v>153</v>
@@ -5290,10 +5414,10 @@
         <v>148</v>
       </c>
       <c r="M41">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N41">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O41" t="s">
         <v>153</v>
@@ -5346,10 +5470,10 @@
         <v>148</v>
       </c>
       <c r="M42">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N42">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O42" t="s">
         <v>153</v>
@@ -5393,7 +5517,7 @@
         <v>0.1524</v>
       </c>
       <c r="J43">
-        <v>0.6236</v>
+        <v>0.6237</v>
       </c>
       <c r="K43" t="s">
         <v>18</v>
@@ -5402,10 +5526,10 @@
         <v>148</v>
       </c>
       <c r="M43">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N43">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O43" t="s">
         <v>153</v>
@@ -5449,7 +5573,7 @@
         <v>0.1162</v>
       </c>
       <c r="J44">
-        <v>0.6127</v>
+        <v>0.6128</v>
       </c>
       <c r="K44" t="s">
         <v>18</v>
@@ -5458,10 +5582,10 @@
         <v>148</v>
       </c>
       <c r="M44">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N44">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O44" t="s">
         <v>153</v>
@@ -5626,10 +5750,10 @@
         <v>148</v>
       </c>
       <c r="M47">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N47">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O47" t="s">
         <v>153</v>
@@ -5738,10 +5862,10 @@
         <v>148</v>
       </c>
       <c r="M49">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N49">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O49" t="s">
         <v>153</v>
@@ -5794,10 +5918,10 @@
         <v>148</v>
       </c>
       <c r="M50">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N50">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O50" t="s">
         <v>153</v>
@@ -5850,10 +5974,10 @@
         <v>148</v>
       </c>
       <c r="M51">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N51">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O51" t="s">
         <v>153</v>
@@ -5906,10 +6030,10 @@
         <v>148</v>
       </c>
       <c r="M52">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N52">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O52" t="s">
         <v>153</v>
@@ -5962,10 +6086,10 @@
         <v>148</v>
       </c>
       <c r="M53">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N53">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O53" t="s">
         <v>153</v>
@@ -6018,10 +6142,10 @@
         <v>148</v>
       </c>
       <c r="M54">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N54">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O54" t="s">
         <v>153</v>
@@ -6074,10 +6198,10 @@
         <v>148</v>
       </c>
       <c r="M55">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N55">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O55" t="s">
         <v>153</v>
@@ -6130,10 +6254,10 @@
         <v>148</v>
       </c>
       <c r="M56">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N56">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O56" t="s">
         <v>153</v>
@@ -6186,10 +6310,10 @@
         <v>148</v>
       </c>
       <c r="M57">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N57">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O57" t="s">
         <v>153</v>
@@ -6233,7 +6357,7 @@
         <v>0.4911</v>
       </c>
       <c r="J58">
-        <v>0.372</v>
+        <v>0.3721</v>
       </c>
       <c r="K58" t="s">
         <v>144</v>
@@ -6242,10 +6366,10 @@
         <v>148</v>
       </c>
       <c r="M58">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N58">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O58" t="s">
         <v>153</v>
@@ -6298,10 +6422,10 @@
         <v>148</v>
       </c>
       <c r="M59">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N59">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O59" t="s">
         <v>153</v>
@@ -6354,10 +6478,10 @@
         <v>148</v>
       </c>
       <c r="M60">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N60">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O60" t="s">
         <v>153</v>
@@ -6410,10 +6534,10 @@
         <v>148</v>
       </c>
       <c r="M61">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N61">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O61" t="s">
         <v>153</v>
@@ -6466,10 +6590,10 @@
         <v>148</v>
       </c>
       <c r="M62">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N62">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O62" t="s">
         <v>153</v>
@@ -6522,10 +6646,10 @@
         <v>148</v>
       </c>
       <c r="M63">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N63">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O63" t="s">
         <v>153</v>
@@ -6578,10 +6702,10 @@
         <v>148</v>
       </c>
       <c r="M64">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N64">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O64" t="s">
         <v>153</v>
@@ -6634,10 +6758,10 @@
         <v>148</v>
       </c>
       <c r="M65">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N65">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O65" t="s">
         <v>153</v>
@@ -6690,10 +6814,10 @@
         <v>148</v>
       </c>
       <c r="M66">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N66">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O66" t="s">
         <v>153</v>
@@ -6746,10 +6870,10 @@
         <v>148</v>
       </c>
       <c r="M67">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N67">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O67" t="s">
         <v>153</v>
@@ -6802,10 +6926,10 @@
         <v>148</v>
       </c>
       <c r="M68">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N68">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O68" t="s">
         <v>153</v>
@@ -6849,7 +6973,7 @@
         <v>0.3708</v>
       </c>
       <c r="J69">
-        <v>0.3527</v>
+        <v>0.3528</v>
       </c>
       <c r="K69" t="s">
         <v>144</v>
@@ -6858,10 +6982,10 @@
         <v>148</v>
       </c>
       <c r="M69">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N69">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O69" t="s">
         <v>153</v>
@@ -6914,10 +7038,10 @@
         <v>148</v>
       </c>
       <c r="M70">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N70">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O70" t="s">
         <v>153</v>
@@ -6961,7 +7085,7 @@
         <v>0.3412</v>
       </c>
       <c r="J71">
-        <v>0.3495</v>
+        <v>0.3496</v>
       </c>
       <c r="K71" t="s">
         <v>144</v>
@@ -6970,10 +7094,10 @@
         <v>148</v>
       </c>
       <c r="M71">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N71">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O71" t="s">
         <v>153</v>
@@ -7026,10 +7150,10 @@
         <v>148</v>
       </c>
       <c r="M72">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N72">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O72" t="s">
         <v>153</v>
@@ -7082,10 +7206,10 @@
         <v>148</v>
       </c>
       <c r="M73">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N73">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O73" t="s">
         <v>153</v>
@@ -7138,10 +7262,10 @@
         <v>148</v>
       </c>
       <c r="M74">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N74">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O74" t="s">
         <v>153</v>
@@ -7185,7 +7309,7 @@
         <v>0.2727</v>
       </c>
       <c r="J75">
-        <v>0.3407</v>
+        <v>0.3408</v>
       </c>
       <c r="K75" t="s">
         <v>144</v>
@@ -7194,10 +7318,10 @@
         <v>148</v>
       </c>
       <c r="M75">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N75">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O75" t="s">
         <v>153</v>
@@ -7250,10 +7374,10 @@
         <v>148</v>
       </c>
       <c r="M76">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N76">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O76" t="s">
         <v>153</v>
@@ -7306,10 +7430,10 @@
         <v>148</v>
       </c>
       <c r="M77">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N77">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O77" t="s">
         <v>153</v>
@@ -7362,10 +7486,10 @@
         <v>148</v>
       </c>
       <c r="M78">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N78">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O78" t="s">
         <v>153</v>
@@ -7418,10 +7542,10 @@
         <v>148</v>
       </c>
       <c r="M79">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N79">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O79" t="s">
         <v>153</v>
@@ -7474,10 +7598,10 @@
         <v>148</v>
       </c>
       <c r="M80">
-        <v>33.97</v>
+        <v>33.95</v>
       </c>
       <c r="N80">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="O80" t="s">
         <v>153</v>
@@ -7653,7 +7777,7 @@
         <v>10.6201000213623</v>
       </c>
       <c r="D5">
-        <v>0.8011</v>
+        <v>0.8007</v>
       </c>
       <c r="E5">
         <v>11.68120206832886</v>
@@ -7671,7 +7795,7 @@
         <v>29.84059297913404</v>
       </c>
       <c r="J5">
-        <v>0.8272</v>
+        <v>0.8243</v>
       </c>
       <c r="K5" t="s">
         <v>157</v>
@@ -7688,7 +7812,7 @@
         <v>12.17000007629395</v>
       </c>
       <c r="D6">
-        <v>0.7638</v>
+        <v>0.7634</v>
       </c>
       <c r="E6">
         <v>9.490199975967407</v>
@@ -7706,7 +7830,7 @@
         <v>52.79048555853054</v>
       </c>
       <c r="J6">
-        <v>0.8272</v>
+        <v>0.8243</v>
       </c>
       <c r="K6" t="s">
         <v>156</v>
@@ -7741,7 +7865,7 @@
         <v>24.32237410558415</v>
       </c>
       <c r="J7">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K7" t="s">
         <v>158</v>
@@ -7776,7 +7900,7 @@
         <v>34.93956665818956</v>
       </c>
       <c r="J8">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K8" t="s">
         <v>158</v>
@@ -7811,7 +7935,7 @@
         <v>55.74873620999067</v>
       </c>
       <c r="J9">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K9" t="s">
         <v>159</v>
@@ -7846,7 +7970,7 @@
         <v>42.79099330023248</v>
       </c>
       <c r="J10">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K10" t="s">
         <v>159</v>
@@ -7881,7 +8005,7 @@
         <v>39.25098385656076</v>
       </c>
       <c r="J11">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K11" t="s">
         <v>158</v>
@@ -7916,7 +8040,7 @@
         <v>41.29244115486681</v>
       </c>
       <c r="J12">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K12" t="s">
         <v>159</v>
@@ -7951,7 +8075,7 @@
         <v>47.29547809343844</v>
       </c>
       <c r="J13">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K13" t="s">
         <v>159</v>
@@ -7968,7 +8092,7 @@
         <v>156.1300048828125</v>
       </c>
       <c r="D14">
-        <v>0.6749000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="E14">
         <v>147.9280003356934</v>
@@ -7986,7 +8110,7 @@
         <v>52.01954969224415</v>
       </c>
       <c r="J14">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K14" t="s">
         <v>159</v>
@@ -8021,7 +8145,7 @@
         <v>50.0953380320746</v>
       </c>
       <c r="J15">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K15" t="s">
         <v>159</v>
@@ -8056,7 +8180,7 @@
         <v>49.58712417755017</v>
       </c>
       <c r="J16">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K16" t="s">
         <v>159</v>
@@ -8091,7 +8215,7 @@
         <v>55.81680137154054</v>
       </c>
       <c r="J17">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K17" t="s">
         <v>159</v>
@@ -8126,7 +8250,7 @@
         <v>52.52196685210854</v>
       </c>
       <c r="J18">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K18" t="s">
         <v>159</v>
@@ -8143,7 +8267,7 @@
         <v>437.3999938964844</v>
       </c>
       <c r="D19">
-        <v>0.6627</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="E19">
         <v>385.4850103759766</v>
@@ -8161,7 +8285,7 @@
         <v>53.74493548838463</v>
       </c>
       <c r="J19">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K19" t="s">
         <v>159</v>
@@ -8196,7 +8320,7 @@
         <v>53.33591079169458</v>
       </c>
       <c r="J20">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K20" t="s">
         <v>159</v>
@@ -8213,7 +8337,7 @@
         <v>1930.010009765625</v>
       </c>
       <c r="D21">
-        <v>0.6621</v>
+        <v>0.6622</v>
       </c>
       <c r="E21">
         <v>1730.606733398437</v>
@@ -8231,7 +8355,7 @@
         <v>54.89072413854991</v>
       </c>
       <c r="J21">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K21" t="s">
         <v>159</v>
@@ -8248,7 +8372,7 @@
         <v>104.2600021362305</v>
       </c>
       <c r="D22">
-        <v>0.6616</v>
+        <v>0.6617</v>
       </c>
       <c r="E22">
         <v>57.82180000305176</v>
@@ -8266,7 +8390,7 @@
         <v>61.68698087643116</v>
       </c>
       <c r="J22">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K22" t="s">
         <v>159</v>
@@ -8283,7 +8407,7 @@
         <v>270.2804870605469</v>
       </c>
       <c r="D23">
-        <v>0.6529</v>
+        <v>0.6533</v>
       </c>
       <c r="E23">
         <v>246.6624099731445</v>
@@ -8301,7 +8425,7 @@
         <v>47.50671781742124</v>
       </c>
       <c r="J23">
-        <v>0.5125</v>
+        <v>0.5152</v>
       </c>
       <c r="K23" t="s">
         <v>159</v>
@@ -8318,7 +8442,7 @@
         <v>289.6799926757812</v>
       </c>
       <c r="D24">
-        <v>0.6524</v>
+        <v>0.6525</v>
       </c>
       <c r="E24">
         <v>270.0206011962891</v>
@@ -8336,7 +8460,7 @@
         <v>57.0804147127497</v>
       </c>
       <c r="J24">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K24" t="s">
         <v>159</v>
@@ -8353,7 +8477,7 @@
         <v>229.1600036621094</v>
       </c>
       <c r="D25">
-        <v>0.6509</v>
+        <v>0.651</v>
       </c>
       <c r="E25">
         <v>158.9171002197266</v>
@@ -8371,7 +8495,7 @@
         <v>63.60836779223327</v>
       </c>
       <c r="J25">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K25" t="s">
         <v>159</v>
@@ -8406,7 +8530,7 @@
         <v>72.55699795767705</v>
       </c>
       <c r="J26">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K26" t="s">
         <v>159</v>
@@ -8423,7 +8547,7 @@
         <v>160.1600036621094</v>
       </c>
       <c r="D27">
-        <v>0.649</v>
+        <v>0.6491</v>
       </c>
       <c r="E27">
         <v>148.8601998901367</v>
@@ -8441,7 +8565,7 @@
         <v>66.77614060250662</v>
       </c>
       <c r="J27">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K27" t="s">
         <v>159</v>
@@ -8458,7 +8582,7 @@
         <v>599.510009765625</v>
       </c>
       <c r="D28">
-        <v>0.6448</v>
+        <v>0.6449</v>
       </c>
       <c r="E28">
         <v>484.7420007324219</v>
@@ -8476,7 +8600,7 @@
         <v>61.30891593465972</v>
       </c>
       <c r="J28">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K28" t="s">
         <v>159</v>
@@ -8511,7 +8635,7 @@
         <v>68.00380242260704</v>
       </c>
       <c r="J29">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K29" t="s">
         <v>159</v>
@@ -8546,7 +8670,7 @@
         <v>68.7262179373717</v>
       </c>
       <c r="J30">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K30" t="s">
         <v>159</v>
@@ -8581,7 +8705,7 @@
         <v>73.3756782876756</v>
       </c>
       <c r="J31">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K31" t="s">
         <v>159</v>
@@ -8616,7 +8740,7 @@
         <v>63.72471183466363</v>
       </c>
       <c r="J32">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K32" t="s">
         <v>159</v>
@@ -8651,7 +8775,7 @@
         <v>75.71506554383619</v>
       </c>
       <c r="J33">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K33" t="s">
         <v>159</v>
@@ -8686,7 +8810,7 @@
         <v>79.18690654428941</v>
       </c>
       <c r="J34">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K34" t="s">
         <v>159</v>
@@ -8721,7 +8845,7 @@
         <v>67.11149544232157</v>
       </c>
       <c r="J35">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K35" t="s">
         <v>159</v>
@@ -8756,7 +8880,7 @@
         <v>68.69012892264033</v>
       </c>
       <c r="J36">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K36" t="s">
         <v>159</v>
@@ -8791,7 +8915,7 @@
         <v>80.7508215679068</v>
       </c>
       <c r="J37">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K37" t="s">
         <v>159</v>
@@ -8826,7 +8950,7 @@
         <v>84.59564438781432</v>
       </c>
       <c r="J38">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K38" t="s">
         <v>159</v>
@@ -8843,7 +8967,7 @@
         <v>279.1600036621094</v>
       </c>
       <c r="D39">
-        <v>0.6253</v>
+        <v>0.6254</v>
       </c>
       <c r="E39">
         <v>191.3692004394531</v>
@@ -8861,7 +8985,7 @@
         <v>82.30017258450833</v>
       </c>
       <c r="J39">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K39" t="s">
         <v>159</v>
@@ -8896,7 +9020,7 @@
         <v>83.40800204702586</v>
       </c>
       <c r="J40">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K40" t="s">
         <v>159</v>
@@ -8931,7 +9055,7 @@
         <v>80.72804757289227</v>
       </c>
       <c r="J41">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K41" t="s">
         <v>159</v>
@@ -8966,7 +9090,7 @@
         <v>82.2306288932008</v>
       </c>
       <c r="J42">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K42" t="s">
         <v>159</v>
@@ -8983,7 +9107,7 @@
         <v>416.2999877929688</v>
       </c>
       <c r="D43">
-        <v>0.6236</v>
+        <v>0.6237</v>
       </c>
       <c r="E43">
         <v>215.5247280883789</v>
@@ -9001,7 +9125,7 @@
         <v>84.76398843833833</v>
       </c>
       <c r="J43">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K43" t="s">
         <v>159</v>
@@ -9018,7 +9142,7 @@
         <v>726.155029296875</v>
       </c>
       <c r="D44">
-        <v>0.6127</v>
+        <v>0.6128</v>
       </c>
       <c r="E44">
         <v>482.4160998535156</v>
@@ -9036,7 +9160,7 @@
         <v>88.38347146788549</v>
       </c>
       <c r="J44">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K44" t="s">
         <v>159</v>
@@ -9141,7 +9265,7 @@
         <v>40.11494958459248</v>
       </c>
       <c r="J47">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K47" t="s">
         <v>161</v>
@@ -9211,7 +9335,7 @@
         <v>33.9729473260635</v>
       </c>
       <c r="J49">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K49" t="s">
         <v>162</v>
@@ -9246,7 +9370,7 @@
         <v>37.02109183728933</v>
       </c>
       <c r="J50">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K50" t="s">
         <v>162</v>
@@ -9281,7 +9405,7 @@
         <v>44.54939598291897</v>
       </c>
       <c r="J51">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K51" t="s">
         <v>161</v>
@@ -9316,7 +9440,7 @@
         <v>41.9093713425007</v>
       </c>
       <c r="J52">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K52" t="s">
         <v>161</v>
@@ -9351,7 +9475,7 @@
         <v>45.24736162443781</v>
       </c>
       <c r="J53">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K53" t="s">
         <v>161</v>
@@ -9386,7 +9510,7 @@
         <v>45.78635887349753</v>
       </c>
       <c r="J54">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K54" t="s">
         <v>161</v>
@@ -9421,7 +9545,7 @@
         <v>52.4694725609674</v>
       </c>
       <c r="J55">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K55" t="s">
         <v>161</v>
@@ -9456,7 +9580,7 @@
         <v>49.34571546247042</v>
       </c>
       <c r="J56">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K56" t="s">
         <v>161</v>
@@ -9491,7 +9615,7 @@
         <v>48.56229749649761</v>
       </c>
       <c r="J57">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K57" t="s">
         <v>161</v>
@@ -9508,7 +9632,7 @@
         <v>50.13999938964844</v>
       </c>
       <c r="D58">
-        <v>0.372</v>
+        <v>0.3721</v>
       </c>
       <c r="E58">
         <v>49.06369972229004</v>
@@ -9526,7 +9650,7 @@
         <v>50.89285279849747</v>
       </c>
       <c r="J58">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K58" t="s">
         <v>161</v>
@@ -9561,7 +9685,7 @@
         <v>51.77304029140512</v>
       </c>
       <c r="J59">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K59" t="s">
         <v>161</v>
@@ -9596,7 +9720,7 @@
         <v>55.20473843066302</v>
       </c>
       <c r="J60">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K60" t="s">
         <v>161</v>
@@ -9631,7 +9755,7 @@
         <v>59.28286837585451</v>
       </c>
       <c r="J61">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K61" t="s">
         <v>161</v>
@@ -9666,7 +9790,7 @@
         <v>57.49129481397203</v>
       </c>
       <c r="J62">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K62" t="s">
         <v>161</v>
@@ -9701,7 +9825,7 @@
         <v>60.49079921150475</v>
       </c>
       <c r="J63">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K63" t="s">
         <v>161</v>
@@ -9736,7 +9860,7 @@
         <v>63.52941319169427</v>
       </c>
       <c r="J64">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K64" t="s">
         <v>161</v>
@@ -9771,7 +9895,7 @@
         <v>61.87049520601642</v>
       </c>
       <c r="J65">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K65" t="s">
         <v>161</v>
@@ -9806,7 +9930,7 @@
         <v>58.27090592171268</v>
       </c>
       <c r="J66">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K66" t="s">
         <v>161</v>
@@ -9841,7 +9965,7 @@
         <v>61.54747452974244</v>
       </c>
       <c r="J67">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K67" t="s">
         <v>161</v>
@@ -9876,7 +10000,7 @@
         <v>69.46505928053598</v>
       </c>
       <c r="J68">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K68" t="s">
         <v>161</v>
@@ -9893,7 +10017,7 @@
         <v>8.024999618530273</v>
       </c>
       <c r="D69">
-        <v>0.3527</v>
+        <v>0.3528</v>
       </c>
       <c r="E69">
         <v>6.22210000038147</v>
@@ -9911,7 +10035,7 @@
         <v>62.92237220217377</v>
       </c>
       <c r="J69">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K69" t="s">
         <v>161</v>
@@ -9946,7 +10070,7 @@
         <v>67.58864039885938</v>
       </c>
       <c r="J70">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K70" t="s">
         <v>161</v>
@@ -9963,7 +10087,7 @@
         <v>78.55000305175781</v>
       </c>
       <c r="D71">
-        <v>0.3495</v>
+        <v>0.3496</v>
       </c>
       <c r="E71">
         <v>62.95691932678223</v>
@@ -9981,7 +10105,7 @@
         <v>65.88147838728383</v>
       </c>
       <c r="J71">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K71" t="s">
         <v>161</v>
@@ -10016,7 +10140,7 @@
         <v>58.07715318316384</v>
       </c>
       <c r="J72">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K72" t="s">
         <v>161</v>
@@ -10051,7 +10175,7 @@
         <v>69.011043961692</v>
       </c>
       <c r="J73">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K73" t="s">
         <v>161</v>
@@ -10086,7 +10210,7 @@
         <v>68.86465938081456</v>
       </c>
       <c r="J74">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K74" t="s">
         <v>161</v>
@@ -10103,7 +10227,7 @@
         <v>68.98000335693359</v>
       </c>
       <c r="D75">
-        <v>0.3407</v>
+        <v>0.3408</v>
       </c>
       <c r="E75">
         <v>43.68120010375976</v>
@@ -10121,7 +10245,7 @@
         <v>72.73146105094992</v>
       </c>
       <c r="J75">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K75" t="s">
         <v>161</v>
@@ -10156,7 +10280,7 @@
         <v>73.36374709939457</v>
       </c>
       <c r="J76">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K76" t="s">
         <v>161</v>
@@ -10191,7 +10315,7 @@
         <v>76.23765512710006</v>
       </c>
       <c r="J77">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K77" t="s">
         <v>161</v>
@@ -10226,7 +10350,7 @@
         <v>78.60111662018215</v>
       </c>
       <c r="J78">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K78" t="s">
         <v>161</v>
@@ -10261,7 +10385,7 @@
         <v>82.27680786422185</v>
       </c>
       <c r="J79">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K79" t="s">
         <v>161</v>
@@ -10296,7 +10420,7 @@
         <v>92.49556488986379</v>
       </c>
       <c r="J80">
-        <v>0.6603</v>
+        <v>0.6605</v>
       </c>
       <c r="K80" t="s">
         <v>161</v>
@@ -10361,22 +10485,22 @@
         <v>0.8158</v>
       </c>
       <c r="D2">
-        <v>0.2573</v>
+        <v>0.2566</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>7.27</v>
+        <v>7.28</v>
       </c>
       <c r="G2">
-        <v>584.4400000000001</v>
+        <v>587.8200000000001</v>
       </c>
       <c r="H2">
         <v>217.2599945068359</v>
       </c>
       <c r="I2">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="J2" t="s">
         <v>153</v>
@@ -10399,16 +10523,16 @@
         <v>0.8028</v>
       </c>
       <c r="D3">
-        <v>0.4743</v>
+        <v>0.4729</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="G3">
-        <v>406.78</v>
+        <v>410.18</v>
       </c>
       <c r="H3">
         <v>504.6749877929688</v>
@@ -10437,7 +10561,7 @@
         <v>0.6987</v>
       </c>
       <c r="D4">
-        <v>0.1222</v>
+        <v>0.1219</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -10446,13 +10570,13 @@
         <v>3.41</v>
       </c>
       <c r="G4">
-        <v>274.13</v>
+        <v>275.34</v>
       </c>
       <c r="H4">
         <v>79.44499969482422</v>
       </c>
       <c r="I4">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="J4" t="s">
         <v>153</v>
@@ -10475,22 +10599,22 @@
         <v>0.8250999999999999</v>
       </c>
       <c r="D5">
-        <v>0.6728</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="G5">
-        <v>260.47</v>
+        <v>263.23</v>
       </c>
       <c r="H5">
         <v>105.504997253418</v>
       </c>
       <c r="I5">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="J5" t="s">
         <v>153</v>
@@ -10513,7 +10637,7 @@
         <v>0.6322</v>
       </c>
       <c r="D6">
-        <v>0.1066</v>
+        <v>0.1063</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -10522,13 +10646,13 @@
         <v>3.14</v>
       </c>
       <c r="G6">
-        <v>252.43</v>
+        <v>253.54</v>
       </c>
       <c r="H6">
         <v>756.3519897460938</v>
       </c>
       <c r="I6">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J6" t="s">
         <v>153</v>
@@ -10548,10 +10672,10 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>0.6524</v>
+        <v>0.6525</v>
       </c>
       <c r="D7">
-        <v>0.1517</v>
+        <v>0.1515</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -10560,13 +10684,13 @@
         <v>3.07</v>
       </c>
       <c r="G7">
-        <v>246.8</v>
+        <v>247.89</v>
       </c>
       <c r="H7">
         <v>289.6799926757812</v>
       </c>
       <c r="I7">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J7" t="s">
         <v>153</v>
@@ -10589,7 +10713,7 @@
         <v>0.6333</v>
       </c>
       <c r="D8">
-        <v>0.1443</v>
+        <v>0.1439</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -10598,7 +10722,7 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>241.17</v>
+        <v>242.24</v>
       </c>
       <c r="H8">
         <v>737.3900146484375</v>
@@ -10636,7 +10760,7 @@
         <v>2.92</v>
       </c>
       <c r="G9">
-        <v>234.74</v>
+        <v>235.78</v>
       </c>
       <c r="H9">
         <v>378.1099853515625</v>
@@ -10665,7 +10789,7 @@
         <v>0.6245000000000001</v>
       </c>
       <c r="D10">
-        <v>0.1759</v>
+        <v>0.1764</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -10674,7 +10798,7 @@
         <v>2.85</v>
       </c>
       <c r="G10">
-        <v>229.11</v>
+        <v>230.12</v>
       </c>
       <c r="H10">
         <v>311.3699951171875</v>
@@ -10703,7 +10827,7 @@
         <v>0.6708</v>
       </c>
       <c r="D11">
-        <v>0.2467</v>
+        <v>0.2484</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -10712,7 +10836,7 @@
         <v>2.8</v>
       </c>
       <c r="G11">
-        <v>225.09</v>
+        <v>226.09</v>
       </c>
       <c r="H11">
         <v>400.5350036621094</v>
@@ -10741,16 +10865,16 @@
         <v>0.6714</v>
       </c>
       <c r="D12">
-        <v>0.2589</v>
+        <v>0.2586</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="G12">
-        <v>221.88</v>
+        <v>223.66</v>
       </c>
       <c r="H12">
         <v>452.6400146484375</v>
@@ -10776,19 +10900,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.6448</v>
+        <v>0.6449</v>
       </c>
       <c r="D13">
-        <v>0.2471</v>
+        <v>0.2476</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="G13">
-        <v>217.06</v>
+        <v>217.2</v>
       </c>
       <c r="H13">
         <v>599.510009765625</v>
@@ -10808,31 +10932,31 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14">
-        <v>0.6313</v>
+        <v>0.6625</v>
       </c>
       <c r="D14">
-        <v>0.2495</v>
+        <v>0.2822</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="G14">
-        <v>211.43</v>
+        <v>213.17</v>
       </c>
       <c r="H14">
-        <v>120.9800033569336</v>
+        <v>418.6000061035156</v>
       </c>
       <c r="I14">
-        <v>1.75</v>
+        <v>0.51</v>
       </c>
       <c r="J14" t="s">
         <v>153</v>
@@ -10846,31 +10970,31 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0.6625</v>
+        <v>0.6313</v>
       </c>
       <c r="D15">
-        <v>0.2827</v>
+        <v>0.2518</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="G15">
-        <v>211.43</v>
+        <v>211.55</v>
       </c>
       <c r="H15">
-        <v>418.6000061035156</v>
+        <v>120.9800033569336</v>
       </c>
       <c r="I15">
-        <v>0.51</v>
+        <v>1.75</v>
       </c>
       <c r="J15" t="s">
         <v>153</v>
@@ -10893,7 +11017,7 @@
         <v>0.6421</v>
       </c>
       <c r="D16">
-        <v>0.2724</v>
+        <v>0.2738</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -10902,7 +11026,7 @@
         <v>2.59</v>
       </c>
       <c r="G16">
-        <v>208.21</v>
+        <v>209.13</v>
       </c>
       <c r="H16">
         <v>566.0499877929688</v>
@@ -10931,7 +11055,7 @@
         <v>0.6666</v>
       </c>
       <c r="D17">
-        <v>0.3203</v>
+        <v>0.3213</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -10940,13 +11064,13 @@
         <v>2.51</v>
       </c>
       <c r="G17">
-        <v>201.78</v>
+        <v>202.67</v>
       </c>
       <c r="H17">
         <v>1616.579956054688</v>
       </c>
       <c r="I17">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="J17" t="s">
         <v>153</v>
@@ -10978,13 +11102,13 @@
         <v>2.44</v>
       </c>
       <c r="G18">
-        <v>196.15</v>
+        <v>197.02</v>
       </c>
       <c r="H18">
         <v>136.8999938964844</v>
       </c>
       <c r="I18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="J18" t="s">
         <v>153</v>
@@ -11004,19 +11128,19 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>0.6627</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="D19">
-        <v>0.3569</v>
+        <v>0.3586</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="G19">
-        <v>190.53</v>
+        <v>190.56</v>
       </c>
       <c r="H19">
         <v>437.3999938964844</v>
@@ -11042,10 +11166,10 @@
         <v>18</v>
       </c>
       <c r="C20">
-        <v>0.6621</v>
+        <v>0.6622</v>
       </c>
       <c r="D20">
-        <v>0.3757</v>
+        <v>0.3761</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -11054,7 +11178,7 @@
         <v>2.29</v>
       </c>
       <c r="G20">
-        <v>184.1</v>
+        <v>184.91</v>
       </c>
       <c r="H20">
         <v>1930.010009765625</v>
@@ -11080,10 +11204,10 @@
         <v>18</v>
       </c>
       <c r="C21">
-        <v>0.6253</v>
+        <v>0.6254</v>
       </c>
       <c r="D21">
-        <v>0.3667</v>
+        <v>0.3672</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -11092,13 +11216,13 @@
         <v>2.2</v>
       </c>
       <c r="G21">
-        <v>176.86</v>
+        <v>177.64</v>
       </c>
       <c r="H21">
         <v>279.1600036621094</v>
       </c>
       <c r="I21">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J21" t="s">
         <v>153</v>
@@ -11118,10 +11242,10 @@
         <v>18</v>
       </c>
       <c r="C22">
-        <v>0.649</v>
+        <v>0.6491</v>
       </c>
       <c r="D22">
-        <v>0.3975</v>
+        <v>0.3971</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -11130,7 +11254,7 @@
         <v>2.17</v>
       </c>
       <c r="G22">
-        <v>174.45</v>
+        <v>175.22</v>
       </c>
       <c r="H22">
         <v>160.1600036621094</v>
@@ -11159,7 +11283,7 @@
         <v>0.6884</v>
       </c>
       <c r="D23">
-        <v>0.4345</v>
+        <v>0.4344</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -11168,13 +11292,13 @@
         <v>2.16</v>
       </c>
       <c r="G23">
-        <v>173.64</v>
+        <v>174.41</v>
       </c>
       <c r="H23">
         <v>313.2200012207031</v>
       </c>
       <c r="I23">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J23" t="s">
         <v>153</v>
@@ -11197,22 +11321,22 @@
         <v>0.6871</v>
       </c>
       <c r="D24">
-        <v>0.4402</v>
+        <v>0.4392</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="G24">
-        <v>171.23</v>
+        <v>172.79</v>
       </c>
       <c r="H24">
         <v>192.1600036621094</v>
       </c>
       <c r="I24">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="s">
         <v>153</v>
@@ -11226,31 +11350,31 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
         <v>18</v>
       </c>
       <c r="C25">
-        <v>0.6445</v>
+        <v>0.6128</v>
       </c>
       <c r="D25">
-        <v>0.4439</v>
+        <v>0.4227</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G25">
-        <v>159.98</v>
+        <v>158.26</v>
       </c>
       <c r="H25">
-        <v>204.1499938964844</v>
+        <v>726.155029296875</v>
       </c>
       <c r="I25">
-        <v>0.78</v>
+        <v>0.22</v>
       </c>
       <c r="J25" t="s">
         <v>153</v>
@@ -11264,31 +11388,31 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
       </c>
       <c r="C26">
-        <v>0.6127</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="D26">
-        <v>0.4215</v>
+        <v>0.4764</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="G26">
-        <v>158.37</v>
+        <v>150.99</v>
       </c>
       <c r="H26">
-        <v>726.155029296875</v>
+        <v>38.50500106811523</v>
       </c>
       <c r="I26">
-        <v>0.22</v>
+        <v>3.92</v>
       </c>
       <c r="J26" t="s">
         <v>153</v>
@@ -11302,31 +11426,31 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
       <c r="C27">
-        <v>0.6435999999999999</v>
+        <v>0.6445</v>
       </c>
       <c r="D27">
-        <v>0.4773</v>
+        <v>0.4971</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="G27">
-        <v>150.33</v>
+        <v>145.34</v>
       </c>
       <c r="H27">
-        <v>38.50500106811523</v>
+        <v>204.1499938964844</v>
       </c>
       <c r="I27">
-        <v>3.9</v>
+        <v>0.71</v>
       </c>
       <c r="J27" t="s">
         <v>153</v>
@@ -11349,22 +11473,22 @@
         <v>0.6895</v>
       </c>
       <c r="D28">
-        <v>0.5324</v>
+        <v>0.5309</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G28">
-        <v>143.9</v>
+        <v>145.34</v>
       </c>
       <c r="H28">
         <v>118.0699996948242</v>
       </c>
       <c r="I28">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="J28" t="s">
         <v>153</v>
@@ -11387,7 +11511,7 @@
         <v>0.6356000000000001</v>
       </c>
       <c r="D29">
-        <v>0.5026</v>
+        <v>0.5011</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -11396,13 +11520,13 @@
         <v>1.76</v>
       </c>
       <c r="G29">
-        <v>141.49</v>
+        <v>142.11</v>
       </c>
       <c r="H29">
         <v>238.2949981689453</v>
       </c>
       <c r="I29">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="s">
         <v>153</v>
@@ -11422,10 +11546,10 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>0.6236</v>
+        <v>0.6237</v>
       </c>
       <c r="D30">
-        <v>0.5076000000000001</v>
+        <v>0.5078</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -11434,7 +11558,7 @@
         <v>1.7</v>
       </c>
       <c r="G30">
-        <v>136.66</v>
+        <v>137.27</v>
       </c>
       <c r="H30">
         <v>416.2999877929688</v>
@@ -11463,7 +11587,7 @@
         <v>0.6249</v>
       </c>
       <c r="D31">
-        <v>0.5285</v>
+        <v>0.5269</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -11472,7 +11596,7 @@
         <v>1.64</v>
       </c>
       <c r="G31">
-        <v>131.84</v>
+        <v>132.42</v>
       </c>
       <c r="H31">
         <v>351.0299987792969</v>
@@ -11501,7 +11625,7 @@
         <v>0.6441</v>
       </c>
       <c r="D32">
-        <v>0.5443</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -11510,7 +11634,7 @@
         <v>1.63</v>
       </c>
       <c r="G32">
-        <v>131.04</v>
+        <v>131.61</v>
       </c>
       <c r="H32">
         <v>946.5999755859375</v>
@@ -11539,7 +11663,7 @@
         <v>0.627</v>
       </c>
       <c r="D33">
-        <v>0.5462</v>
+        <v>0.5458</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -11548,7 +11672,7 @@
         <v>1.58</v>
       </c>
       <c r="G33">
-        <v>127.02</v>
+        <v>127.58</v>
       </c>
       <c r="H33">
         <v>243.2799987792969</v>
@@ -11577,16 +11701,16 @@
         <v>0.4589</v>
       </c>
       <c r="D34">
-        <v>0.3435</v>
+        <v>0.343</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G34">
-        <v>115.76</v>
+        <v>117.08</v>
       </c>
       <c r="H34">
         <v>434.2398986816406</v>
@@ -11615,7 +11739,7 @@
         <v>0.6681</v>
       </c>
       <c r="D35">
-        <v>0.6424</v>
+        <v>0.641</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -11624,13 +11748,13 @@
         <v>1.33</v>
       </c>
       <c r="G35">
-        <v>106.92</v>
+        <v>107.39</v>
       </c>
       <c r="H35">
         <v>1646.010009765625</v>
       </c>
       <c r="I35">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J35" t="s">
         <v>153</v>
@@ -11653,7 +11777,7 @@
         <v>0.4093</v>
       </c>
       <c r="D36">
-        <v>0.3324</v>
+        <v>0.3318</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -11662,7 +11786,7 @@
         <v>1.31</v>
       </c>
       <c r="G36">
-        <v>105.31</v>
+        <v>105.78</v>
       </c>
       <c r="H36">
         <v>627.8200073242188</v>
@@ -11688,25 +11812,25 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>0.6529</v>
+        <v>0.6533</v>
       </c>
       <c r="D37">
-        <v>0.2408</v>
+        <v>0.2402</v>
       </c>
       <c r="E37">
-        <v>0.4285</v>
+        <v>0.4272</v>
       </c>
       <c r="F37">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G37">
-        <v>98.08</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="H37">
         <v>270.2804870605469</v>
       </c>
       <c r="I37">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J37" t="s">
         <v>153</v>
@@ -11729,22 +11853,22 @@
         <v>0.7183</v>
       </c>
       <c r="D38">
-        <v>0.7488</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G38">
-        <v>80.39</v>
+        <v>81.55</v>
       </c>
       <c r="H38">
         <v>32.22999954223633</v>
       </c>
       <c r="I38">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="J38" t="s">
         <v>153</v>
@@ -11764,10 +11888,10 @@
         <v>18</v>
       </c>
       <c r="C39">
-        <v>0.6509</v>
+        <v>0.651</v>
       </c>
       <c r="D39">
-        <v>0.7318</v>
+        <v>0.7301</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -11776,7 +11900,7 @@
         <v>0.97</v>
       </c>
       <c r="G39">
-        <v>77.98</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="H39">
         <v>229.1600036621094</v>
@@ -11805,7 +11929,7 @@
         <v>0.6251</v>
       </c>
       <c r="D40">
-        <v>0.7252</v>
+        <v>0.7268</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -11814,7 +11938,7 @@
         <v>0.95</v>
       </c>
       <c r="G40">
-        <v>76.37</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="H40">
         <v>335.5</v>
@@ -11843,16 +11967,16 @@
         <v>0.4099</v>
       </c>
       <c r="D41">
-        <v>0.317</v>
+        <v>0.32</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="G41">
-        <v>71.55</v>
+        <v>71.06</v>
       </c>
       <c r="H41">
         <v>842.4000244140625</v>
@@ -11881,7 +12005,7 @@
         <v>0.6493</v>
       </c>
       <c r="D42">
-        <v>0.7651</v>
+        <v>0.7637</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -11890,13 +12014,13 @@
         <v>0.85</v>
       </c>
       <c r="G42">
-        <v>68.33</v>
+        <v>68.63</v>
       </c>
       <c r="H42">
         <v>17.04999923706055</v>
       </c>
       <c r="I42">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="J42" t="s">
         <v>153</v>
@@ -11910,31 +12034,31 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C43">
-        <v>0.8011</v>
+        <v>0.4012</v>
       </c>
       <c r="D43">
-        <v>0.8985</v>
+        <v>0.3581</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G43">
-        <v>65.12</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="H43">
-        <v>10.6201000213623</v>
+        <v>477.3900146484375</v>
       </c>
       <c r="I43">
-        <v>6.13</v>
+        <v>0.14</v>
       </c>
       <c r="J43" t="s">
         <v>153</v>
@@ -11943,36 +12067,36 @@
         <v>1.2</v>
       </c>
       <c r="L43" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
       </c>
       <c r="C44">
-        <v>0.4012</v>
+        <v>0.4315</v>
       </c>
       <c r="D44">
-        <v>0.3589</v>
+        <v>0.6191</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G44">
-        <v>65.12</v>
+        <v>63.79</v>
       </c>
       <c r="H44">
-        <v>477.3900146484375</v>
+        <v>92.66010284423828</v>
       </c>
       <c r="I44">
-        <v>0.14</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J44" t="s">
         <v>153</v>
@@ -11981,7 +12105,7 @@
         <v>1.2</v>
       </c>
       <c r="L44" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -11995,22 +12119,22 @@
         <v>0.6788999999999999</v>
       </c>
       <c r="D45">
-        <v>0.7842</v>
+        <v>0.7948</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="G45">
-        <v>65.12</v>
+        <v>62.17</v>
       </c>
       <c r="H45">
         <v>92</v>
       </c>
       <c r="I45">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="J45" t="s">
         <v>153</v>
@@ -12024,31 +12148,31 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C46">
-        <v>0.4315</v>
+        <v>0.8007</v>
       </c>
       <c r="D46">
-        <v>0.6197</v>
+        <v>0.9114</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="G46">
-        <v>63.51</v>
+        <v>56.52</v>
       </c>
       <c r="H46">
-        <v>92.66010284423828</v>
+        <v>10.6201000213623</v>
       </c>
       <c r="I46">
-        <v>0.6899999999999999</v>
+        <v>5.32</v>
       </c>
       <c r="J46" t="s">
         <v>153</v>
@@ -12057,7 +12181,7 @@
         <v>1.2</v>
       </c>
       <c r="L46" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -12071,7 +12195,7 @@
         <v>0.385</v>
       </c>
       <c r="D47">
-        <v>0.2378</v>
+        <v>0.2386</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -12080,7 +12204,7 @@
         <v>0.24</v>
       </c>
       <c r="G47">
-        <v>19.29</v>
+        <v>19.38</v>
       </c>
       <c r="H47">
         <v>86.90000152587891</v>
@@ -12109,7 +12233,7 @@
         <v>0.3491</v>
       </c>
       <c r="D48">
-        <v>0.2971</v>
+        <v>0.2967</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -12118,7 +12242,7 @@
         <v>0.2</v>
       </c>
       <c r="G48">
-        <v>16.08</v>
+        <v>16.15</v>
       </c>
       <c r="H48">
         <v>81.58999633789062</v>
@@ -12147,7 +12271,7 @@
         <v>0.3449</v>
       </c>
       <c r="D49">
-        <v>0.2911</v>
+        <v>0.2928</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -12156,7 +12280,7 @@
         <v>0.19</v>
       </c>
       <c r="G49">
-        <v>15.27</v>
+        <v>15.34</v>
       </c>
       <c r="H49">
         <v>442.6698913574219</v>
@@ -12194,7 +12318,7 @@
         <v>0.19</v>
       </c>
       <c r="G50">
-        <v>15.27</v>
+        <v>15.34</v>
       </c>
       <c r="H50">
         <v>376.1700134277344</v>
@@ -12214,31 +12338,31 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
         <v>144</v>
       </c>
       <c r="C51">
-        <v>0.3778</v>
+        <v>0.3765</v>
       </c>
       <c r="D51">
-        <v>0.3827</v>
+        <v>0.4146</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="G51">
-        <v>15.27</v>
+        <v>14.53</v>
       </c>
       <c r="H51">
-        <v>256.6799926757812</v>
+        <v>16.40999984741211</v>
       </c>
       <c r="I51">
-        <v>0.06</v>
+        <v>0.89</v>
       </c>
       <c r="J51" t="s">
         <v>153</v>
@@ -12252,16 +12376,16 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s">
         <v>144</v>
       </c>
       <c r="C52">
-        <v>0.3765</v>
+        <v>0.3496</v>
       </c>
       <c r="D52">
-        <v>0.4138</v>
+        <v>0.359</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -12270,13 +12394,13 @@
         <v>0.18</v>
       </c>
       <c r="G52">
-        <v>14.47</v>
+        <v>14.53</v>
       </c>
       <c r="H52">
-        <v>16.40999984741211</v>
+        <v>78.55000305175781</v>
       </c>
       <c r="I52">
-        <v>0.88</v>
+        <v>0.18</v>
       </c>
       <c r="J52" t="s">
         <v>153</v>
@@ -12290,16 +12414,16 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
         <v>144</v>
       </c>
       <c r="C53">
-        <v>0.3495</v>
+        <v>0.369</v>
       </c>
       <c r="D53">
-        <v>0.3559</v>
+        <v>0.3835</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -12308,13 +12432,13 @@
         <v>0.18</v>
       </c>
       <c r="G53">
-        <v>14.47</v>
+        <v>14.53</v>
       </c>
       <c r="H53">
-        <v>78.55000305175781</v>
+        <v>42.81000137329102</v>
       </c>
       <c r="I53">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="J53" t="s">
         <v>153</v>
@@ -12328,16 +12452,16 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
         <v>144</v>
       </c>
       <c r="C54">
-        <v>0.369</v>
+        <v>0.3778</v>
       </c>
       <c r="D54">
-        <v>0.3842</v>
+        <v>0.3851</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -12346,13 +12470,13 @@
         <v>0.18</v>
       </c>
       <c r="G54">
-        <v>14.47</v>
+        <v>14.53</v>
       </c>
       <c r="H54">
-        <v>42.81000137329102</v>
+        <v>256.6799926757812</v>
       </c>
       <c r="I54">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="J54" t="s">
         <v>153</v>
@@ -12375,7 +12499,7 @@
         <v>0.3863</v>
       </c>
       <c r="D55">
-        <v>0.4354</v>
+        <v>0.435</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -12384,7 +12508,7 @@
         <v>0.18</v>
       </c>
       <c r="G55">
-        <v>14.47</v>
+        <v>14.53</v>
       </c>
       <c r="H55">
         <v>286.9700012207031</v>
@@ -12413,7 +12537,7 @@
         <v>0.3325</v>
       </c>
       <c r="D56">
-        <v>0.3907</v>
+        <v>0.3899</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -12422,7 +12546,7 @@
         <v>0.16</v>
       </c>
       <c r="G56">
-        <v>12.86</v>
+        <v>12.92</v>
       </c>
       <c r="H56">
         <v>297.8349914550781</v>
@@ -12451,7 +12575,7 @@
         <v>0.3971</v>
       </c>
       <c r="D57">
-        <v>0.5256999999999999</v>
+        <v>0.5245</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -12460,7 +12584,7 @@
         <v>0.15</v>
       </c>
       <c r="G57">
-        <v>12.06</v>
+        <v>12.11</v>
       </c>
       <c r="H57">
         <v>46.2599983215332</v>
@@ -12489,7 +12613,7 @@
         <v>0.3798</v>
       </c>
       <c r="D58">
-        <v>0.5144</v>
+        <v>0.5154</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -12498,7 +12622,7 @@
         <v>0.15</v>
       </c>
       <c r="G58">
-        <v>12.06</v>
+        <v>12.11</v>
       </c>
       <c r="H58">
         <v>71.58999633789062</v>
@@ -12527,7 +12651,7 @@
         <v>0.3554</v>
       </c>
       <c r="D59">
-        <v>0.5096000000000001</v>
+        <v>0.5101</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -12536,7 +12660,7 @@
         <v>0.14</v>
       </c>
       <c r="G59">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="H59">
         <v>109.3625030517578</v>
@@ -12565,7 +12689,7 @@
         <v>0.3507</v>
       </c>
       <c r="D60">
-        <v>0.4861</v>
+        <v>0.4859</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12574,7 +12698,7 @@
         <v>0.14</v>
       </c>
       <c r="G60">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="H60">
         <v>223.4850006103516</v>
@@ -12603,7 +12727,7 @@
         <v>0.3615</v>
       </c>
       <c r="D61">
-        <v>0.5157</v>
+        <v>0.5199</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -12612,7 +12736,7 @@
         <v>0.14</v>
       </c>
       <c r="G61">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="H61">
         <v>144.8500061035156</v>
@@ -12638,10 +12762,10 @@
         <v>144</v>
       </c>
       <c r="C62">
-        <v>0.372</v>
+        <v>0.3721</v>
       </c>
       <c r="D62">
-        <v>0.5313</v>
+        <v>0.5316</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -12650,13 +12774,13 @@
         <v>0.14</v>
       </c>
       <c r="G62">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="H62">
         <v>50.13999938964844</v>
       </c>
       <c r="I62">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J62" t="s">
         <v>153</v>
@@ -12679,7 +12803,7 @@
         <v>0.3629</v>
       </c>
       <c r="D63">
-        <v>0.5326</v>
+        <v>0.5329</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -12688,13 +12812,13 @@
         <v>0.14</v>
       </c>
       <c r="G63">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="H63">
         <v>3.535000085830688</v>
       </c>
       <c r="I63">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="s">
         <v>153</v>
@@ -12717,7 +12841,7 @@
         <v>0.3571</v>
       </c>
       <c r="D64">
-        <v>0.5459000000000001</v>
+        <v>0.5464</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -12726,13 +12850,13 @@
         <v>0.13</v>
       </c>
       <c r="G64">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
       <c r="H64">
         <v>24.07999992370605</v>
       </c>
       <c r="I64">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J64" t="s">
         <v>153</v>
@@ -12755,7 +12879,7 @@
         <v>0.3647</v>
       </c>
       <c r="D65">
-        <v>0.6032999999999999</v>
+        <v>0.6021</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -12764,7 +12888,7 @@
         <v>0.12</v>
       </c>
       <c r="G65">
-        <v>9.65</v>
+        <v>9.69</v>
       </c>
       <c r="H65">
         <v>326.5499877929688</v>
@@ -12793,7 +12917,7 @@
         <v>0.3866</v>
       </c>
       <c r="D66">
-        <v>0.6338</v>
+        <v>0.6384</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12802,7 +12926,7 @@
         <v>0.11</v>
       </c>
       <c r="G66">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H66">
         <v>138.6849975585938</v>
@@ -12831,7 +12955,7 @@
         <v>0.3343</v>
       </c>
       <c r="D67">
-        <v>0.5817</v>
+        <v>0.5851</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12840,7 +12964,7 @@
         <v>0.11</v>
       </c>
       <c r="G67">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H67">
         <v>122.8566970825195</v>
@@ -12869,7 +12993,7 @@
         <v>0.3627</v>
       </c>
       <c r="D68">
-        <v>0.6091</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -12878,7 +13002,7 @@
         <v>0.11</v>
       </c>
       <c r="G68">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H68">
         <v>11.64500045776367</v>
@@ -12907,7 +13031,7 @@
         <v>0.3557</v>
       </c>
       <c r="D69">
-        <v>0.5955</v>
+        <v>0.5954</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -12916,13 +13040,13 @@
         <v>0.11</v>
       </c>
       <c r="G69">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H69">
         <v>10.85499954223633</v>
       </c>
       <c r="I69">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="J69" t="s">
         <v>153</v>
@@ -12945,7 +13069,7 @@
         <v>0.3691</v>
       </c>
       <c r="D70">
-        <v>0.6439</v>
+        <v>0.6434</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -12954,7 +13078,7 @@
         <v>0.1</v>
       </c>
       <c r="G70">
-        <v>8.039999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="H70">
         <v>8.979999542236328</v>
@@ -12980,10 +13104,10 @@
         <v>144</v>
       </c>
       <c r="C71">
-        <v>0.3527</v>
+        <v>0.3528</v>
       </c>
       <c r="D71">
-        <v>0.6412</v>
+        <v>0.6419</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -12992,13 +13116,13 @@
         <v>0.1</v>
       </c>
       <c r="G71">
-        <v>8.039999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="H71">
         <v>8.024999618530273</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J71" t="s">
         <v>153</v>
@@ -13021,7 +13145,7 @@
         <v>0.3364</v>
       </c>
       <c r="D72">
-        <v>0.6568000000000001</v>
+        <v>0.6555</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -13030,7 +13154,7 @@
         <v>0.09</v>
       </c>
       <c r="G72">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="H72">
         <v>613.1300048828125</v>
@@ -13059,7 +13183,7 @@
         <v>0.34</v>
       </c>
       <c r="D73">
-        <v>0.6641</v>
+        <v>0.6649</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -13068,7 +13192,7 @@
         <v>0.09</v>
       </c>
       <c r="G73">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="H73">
         <v>45.6150016784668</v>
@@ -13097,7 +13221,7 @@
         <v>0.348</v>
       </c>
       <c r="D74">
-        <v>0.6959</v>
+        <v>0.6954</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -13106,13 +13230,13 @@
         <v>0.09</v>
       </c>
       <c r="G74">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="H74">
         <v>5.026599884033203</v>
       </c>
       <c r="I74">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J74" t="s">
         <v>153</v>
@@ -13135,7 +13259,7 @@
         <v>0.3132</v>
       </c>
       <c r="D75">
-        <v>0.6752</v>
+        <v>0.6778</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -13144,7 +13268,7 @@
         <v>0.08</v>
       </c>
       <c r="G75">
-        <v>6.43</v>
+        <v>6.46</v>
       </c>
       <c r="H75">
         <v>253.3600006103516</v>
@@ -13170,10 +13294,10 @@
         <v>144</v>
       </c>
       <c r="C76">
-        <v>0.3407</v>
+        <v>0.3408</v>
       </c>
       <c r="D76">
-        <v>0.7524999999999999</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -13182,7 +13306,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G76">
-        <v>5.63</v>
+        <v>5.65</v>
       </c>
       <c r="H76">
         <v>68.98000335693359</v>
@@ -13202,16 +13326,16 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="C77">
-        <v>0.3768</v>
+        <v>0.675</v>
       </c>
       <c r="D77">
-        <v>0.7939000000000001</v>
+        <v>0.9833</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -13220,13 +13344,13 @@
         <v>0.06</v>
       </c>
       <c r="G77">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="H77">
-        <v>12.4601001739502</v>
+        <v>156.1300048828125</v>
       </c>
       <c r="I77">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="J77" t="s">
         <v>153</v>
@@ -13235,36 +13359,36 @@
         <v>1.2</v>
       </c>
       <c r="L77" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="C78">
-        <v>0.6749000000000001</v>
+        <v>0.3768</v>
       </c>
       <c r="D78">
-        <v>0.9859</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G78">
-        <v>4.02</v>
+        <v>4.84</v>
       </c>
       <c r="H78">
-        <v>156.1300048828125</v>
+        <v>12.4601001739502</v>
       </c>
       <c r="I78">
-        <v>0.03</v>
+        <v>0.39</v>
       </c>
       <c r="J78" t="s">
         <v>153</v>
@@ -13273,7 +13397,7 @@
         <v>1.2</v>
       </c>
       <c r="L78" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -13284,19 +13408,19 @@
         <v>18</v>
       </c>
       <c r="C79">
-        <v>0.6616</v>
+        <v>0.6617</v>
       </c>
       <c r="D79">
-        <v>0.9947</v>
+        <v>0.9916</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G79">
-        <v>1.61</v>
+        <v>2.42</v>
       </c>
       <c r="H79">
         <v>104.2600021362305</v>
@@ -13364,16 +13488,16 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>1389</v>
+        <v>1418</v>
       </c>
       <c r="D2">
-        <v>836</v>
+        <v>865</v>
       </c>
       <c r="E2">
-        <v>8.359999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="F2">
-        <v>0.9835</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -13396,22 +13520,22 @@
         <v>60</v>
       </c>
       <c r="C3">
-        <v>2731.2</v>
+        <v>2741.4</v>
       </c>
       <c r="D3">
-        <v>2281.2</v>
+        <v>2291.4</v>
       </c>
       <c r="E3">
-        <v>38.02</v>
+        <v>38.19</v>
       </c>
       <c r="F3">
-        <v>0.9199000000000001</v>
+        <v>0.9144</v>
       </c>
       <c r="G3">
-        <v>0.7655</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="H3">
-        <v>0.5305</v>
+        <v>0.5298</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -13425,19 +13549,19 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="C4">
-        <v>879.8</v>
+        <v>840.6</v>
       </c>
       <c r="D4">
-        <v>454.14</v>
+        <v>433.6</v>
       </c>
       <c r="E4">
-        <v>134.86</v>
+        <v>134.66</v>
       </c>
       <c r="F4">
-        <v>0.4572</v>
+        <v>0.4547</v>
       </c>
       <c r="G4">
         <v>0</v>

--- a/data/exports/dev-portfolio_intelligence.xlsx
+++ b/data/exports/dev-portfolio_intelligence.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="215">
   <si>
     <t>trade_date</t>
   </si>
@@ -561,9 +561,6 @@
   </si>
   <si>
     <t>Recommended because of high tax efficiency, large unrealised gains, long holding period.</t>
-  </si>
-  <si>
-    <t>Recommended because of high potential tax impact, large unrealised gains, high concentration risk.</t>
   </si>
   <si>
     <t>priority</t>
@@ -1525,13 +1522,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" t="s">
         <v>179</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>180</v>
-      </c>
-      <c r="E1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1539,16 +1536,16 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" t="s">
         <v>182</v>
       </c>
-      <c r="C2" t="s">
-        <v>183</v>
-      </c>
       <c r="D2">
-        <v>3815.2</v>
+        <v>3800.96</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1556,16 +1553,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
         <v>182</v>
       </c>
-      <c r="C3" t="s">
-        <v>183</v>
-      </c>
       <c r="D3">
-        <v>2741.29</v>
+        <v>2740.53</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1573,16 +1570,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D4">
-        <v>1418.69</v>
+        <v>1417.4</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -1603,10 +1600,10 @@
         <v>48</v>
       </c>
       <c r="C1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" t="s">
         <v>187</v>
-      </c>
-      <c r="D1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1614,13 +1611,13 @@
         <v>149</v>
       </c>
       <c r="B2">
-        <v>3915.9</v>
+        <v>3900.45</v>
       </c>
       <c r="C2">
-        <v>48.49</v>
+        <v>48.4</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1631,10 +1628,10 @@
         <v>2741.4</v>
       </c>
       <c r="C3">
-        <v>33.95</v>
+        <v>34.02</v>
       </c>
       <c r="D3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1642,13 +1639,13 @@
         <v>147</v>
       </c>
       <c r="B4">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C4">
-        <v>17.56</v>
+        <v>17.58</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -1658,12 +1655,12 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1683,7 +1680,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1692,10 +1689,10 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F2">
         <v>1.0267</v>
@@ -1703,22 +1700,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="D3">
-        <v>2741.4</v>
+        <v>1000.66</v>
       </c>
       <c r="E3">
-        <v>2291.4</v>
+        <v>836.4</v>
       </c>
       <c r="F3">
-        <v>0.8206</v>
+        <v>0.8201000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1726,39 +1723,39 @@
         <v>191</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>3.22</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>840.6</v>
+        <v>1417</v>
       </c>
       <c r="E4">
-        <v>433.6</v>
+        <v>864</v>
       </c>
       <c r="F4">
-        <v>0.4547</v>
+        <v>0.9824000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>21.9</v>
       </c>
       <c r="D5">
-        <v>1418</v>
+        <v>1000.66</v>
       </c>
       <c r="E5">
-        <v>865</v>
+        <v>836.4</v>
       </c>
       <c r="F5">
-        <v>0.9824000000000001</v>
+        <v>0.9147</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1766,19 +1763,19 @@
         <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>2741.4</v>
+        <v>1417</v>
       </c>
       <c r="E6">
-        <v>2291.4</v>
+        <v>864</v>
       </c>
       <c r="F6">
-        <v>0.9144</v>
+        <v>0.6267</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1786,79 +1783,19 @@
         <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>3.22</v>
+        <v>21.9</v>
       </c>
       <c r="D7">
-        <v>840.6</v>
+        <v>1000.66</v>
       </c>
       <c r="E7">
-        <v>433.6</v>
+        <v>836.4</v>
       </c>
       <c r="F7">
-        <v>0.4547</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-      <c r="D8">
-        <v>1418</v>
-      </c>
-      <c r="E8">
-        <v>865</v>
-      </c>
-      <c r="F8">
-        <v>0.6267</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>60</v>
-      </c>
-      <c r="D9">
-        <v>2741.4</v>
-      </c>
-      <c r="E9">
-        <v>2291.4</v>
-      </c>
-      <c r="F9">
-        <v>0.7262999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>3.22</v>
-      </c>
-      <c r="D10">
-        <v>840.6</v>
-      </c>
-      <c r="E10">
-        <v>433.6</v>
-      </c>
-      <c r="F10">
-        <v>0.8547</v>
+        <v>0.728</v>
       </c>
     </row>
   </sheetData>
@@ -1879,13 +1816,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1896,13 +1833,13 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>3815.2</v>
+        <v>3800.96</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1913,13 +1850,13 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>2741.29</v>
+        <v>2740.53</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1930,13 +1867,13 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>1418.69</v>
+        <v>1417.4</v>
       </c>
       <c r="D4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -1956,15 +1893,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" t="s">
         <v>194</v>
-      </c>
-      <c r="B1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1972,7 +1909,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B3">
         <v>12000</v>
@@ -1980,7 +1917,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B4">
         <v>12000</v>
@@ -1988,7 +1925,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1996,23 +1933,23 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B6">
-        <v>8076.62</v>
+        <v>8058.01</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B7">
-        <v>8076.62</v>
+        <v>8058.01</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B8">
         <v>70</v>
@@ -2020,31 +1957,31 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B9">
-        <v>5653.63</v>
+        <v>5640.61</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B10">
-        <v>2422.99</v>
+        <v>2417.4</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B11">
-        <v>2422.99</v>
+        <v>2417.4</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2052,7 +1989,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2060,7 +1997,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14">
         <v>12000</v>
@@ -2068,15 +2005,15 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B15">
-        <v>2422.99</v>
+        <v>2417.4</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B16" t="b">
         <v>0</v>
@@ -2084,15 +2021,15 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2100,7 +2037,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2108,7 +2045,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -2738,7 +2675,7 @@
         <v>34</v>
       </c>
       <c r="K2">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2782,19 +2719,19 @@
         <v>553</v>
       </c>
       <c r="K3">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="L3">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="M3">
         <v>553</v>
       </c>
       <c r="N3">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="O3">
-        <v>156.42</v>
+        <v>156.24</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2829,7 +2766,7 @@
         <v>32</v>
       </c>
       <c r="K4">
-        <v>607.37</v>
+        <v>607.01</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2876,7 +2813,7 @@
         <v>33</v>
       </c>
       <c r="K5">
-        <v>225.99</v>
+        <v>225.84</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2923,7 +2860,7 @@
         <v>34</v>
       </c>
       <c r="K6">
-        <v>422.15</v>
+        <v>422.49</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2970,19 +2907,19 @@
         <v>34</v>
       </c>
       <c r="K7">
-        <v>261.06</v>
+        <v>260.03</v>
       </c>
       <c r="L7">
-        <v>3915.9</v>
+        <v>3900.45</v>
       </c>
       <c r="M7">
         <v>1896</v>
       </c>
       <c r="N7">
-        <v>2019.9</v>
+        <v>2004.45</v>
       </c>
       <c r="O7">
-        <v>106.53</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -3017,7 +2954,7 @@
         <v>34</v>
       </c>
       <c r="K8">
-        <v>366.7</v>
+        <v>363.68</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -3064,7 +3001,7 @@
         <v>34</v>
       </c>
       <c r="K9">
-        <v>150.9</v>
+        <v>152.9</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3398,10 +3335,10 @@
         <v>147</v>
       </c>
       <c r="M5">
-        <v>17.57</v>
+        <v>17.59</v>
       </c>
       <c r="N5">
-        <v>0.8243</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="O5" t="s">
         <v>153</v>
@@ -3445,7 +3382,7 @@
         <v>0.4721</v>
       </c>
       <c r="J6">
-        <v>0.7634</v>
+        <v>0.7633</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -3454,10 +3391,10 @@
         <v>147</v>
       </c>
       <c r="M6">
-        <v>17.57</v>
+        <v>17.59</v>
       </c>
       <c r="N6">
-        <v>0.8243</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="O6" t="s">
         <v>153</v>
@@ -3510,10 +3447,10 @@
         <v>148</v>
       </c>
       <c r="M7">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N7">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O7" t="s">
         <v>153</v>
@@ -3557,7 +3494,7 @@
         <v>0.6506</v>
       </c>
       <c r="J8">
-        <v>0.6989</v>
+        <v>0.6988</v>
       </c>
       <c r="K8" t="s">
         <v>18</v>
@@ -3566,10 +3503,10 @@
         <v>148</v>
       </c>
       <c r="M8">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N8">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O8" t="s">
         <v>153</v>
@@ -3613,7 +3550,7 @@
         <v>0.4425</v>
       </c>
       <c r="J9">
-        <v>0.6987</v>
+        <v>0.6986</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -3622,10 +3559,10 @@
         <v>148</v>
       </c>
       <c r="M9">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N9">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O9" t="s">
         <v>153</v>
@@ -3669,7 +3606,7 @@
         <v>0.5721000000000001</v>
       </c>
       <c r="J10">
-        <v>0.6895</v>
+        <v>0.6894</v>
       </c>
       <c r="K10" t="s">
         <v>18</v>
@@ -3678,10 +3615,10 @@
         <v>148</v>
       </c>
       <c r="M10">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N10">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O10" t="s">
         <v>153</v>
@@ -3725,7 +3662,7 @@
         <v>0.6075</v>
       </c>
       <c r="J11">
-        <v>0.6884</v>
+        <v>0.6883</v>
       </c>
       <c r="K11" t="s">
         <v>18</v>
@@ -3734,10 +3671,10 @@
         <v>148</v>
       </c>
       <c r="M11">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N11">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O11" t="s">
         <v>153</v>
@@ -3781,7 +3718,7 @@
         <v>0.5871</v>
       </c>
       <c r="J12">
-        <v>0.6871</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K12" t="s">
         <v>18</v>
@@ -3790,10 +3727,10 @@
         <v>148</v>
       </c>
       <c r="M12">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N12">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O12" t="s">
         <v>153</v>
@@ -3846,10 +3783,10 @@
         <v>148</v>
       </c>
       <c r="M13">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N13">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O13" t="s">
         <v>153</v>
@@ -3893,7 +3830,7 @@
         <v>0.4798</v>
       </c>
       <c r="J14">
-        <v>0.675</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="K14" t="s">
         <v>18</v>
@@ -3902,10 +3839,10 @@
         <v>148</v>
       </c>
       <c r="M14">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N14">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O14" t="s">
         <v>153</v>
@@ -3949,7 +3886,7 @@
         <v>0.499</v>
       </c>
       <c r="J15">
-        <v>0.6714</v>
+        <v>0.6713</v>
       </c>
       <c r="K15" t="s">
         <v>18</v>
@@ -3958,10 +3895,10 @@
         <v>148</v>
       </c>
       <c r="M15">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N15">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O15" t="s">
         <v>153</v>
@@ -4014,10 +3951,10 @@
         <v>148</v>
       </c>
       <c r="M16">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N16">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O16" t="s">
         <v>153</v>
@@ -4061,7 +3998,7 @@
         <v>0.4418</v>
       </c>
       <c r="J17">
-        <v>0.6681</v>
+        <v>0.668</v>
       </c>
       <c r="K17" t="s">
         <v>18</v>
@@ -4070,10 +4007,10 @@
         <v>148</v>
       </c>
       <c r="M17">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N17">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O17" t="s">
         <v>153</v>
@@ -4126,10 +4063,10 @@
         <v>148</v>
       </c>
       <c r="M18">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N18">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O18" t="s">
         <v>153</v>
@@ -4173,7 +4110,7 @@
         <v>0.4626</v>
       </c>
       <c r="J19">
-        <v>0.6627999999999999</v>
+        <v>0.6627</v>
       </c>
       <c r="K19" t="s">
         <v>18</v>
@@ -4182,10 +4119,10 @@
         <v>148</v>
       </c>
       <c r="M19">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N19">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O19" t="s">
         <v>153</v>
@@ -4229,7 +4166,7 @@
         <v>0.4666</v>
       </c>
       <c r="J20">
-        <v>0.6625</v>
+        <v>0.6624</v>
       </c>
       <c r="K20" t="s">
         <v>18</v>
@@ -4238,10 +4175,10 @@
         <v>148</v>
       </c>
       <c r="M20">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N20">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O20" t="s">
         <v>153</v>
@@ -4285,7 +4222,7 @@
         <v>0.4511</v>
       </c>
       <c r="J21">
-        <v>0.6622</v>
+        <v>0.6621</v>
       </c>
       <c r="K21" t="s">
         <v>18</v>
@@ -4294,10 +4231,10 @@
         <v>148</v>
       </c>
       <c r="M21">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N21">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O21" t="s">
         <v>153</v>
@@ -4341,7 +4278,7 @@
         <v>0.3831</v>
       </c>
       <c r="J22">
-        <v>0.6617</v>
+        <v>0.6616</v>
       </c>
       <c r="K22" t="s">
         <v>18</v>
@@ -4350,10 +4287,10 @@
         <v>148</v>
       </c>
       <c r="M22">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N22">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O22" t="s">
         <v>153</v>
@@ -4397,7 +4334,7 @@
         <v>0.5249</v>
       </c>
       <c r="J23">
-        <v>0.6533</v>
+        <v>0.6534</v>
       </c>
       <c r="K23" t="s">
         <v>18</v>
@@ -4406,10 +4343,10 @@
         <v>149</v>
       </c>
       <c r="M23">
-        <v>48.48</v>
+        <v>48.4</v>
       </c>
       <c r="N23">
-        <v>0.5152</v>
+        <v>0.516</v>
       </c>
       <c r="O23" t="s">
         <v>153</v>
@@ -4453,7 +4390,7 @@
         <v>0.4292</v>
       </c>
       <c r="J24">
-        <v>0.6525</v>
+        <v>0.6524</v>
       </c>
       <c r="K24" t="s">
         <v>18</v>
@@ -4462,10 +4399,10 @@
         <v>148</v>
       </c>
       <c r="M24">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N24">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O24" t="s">
         <v>153</v>
@@ -4509,7 +4446,7 @@
         <v>0.3639</v>
       </c>
       <c r="J25">
-        <v>0.651</v>
+        <v>0.6509</v>
       </c>
       <c r="K25" t="s">
         <v>18</v>
@@ -4518,10 +4455,10 @@
         <v>148</v>
       </c>
       <c r="M25">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N25">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O25" t="s">
         <v>153</v>
@@ -4565,7 +4502,7 @@
         <v>0.2744</v>
       </c>
       <c r="J26">
-        <v>0.6493</v>
+        <v>0.6492</v>
       </c>
       <c r="K26" t="s">
         <v>18</v>
@@ -4574,10 +4511,10 @@
         <v>148</v>
       </c>
       <c r="M26">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N26">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O26" t="s">
         <v>153</v>
@@ -4621,7 +4558,7 @@
         <v>0.3322</v>
       </c>
       <c r="J27">
-        <v>0.6491</v>
+        <v>0.649</v>
       </c>
       <c r="K27" t="s">
         <v>18</v>
@@ -4630,10 +4567,10 @@
         <v>148</v>
       </c>
       <c r="M27">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N27">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O27" t="s">
         <v>153</v>
@@ -4677,7 +4614,7 @@
         <v>0.3869</v>
       </c>
       <c r="J28">
-        <v>0.6449</v>
+        <v>0.6448</v>
       </c>
       <c r="K28" t="s">
         <v>18</v>
@@ -4686,10 +4623,10 @@
         <v>148</v>
       </c>
       <c r="M28">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N28">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O28" t="s">
         <v>153</v>
@@ -4733,7 +4670,7 @@
         <v>0.32</v>
       </c>
       <c r="J29">
-        <v>0.6445</v>
+        <v>0.6444</v>
       </c>
       <c r="K29" t="s">
         <v>18</v>
@@ -4742,10 +4679,10 @@
         <v>148</v>
       </c>
       <c r="M29">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N29">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O29" t="s">
         <v>153</v>
@@ -4798,10 +4735,10 @@
         <v>148</v>
       </c>
       <c r="M30">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N30">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O30" t="s">
         <v>153</v>
@@ -4845,7 +4782,7 @@
         <v>0.2662</v>
       </c>
       <c r="J31">
-        <v>0.6435999999999999</v>
+        <v>0.6435</v>
       </c>
       <c r="K31" t="s">
         <v>18</v>
@@ -4854,10 +4791,10 @@
         <v>148</v>
       </c>
       <c r="M31">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N31">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O31" t="s">
         <v>153</v>
@@ -4901,7 +4838,7 @@
         <v>0.3628</v>
       </c>
       <c r="J32">
-        <v>0.6421</v>
+        <v>0.642</v>
       </c>
       <c r="K32" t="s">
         <v>18</v>
@@ -4910,10 +4847,10 @@
         <v>148</v>
       </c>
       <c r="M32">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N32">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O32" t="s">
         <v>153</v>
@@ -4957,7 +4894,7 @@
         <v>0.2428</v>
       </c>
       <c r="J33">
-        <v>0.6356000000000001</v>
+        <v>0.6355</v>
       </c>
       <c r="K33" t="s">
         <v>18</v>
@@ -4966,10 +4903,10 @@
         <v>148</v>
       </c>
       <c r="M33">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N33">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O33" t="s">
         <v>153</v>
@@ -5013,7 +4950,7 @@
         <v>0.2081</v>
       </c>
       <c r="J34">
-        <v>0.6335</v>
+        <v>0.6334</v>
       </c>
       <c r="K34" t="s">
         <v>18</v>
@@ -5022,10 +4959,10 @@
         <v>148</v>
       </c>
       <c r="M34">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N34">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O34" t="s">
         <v>153</v>
@@ -5069,7 +5006,7 @@
         <v>0.3289</v>
       </c>
       <c r="J35">
-        <v>0.6333</v>
+        <v>0.6332</v>
       </c>
       <c r="K35" t="s">
         <v>18</v>
@@ -5078,10 +5015,10 @@
         <v>148</v>
       </c>
       <c r="M35">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N35">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O35" t="s">
         <v>153</v>
@@ -5125,7 +5062,7 @@
         <v>0.3131</v>
       </c>
       <c r="J36">
-        <v>0.6322</v>
+        <v>0.6321</v>
       </c>
       <c r="K36" t="s">
         <v>18</v>
@@ -5134,10 +5071,10 @@
         <v>148</v>
       </c>
       <c r="M36">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N36">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O36" t="s">
         <v>153</v>
@@ -5181,7 +5118,7 @@
         <v>0.1925</v>
       </c>
       <c r="J37">
-        <v>0.6313</v>
+        <v>0.6312</v>
       </c>
       <c r="K37" t="s">
         <v>18</v>
@@ -5190,10 +5127,10 @@
         <v>148</v>
       </c>
       <c r="M37">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N37">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O37" t="s">
         <v>153</v>
@@ -5237,7 +5174,7 @@
         <v>0.154</v>
       </c>
       <c r="J38">
-        <v>0.627</v>
+        <v>0.6269</v>
       </c>
       <c r="K38" t="s">
         <v>18</v>
@@ -5246,10 +5183,10 @@
         <v>148</v>
       </c>
       <c r="M38">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N38">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O38" t="s">
         <v>153</v>
@@ -5293,7 +5230,7 @@
         <v>0.177</v>
       </c>
       <c r="J39">
-        <v>0.6254</v>
+        <v>0.6253</v>
       </c>
       <c r="K39" t="s">
         <v>18</v>
@@ -5302,10 +5239,10 @@
         <v>148</v>
       </c>
       <c r="M39">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N39">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O39" t="s">
         <v>153</v>
@@ -5349,7 +5286,7 @@
         <v>0.1659</v>
       </c>
       <c r="J40">
-        <v>0.6251</v>
+        <v>0.625</v>
       </c>
       <c r="K40" t="s">
         <v>18</v>
@@ -5358,10 +5295,10 @@
         <v>148</v>
       </c>
       <c r="M40">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N40">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O40" t="s">
         <v>153</v>
@@ -5405,7 +5342,7 @@
         <v>0.1927</v>
       </c>
       <c r="J41">
-        <v>0.6249</v>
+        <v>0.6248</v>
       </c>
       <c r="K41" t="s">
         <v>18</v>
@@ -5414,10 +5351,10 @@
         <v>148</v>
       </c>
       <c r="M41">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N41">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O41" t="s">
         <v>153</v>
@@ -5461,7 +5398,7 @@
         <v>0.1777</v>
       </c>
       <c r="J42">
-        <v>0.6245000000000001</v>
+        <v>0.6244</v>
       </c>
       <c r="K42" t="s">
         <v>18</v>
@@ -5470,10 +5407,10 @@
         <v>148</v>
       </c>
       <c r="M42">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N42">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O42" t="s">
         <v>153</v>
@@ -5517,7 +5454,7 @@
         <v>0.1524</v>
       </c>
       <c r="J43">
-        <v>0.6237</v>
+        <v>0.6236</v>
       </c>
       <c r="K43" t="s">
         <v>18</v>
@@ -5526,10 +5463,10 @@
         <v>148</v>
       </c>
       <c r="M43">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N43">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O43" t="s">
         <v>153</v>
@@ -5573,7 +5510,7 @@
         <v>0.1162</v>
       </c>
       <c r="J44">
-        <v>0.6128</v>
+        <v>0.6127</v>
       </c>
       <c r="K44" t="s">
         <v>18</v>
@@ -5582,10 +5519,10 @@
         <v>148</v>
       </c>
       <c r="M44">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N44">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O44" t="s">
         <v>153</v>
@@ -5741,7 +5678,7 @@
         <v>0.5989</v>
       </c>
       <c r="J47">
-        <v>0.4099</v>
+        <v>0.4098</v>
       </c>
       <c r="K47" t="s">
         <v>143</v>
@@ -5750,10 +5687,10 @@
         <v>148</v>
       </c>
       <c r="M47">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N47">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O47" t="s">
         <v>153</v>
@@ -5862,10 +5799,10 @@
         <v>148</v>
       </c>
       <c r="M49">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N49">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O49" t="s">
         <v>153</v>
@@ -5918,10 +5855,10 @@
         <v>148</v>
       </c>
       <c r="M50">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N50">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O50" t="s">
         <v>153</v>
@@ -5965,7 +5902,7 @@
         <v>0.5545</v>
       </c>
       <c r="J51">
-        <v>0.3866</v>
+        <v>0.3865</v>
       </c>
       <c r="K51" t="s">
         <v>144</v>
@@ -5974,10 +5911,10 @@
         <v>148</v>
       </c>
       <c r="M51">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N51">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O51" t="s">
         <v>153</v>
@@ -6021,7 +5958,7 @@
         <v>0.5809</v>
       </c>
       <c r="J52">
-        <v>0.3863</v>
+        <v>0.3862</v>
       </c>
       <c r="K52" t="s">
         <v>144</v>
@@ -6030,10 +5967,10 @@
         <v>148</v>
       </c>
       <c r="M52">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N52">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O52" t="s">
         <v>153</v>
@@ -6077,7 +6014,7 @@
         <v>0.5475</v>
       </c>
       <c r="J53">
-        <v>0.385</v>
+        <v>0.3849</v>
       </c>
       <c r="K53" t="s">
         <v>144</v>
@@ -6086,10 +6023,10 @@
         <v>148</v>
       </c>
       <c r="M53">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N53">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O53" t="s">
         <v>153</v>
@@ -6133,7 +6070,7 @@
         <v>0.5421</v>
       </c>
       <c r="J54">
-        <v>0.3798</v>
+        <v>0.3797</v>
       </c>
       <c r="K54" t="s">
         <v>144</v>
@@ -6142,10 +6079,10 @@
         <v>148</v>
       </c>
       <c r="M54">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N54">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O54" t="s">
         <v>153</v>
@@ -6189,7 +6126,7 @@
         <v>0.4753</v>
       </c>
       <c r="J55">
-        <v>0.3778</v>
+        <v>0.3777</v>
       </c>
       <c r="K55" t="s">
         <v>144</v>
@@ -6198,10 +6135,10 @@
         <v>148</v>
       </c>
       <c r="M55">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N55">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O55" t="s">
         <v>153</v>
@@ -6245,7 +6182,7 @@
         <v>0.5065</v>
       </c>
       <c r="J56">
-        <v>0.3768</v>
+        <v>0.3767</v>
       </c>
       <c r="K56" t="s">
         <v>144</v>
@@ -6254,10 +6191,10 @@
         <v>148</v>
       </c>
       <c r="M56">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N56">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O56" t="s">
         <v>153</v>
@@ -6301,7 +6238,7 @@
         <v>0.5144</v>
       </c>
       <c r="J57">
-        <v>0.3765</v>
+        <v>0.3764</v>
       </c>
       <c r="K57" t="s">
         <v>144</v>
@@ -6310,10 +6247,10 @@
         <v>148</v>
       </c>
       <c r="M57">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N57">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O57" t="s">
         <v>153</v>
@@ -6357,7 +6294,7 @@
         <v>0.4911</v>
       </c>
       <c r="J58">
-        <v>0.3721</v>
+        <v>0.372</v>
       </c>
       <c r="K58" t="s">
         <v>144</v>
@@ -6366,10 +6303,10 @@
         <v>148</v>
       </c>
       <c r="M58">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N58">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O58" t="s">
         <v>153</v>
@@ -6413,7 +6350,7 @@
         <v>0.4823</v>
       </c>
       <c r="J59">
-        <v>0.3691</v>
+        <v>0.369</v>
       </c>
       <c r="K59" t="s">
         <v>144</v>
@@ -6422,10 +6359,10 @@
         <v>148</v>
       </c>
       <c r="M59">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N59">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O59" t="s">
         <v>153</v>
@@ -6478,10 +6415,10 @@
         <v>148</v>
       </c>
       <c r="M60">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N60">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O60" t="s">
         <v>153</v>
@@ -6525,7 +6462,7 @@
         <v>0.4072</v>
       </c>
       <c r="J61">
-        <v>0.3647</v>
+        <v>0.3646</v>
       </c>
       <c r="K61" t="s">
         <v>144</v>
@@ -6534,10 +6471,10 @@
         <v>148</v>
       </c>
       <c r="M61">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N61">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O61" t="s">
         <v>153</v>
@@ -6581,7 +6518,7 @@
         <v>0.4251</v>
       </c>
       <c r="J62">
-        <v>0.3629</v>
+        <v>0.3628</v>
       </c>
       <c r="K62" t="s">
         <v>144</v>
@@ -6590,10 +6527,10 @@
         <v>148</v>
       </c>
       <c r="M62">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N62">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O62" t="s">
         <v>153</v>
@@ -6637,7 +6574,7 @@
         <v>0.3951</v>
       </c>
       <c r="J63">
-        <v>0.3627</v>
+        <v>0.3626</v>
       </c>
       <c r="K63" t="s">
         <v>144</v>
@@ -6646,10 +6583,10 @@
         <v>148</v>
       </c>
       <c r="M63">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N63">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O63" t="s">
         <v>153</v>
@@ -6693,7 +6630,7 @@
         <v>0.3647</v>
       </c>
       <c r="J64">
-        <v>0.3615</v>
+        <v>0.3614</v>
       </c>
       <c r="K64" t="s">
         <v>144</v>
@@ -6702,10 +6639,10 @@
         <v>148</v>
       </c>
       <c r="M64">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N64">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O64" t="s">
         <v>153</v>
@@ -6749,7 +6686,7 @@
         <v>0.3813</v>
       </c>
       <c r="J65">
-        <v>0.3571</v>
+        <v>0.357</v>
       </c>
       <c r="K65" t="s">
         <v>144</v>
@@ -6758,10 +6695,10 @@
         <v>148</v>
       </c>
       <c r="M65">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N65">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O65" t="s">
         <v>153</v>
@@ -6805,7 +6742,7 @@
         <v>0.4173</v>
       </c>
       <c r="J66">
-        <v>0.3567</v>
+        <v>0.3566</v>
       </c>
       <c r="K66" t="s">
         <v>144</v>
@@ -6814,10 +6751,10 @@
         <v>148</v>
       </c>
       <c r="M66">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N66">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O66" t="s">
         <v>153</v>
@@ -6861,7 +6798,7 @@
         <v>0.3845</v>
       </c>
       <c r="J67">
-        <v>0.3557</v>
+        <v>0.3556</v>
       </c>
       <c r="K67" t="s">
         <v>144</v>
@@ -6870,10 +6807,10 @@
         <v>148</v>
       </c>
       <c r="M67">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N67">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O67" t="s">
         <v>153</v>
@@ -6917,7 +6854,7 @@
         <v>0.3053</v>
       </c>
       <c r="J68">
-        <v>0.3554</v>
+        <v>0.3553</v>
       </c>
       <c r="K68" t="s">
         <v>144</v>
@@ -6926,10 +6863,10 @@
         <v>148</v>
       </c>
       <c r="M68">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N68">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O68" t="s">
         <v>153</v>
@@ -6973,7 +6910,7 @@
         <v>0.3708</v>
       </c>
       <c r="J69">
-        <v>0.3528</v>
+        <v>0.3527</v>
       </c>
       <c r="K69" t="s">
         <v>144</v>
@@ -6982,10 +6919,10 @@
         <v>148</v>
       </c>
       <c r="M69">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N69">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O69" t="s">
         <v>153</v>
@@ -7029,7 +6966,7 @@
         <v>0.3241</v>
       </c>
       <c r="J70">
-        <v>0.3507</v>
+        <v>0.3506</v>
       </c>
       <c r="K70" t="s">
         <v>144</v>
@@ -7038,10 +6975,10 @@
         <v>148</v>
       </c>
       <c r="M70">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N70">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O70" t="s">
         <v>153</v>
@@ -7085,7 +7022,7 @@
         <v>0.3412</v>
       </c>
       <c r="J71">
-        <v>0.3496</v>
+        <v>0.3495</v>
       </c>
       <c r="K71" t="s">
         <v>144</v>
@@ -7094,10 +7031,10 @@
         <v>148</v>
       </c>
       <c r="M71">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N71">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O71" t="s">
         <v>153</v>
@@ -7150,10 +7087,10 @@
         <v>148</v>
       </c>
       <c r="M72">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N72">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O72" t="s">
         <v>153</v>
@@ -7197,7 +7134,7 @@
         <v>0.3099</v>
       </c>
       <c r="J73">
-        <v>0.348</v>
+        <v>0.3479</v>
       </c>
       <c r="K73" t="s">
         <v>144</v>
@@ -7206,10 +7143,10 @@
         <v>148</v>
       </c>
       <c r="M73">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N73">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O73" t="s">
         <v>153</v>
@@ -7253,7 +7190,7 @@
         <v>0.3114</v>
       </c>
       <c r="J74">
-        <v>0.3449</v>
+        <v>0.3448</v>
       </c>
       <c r="K74" t="s">
         <v>144</v>
@@ -7262,10 +7199,10 @@
         <v>148</v>
       </c>
       <c r="M74">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N74">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O74" t="s">
         <v>153</v>
@@ -7309,7 +7246,7 @@
         <v>0.2727</v>
       </c>
       <c r="J75">
-        <v>0.3408</v>
+        <v>0.3407</v>
       </c>
       <c r="K75" t="s">
         <v>144</v>
@@ -7318,10 +7255,10 @@
         <v>148</v>
       </c>
       <c r="M75">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N75">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O75" t="s">
         <v>153</v>
@@ -7365,7 +7302,7 @@
         <v>0.2664</v>
       </c>
       <c r="J76">
-        <v>0.34</v>
+        <v>0.3399</v>
       </c>
       <c r="K76" t="s">
         <v>144</v>
@@ -7374,10 +7311,10 @@
         <v>148</v>
       </c>
       <c r="M76">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N76">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O76" t="s">
         <v>153</v>
@@ -7421,7 +7358,7 @@
         <v>0.2376</v>
       </c>
       <c r="J77">
-        <v>0.3364</v>
+        <v>0.3363</v>
       </c>
       <c r="K77" t="s">
         <v>144</v>
@@ -7430,10 +7367,10 @@
         <v>148</v>
       </c>
       <c r="M77">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N77">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O77" t="s">
         <v>153</v>
@@ -7477,7 +7414,7 @@
         <v>0.214</v>
       </c>
       <c r="J78">
-        <v>0.3343</v>
+        <v>0.3342</v>
       </c>
       <c r="K78" t="s">
         <v>144</v>
@@ -7486,10 +7423,10 @@
         <v>148</v>
       </c>
       <c r="M78">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N78">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O78" t="s">
         <v>153</v>
@@ -7533,7 +7470,7 @@
         <v>0.1772</v>
       </c>
       <c r="J79">
-        <v>0.3325</v>
+        <v>0.3324</v>
       </c>
       <c r="K79" t="s">
         <v>144</v>
@@ -7542,10 +7479,10 @@
         <v>148</v>
       </c>
       <c r="M79">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N79">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O79" t="s">
         <v>153</v>
@@ -7589,7 +7526,7 @@
         <v>0.075</v>
       </c>
       <c r="J80">
-        <v>0.3132</v>
+        <v>0.3131</v>
       </c>
       <c r="K80" t="s">
         <v>144</v>
@@ -7598,10 +7535,10 @@
         <v>148</v>
       </c>
       <c r="M80">
-        <v>33.95</v>
+        <v>34.01</v>
       </c>
       <c r="N80">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="O80" t="s">
         <v>153</v>
@@ -7795,7 +7732,7 @@
         <v>29.84059297913404</v>
       </c>
       <c r="J5">
-        <v>0.8243</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="K5" t="s">
         <v>157</v>
@@ -7812,7 +7749,7 @@
         <v>12.17000007629395</v>
       </c>
       <c r="D6">
-        <v>0.7634</v>
+        <v>0.7633</v>
       </c>
       <c r="E6">
         <v>9.490199975967407</v>
@@ -7830,7 +7767,7 @@
         <v>52.79048555853054</v>
       </c>
       <c r="J6">
-        <v>0.8243</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="K6" t="s">
         <v>156</v>
@@ -7865,7 +7802,7 @@
         <v>24.32237410558415</v>
       </c>
       <c r="J7">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K7" t="s">
         <v>158</v>
@@ -7882,7 +7819,7 @@
         <v>378.1099853515625</v>
       </c>
       <c r="D8">
-        <v>0.6989</v>
+        <v>0.6988</v>
       </c>
       <c r="E8">
         <v>345.0875982666016</v>
@@ -7900,7 +7837,7 @@
         <v>34.93956665818956</v>
       </c>
       <c r="J8">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K8" t="s">
         <v>158</v>
@@ -7917,7 +7854,7 @@
         <v>79.44499969482422</v>
       </c>
       <c r="D9">
-        <v>0.6987</v>
+        <v>0.6986</v>
       </c>
       <c r="E9">
         <v>77.7081005859375</v>
@@ -7935,7 +7872,7 @@
         <v>55.74873620999067</v>
       </c>
       <c r="J9">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K9" t="s">
         <v>159</v>
@@ -7952,7 +7889,7 @@
         <v>118.0699996948242</v>
       </c>
       <c r="D10">
-        <v>0.6895</v>
+        <v>0.6894</v>
       </c>
       <c r="E10">
         <v>82.51759986877441</v>
@@ -7970,7 +7907,7 @@
         <v>42.79099330023248</v>
       </c>
       <c r="J10">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K10" t="s">
         <v>159</v>
@@ -7987,7 +7924,7 @@
         <v>313.2200012207031</v>
       </c>
       <c r="D11">
-        <v>0.6884</v>
+        <v>0.6883</v>
       </c>
       <c r="E11">
         <v>307.3132015991211</v>
@@ -8005,7 +7942,7 @@
         <v>39.25098385656076</v>
       </c>
       <c r="J11">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K11" t="s">
         <v>158</v>
@@ -8022,7 +7959,7 @@
         <v>192.1600036621094</v>
       </c>
       <c r="D12">
-        <v>0.6871</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E12">
         <v>156.3657997131348</v>
@@ -8040,7 +7977,7 @@
         <v>41.29244115486681</v>
       </c>
       <c r="J12">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K12" t="s">
         <v>159</v>
@@ -8075,7 +8012,7 @@
         <v>47.29547809343844</v>
       </c>
       <c r="J13">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K13" t="s">
         <v>159</v>
@@ -8092,7 +8029,7 @@
         <v>156.1300048828125</v>
       </c>
       <c r="D14">
-        <v>0.675</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E14">
         <v>147.9280003356934</v>
@@ -8110,7 +8047,7 @@
         <v>52.01954969224415</v>
       </c>
       <c r="J14">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K14" t="s">
         <v>159</v>
@@ -8127,7 +8064,7 @@
         <v>452.6400146484375</v>
       </c>
       <c r="D15">
-        <v>0.6714</v>
+        <v>0.6713</v>
       </c>
       <c r="E15">
         <v>407.5396551513672</v>
@@ -8145,7 +8082,7 @@
         <v>50.0953380320746</v>
       </c>
       <c r="J15">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K15" t="s">
         <v>159</v>
@@ -8180,7 +8117,7 @@
         <v>49.58712417755017</v>
       </c>
       <c r="J16">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K16" t="s">
         <v>159</v>
@@ -8197,7 +8134,7 @@
         <v>1646.010009765625</v>
       </c>
       <c r="D17">
-        <v>0.6681</v>
+        <v>0.668</v>
       </c>
       <c r="E17">
         <v>1077.626197509766</v>
@@ -8215,7 +8152,7 @@
         <v>55.81680137154054</v>
       </c>
       <c r="J17">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K17" t="s">
         <v>159</v>
@@ -8250,7 +8187,7 @@
         <v>52.52196685210854</v>
       </c>
       <c r="J18">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K18" t="s">
         <v>159</v>
@@ -8267,7 +8204,7 @@
         <v>437.3999938964844</v>
       </c>
       <c r="D19">
-        <v>0.6627999999999999</v>
+        <v>0.6627</v>
       </c>
       <c r="E19">
         <v>385.4850103759766</v>
@@ -8285,7 +8222,7 @@
         <v>53.74493548838463</v>
       </c>
       <c r="J19">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K19" t="s">
         <v>159</v>
@@ -8302,7 +8239,7 @@
         <v>418.6000061035156</v>
       </c>
       <c r="D20">
-        <v>0.6625</v>
+        <v>0.6624</v>
       </c>
       <c r="E20">
         <v>379.3989996337891</v>
@@ -8320,7 +8257,7 @@
         <v>53.33591079169458</v>
       </c>
       <c r="J20">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K20" t="s">
         <v>159</v>
@@ -8337,7 +8274,7 @@
         <v>1930.010009765625</v>
       </c>
       <c r="D21">
-        <v>0.6622</v>
+        <v>0.6621</v>
       </c>
       <c r="E21">
         <v>1730.606733398437</v>
@@ -8355,7 +8292,7 @@
         <v>54.89072413854991</v>
       </c>
       <c r="J21">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K21" t="s">
         <v>159</v>
@@ -8372,7 +8309,7 @@
         <v>104.2600021362305</v>
       </c>
       <c r="D22">
-        <v>0.6617</v>
+        <v>0.6616</v>
       </c>
       <c r="E22">
         <v>57.82180000305176</v>
@@ -8390,7 +8327,7 @@
         <v>61.68698087643116</v>
       </c>
       <c r="J22">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K22" t="s">
         <v>159</v>
@@ -8407,7 +8344,7 @@
         <v>270.2804870605469</v>
       </c>
       <c r="D23">
-        <v>0.6533</v>
+        <v>0.6534</v>
       </c>
       <c r="E23">
         <v>246.6624099731445</v>
@@ -8425,7 +8362,7 @@
         <v>47.50671781742124</v>
       </c>
       <c r="J23">
-        <v>0.5152</v>
+        <v>0.516</v>
       </c>
       <c r="K23" t="s">
         <v>159</v>
@@ -8442,7 +8379,7 @@
         <v>289.6799926757812</v>
       </c>
       <c r="D24">
-        <v>0.6525</v>
+        <v>0.6524</v>
       </c>
       <c r="E24">
         <v>270.0206011962891</v>
@@ -8460,7 +8397,7 @@
         <v>57.0804147127497</v>
       </c>
       <c r="J24">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K24" t="s">
         <v>159</v>
@@ -8477,7 +8414,7 @@
         <v>229.1600036621094</v>
       </c>
       <c r="D25">
-        <v>0.651</v>
+        <v>0.6509</v>
       </c>
       <c r="E25">
         <v>158.9171002197266</v>
@@ -8495,7 +8432,7 @@
         <v>63.60836779223327</v>
       </c>
       <c r="J25">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K25" t="s">
         <v>159</v>
@@ -8512,7 +8449,7 @@
         <v>17.04999923706055</v>
       </c>
       <c r="D26">
-        <v>0.6493</v>
+        <v>0.6492</v>
       </c>
       <c r="E26">
         <v>13.00539991378784</v>
@@ -8530,7 +8467,7 @@
         <v>72.55699795767705</v>
       </c>
       <c r="J26">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K26" t="s">
         <v>159</v>
@@ -8547,7 +8484,7 @@
         <v>160.1600036621094</v>
       </c>
       <c r="D27">
-        <v>0.6491</v>
+        <v>0.649</v>
       </c>
       <c r="E27">
         <v>148.8601998901367</v>
@@ -8565,7 +8502,7 @@
         <v>66.77614060250662</v>
       </c>
       <c r="J27">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K27" t="s">
         <v>159</v>
@@ -8582,7 +8519,7 @@
         <v>599.510009765625</v>
       </c>
       <c r="D28">
-        <v>0.6449</v>
+        <v>0.6448</v>
       </c>
       <c r="E28">
         <v>484.7420007324219</v>
@@ -8600,7 +8537,7 @@
         <v>61.30891593465972</v>
       </c>
       <c r="J28">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K28" t="s">
         <v>159</v>
@@ -8617,7 +8554,7 @@
         <v>204.1499938964844</v>
       </c>
       <c r="D29">
-        <v>0.6445</v>
+        <v>0.6444</v>
       </c>
       <c r="E29">
         <v>146.6463409423828</v>
@@ -8635,7 +8572,7 @@
         <v>68.00380242260704</v>
       </c>
       <c r="J29">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K29" t="s">
         <v>159</v>
@@ -8670,7 +8607,7 @@
         <v>68.7262179373717</v>
       </c>
       <c r="J30">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K30" t="s">
         <v>159</v>
@@ -8687,7 +8624,7 @@
         <v>38.50500106811523</v>
       </c>
       <c r="D31">
-        <v>0.6435999999999999</v>
+        <v>0.6435</v>
       </c>
       <c r="E31">
         <v>32.1243002319336</v>
@@ -8705,7 +8642,7 @@
         <v>73.3756782876756</v>
       </c>
       <c r="J31">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K31" t="s">
         <v>159</v>
@@ -8722,7 +8659,7 @@
         <v>566.0499877929688</v>
       </c>
       <c r="D32">
-        <v>0.6421</v>
+        <v>0.642</v>
       </c>
       <c r="E32">
         <v>437.5693994140625</v>
@@ -8740,7 +8677,7 @@
         <v>63.72471183466363</v>
       </c>
       <c r="J32">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K32" t="s">
         <v>159</v>
@@ -8757,7 +8694,7 @@
         <v>238.2949981689453</v>
       </c>
       <c r="D33">
-        <v>0.6356000000000001</v>
+        <v>0.6355</v>
       </c>
       <c r="E33">
         <v>208.7752996826172</v>
@@ -8775,7 +8712,7 @@
         <v>75.71506554383619</v>
       </c>
       <c r="J33">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K33" t="s">
         <v>159</v>
@@ -8792,7 +8729,7 @@
         <v>136.8999938964844</v>
       </c>
       <c r="D34">
-        <v>0.6335</v>
+        <v>0.6334</v>
       </c>
       <c r="E34">
         <v>96.12719970703125</v>
@@ -8810,7 +8747,7 @@
         <v>79.18690654428941</v>
       </c>
       <c r="J34">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K34" t="s">
         <v>159</v>
@@ -8827,7 +8764,7 @@
         <v>737.3900146484375</v>
       </c>
       <c r="D35">
-        <v>0.6333</v>
+        <v>0.6332</v>
       </c>
       <c r="E35">
         <v>652.883203125</v>
@@ -8845,7 +8782,7 @@
         <v>67.11149544232157</v>
       </c>
       <c r="J35">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K35" t="s">
         <v>159</v>
@@ -8862,7 +8799,7 @@
         <v>756.3519897460938</v>
       </c>
       <c r="D36">
-        <v>0.6322</v>
+        <v>0.6321</v>
       </c>
       <c r="E36">
         <v>703.6085009765625</v>
@@ -8880,7 +8817,7 @@
         <v>68.69012892264033</v>
       </c>
       <c r="J36">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K36" t="s">
         <v>159</v>
@@ -8897,7 +8834,7 @@
         <v>120.9800033569336</v>
       </c>
       <c r="D37">
-        <v>0.6313</v>
+        <v>0.6312</v>
       </c>
       <c r="E37">
         <v>93.07899780273438</v>
@@ -8915,7 +8852,7 @@
         <v>80.7508215679068</v>
       </c>
       <c r="J37">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K37" t="s">
         <v>159</v>
@@ -8932,7 +8869,7 @@
         <v>243.2799987792969</v>
       </c>
       <c r="D38">
-        <v>0.627</v>
+        <v>0.6269</v>
       </c>
       <c r="E38">
         <v>153.0168003845215</v>
@@ -8950,7 +8887,7 @@
         <v>84.59564438781432</v>
       </c>
       <c r="J38">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K38" t="s">
         <v>159</v>
@@ -8967,7 +8904,7 @@
         <v>279.1600036621094</v>
       </c>
       <c r="D39">
-        <v>0.6254</v>
+        <v>0.6253</v>
       </c>
       <c r="E39">
         <v>191.3692004394531</v>
@@ -8985,7 +8922,7 @@
         <v>82.30017258450833</v>
       </c>
       <c r="J39">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K39" t="s">
         <v>159</v>
@@ -9002,7 +8939,7 @@
         <v>335.5</v>
       </c>
       <c r="D40">
-        <v>0.6251</v>
+        <v>0.625</v>
       </c>
       <c r="E40">
         <v>190.2706001281738</v>
@@ -9020,7 +8957,7 @@
         <v>83.40800204702586</v>
       </c>
       <c r="J40">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K40" t="s">
         <v>159</v>
@@ -9037,7 +8974,7 @@
         <v>351.0299987792969</v>
       </c>
       <c r="D41">
-        <v>0.6249</v>
+        <v>0.6248</v>
       </c>
       <c r="E41">
         <v>198.3919012451172</v>
@@ -9055,7 +8992,7 @@
         <v>80.72804757289227</v>
       </c>
       <c r="J41">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K41" t="s">
         <v>159</v>
@@ -9072,7 +9009,7 @@
         <v>311.3699951171875</v>
       </c>
       <c r="D42">
-        <v>0.6245000000000001</v>
+        <v>0.6244</v>
       </c>
       <c r="E42">
         <v>275.0954885864258</v>
@@ -9090,7 +9027,7 @@
         <v>82.2306288932008</v>
       </c>
       <c r="J42">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K42" t="s">
         <v>159</v>
@@ -9107,7 +9044,7 @@
         <v>416.2999877929688</v>
       </c>
       <c r="D43">
-        <v>0.6237</v>
+        <v>0.6236</v>
       </c>
       <c r="E43">
         <v>215.5247280883789</v>
@@ -9125,7 +9062,7 @@
         <v>84.76398843833833</v>
       </c>
       <c r="J43">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K43" t="s">
         <v>159</v>
@@ -9142,7 +9079,7 @@
         <v>726.155029296875</v>
       </c>
       <c r="D44">
-        <v>0.6128</v>
+        <v>0.6127</v>
       </c>
       <c r="E44">
         <v>482.4160998535156</v>
@@ -9160,7 +9097,7 @@
         <v>88.38347146788549</v>
       </c>
       <c r="J44">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K44" t="s">
         <v>159</v>
@@ -9247,7 +9184,7 @@
         <v>842.4000244140625</v>
       </c>
       <c r="D47">
-        <v>0.4099</v>
+        <v>0.4098</v>
       </c>
       <c r="E47">
         <v>865.7679956054687</v>
@@ -9265,7 +9202,7 @@
         <v>40.11494958459248</v>
       </c>
       <c r="J47">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K47" t="s">
         <v>161</v>
@@ -9335,7 +9272,7 @@
         <v>33.9729473260635</v>
       </c>
       <c r="J49">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K49" t="s">
         <v>162</v>
@@ -9370,7 +9307,7 @@
         <v>37.02109183728933</v>
       </c>
       <c r="J50">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K50" t="s">
         <v>162</v>
@@ -9387,7 +9324,7 @@
         <v>138.6849975585938</v>
       </c>
       <c r="D51">
-        <v>0.3866</v>
+        <v>0.3865</v>
       </c>
       <c r="E51">
         <v>143.5598994445801</v>
@@ -9405,7 +9342,7 @@
         <v>44.54939598291897</v>
       </c>
       <c r="J51">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K51" t="s">
         <v>161</v>
@@ -9422,7 +9359,7 @@
         <v>286.9700012207031</v>
       </c>
       <c r="D52">
-        <v>0.3863</v>
+        <v>0.3862</v>
       </c>
       <c r="E52">
         <v>292.132578125</v>
@@ -9440,7 +9377,7 @@
         <v>41.9093713425007</v>
       </c>
       <c r="J52">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K52" t="s">
         <v>161</v>
@@ -9457,7 +9394,7 @@
         <v>86.90000152587891</v>
       </c>
       <c r="D53">
-        <v>0.385</v>
+        <v>0.3849</v>
       </c>
       <c r="E53">
         <v>91.8866683959961</v>
@@ -9475,7 +9412,7 @@
         <v>45.24736162443781</v>
       </c>
       <c r="J53">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K53" t="s">
         <v>161</v>
@@ -9492,7 +9429,7 @@
         <v>71.58999633789062</v>
       </c>
       <c r="D54">
-        <v>0.3798</v>
+        <v>0.3797</v>
       </c>
       <c r="E54">
         <v>65.93580032348633</v>
@@ -9510,7 +9447,7 @@
         <v>45.78635887349753</v>
       </c>
       <c r="J54">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K54" t="s">
         <v>161</v>
@@ -9527,7 +9464,7 @@
         <v>256.6799926757812</v>
       </c>
       <c r="D55">
-        <v>0.3778</v>
+        <v>0.3777</v>
       </c>
       <c r="E55">
         <v>244.4010006713867</v>
@@ -9545,7 +9482,7 @@
         <v>52.4694725609674</v>
       </c>
       <c r="J55">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K55" t="s">
         <v>161</v>
@@ -9562,7 +9499,7 @@
         <v>12.4601001739502</v>
       </c>
       <c r="D56">
-        <v>0.3768</v>
+        <v>0.3767</v>
       </c>
       <c r="E56">
         <v>11.46560195922851</v>
@@ -9580,7 +9517,7 @@
         <v>49.34571546247042</v>
       </c>
       <c r="J56">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K56" t="s">
         <v>161</v>
@@ -9597,7 +9534,7 @@
         <v>16.40999984741211</v>
       </c>
       <c r="D57">
-        <v>0.3765</v>
+        <v>0.3764</v>
       </c>
       <c r="E57">
         <v>14.91660001754761</v>
@@ -9615,7 +9552,7 @@
         <v>48.56229749649761</v>
       </c>
       <c r="J57">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K57" t="s">
         <v>161</v>
@@ -9632,7 +9569,7 @@
         <v>50.13999938964844</v>
       </c>
       <c r="D58">
-        <v>0.3721</v>
+        <v>0.372</v>
       </c>
       <c r="E58">
         <v>49.06369972229004</v>
@@ -9650,7 +9587,7 @@
         <v>50.89285279849747</v>
       </c>
       <c r="J58">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K58" t="s">
         <v>161</v>
@@ -9667,7 +9604,7 @@
         <v>8.979999542236328</v>
       </c>
       <c r="D59">
-        <v>0.3691</v>
+        <v>0.369</v>
       </c>
       <c r="E59">
         <v>7.755500020980835</v>
@@ -9685,7 +9622,7 @@
         <v>51.77304029140512</v>
       </c>
       <c r="J59">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K59" t="s">
         <v>161</v>
@@ -9720,7 +9657,7 @@
         <v>55.20473843066302</v>
       </c>
       <c r="J60">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K60" t="s">
         <v>161</v>
@@ -9737,7 +9674,7 @@
         <v>326.5499877929688</v>
       </c>
       <c r="D61">
-        <v>0.3647</v>
+        <v>0.3646</v>
       </c>
       <c r="E61">
         <v>272.237200012207</v>
@@ -9755,7 +9692,7 @@
         <v>59.28286837585451</v>
       </c>
       <c r="J61">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K61" t="s">
         <v>161</v>
@@ -9772,7 +9709,7 @@
         <v>3.535000085830688</v>
       </c>
       <c r="D62">
-        <v>0.3629</v>
+        <v>0.3628</v>
       </c>
       <c r="E62">
         <v>3.281500005722046</v>
@@ -9790,7 +9727,7 @@
         <v>57.49129481397203</v>
       </c>
       <c r="J62">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K62" t="s">
         <v>161</v>
@@ -9807,7 +9744,7 @@
         <v>11.64500045776367</v>
       </c>
       <c r="D63">
-        <v>0.3627</v>
+        <v>0.3626</v>
       </c>
       <c r="E63">
         <v>10.71590005874634</v>
@@ -9825,7 +9762,7 @@
         <v>60.49079921150475</v>
       </c>
       <c r="J63">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K63" t="s">
         <v>161</v>
@@ -9842,7 +9779,7 @@
         <v>144.8500061035156</v>
       </c>
       <c r="D64">
-        <v>0.3615</v>
+        <v>0.3614</v>
       </c>
       <c r="E64">
         <v>125.4602005004883</v>
@@ -9860,7 +9797,7 @@
         <v>63.52941319169427</v>
       </c>
       <c r="J64">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K64" t="s">
         <v>161</v>
@@ -9877,7 +9814,7 @@
         <v>24.07999992370605</v>
       </c>
       <c r="D65">
-        <v>0.3571</v>
+        <v>0.357</v>
       </c>
       <c r="E65">
         <v>18.156100025177</v>
@@ -9895,7 +9832,7 @@
         <v>61.87049520601642</v>
       </c>
       <c r="J65">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K65" t="s">
         <v>161</v>
@@ -9912,7 +9849,7 @@
         <v>376.1700134277344</v>
       </c>
       <c r="D66">
-        <v>0.3567</v>
+        <v>0.3566</v>
       </c>
       <c r="E66">
         <v>322.0032006835938</v>
@@ -9930,7 +9867,7 @@
         <v>58.27090592171268</v>
       </c>
       <c r="J66">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K66" t="s">
         <v>161</v>
@@ -9947,7 +9884,7 @@
         <v>10.85499954223633</v>
       </c>
       <c r="D67">
-        <v>0.3557</v>
+        <v>0.3556</v>
       </c>
       <c r="E67">
         <v>8.953699989318848</v>
@@ -9965,7 +9902,7 @@
         <v>61.54747452974244</v>
       </c>
       <c r="J67">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K67" t="s">
         <v>161</v>
@@ -9982,7 +9919,7 @@
         <v>109.3625030517578</v>
       </c>
       <c r="D68">
-        <v>0.3554</v>
+        <v>0.3553</v>
       </c>
       <c r="E68">
         <v>90.37204956054687</v>
@@ -10000,7 +9937,7 @@
         <v>69.46505928053598</v>
       </c>
       <c r="J68">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K68" t="s">
         <v>161</v>
@@ -10017,7 +9954,7 @@
         <v>8.024999618530273</v>
       </c>
       <c r="D69">
-        <v>0.3528</v>
+        <v>0.3527</v>
       </c>
       <c r="E69">
         <v>6.22210000038147</v>
@@ -10035,7 +9972,7 @@
         <v>62.92237220217377</v>
       </c>
       <c r="J69">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K69" t="s">
         <v>161</v>
@@ -10052,7 +9989,7 @@
         <v>223.4850006103516</v>
       </c>
       <c r="D70">
-        <v>0.3507</v>
+        <v>0.3506</v>
       </c>
       <c r="E70">
         <v>170.9187496948242</v>
@@ -10070,7 +10007,7 @@
         <v>67.58864039885938</v>
       </c>
       <c r="J70">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K70" t="s">
         <v>161</v>
@@ -10087,7 +10024,7 @@
         <v>78.55000305175781</v>
       </c>
       <c r="D71">
-        <v>0.3496</v>
+        <v>0.3495</v>
       </c>
       <c r="E71">
         <v>62.95691932678223</v>
@@ -10105,7 +10042,7 @@
         <v>65.88147838728383</v>
       </c>
       <c r="J71">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K71" t="s">
         <v>161</v>
@@ -10140,7 +10077,7 @@
         <v>58.07715318316384</v>
       </c>
       <c r="J72">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K72" t="s">
         <v>161</v>
@@ -10157,7 +10094,7 @@
         <v>5.026599884033203</v>
       </c>
       <c r="D73">
-        <v>0.348</v>
+        <v>0.3479</v>
       </c>
       <c r="E73">
         <v>3.864331970214844</v>
@@ -10175,7 +10112,7 @@
         <v>69.011043961692</v>
       </c>
       <c r="J73">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K73" t="s">
         <v>161</v>
@@ -10192,7 +10129,7 @@
         <v>442.6698913574219</v>
       </c>
       <c r="D74">
-        <v>0.3449</v>
+        <v>0.3448</v>
       </c>
       <c r="E74">
         <v>401.9135546875</v>
@@ -10210,7 +10147,7 @@
         <v>68.86465938081456</v>
       </c>
       <c r="J74">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K74" t="s">
         <v>161</v>
@@ -10227,7 +10164,7 @@
         <v>68.98000335693359</v>
       </c>
       <c r="D75">
-        <v>0.3408</v>
+        <v>0.3407</v>
       </c>
       <c r="E75">
         <v>43.68120010375976</v>
@@ -10245,7 +10182,7 @@
         <v>72.73146105094992</v>
       </c>
       <c r="J75">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K75" t="s">
         <v>161</v>
@@ -10262,7 +10199,7 @@
         <v>45.6150016784668</v>
       </c>
       <c r="D76">
-        <v>0.34</v>
+        <v>0.3399</v>
       </c>
       <c r="E76">
         <v>28.65929988861084</v>
@@ -10280,7 +10217,7 @@
         <v>73.36374709939457</v>
       </c>
       <c r="J76">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K76" t="s">
         <v>161</v>
@@ -10297,7 +10234,7 @@
         <v>613.1300048828125</v>
       </c>
       <c r="D77">
-        <v>0.3364</v>
+        <v>0.3363</v>
       </c>
       <c r="E77">
         <v>457.9214019775391</v>
@@ -10315,7 +10252,7 @@
         <v>76.23765512710006</v>
       </c>
       <c r="J77">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K77" t="s">
         <v>161</v>
@@ -10332,7 +10269,7 @@
         <v>122.8566970825195</v>
       </c>
       <c r="D78">
-        <v>0.3343</v>
+        <v>0.3342</v>
       </c>
       <c r="E78">
         <v>97.60793411254883</v>
@@ -10350,7 +10287,7 @@
         <v>78.60111662018215</v>
       </c>
       <c r="J78">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K78" t="s">
         <v>161</v>
@@ -10367,7 +10304,7 @@
         <v>297.8349914550781</v>
       </c>
       <c r="D79">
-        <v>0.3325</v>
+        <v>0.3324</v>
       </c>
       <c r="E79">
         <v>237.9992828369141</v>
@@ -10385,7 +10322,7 @@
         <v>82.27680786422185</v>
       </c>
       <c r="J79">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K79" t="s">
         <v>161</v>
@@ -10402,7 +10339,7 @@
         <v>253.3600006103516</v>
       </c>
       <c r="D80">
-        <v>0.3132</v>
+        <v>0.3131</v>
       </c>
       <c r="E80">
         <v>155.9348007202148</v>
@@ -10420,7 +10357,7 @@
         <v>92.49556488986379</v>
       </c>
       <c r="J80">
-        <v>0.6605</v>
+        <v>0.6599</v>
       </c>
       <c r="K80" t="s">
         <v>161</v>
@@ -10494,13 +10431,13 @@
         <v>7.28</v>
       </c>
       <c r="G2">
-        <v>587.8200000000001</v>
+        <v>586.62</v>
       </c>
       <c r="H2">
         <v>217.2599945068359</v>
       </c>
       <c r="I2">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="s">
         <v>153</v>
@@ -10523,7 +10460,7 @@
         <v>0.8028</v>
       </c>
       <c r="D3">
-        <v>0.4729</v>
+        <v>0.4728</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -10532,7 +10469,7 @@
         <v>5.08</v>
       </c>
       <c r="G3">
-        <v>410.18</v>
+        <v>409.35</v>
       </c>
       <c r="H3">
         <v>504.6749877929688</v>
@@ -10558,7 +10495,7 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>0.6987</v>
+        <v>0.6986</v>
       </c>
       <c r="D4">
         <v>0.1219</v>
@@ -10567,16 +10504,16 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="G4">
-        <v>275.34</v>
+        <v>273.97</v>
       </c>
       <c r="H4">
         <v>79.44499969482422</v>
       </c>
       <c r="I4">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="s">
         <v>153</v>
@@ -10608,7 +10545,7 @@
         <v>3.26</v>
       </c>
       <c r="G5">
-        <v>263.23</v>
+        <v>262.69</v>
       </c>
       <c r="H5">
         <v>105.504997253418</v>
@@ -10634,7 +10571,7 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>0.6322</v>
+        <v>0.6321</v>
       </c>
       <c r="D6">
         <v>0.1063</v>
@@ -10643,16 +10580,16 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="G6">
-        <v>253.54</v>
+        <v>252.22</v>
       </c>
       <c r="H6">
         <v>756.3519897460938</v>
       </c>
       <c r="I6">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J6" t="s">
         <v>153</v>
@@ -10672,10 +10609,10 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>0.6525</v>
+        <v>0.6524</v>
       </c>
       <c r="D7">
-        <v>0.1515</v>
+        <v>0.1514</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -10684,13 +10621,13 @@
         <v>3.07</v>
       </c>
       <c r="G7">
-        <v>247.89</v>
+        <v>247.38</v>
       </c>
       <c r="H7">
         <v>289.6799926757812</v>
       </c>
       <c r="I7">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="s">
         <v>153</v>
@@ -10710,7 +10647,7 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>0.6333</v>
+        <v>0.6332</v>
       </c>
       <c r="D8">
         <v>0.1439</v>
@@ -10722,7 +10659,7 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>242.24</v>
+        <v>241.74</v>
       </c>
       <c r="H8">
         <v>737.3900146484375</v>
@@ -10748,19 +10685,19 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>0.6989</v>
+        <v>0.6988</v>
       </c>
       <c r="D9">
-        <v>0.2465</v>
+        <v>0.2471</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="G9">
-        <v>235.78</v>
+        <v>234.49</v>
       </c>
       <c r="H9">
         <v>378.1099853515625</v>
@@ -10786,10 +10723,10 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0.6245000000000001</v>
+        <v>0.6244</v>
       </c>
       <c r="D10">
-        <v>0.1764</v>
+        <v>0.1763</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -10798,7 +10735,7 @@
         <v>2.85</v>
       </c>
       <c r="G10">
-        <v>230.12</v>
+        <v>229.65</v>
       </c>
       <c r="H10">
         <v>311.3699951171875</v>
@@ -10836,7 +10773,7 @@
         <v>2.8</v>
       </c>
       <c r="G11">
-        <v>226.09</v>
+        <v>225.62</v>
       </c>
       <c r="H11">
         <v>400.5350036621094</v>
@@ -10862,7 +10799,7 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <v>0.6714</v>
+        <v>0.6713</v>
       </c>
       <c r="D12">
         <v>0.2586</v>
@@ -10871,10 +10808,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>223.66</v>
+        <v>222.4</v>
       </c>
       <c r="H12">
         <v>452.6400146484375</v>
@@ -10900,10 +10837,10 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.6449</v>
+        <v>0.6448</v>
       </c>
       <c r="D13">
-        <v>0.2476</v>
+        <v>0.2477</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -10912,7 +10849,7 @@
         <v>2.69</v>
       </c>
       <c r="G13">
-        <v>217.2</v>
+        <v>216.76</v>
       </c>
       <c r="H13">
         <v>599.510009765625</v>
@@ -10938,19 +10875,19 @@
         <v>18</v>
       </c>
       <c r="C14">
-        <v>0.6625</v>
+        <v>0.6624</v>
       </c>
       <c r="D14">
-        <v>0.2822</v>
+        <v>0.2824</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="G14">
-        <v>213.17</v>
+        <v>211.93</v>
       </c>
       <c r="H14">
         <v>418.6000061035156</v>
@@ -10976,10 +10913,10 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0.6313</v>
+        <v>0.6312</v>
       </c>
       <c r="D15">
-        <v>0.2518</v>
+        <v>0.2513</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10988,7 +10925,7 @@
         <v>2.62</v>
       </c>
       <c r="G15">
-        <v>211.55</v>
+        <v>211.12</v>
       </c>
       <c r="H15">
         <v>120.9800033569336</v>
@@ -11014,19 +10951,19 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>0.6421</v>
+        <v>0.642</v>
       </c>
       <c r="D16">
-        <v>0.2738</v>
+        <v>0.2739</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="G16">
-        <v>209.13</v>
+        <v>207.9</v>
       </c>
       <c r="H16">
         <v>566.0499877929688</v>
@@ -11055,7 +10992,7 @@
         <v>0.6666</v>
       </c>
       <c r="D17">
-        <v>0.3213</v>
+        <v>0.321</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -11064,7 +11001,7 @@
         <v>2.51</v>
       </c>
       <c r="G17">
-        <v>202.67</v>
+        <v>202.26</v>
       </c>
       <c r="H17">
         <v>1616.579956054688</v>
@@ -11090,19 +11027,19 @@
         <v>18</v>
       </c>
       <c r="C18">
-        <v>0.6335</v>
+        <v>0.6334</v>
       </c>
       <c r="D18">
-        <v>0.3038</v>
+        <v>0.3034</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="G18">
-        <v>197.02</v>
+        <v>197.42</v>
       </c>
       <c r="H18">
         <v>136.8999938964844</v>
@@ -11128,25 +11065,25 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>0.6627999999999999</v>
+        <v>0.6627</v>
       </c>
       <c r="D19">
-        <v>0.3586</v>
+        <v>0.3588</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="G19">
-        <v>190.56</v>
+        <v>189.36</v>
       </c>
       <c r="H19">
         <v>437.3999938964844</v>
       </c>
       <c r="I19">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J19" t="s">
         <v>153</v>
@@ -11166,10 +11103,10 @@
         <v>18</v>
       </c>
       <c r="C20">
-        <v>0.6622</v>
+        <v>0.6621</v>
       </c>
       <c r="D20">
-        <v>0.3761</v>
+        <v>0.3759</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -11178,7 +11115,7 @@
         <v>2.29</v>
       </c>
       <c r="G20">
-        <v>184.91</v>
+        <v>184.53</v>
       </c>
       <c r="H20">
         <v>1930.010009765625</v>
@@ -11204,10 +11141,10 @@
         <v>18</v>
       </c>
       <c r="C21">
-        <v>0.6254</v>
+        <v>0.6253</v>
       </c>
       <c r="D21">
-        <v>0.3672</v>
+        <v>0.3666</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -11216,7 +11153,7 @@
         <v>2.2</v>
       </c>
       <c r="G21">
-        <v>177.64</v>
+        <v>177.28</v>
       </c>
       <c r="H21">
         <v>279.1600036621094</v>
@@ -11242,10 +11179,10 @@
         <v>18</v>
       </c>
       <c r="C22">
-        <v>0.6491</v>
+        <v>0.649</v>
       </c>
       <c r="D22">
-        <v>0.3971</v>
+        <v>0.3968</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -11254,7 +11191,7 @@
         <v>2.17</v>
       </c>
       <c r="G22">
-        <v>175.22</v>
+        <v>174.86</v>
       </c>
       <c r="H22">
         <v>160.1600036621094</v>
@@ -11280,10 +11217,10 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>0.6884</v>
+        <v>0.6883</v>
       </c>
       <c r="D23">
-        <v>0.4344</v>
+        <v>0.4345</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -11292,7 +11229,7 @@
         <v>2.16</v>
       </c>
       <c r="G23">
-        <v>174.41</v>
+        <v>174.05</v>
       </c>
       <c r="H23">
         <v>313.2200012207031</v>
@@ -11318,10 +11255,10 @@
         <v>18</v>
       </c>
       <c r="C24">
-        <v>0.6871</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="D24">
-        <v>0.4392</v>
+        <v>0.4391</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -11330,7 +11267,7 @@
         <v>2.14</v>
       </c>
       <c r="G24">
-        <v>172.79</v>
+        <v>172.44</v>
       </c>
       <c r="H24">
         <v>192.1600036621094</v>
@@ -11356,19 +11293,19 @@
         <v>18</v>
       </c>
       <c r="C25">
-        <v>0.6128</v>
+        <v>0.6127</v>
       </c>
       <c r="D25">
-        <v>0.4227</v>
+        <v>0.4215</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G25">
-        <v>158.26</v>
+        <v>158.74</v>
       </c>
       <c r="H25">
         <v>726.155029296875</v>
@@ -11394,7 +11331,7 @@
         <v>18</v>
       </c>
       <c r="C26">
-        <v>0.6435999999999999</v>
+        <v>0.6435</v>
       </c>
       <c r="D26">
         <v>0.4764</v>
@@ -11406,13 +11343,13 @@
         <v>1.87</v>
       </c>
       <c r="G26">
-        <v>150.99</v>
+        <v>150.68</v>
       </c>
       <c r="H26">
         <v>38.50500106811523</v>
       </c>
       <c r="I26">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="J26" t="s">
         <v>153</v>
@@ -11426,31 +11363,31 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
       <c r="C27">
-        <v>0.6445</v>
+        <v>0.6894</v>
       </c>
       <c r="D27">
-        <v>0.4971</v>
+        <v>0.5311</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G27">
-        <v>145.34</v>
+        <v>144.24</v>
       </c>
       <c r="H27">
-        <v>204.1499938964844</v>
+        <v>118.0699996948242</v>
       </c>
       <c r="I27">
-        <v>0.71</v>
+        <v>1.22</v>
       </c>
       <c r="J27" t="s">
         <v>153</v>
@@ -11464,31 +11401,31 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
       </c>
       <c r="C28">
-        <v>0.6895</v>
+        <v>0.6444</v>
       </c>
       <c r="D28">
-        <v>0.5309</v>
+        <v>0.5024</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G28">
-        <v>145.34</v>
+        <v>143.43</v>
       </c>
       <c r="H28">
-        <v>118.0699996948242</v>
+        <v>204.1499938964844</v>
       </c>
       <c r="I28">
-        <v>1.23</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="s">
         <v>153</v>
@@ -11508,7 +11445,7 @@
         <v>18</v>
       </c>
       <c r="C29">
-        <v>0.6356000000000001</v>
+        <v>0.6355</v>
       </c>
       <c r="D29">
         <v>0.5011</v>
@@ -11520,7 +11457,7 @@
         <v>1.76</v>
       </c>
       <c r="G29">
-        <v>142.11</v>
+        <v>141.82</v>
       </c>
       <c r="H29">
         <v>238.2949981689453</v>
@@ -11546,10 +11483,10 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>0.6237</v>
+        <v>0.6236</v>
       </c>
       <c r="D30">
-        <v>0.5078</v>
+        <v>0.5082</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -11558,7 +11495,7 @@
         <v>1.7</v>
       </c>
       <c r="G30">
-        <v>137.27</v>
+        <v>136.99</v>
       </c>
       <c r="H30">
         <v>416.2999877929688</v>
@@ -11584,10 +11521,10 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>0.6249</v>
+        <v>0.6248</v>
       </c>
       <c r="D31">
-        <v>0.5269</v>
+        <v>0.5273</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -11596,7 +11533,7 @@
         <v>1.64</v>
       </c>
       <c r="G31">
-        <v>132.42</v>
+        <v>132.15</v>
       </c>
       <c r="H31">
         <v>351.0299987792969</v>
@@ -11634,7 +11571,7 @@
         <v>1.63</v>
       </c>
       <c r="G32">
-        <v>131.61</v>
+        <v>131.35</v>
       </c>
       <c r="H32">
         <v>946.5999755859375</v>
@@ -11660,10 +11597,10 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>0.627</v>
+        <v>0.6269</v>
       </c>
       <c r="D33">
-        <v>0.5458</v>
+        <v>0.5457</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -11672,7 +11609,7 @@
         <v>1.58</v>
       </c>
       <c r="G33">
-        <v>127.58</v>
+        <v>127.32</v>
       </c>
       <c r="H33">
         <v>243.2799987792969</v>
@@ -11710,7 +11647,7 @@
         <v>1.45</v>
       </c>
       <c r="G34">
-        <v>117.08</v>
+        <v>116.84</v>
       </c>
       <c r="H34">
         <v>434.2398986816406</v>
@@ -11736,10 +11673,10 @@
         <v>18</v>
       </c>
       <c r="C35">
-        <v>0.6681</v>
+        <v>0.668</v>
       </c>
       <c r="D35">
-        <v>0.641</v>
+        <v>0.6409</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -11748,7 +11685,7 @@
         <v>1.33</v>
       </c>
       <c r="G35">
-        <v>107.39</v>
+        <v>107.17</v>
       </c>
       <c r="H35">
         <v>1646.010009765625</v>
@@ -11786,7 +11723,7 @@
         <v>1.31</v>
       </c>
       <c r="G36">
-        <v>105.78</v>
+        <v>105.56</v>
       </c>
       <c r="H36">
         <v>627.8200073242188</v>
@@ -11812,19 +11749,19 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>0.6533</v>
+        <v>0.6534</v>
       </c>
       <c r="D37">
-        <v>0.2402</v>
+        <v>0.2403</v>
       </c>
       <c r="E37">
-        <v>0.4272</v>
+        <v>0.4268</v>
       </c>
       <c r="F37">
         <v>1.23</v>
       </c>
       <c r="G37">
-        <v>99.31999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H37">
         <v>270.2804870605469</v>
@@ -11853,7 +11790,7 @@
         <v>0.7183</v>
       </c>
       <c r="D38">
-        <v>0.7475000000000001</v>
+        <v>0.7474</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -11862,7 +11799,7 @@
         <v>1.01</v>
       </c>
       <c r="G38">
-        <v>81.55</v>
+        <v>81.39</v>
       </c>
       <c r="H38">
         <v>32.22999954223633</v>
@@ -11888,10 +11825,10 @@
         <v>18</v>
       </c>
       <c r="C39">
-        <v>0.651</v>
+        <v>0.6509</v>
       </c>
       <c r="D39">
-        <v>0.7301</v>
+        <v>0.7309</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -11900,7 +11837,7 @@
         <v>0.97</v>
       </c>
       <c r="G39">
-        <v>78.31999999999999</v>
+        <v>78.16</v>
       </c>
       <c r="H39">
         <v>229.1600036621094</v>
@@ -11926,10 +11863,10 @@
         <v>18</v>
       </c>
       <c r="C40">
-        <v>0.6251</v>
+        <v>0.625</v>
       </c>
       <c r="D40">
-        <v>0.7268</v>
+        <v>0.7262</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -11938,7 +11875,7 @@
         <v>0.95</v>
       </c>
       <c r="G40">
-        <v>76.70999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="H40">
         <v>335.5</v>
@@ -11964,10 +11901,10 @@
         <v>143</v>
       </c>
       <c r="C41">
-        <v>0.4099</v>
+        <v>0.4098</v>
       </c>
       <c r="D41">
-        <v>0.32</v>
+        <v>0.3195</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -11976,7 +11913,7 @@
         <v>0.88</v>
       </c>
       <c r="G41">
-        <v>71.06</v>
+        <v>70.91</v>
       </c>
       <c r="H41">
         <v>842.4000244140625</v>
@@ -12002,10 +11939,10 @@
         <v>18</v>
       </c>
       <c r="C42">
-        <v>0.6493</v>
+        <v>0.6492</v>
       </c>
       <c r="D42">
-        <v>0.7637</v>
+        <v>0.7643</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -12014,13 +11951,13 @@
         <v>0.85</v>
       </c>
       <c r="G42">
-        <v>68.63</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H42">
         <v>17.04999923706055</v>
       </c>
       <c r="I42">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="J42" t="s">
         <v>153</v>
@@ -12043,7 +11980,7 @@
         <v>0.4012</v>
       </c>
       <c r="D43">
-        <v>0.3581</v>
+        <v>0.3582</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -12052,7 +11989,7 @@
         <v>0.82</v>
       </c>
       <c r="G43">
-        <v>66.20999999999999</v>
+        <v>66.08</v>
       </c>
       <c r="H43">
         <v>477.3900146484375</v>
@@ -12081,7 +12018,7 @@
         <v>0.4315</v>
       </c>
       <c r="D44">
-        <v>0.6191</v>
+        <v>0.619</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -12090,7 +12027,7 @@
         <v>0.79</v>
       </c>
       <c r="G44">
-        <v>63.79</v>
+        <v>63.66</v>
       </c>
       <c r="H44">
         <v>92.66010284423828</v>
@@ -12119,7 +12056,7 @@
         <v>0.6788999999999999</v>
       </c>
       <c r="D45">
-        <v>0.7948</v>
+        <v>0.7942</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -12128,13 +12065,13 @@
         <v>0.77</v>
       </c>
       <c r="G45">
-        <v>62.17</v>
+        <v>62.05</v>
       </c>
       <c r="H45">
         <v>92</v>
       </c>
       <c r="I45">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J45" t="s">
         <v>153</v>
@@ -12157,7 +12094,7 @@
         <v>0.8007</v>
       </c>
       <c r="D46">
-        <v>0.9114</v>
+        <v>0.9113</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -12166,13 +12103,13 @@
         <v>0.7</v>
       </c>
       <c r="G46">
-        <v>56.52</v>
+        <v>56.41</v>
       </c>
       <c r="H46">
         <v>10.6201000213623</v>
       </c>
       <c r="I46">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="J46" t="s">
         <v>153</v>
@@ -12192,25 +12129,25 @@
         <v>144</v>
       </c>
       <c r="C47">
-        <v>0.385</v>
+        <v>0.3849</v>
       </c>
       <c r="D47">
-        <v>0.2386</v>
+        <v>0.2381</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G47">
-        <v>19.38</v>
+        <v>18.53</v>
       </c>
       <c r="H47">
         <v>86.90000152587891</v>
       </c>
       <c r="I47">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J47" t="s">
         <v>153</v>
@@ -12242,7 +12179,7 @@
         <v>0.2</v>
       </c>
       <c r="G48">
-        <v>16.15</v>
+        <v>16.12</v>
       </c>
       <c r="H48">
         <v>81.58999633789062</v>
@@ -12268,10 +12205,10 @@
         <v>144</v>
       </c>
       <c r="C49">
-        <v>0.3449</v>
+        <v>0.3448</v>
       </c>
       <c r="D49">
-        <v>0.2928</v>
+        <v>0.2925</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -12280,7 +12217,7 @@
         <v>0.19</v>
       </c>
       <c r="G49">
-        <v>15.34</v>
+        <v>15.31</v>
       </c>
       <c r="H49">
         <v>442.6698913574219</v>
@@ -12306,10 +12243,10 @@
         <v>144</v>
       </c>
       <c r="C50">
-        <v>0.3567</v>
+        <v>0.3566</v>
       </c>
       <c r="D50">
-        <v>0.3226</v>
+        <v>0.3222</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -12318,7 +12255,7 @@
         <v>0.19</v>
       </c>
       <c r="G50">
-        <v>15.34</v>
+        <v>15.31</v>
       </c>
       <c r="H50">
         <v>376.1700134277344</v>
@@ -12344,10 +12281,10 @@
         <v>144</v>
       </c>
       <c r="C51">
-        <v>0.3765</v>
+        <v>0.3764</v>
       </c>
       <c r="D51">
-        <v>0.4146</v>
+        <v>0.4134</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -12356,13 +12293,13 @@
         <v>0.18</v>
       </c>
       <c r="G51">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="H51">
         <v>16.40999984741211</v>
       </c>
       <c r="I51">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="J51" t="s">
         <v>153</v>
@@ -12382,10 +12319,10 @@
         <v>144</v>
       </c>
       <c r="C52">
-        <v>0.3496</v>
+        <v>0.3495</v>
       </c>
       <c r="D52">
-        <v>0.359</v>
+        <v>0.3586</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -12394,7 +12331,7 @@
         <v>0.18</v>
       </c>
       <c r="G52">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="H52">
         <v>78.55000305175781</v>
@@ -12423,7 +12360,7 @@
         <v>0.369</v>
       </c>
       <c r="D53">
-        <v>0.3835</v>
+        <v>0.3833</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -12432,7 +12369,7 @@
         <v>0.18</v>
       </c>
       <c r="G53">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="H53">
         <v>42.81000137329102</v>
@@ -12458,10 +12395,10 @@
         <v>144</v>
       </c>
       <c r="C54">
-        <v>0.3778</v>
+        <v>0.3777</v>
       </c>
       <c r="D54">
-        <v>0.3851</v>
+        <v>0.3845</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -12470,7 +12407,7 @@
         <v>0.18</v>
       </c>
       <c r="G54">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="H54">
         <v>256.6799926757812</v>
@@ -12496,7 +12433,7 @@
         <v>144</v>
       </c>
       <c r="C55">
-        <v>0.3863</v>
+        <v>0.3862</v>
       </c>
       <c r="D55">
         <v>0.435</v>
@@ -12508,7 +12445,7 @@
         <v>0.18</v>
       </c>
       <c r="G55">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="H55">
         <v>286.9700012207031</v>
@@ -12534,10 +12471,10 @@
         <v>144</v>
       </c>
       <c r="C56">
-        <v>0.3325</v>
+        <v>0.3324</v>
       </c>
       <c r="D56">
-        <v>0.3899</v>
+        <v>0.3898</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -12546,7 +12483,7 @@
         <v>0.16</v>
       </c>
       <c r="G56">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="H56">
         <v>297.8349914550781</v>
@@ -12575,7 +12512,7 @@
         <v>0.3971</v>
       </c>
       <c r="D57">
-        <v>0.5245</v>
+        <v>0.5243</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -12584,7 +12521,7 @@
         <v>0.15</v>
       </c>
       <c r="G57">
-        <v>12.11</v>
+        <v>12.09</v>
       </c>
       <c r="H57">
         <v>46.2599983215332</v>
@@ -12610,7 +12547,7 @@
         <v>144</v>
       </c>
       <c r="C58">
-        <v>0.3798</v>
+        <v>0.3797</v>
       </c>
       <c r="D58">
         <v>0.5154</v>
@@ -12622,7 +12559,7 @@
         <v>0.15</v>
       </c>
       <c r="G58">
-        <v>12.11</v>
+        <v>12.09</v>
       </c>
       <c r="H58">
         <v>71.58999633789062</v>
@@ -12648,10 +12585,10 @@
         <v>144</v>
       </c>
       <c r="C59">
-        <v>0.3554</v>
+        <v>0.3553</v>
       </c>
       <c r="D59">
-        <v>0.5101</v>
+        <v>0.5093</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -12660,7 +12597,7 @@
         <v>0.14</v>
       </c>
       <c r="G59">
-        <v>11.3</v>
+        <v>11.28</v>
       </c>
       <c r="H59">
         <v>109.3625030517578</v>
@@ -12686,10 +12623,10 @@
         <v>144</v>
       </c>
       <c r="C60">
-        <v>0.3507</v>
+        <v>0.3506</v>
       </c>
       <c r="D60">
-        <v>0.4859</v>
+        <v>0.4855</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12698,7 +12635,7 @@
         <v>0.14</v>
       </c>
       <c r="G60">
-        <v>11.3</v>
+        <v>11.28</v>
       </c>
       <c r="H60">
         <v>223.4850006103516</v>
@@ -12724,10 +12661,10 @@
         <v>144</v>
       </c>
       <c r="C61">
-        <v>0.3615</v>
+        <v>0.3614</v>
       </c>
       <c r="D61">
-        <v>0.5199</v>
+        <v>0.5191</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -12736,7 +12673,7 @@
         <v>0.14</v>
       </c>
       <c r="G61">
-        <v>11.3</v>
+        <v>11.28</v>
       </c>
       <c r="H61">
         <v>144.8500061035156</v>
@@ -12762,10 +12699,10 @@
         <v>144</v>
       </c>
       <c r="C62">
-        <v>0.3721</v>
+        <v>0.372</v>
       </c>
       <c r="D62">
-        <v>0.5316</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -12774,13 +12711,13 @@
         <v>0.14</v>
       </c>
       <c r="G62">
-        <v>11.3</v>
+        <v>11.28</v>
       </c>
       <c r="H62">
         <v>50.13999938964844</v>
       </c>
       <c r="I62">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J62" t="s">
         <v>153</v>
@@ -12800,10 +12737,10 @@
         <v>144</v>
       </c>
       <c r="C63">
-        <v>0.3629</v>
+        <v>0.3628</v>
       </c>
       <c r="D63">
-        <v>0.5329</v>
+        <v>0.5326</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -12812,13 +12749,13 @@
         <v>0.14</v>
       </c>
       <c r="G63">
-        <v>11.3</v>
+        <v>11.28</v>
       </c>
       <c r="H63">
         <v>3.535000085830688</v>
       </c>
       <c r="I63">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="J63" t="s">
         <v>153</v>
@@ -12838,10 +12775,10 @@
         <v>144</v>
       </c>
       <c r="C64">
-        <v>0.3571</v>
+        <v>0.357</v>
       </c>
       <c r="D64">
-        <v>0.5464</v>
+        <v>0.546</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -12850,7 +12787,7 @@
         <v>0.13</v>
       </c>
       <c r="G64">
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
       <c r="H64">
         <v>24.07999992370605</v>
@@ -12876,10 +12813,10 @@
         <v>144</v>
       </c>
       <c r="C65">
-        <v>0.3647</v>
+        <v>0.3646</v>
       </c>
       <c r="D65">
-        <v>0.6021</v>
+        <v>0.6019</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -12888,7 +12825,7 @@
         <v>0.12</v>
       </c>
       <c r="G65">
-        <v>9.69</v>
+        <v>9.67</v>
       </c>
       <c r="H65">
         <v>326.5499877929688</v>
@@ -12914,10 +12851,10 @@
         <v>144</v>
       </c>
       <c r="C66">
-        <v>0.3866</v>
+        <v>0.3865</v>
       </c>
       <c r="D66">
-        <v>0.6384</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12926,7 +12863,7 @@
         <v>0.11</v>
       </c>
       <c r="G66">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H66">
         <v>138.6849975585938</v>
@@ -12952,10 +12889,10 @@
         <v>144</v>
       </c>
       <c r="C67">
-        <v>0.3343</v>
+        <v>0.3342</v>
       </c>
       <c r="D67">
-        <v>0.5851</v>
+        <v>0.584</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12964,7 +12901,7 @@
         <v>0.11</v>
       </c>
       <c r="G67">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H67">
         <v>122.8566970825195</v>
@@ -12990,10 +12927,10 @@
         <v>144</v>
       </c>
       <c r="C68">
-        <v>0.3627</v>
+        <v>0.3626</v>
       </c>
       <c r="D68">
-        <v>0.6143999999999999</v>
+        <v>0.6125</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -13002,7 +12939,7 @@
         <v>0.11</v>
       </c>
       <c r="G68">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H68">
         <v>11.64500045776367</v>
@@ -13028,10 +12965,10 @@
         <v>144</v>
       </c>
       <c r="C69">
-        <v>0.3557</v>
+        <v>0.3556</v>
       </c>
       <c r="D69">
-        <v>0.5954</v>
+        <v>0.595</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -13040,7 +12977,7 @@
         <v>0.11</v>
       </c>
       <c r="G69">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H69">
         <v>10.85499954223633</v>
@@ -13066,10 +13003,10 @@
         <v>144</v>
       </c>
       <c r="C70">
-        <v>0.3691</v>
+        <v>0.369</v>
       </c>
       <c r="D70">
-        <v>0.6434</v>
+        <v>0.6432</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -13078,7 +13015,7 @@
         <v>0.1</v>
       </c>
       <c r="G70">
-        <v>8.07</v>
+        <v>8.06</v>
       </c>
       <c r="H70">
         <v>8.979999542236328</v>
@@ -13104,10 +13041,10 @@
         <v>144</v>
       </c>
       <c r="C71">
-        <v>0.3528</v>
+        <v>0.3527</v>
       </c>
       <c r="D71">
-        <v>0.6419</v>
+        <v>0.6413</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -13116,13 +13053,13 @@
         <v>0.1</v>
       </c>
       <c r="G71">
-        <v>8.07</v>
+        <v>8.06</v>
       </c>
       <c r="H71">
         <v>8.024999618530273</v>
       </c>
       <c r="I71">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J71" t="s">
         <v>153</v>
@@ -13142,10 +13079,10 @@
         <v>144</v>
       </c>
       <c r="C72">
-        <v>0.3364</v>
+        <v>0.3363</v>
       </c>
       <c r="D72">
-        <v>0.6555</v>
+        <v>0.6554</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -13154,7 +13091,7 @@
         <v>0.09</v>
       </c>
       <c r="G72">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="H72">
         <v>613.1300048828125</v>
@@ -13180,10 +13117,10 @@
         <v>144</v>
       </c>
       <c r="C73">
-        <v>0.34</v>
+        <v>0.3399</v>
       </c>
       <c r="D73">
-        <v>0.6649</v>
+        <v>0.664</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -13192,7 +13129,7 @@
         <v>0.09</v>
       </c>
       <c r="G73">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="H73">
         <v>45.6150016784668</v>
@@ -13218,10 +13155,10 @@
         <v>144</v>
       </c>
       <c r="C74">
-        <v>0.348</v>
+        <v>0.3479</v>
       </c>
       <c r="D74">
-        <v>0.6954</v>
+        <v>0.6955</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -13230,13 +13167,13 @@
         <v>0.09</v>
       </c>
       <c r="G74">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="H74">
         <v>5.026599884033203</v>
       </c>
       <c r="I74">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J74" t="s">
         <v>153</v>
@@ -13256,7 +13193,7 @@
         <v>144</v>
       </c>
       <c r="C75">
-        <v>0.3132</v>
+        <v>0.3131</v>
       </c>
       <c r="D75">
         <v>0.6778</v>
@@ -13268,7 +13205,7 @@
         <v>0.08</v>
       </c>
       <c r="G75">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="H75">
         <v>253.3600006103516</v>
@@ -13294,7 +13231,7 @@
         <v>144</v>
       </c>
       <c r="C76">
-        <v>0.3408</v>
+        <v>0.3407</v>
       </c>
       <c r="D76">
         <v>0.7504999999999999</v>
@@ -13306,7 +13243,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G76">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="H76">
         <v>68.98000335693359</v>
@@ -13332,10 +13269,10 @@
         <v>18</v>
       </c>
       <c r="C77">
-        <v>0.675</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="D77">
-        <v>0.9833</v>
+        <v>0.9841</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -13344,7 +13281,7 @@
         <v>0.06</v>
       </c>
       <c r="G77">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="H77">
         <v>156.1300048828125</v>
@@ -13370,10 +13307,10 @@
         <v>144</v>
       </c>
       <c r="C78">
-        <v>0.3768</v>
+        <v>0.3767</v>
       </c>
       <c r="D78">
-        <v>0.7959000000000001</v>
+        <v>0.7978</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -13382,7 +13319,7 @@
         <v>0.06</v>
       </c>
       <c r="G78">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="H78">
         <v>12.4601001739502</v>
@@ -13408,7 +13345,7 @@
         <v>18</v>
       </c>
       <c r="C79">
-        <v>0.6617</v>
+        <v>0.6616</v>
       </c>
       <c r="D79">
         <v>0.9916</v>
@@ -13445,7 +13382,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -13488,13 +13425,13 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="D2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E2">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F2">
         <v>0.9824000000000001</v>
@@ -13517,63 +13454,31 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="C3">
-        <v>2741.4</v>
+        <v>1000.4</v>
       </c>
       <c r="D3">
-        <v>2291.4</v>
+        <v>836.1799999999999</v>
       </c>
       <c r="E3">
         <v>38.19</v>
       </c>
       <c r="F3">
-        <v>0.9144</v>
+        <v>0.9147</v>
       </c>
       <c r="G3">
-        <v>0.7655999999999999</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="H3">
-        <v>0.5298</v>
+        <v>0.5333</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>3.22</v>
-      </c>
-      <c r="C4">
-        <v>840.6</v>
-      </c>
-      <c r="D4">
-        <v>433.6</v>
-      </c>
-      <c r="E4">
-        <v>134.66</v>
-      </c>
-      <c r="F4">
-        <v>0.4547</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>
